--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="480">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -393,834 +393,825 @@
     <t>ADELL</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>GEOMETRÍA ANALÍTICA</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>ÉTICA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
+    <t>VANELY JUDITH</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ARLET</t>
+  </si>
+  <si>
+    <t>JENIFER</t>
+  </si>
+  <si>
+    <t>INGLÉS III</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>APLICA LA METODOLOGÍA DE DESARROLLO RÁPIDO DE APLICACIONES CON PROGRAMACIÓN ORIENTADA A EVENTOS</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>YAMILE</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>ELIDETH</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>AYELEN</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>MARTHA</t>
+  </si>
+  <si>
+    <t>ANALIZA Y FRACCIONA SANGRE CON FINES TRANSFUSIONALES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CELICEO</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>CESAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
+  </si>
+  <si>
+    <t>YESUA ISIDRO</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>MARLENE ALICIA</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MORO</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>GUILLERMO UBALDO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>FRIAS</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>ORLANDO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>PAOLA JAZMIN</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>FERGIE PAULETTE</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>DAVID OSWALDO</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>KELLY ITZEL</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO CORRECTIVO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>GEOMETRÍA ANALÍTICA</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>VANELY JUDITH</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ARLET</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
-    <t>INGLÉS III</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ÉTICA</t>
-  </si>
-  <si>
-    <t>APLICA LA METODOLOGÍA DE DESARROLLO RÁPIDO DE APLICACIONES CON PROGRAMACIÓN ORIENTADA A EVENTOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>ESTHER ARISBETH</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ANASTACIO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>ELIDETH</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>AYELEN</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>MARTHA</t>
-  </si>
-  <si>
-    <t>ANALIZA Y FRACCIONA SANGRE CON FINES TRANSFUSIONALES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>MARLENE ALICIA</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ADRIANA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>FRIAS</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>ORLANDO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>PAOLA JAZMIN</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>FERGIE PAULETTE</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>DAVID OSWALDO</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>KELLY ITZEL</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO CORRECTIVO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
     <t>TZOYONTLE</t>
   </si>
   <si>
@@ -1350,9 +1341,6 @@
     <t>AZAEL</t>
   </si>
   <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
     <t>CERVANTES</t>
   </si>
   <si>
@@ -1395,18 +1383,12 @@
     <t>VALDES</t>
   </si>
   <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
     <t>CORDOBA</t>
   </si>
   <si>
     <t>MARIN</t>
   </si>
   <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
     <t>HILARIO</t>
   </si>
   <si>
@@ -1416,9 +1398,6 @@
     <t>BRENDA ELENA</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>JENNIFER</t>
   </si>
   <si>
@@ -1428,6 +1407,9 @@
     <t>DARIANA MONSERRAT</t>
   </si>
   <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
     <t>ASTRID</t>
   </si>
   <si>
@@ -1450,9 +1432,6 @@
   </si>
   <si>
     <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>VERA</t>
   </si>
   <si>
     <t>TREJO</t>
@@ -2054,7 +2033,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2079,39 +2058,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920156</v>
+        <v>20330051920158</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E2" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="F2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920158</v>
+        <v>20330051920161</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
         <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2119,19 +2098,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920161</v>
+        <v>20330051920172</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2139,22 +2118,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920172</v>
+        <v>20330051920174</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2162,16 +2141,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2179,122 +2158,22 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920174</v>
+        <v>20330051920178</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920178</v>
-      </c>
-      <c r="B8" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920179</v>
-      </c>
-      <c r="B9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920306</v>
-      </c>
-      <c r="B10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920306</v>
-      </c>
-      <c r="B11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" t="s">
-        <v>177</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920393</v>
-      </c>
-      <c r="B12" t="s">
-        <v>163</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" t="s">
-        <v>176</v>
-      </c>
-      <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2304,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2332,16 +2211,16 @@
         <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2352,16 +2231,16 @@
         <v>20330051920039</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2372,16 +2251,16 @@
         <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2392,16 +2271,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2412,16 +2291,16 @@
         <v>20330051920050</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2432,16 +2311,16 @@
         <v>20330051920050</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2452,16 +2331,16 @@
         <v>20330051920052</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2469,16 +2348,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920099</v>
+        <v>20330051920100</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+      <c r="C9" t="s">
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -2489,78 +2371,58 @@
         <v>20330051920100</v>
       </c>
       <c r="B10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" t="s">
         <v>183</v>
       </c>
-      <c r="C10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" t="s">
-        <v>192</v>
-      </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920100</v>
+        <v>20330051920107</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920107</v>
+        <v>20330051920113</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920113</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F13">
         <v>-1</v>
       </c>
     </row>
@@ -2599,16 +2461,16 @@
         <v>20330051920284</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2619,16 +2481,16 @@
         <v>20330051920285</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2639,16 +2501,16 @@
         <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C4" t="s">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2659,16 +2521,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C5" t="s">
         <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2679,16 +2541,16 @@
         <v>20330051920287</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2699,16 +2561,16 @@
         <v>20330051920287</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2719,16 +2581,16 @@
         <v>20330051920295</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D8" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2742,13 +2604,13 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E9" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2762,13 +2624,13 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E10" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2779,16 +2641,16 @@
         <v>20330051920297</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2799,16 +2661,16 @@
         <v>20330051920297</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2819,16 +2681,16 @@
         <v>20330051920298</v>
       </c>
       <c r="B13" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2845,10 +2707,10 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E14" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2865,10 +2727,10 @@
         <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E15" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2915,10 +2777,10 @@
         <v>74</v>
       </c>
       <c r="D2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" t="s">
         <v>219</v>
-      </c>
-      <c r="E2" t="s">
-        <v>226</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2929,16 +2791,16 @@
         <v>18330061460390</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C3" t="s">
         <v>109</v>
       </c>
       <c r="D3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" t="s">
         <v>220</v>
-      </c>
-      <c r="E3" t="s">
-        <v>227</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -2949,16 +2811,16 @@
         <v>19330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D4" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E4" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2972,13 +2834,13 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2992,13 +2854,13 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -3009,16 +2871,16 @@
         <v>19330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C7" t="s">
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E7" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -3032,13 +2894,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D8" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E8" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3049,16 +2911,16 @@
         <v>19330051920034</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D9" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3069,16 +2931,16 @@
         <v>19330051920034</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E10" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3092,16 +2954,16 @@
         <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3112,16 +2974,16 @@
         <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -3159,16 +3021,16 @@
         <v>19330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3179,16 +3041,16 @@
         <v>19330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3199,16 +3061,16 @@
         <v>19330051920159</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3219,16 +3081,16 @@
         <v>19330051920165</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3241,7 +3103,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3269,16 +3131,16 @@
         <v>19330051920234</v>
       </c>
       <c r="B2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" t="s">
         <v>236</v>
       </c>
-      <c r="C2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D2" t="s">
-        <v>242</v>
-      </c>
       <c r="E2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3289,16 +3151,16 @@
         <v>19330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C3" t="s">
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3306,19 +3168,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920237</v>
+        <v>19330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
-        <v>240</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3326,19 +3188,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920237</v>
+        <v>19330051920244</v>
       </c>
       <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
         <v>238</v>
       </c>
-      <c r="C5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D5" t="s">
-        <v>244</v>
-      </c>
       <c r="E5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3346,19 +3208,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920244</v>
+        <v>19330051920245</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3372,15 +3234,35 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>19330051920430</v>
+      </c>
+      <c r="B8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
         <v>241</v>
       </c>
-      <c r="D7" t="s">
-        <v>246</v>
-      </c>
-      <c r="E7" t="s">
-        <v>229</v>
-      </c>
-      <c r="F7">
+      <c r="E8" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8">
         <v>5</v>
       </c>
     </row>
@@ -3391,7 +3273,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3419,16 +3301,16 @@
         <v>19330051920130</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3439,16 +3321,16 @@
         <v>19330051920130</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3456,22 +3338,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920133</v>
+        <v>19330051920139</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3482,16 +3364,56 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" t="s">
         <v>248</v>
       </c>
-      <c r="D5" t="s">
-        <v>251</v>
-      </c>
       <c r="E5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>19330051920140</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>19330051920431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3501,7 +3423,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3526,19 +3448,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920085</v>
+        <v>19330051920092</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>256</v>
       </c>
-      <c r="D2" t="s">
-        <v>258</v>
-      </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3555,10 +3477,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -3566,22 +3488,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920092</v>
+        <v>19330051920095</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3589,16 +3511,16 @@
         <v>19330051920095</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -3606,19 +3528,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920095</v>
+        <v>19330051920099</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E6" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3629,16 +3551,16 @@
         <v>19330051920099</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E7" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -3646,19 +3568,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920099</v>
+        <v>19330051920116</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3672,13 +3594,13 @@
         <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E9" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -3686,39 +3608,39 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920118</v>
+        <v>19330051920119</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920118</v>
+        <v>19330051920119</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E11" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3726,41 +3648,21 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920119</v>
+        <v>19330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>255</v>
       </c>
       <c r="D12" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E12" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920120</v>
-      </c>
-      <c r="B13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C13" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E13" t="s">
-        <v>226</v>
-      </c>
-      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -3771,7 +3673,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3796,21 +3698,61 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
+        <v>19330051920201</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>19330051920203</v>
+      </c>
+      <c r="B3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
         <v>19330051920207</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F2">
+      <c r="C4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4">
         <v>5</v>
       </c>
     </row>
@@ -3849,13 +3791,13 @@
         <v>20330051920291</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -3869,13 +3811,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
@@ -3889,13 +3831,13 @@
         <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E4" t="s">
         <v>106</v>
@@ -3909,13 +3851,13 @@
         <v>21330051920003</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -3932,10 +3874,10 @@
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3949,13 +3891,13 @@
         <v>21330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -3969,13 +3911,13 @@
         <v>21330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -3989,13 +3931,13 @@
         <v>21330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4009,13 +3951,13 @@
         <v>21330051920009</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E10" t="s">
         <v>49</v>
@@ -4032,10 +3974,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E11" t="s">
         <v>106</v>
@@ -4052,10 +3994,10 @@
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4072,10 +4014,10 @@
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E13" t="s">
         <v>49</v>
@@ -4095,7 +4037,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -4109,13 +4051,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4129,13 +4071,13 @@
         <v>21330051920025</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4149,13 +4091,13 @@
         <v>21330051920026</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E17" t="s">
         <v>106</v>
@@ -4169,13 +4111,13 @@
         <v>21330051920026</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4189,13 +4131,13 @@
         <v>21330051920355</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -4212,10 +4154,10 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -4495,7 +4437,7 @@
         <v>298</v>
       </c>
       <c r="D2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -4509,13 +4451,13 @@
         <v>21330051920030</v>
       </c>
       <c r="B3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
@@ -4529,13 +4471,13 @@
         <v>21330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E4" t="s">
         <v>106</v>
@@ -4549,13 +4491,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
         <v>299</v>
       </c>
       <c r="D5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E5" t="s">
         <v>106</v>
@@ -4569,13 +4511,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
         <v>299</v>
       </c>
       <c r="D6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4592,10 +4534,10 @@
         <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>300</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -4615,7 +4557,7 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
@@ -4635,7 +4577,7 @@
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
@@ -4652,10 +4594,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4672,10 +4614,10 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E11" t="s">
         <v>106</v>
@@ -4689,13 +4631,13 @@
         <v>21330051920054</v>
       </c>
       <c r="B12" t="s">
-        <v>295</v>
+        <v>243</v>
       </c>
       <c r="C12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E12" t="s">
         <v>106</v>
@@ -4715,7 +4657,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -4735,7 +4677,7 @@
         <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E14" t="s">
         <v>106</v>
@@ -4752,10 +4694,10 @@
         <v>297</v>
       </c>
       <c r="C15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4772,10 +4714,10 @@
         <v>297</v>
       </c>
       <c r="C16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E16" t="s">
         <v>106</v>
@@ -4789,13 +4731,13 @@
         <v>21330051920390</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E17" t="s">
         <v>106</v>
@@ -4809,13 +4751,13 @@
         <v>21330051920390</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
@@ -4859,13 +4801,13 @@
         <v>21330051920072</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -4879,13 +4821,13 @@
         <v>21330051920073</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
@@ -4899,13 +4841,13 @@
         <v>21330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -4919,13 +4861,13 @@
         <v>21330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -4942,10 +4884,10 @@
         <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E6" t="s">
         <v>106</v>
@@ -4962,10 +4904,10 @@
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -4982,10 +4924,10 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
@@ -5002,10 +4944,10 @@
         <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E9" t="s">
         <v>106</v>
@@ -5022,10 +4964,10 @@
         <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -5039,13 +4981,13 @@
         <v>21330051920097</v>
       </c>
       <c r="B11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -5059,7 +5001,7 @@
         <v>21330051920099</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
         <v>73</v>
@@ -5079,7 +5021,7 @@
         <v>21330051920099</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
@@ -5102,10 +5044,10 @@
         <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E14" t="s">
         <v>106</v>
@@ -5119,13 +5061,13 @@
         <v>21330051920104</v>
       </c>
       <c r="B15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E15" t="s">
         <v>106</v>
@@ -5139,13 +5081,13 @@
         <v>21330051920107</v>
       </c>
       <c r="B16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C16" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E16" t="s">
         <v>106</v>
@@ -5162,10 +5104,10 @@
         <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E17" t="s">
         <v>106</v>
@@ -5209,13 +5151,13 @@
         <v>21330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C2" t="s">
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -5229,13 +5171,13 @@
         <v>21330051920118</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
@@ -5249,13 +5191,13 @@
         <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -5269,13 +5211,13 @@
         <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
         <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -5292,10 +5234,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E6" t="s">
         <v>106</v>
@@ -5309,13 +5251,13 @@
         <v>21330051920127</v>
       </c>
       <c r="B7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -5329,13 +5271,13 @@
         <v>21330051920127</v>
       </c>
       <c r="B8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
@@ -5352,10 +5294,10 @@
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -5399,13 +5341,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -5419,13 +5361,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
@@ -5445,7 +5387,7 @@
         <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E4" t="s">
         <v>106</v>
@@ -5465,7 +5407,7 @@
         <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
@@ -5482,13 +5424,13 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -5502,13 +5444,13 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -5519,13 +5461,13 @@
         <v>21330051920382</v>
       </c>
       <c r="B8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E8" t="s">
         <v>106</v>
@@ -5539,13 +5481,13 @@
         <v>21330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
@@ -5561,7 +5503,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5589,16 +5531,16 @@
         <v>20330051920061</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5615,10 +5557,10 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5629,16 +5571,16 @@
         <v>20330051920072</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5649,16 +5591,16 @@
         <v>20330051920072</v>
       </c>
       <c r="B5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5672,13 +5614,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5686,19 +5628,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920082</v>
+        <v>20330051920087</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>350</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5709,16 +5651,16 @@
         <v>20330051920087</v>
       </c>
       <c r="B8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5726,41 +5668,21 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920087</v>
+        <v>20330051920386</v>
       </c>
       <c r="B9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s">
-        <v>362</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920386</v>
-      </c>
-      <c r="B10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C10" t="s">
-        <v>356</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10">
         <v>5</v>
       </c>
     </row>
@@ -5799,16 +5721,16 @@
         <v>19330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5819,16 +5741,16 @@
         <v>19330051920177</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E3" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5839,16 +5761,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C4" t="s">
         <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -5859,16 +5781,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
         <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5879,16 +5801,16 @@
         <v>20330051920191</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -5905,10 +5827,10 @@
         <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -5922,13 +5844,13 @@
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5942,13 +5864,13 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D9" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -5989,16 +5911,16 @@
         <v>19330051920238</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6012,13 +5934,13 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6032,13 +5954,13 @@
         <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -6052,13 +5974,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -6105,10 +6027,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6119,16 +6041,16 @@
         <v>20330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
         <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E3" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6139,16 +6061,16 @@
         <v>20330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>300</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -6159,16 +6081,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6179,16 +6101,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -6201,7 +6123,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6229,16 +6151,16 @@
         <v>17330051920191</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6249,16 +6171,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" t="s">
         <v>380</v>
       </c>
-      <c r="D3" t="s">
-        <v>383</v>
-      </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6266,19 +6188,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920320</v>
+        <v>20330051920325</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>378</v>
       </c>
-      <c r="C4" t="s">
-        <v>380</v>
-      </c>
       <c r="D4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6292,13 +6214,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D5" t="s">
         <v>381</v>
       </c>
-      <c r="D5" t="s">
-        <v>384</v>
-      </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6306,19 +6228,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>376</v>
       </c>
       <c r="C6" t="s">
-        <v>381</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6329,16 +6251,16 @@
         <v>20330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6346,61 +6268,21 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920329</v>
-      </c>
-      <c r="B9" t="s">
-        <v>346</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>386</v>
-      </c>
-      <c r="E9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920396</v>
-      </c>
-      <c r="B10" t="s">
-        <v>218</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>387</v>
-      </c>
-      <c r="E10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F10">
         <v>5</v>
       </c>
     </row>
@@ -6439,16 +6321,16 @@
         <v>18330051920009</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6459,16 +6341,16 @@
         <v>18330051920022</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6479,19 +6361,19 @@
         <v>18330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E4" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6499,19 +6381,19 @@
         <v>18330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6519,16 +6401,16 @@
         <v>19330051920045</v>
       </c>
       <c r="B6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E6" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6539,16 +6421,16 @@
         <v>19330051920046</v>
       </c>
       <c r="B7" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6559,16 +6441,16 @@
         <v>19330051920055</v>
       </c>
       <c r="B8" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E8" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6582,13 +6464,13 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D9" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E9" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6605,10 +6487,10 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E10" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6622,13 +6504,13 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E11" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6639,16 +6521,16 @@
         <v>19330051920074</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>387</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6665,13 +6547,13 @@
         <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E13" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6685,13 +6567,13 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E14" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -6979,16 +6861,16 @@
         <v>18330051920242</v>
       </c>
       <c r="B2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6999,16 +6881,16 @@
         <v>18330051920319</v>
       </c>
       <c r="B3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C3" t="s">
         <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7019,16 +6901,16 @@
         <v>18330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D4" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7042,13 +6924,13 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7062,13 +6944,13 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -7082,13 +6964,13 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E7" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7102,13 +6984,13 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E8" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7119,16 +7001,16 @@
         <v>19330051920269</v>
       </c>
       <c r="B9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E9" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7139,16 +7021,16 @@
         <v>19330051920273</v>
       </c>
       <c r="B10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E10" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7159,16 +7041,16 @@
         <v>19330051920273</v>
       </c>
       <c r="B11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E11" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7179,16 +7061,16 @@
         <v>19330051920278</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7202,13 +7084,13 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D13" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E13" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7222,13 +7104,13 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D14" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E14" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -7242,13 +7124,13 @@
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D15" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E15" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7262,13 +7144,13 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D16" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E16" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -7279,16 +7161,16 @@
         <v>19330051920292</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D17" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E17" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -7305,10 +7187,10 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E18" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -7319,16 +7201,16 @@
         <v>19330051920295</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C19" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D19" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E19" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -7339,16 +7221,16 @@
         <v>19330051920298</v>
       </c>
       <c r="B20" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C20" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D20" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E20" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -7359,16 +7241,16 @@
         <v>19330051920299</v>
       </c>
       <c r="B21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C21" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D21" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E21" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -7382,13 +7264,13 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D22" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E22" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -7405,10 +7287,10 @@
         <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E23" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -7422,13 +7304,13 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D24" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E24" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -7445,10 +7327,10 @@
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E25" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -7492,13 +7374,13 @@
         <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7509,16 +7391,16 @@
         <v>19330051920312</v>
       </c>
       <c r="B3" t="s">
-        <v>434</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D3" t="s">
         <v>437</v>
       </c>
-      <c r="D3" t="s">
-        <v>441</v>
-      </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7529,16 +7411,16 @@
         <v>19330051920316</v>
       </c>
       <c r="B4" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7552,13 +7434,13 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -7572,13 +7454,13 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E6" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7589,16 +7471,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C7" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7609,16 +7491,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B8" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C8" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E8" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7632,13 +7514,13 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7649,16 +7531,16 @@
         <v>19330051920337</v>
       </c>
       <c r="B10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C10" t="s">
         <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E10" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7669,16 +7551,16 @@
         <v>19330051920345</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E11" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7692,13 +7574,13 @@
         <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D12" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7709,16 +7591,16 @@
         <v>19330051920352</v>
       </c>
       <c r="B13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7729,16 +7611,16 @@
         <v>19330051920352</v>
       </c>
       <c r="B14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7751,7 +7633,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7779,16 +7661,16 @@
         <v>18330051920097</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7799,16 +7681,16 @@
         <v>18330051920108</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D3" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7819,16 +7701,16 @@
         <v>18330051920188</v>
       </c>
       <c r="B4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C4" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D4" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7839,16 +7721,16 @@
         <v>18330051920188</v>
       </c>
       <c r="B5" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C5" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D5" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7856,19 +7738,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920366</v>
+        <v>19330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
-        <v>452</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E6" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7876,19 +7758,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920366</v>
+        <v>19330051920369</v>
       </c>
       <c r="B7" t="s">
-        <v>449</v>
+        <v>317</v>
       </c>
       <c r="C7" t="s">
-        <v>452</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7896,19 +7778,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920369</v>
+        <v>19330051920377</v>
       </c>
       <c r="B8" t="s">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7916,19 +7798,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920377</v>
+        <v>19330051920378</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="E9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7936,19 +7818,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920378</v>
+        <v>19330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E10" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7956,19 +7838,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920436</v>
+        <v>19330051920393</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="D11" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7985,13 +7867,33 @@
         <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E12" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>19330051920436</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>454</v>
+      </c>
+      <c r="E13" t="s">
+        <v>222</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8032,13 +7934,13 @@
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="E2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8049,16 +7951,16 @@
         <v>19330051920250</v>
       </c>
       <c r="B3" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D3" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8072,13 +7974,13 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D4" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -8092,13 +7994,13 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D5" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="E5" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8109,16 +8011,16 @@
         <v>19330051920253</v>
       </c>
       <c r="B6" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D6" t="s">
         <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -8135,10 +8037,10 @@
         <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="E7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8155,10 +8057,10 @@
         <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="E8" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8172,13 +8074,13 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="D9" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E9" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8192,13 +8094,13 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E10" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8215,10 +8117,10 @@
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="E11" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8229,16 +8131,16 @@
         <v>19330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C12" t="s">
-        <v>468</v>
+        <v>231</v>
       </c>
       <c r="D12" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E12" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8252,13 +8154,13 @@
         <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8269,16 +8171,16 @@
         <v>19330051920400</v>
       </c>
       <c r="B14" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C14" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="D14" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="E14" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -8289,16 +8191,16 @@
         <v>19330051920400</v>
       </c>
       <c r="B15" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C15" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="D15" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="E15" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8312,13 +8214,13 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="D16" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="E16" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -8332,13 +8234,13 @@
         <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D17" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="E17" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -8352,13 +8254,13 @@
         <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D18" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="E18" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -8372,13 +8274,13 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="D19" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E19" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -8392,13 +8294,13 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="D20" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E20" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -9021,7 +8923,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9055,10 +8957,10 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9066,19 +8968,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920029</v>
+        <v>20330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9086,19 +8988,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920029</v>
+        <v>20330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9106,19 +9008,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920033</v>
+        <v>20330051920021</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9126,61 +9028,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920033</v>
+        <v>20330051920035</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920060</v>
-      </c>
-      <c r="B7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920060</v>
-      </c>
-      <c r="B8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F8">
         <v>5</v>
       </c>
     </row>
@@ -9225,10 +9087,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9245,10 +9107,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9259,16 +9121,16 @@
         <v>20330051920224</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9282,13 +9144,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9299,16 +9161,16 @@
         <v>20330051920234</v>
       </c>
       <c r="B6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" t="s">
         <v>125</v>
-      </c>
-      <c r="C6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" t="s">
-        <v>121</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9319,16 +9181,16 @@
         <v>20330051920234</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9345,10 +9207,10 @@
         <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9359,16 +9221,16 @@
         <v>20330051920252</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9379,16 +9241,16 @@
         <v>20330051920375</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9429,16 +9291,16 @@
         <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9449,16 +9311,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9469,16 +9331,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9489,16 +9351,16 @@
         <v>20330051920340</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9509,16 +9371,16 @@
         <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9532,13 +9394,13 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9552,13 +9414,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9575,10 +9437,10 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="F9">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="480">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -399,6 +399,9 @@
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>NICIO</t>
+  </si>
+  <si>
     <t>XOCUA</t>
   </si>
   <si>
@@ -411,6 +414,9 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
@@ -420,9 +426,15 @@
     <t>OCTAVIO</t>
   </si>
   <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
     <t>MARCOS URIEL</t>
   </si>
   <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
     <t>GEOMETRÍA ANALÍTICA</t>
   </si>
   <si>
@@ -432,6 +444,9 @@
     <t>ÉTICA</t>
   </si>
   <si>
+    <t>INGLÉS III</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
@@ -474,9 +489,6 @@
     <t>JENIFER</t>
   </si>
   <si>
-    <t>INGLÉS III</t>
-  </si>
-  <si>
     <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
   </si>
   <si>
@@ -978,9 +990,6 @@
     <t>ZURY BETZABE</t>
   </si>
   <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
     <t>ANGEL GABRIEL</t>
   </si>
   <si>
@@ -1347,12 +1356,6 @@
     <t>GALVEZ</t>
   </si>
   <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>AULIS</t>
-  </si>
-  <si>
     <t>ALTAMIRANO</t>
   </si>
   <si>
@@ -1363,9 +1366,6 @@
   </si>
   <si>
     <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>ALDO</t>
   </si>
   <si>
     <t>IGNACIO</t>
@@ -2064,13 +2064,13 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2081,16 +2081,16 @@
         <v>20330051920161</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2101,16 +2101,16 @@
         <v>20330051920172</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2121,16 +2121,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -2141,16 +2141,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2161,16 +2161,16 @@
         <v>20330051920178</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2211,16 +2211,16 @@
         <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2231,16 +2231,16 @@
         <v>20330051920039</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2251,16 +2251,16 @@
         <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2271,16 +2271,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2291,16 +2291,16 @@
         <v>20330051920050</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2311,16 +2311,16 @@
         <v>20330051920050</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2331,16 +2331,16 @@
         <v>20330051920052</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2351,16 +2351,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -2371,16 +2371,16 @@
         <v>20330051920100</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2391,16 +2391,16 @@
         <v>20330051920107</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -2417,10 +2417,10 @@
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -2461,16 +2461,16 @@
         <v>20330051920284</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2481,16 +2481,16 @@
         <v>20330051920285</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2501,16 +2501,16 @@
         <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C4" t="s">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2521,16 +2521,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
         <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2541,16 +2541,16 @@
         <v>20330051920287</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2561,16 +2561,16 @@
         <v>20330051920287</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2581,16 +2581,16 @@
         <v>20330051920295</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2604,13 +2604,13 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2624,13 +2624,13 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2641,16 +2641,16 @@
         <v>20330051920297</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2661,16 +2661,16 @@
         <v>20330051920297</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" t="s">
         <v>132</v>
-      </c>
-      <c r="D12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E12" t="s">
-        <v>142</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2681,16 +2681,16 @@
         <v>20330051920298</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2707,10 +2707,10 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2727,10 +2727,10 @@
         <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E15" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2777,10 +2777,10 @@
         <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2791,16 +2791,16 @@
         <v>18330061460390</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
         <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -2811,16 +2811,16 @@
         <v>19330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2834,13 +2834,13 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2854,13 +2854,13 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -2871,16 +2871,16 @@
         <v>19330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C7" t="s">
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -2894,13 +2894,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2911,16 +2911,16 @@
         <v>19330051920034</v>
       </c>
       <c r="B9" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E9" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2931,16 +2931,16 @@
         <v>19330051920034</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D10" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2954,13 +2954,13 @@
         <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E11" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2974,13 +2974,13 @@
         <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -3021,16 +3021,16 @@
         <v>19330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3041,16 +3041,16 @@
         <v>19330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3061,16 +3061,16 @@
         <v>19330051920159</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3081,16 +3081,16 @@
         <v>19330051920165</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3131,16 +3131,16 @@
         <v>19330051920234</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3151,16 +3151,16 @@
         <v>19330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3171,16 +3171,16 @@
         <v>19330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3197,10 +3197,10 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3211,16 +3211,16 @@
         <v>19330051920245</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3234,13 +3234,13 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3251,16 +3251,16 @@
         <v>19330051920430</v>
       </c>
       <c r="B8" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C8" t="s">
         <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3301,16 +3301,16 @@
         <v>19330051920130</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3321,16 +3321,16 @@
         <v>19330051920130</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3344,13 +3344,13 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3364,13 +3364,13 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3384,13 +3384,13 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -3404,13 +3404,13 @@
         <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3457,10 +3457,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3477,10 +3477,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -3491,16 +3491,16 @@
         <v>19330051920095</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3511,16 +3511,16 @@
         <v>19330051920095</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -3531,16 +3531,16 @@
         <v>19330051920099</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3551,16 +3551,16 @@
         <v>19330051920099</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -3574,13 +3574,13 @@
         <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D8" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3594,13 +3594,13 @@
         <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D9" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -3611,16 +3611,16 @@
         <v>19330051920119</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3631,16 +3631,16 @@
         <v>19330051920119</v>
       </c>
       <c r="B11" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E11" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3651,16 +3651,16 @@
         <v>19330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3704,13 +3704,13 @@
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3721,16 +3721,16 @@
         <v>19330051920203</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3744,13 +3744,13 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3791,13 +3791,13 @@
         <v>20330051920291</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -3811,13 +3811,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
@@ -3831,13 +3831,13 @@
         <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E4" t="s">
         <v>106</v>
@@ -3851,13 +3851,13 @@
         <v>21330051920003</v>
       </c>
       <c r="B5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -3874,10 +3874,10 @@
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -3891,13 +3891,13 @@
         <v>21330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -3911,13 +3911,13 @@
         <v>21330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C8" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D8" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -3931,13 +3931,13 @@
         <v>21330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D9" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -3951,13 +3951,13 @@
         <v>21330051920009</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E10" t="s">
         <v>49</v>
@@ -3974,10 +3974,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E11" t="s">
         <v>106</v>
@@ -3994,10 +3994,10 @@
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4014,10 +4014,10 @@
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E13" t="s">
         <v>49</v>
@@ -4037,7 +4037,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -4051,13 +4051,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4071,13 +4071,13 @@
         <v>21330051920025</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D16" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4091,13 +4091,13 @@
         <v>21330051920026</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E17" t="s">
         <v>106</v>
@@ -4111,13 +4111,13 @@
         <v>21330051920026</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4131,13 +4131,13 @@
         <v>21330051920355</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D19" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -4154,10 +4154,10 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -4403,7 +4403,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4434,10 +4434,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -4451,13 +4451,13 @@
         <v>21330051920030</v>
       </c>
       <c r="B3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
@@ -4471,13 +4471,13 @@
         <v>21330051920035</v>
       </c>
       <c r="B4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E4" t="s">
         <v>106</v>
@@ -4491,13 +4491,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D5" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E5" t="s">
         <v>106</v>
@@ -4511,13 +4511,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D6" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4534,10 +4534,10 @@
         <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -4557,7 +4557,7 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
@@ -4577,7 +4577,7 @@
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
@@ -4594,10 +4594,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4608,16 +4608,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>247</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>304</v>
       </c>
       <c r="D11" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E11" t="s">
         <v>106</v>
@@ -4628,19 +4628,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920054</v>
+        <v>21330051920067</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -4651,16 +4651,16 @@
         <v>21330051920067</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C13" t="s">
         <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -4668,19 +4668,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920067</v>
+        <v>21330051920070</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>305</v>
       </c>
       <c r="D14" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -4691,16 +4691,16 @@
         <v>21330051920070</v>
       </c>
       <c r="B15" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C15" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -4708,16 +4708,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920070</v>
+        <v>21330051920390</v>
       </c>
       <c r="B16" t="s">
-        <v>297</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D16" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E16" t="s">
         <v>106</v>
@@ -4731,38 +4731,18 @@
         <v>21330051920390</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D17" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920390</v>
-      </c>
-      <c r="B18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" t="s">
-        <v>302</v>
-      </c>
-      <c r="D18" t="s">
-        <v>314</v>
-      </c>
-      <c r="E18" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18">
         <v>-1</v>
       </c>
     </row>
@@ -4801,13 +4781,13 @@
         <v>21330051920072</v>
       </c>
       <c r="B2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -4821,13 +4801,13 @@
         <v>21330051920073</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
@@ -4841,13 +4821,13 @@
         <v>21330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -4861,13 +4841,13 @@
         <v>21330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -4884,10 +4864,10 @@
         <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E6" t="s">
         <v>106</v>
@@ -4904,10 +4884,10 @@
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -4924,10 +4904,10 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
@@ -4944,10 +4924,10 @@
         <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E9" t="s">
         <v>106</v>
@@ -4964,10 +4944,10 @@
         <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D10" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4981,13 +4961,13 @@
         <v>21330051920097</v>
       </c>
       <c r="B11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -5001,7 +4981,7 @@
         <v>21330051920099</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
         <v>73</v>
@@ -5021,7 +5001,7 @@
         <v>21330051920099</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
@@ -5044,10 +5024,10 @@
         <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E14" t="s">
         <v>106</v>
@@ -5061,13 +5041,13 @@
         <v>21330051920104</v>
       </c>
       <c r="B15" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E15" t="s">
         <v>106</v>
@@ -5081,13 +5061,13 @@
         <v>21330051920107</v>
       </c>
       <c r="B16" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C16" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D16" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E16" t="s">
         <v>106</v>
@@ -5104,10 +5084,10 @@
         <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D17" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E17" t="s">
         <v>106</v>
@@ -5151,13 +5131,13 @@
         <v>21330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C2" t="s">
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -5171,13 +5151,13 @@
         <v>21330051920118</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
         <v>106</v>
@@ -5191,13 +5171,13 @@
         <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -5211,13 +5191,13 @@
         <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
         <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -5234,10 +5214,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E6" t="s">
         <v>106</v>
@@ -5251,13 +5231,13 @@
         <v>21330051920127</v>
       </c>
       <c r="B7" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -5271,13 +5251,13 @@
         <v>21330051920127</v>
       </c>
       <c r="B8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
@@ -5294,10 +5274,10 @@
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -5341,13 +5321,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E2" t="s">
         <v>106</v>
@@ -5361,13 +5341,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
@@ -5387,7 +5367,7 @@
         <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E4" t="s">
         <v>106</v>
@@ -5407,7 +5387,7 @@
         <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
@@ -5424,10 +5404,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
@@ -5444,10 +5424,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D7" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E7" t="s">
         <v>106</v>
@@ -5461,13 +5441,13 @@
         <v>21330051920382</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E8" t="s">
         <v>106</v>
@@ -5481,13 +5461,13 @@
         <v>21330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
@@ -5531,16 +5511,16 @@
         <v>20330051920061</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5557,10 +5537,10 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5571,16 +5551,16 @@
         <v>20330051920072</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5591,16 +5571,16 @@
         <v>20330051920072</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5614,13 +5594,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5631,16 +5611,16 @@
         <v>20330051920087</v>
       </c>
       <c r="B7" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5651,16 +5631,16 @@
         <v>20330051920087</v>
       </c>
       <c r="B8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5671,16 +5651,16 @@
         <v>20330051920386</v>
       </c>
       <c r="B9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D9" t="s">
         <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5721,16 +5701,16 @@
         <v>19330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5741,16 +5721,16 @@
         <v>19330051920177</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5761,16 +5741,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C4" t="s">
         <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -5781,16 +5761,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C5" t="s">
         <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5801,16 +5781,16 @@
         <v>20330051920191</v>
       </c>
       <c r="B6" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -5827,10 +5807,10 @@
         <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -5844,13 +5824,13 @@
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D8" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5864,13 +5844,13 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -5911,16 +5891,16 @@
         <v>19330051920238</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5934,13 +5914,13 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5954,13 +5934,13 @@
         <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D4" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -5974,13 +5954,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D5" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -6027,10 +6007,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6041,16 +6021,16 @@
         <v>20330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
         <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6061,16 +6041,16 @@
         <v>20330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -6081,16 +6061,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E5" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6101,16 +6081,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -6151,16 +6131,16 @@
         <v>17330051920191</v>
       </c>
       <c r="B2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6171,16 +6151,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6194,13 +6174,13 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6214,13 +6194,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D5" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6231,16 +6211,16 @@
         <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6251,16 +6231,16 @@
         <v>20330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6271,16 +6251,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C8" t="s">
         <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6321,16 +6301,16 @@
         <v>18330051920009</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6341,16 +6321,16 @@
         <v>18330051920022</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6361,16 +6341,16 @@
         <v>18330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -6381,16 +6361,16 @@
         <v>18330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6401,16 +6381,16 @@
         <v>19330051920045</v>
       </c>
       <c r="B6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D6" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6421,16 +6401,16 @@
         <v>19330051920046</v>
       </c>
       <c r="B7" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D7" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6441,16 +6421,16 @@
         <v>19330051920055</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D8" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6464,13 +6444,13 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D9" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6487,10 +6467,10 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6504,13 +6484,13 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D11" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6521,16 +6501,16 @@
         <v>19330051920074</v>
       </c>
       <c r="B12" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6547,10 +6527,10 @@
         <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6567,10 +6547,10 @@
         <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -6861,16 +6841,16 @@
         <v>18330051920242</v>
       </c>
       <c r="B2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6881,16 +6861,16 @@
         <v>18330051920319</v>
       </c>
       <c r="B3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C3" t="s">
         <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6901,16 +6881,16 @@
         <v>18330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D4" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6924,13 +6904,13 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D5" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6944,13 +6924,13 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D6" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -6964,13 +6944,13 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6984,13 +6964,13 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D8" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7001,16 +6981,16 @@
         <v>19330051920269</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7021,16 +7001,16 @@
         <v>19330051920273</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7041,16 +7021,16 @@
         <v>19330051920273</v>
       </c>
       <c r="B11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7061,16 +7041,16 @@
         <v>19330051920278</v>
       </c>
       <c r="B12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7084,13 +7064,13 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D13" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7104,13 +7084,13 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D14" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -7124,13 +7104,13 @@
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D15" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E15" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7144,13 +7124,13 @@
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D16" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -7161,16 +7141,16 @@
         <v>19330051920292</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E17" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -7187,10 +7167,10 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E18" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -7201,16 +7181,16 @@
         <v>19330051920295</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D19" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E19" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -7221,16 +7201,16 @@
         <v>19330051920298</v>
       </c>
       <c r="B20" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C20" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D20" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E20" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -7241,16 +7221,16 @@
         <v>19330051920299</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C21" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D21" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E21" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -7264,13 +7244,13 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D22" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E22" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -7287,10 +7267,10 @@
         <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E23" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -7304,13 +7284,13 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D24" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E24" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -7327,10 +7307,10 @@
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E25" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -7343,7 +7323,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7374,13 +7354,13 @@
         <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7391,16 +7371,16 @@
         <v>19330051920312</v>
       </c>
       <c r="B3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C3" t="s">
-        <v>433</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7411,16 +7391,16 @@
         <v>19330051920316</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7428,39 +7408,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920319</v>
+        <v>19330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>434</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920321</v>
+        <v>19330051920323</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>435</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>436</v>
       </c>
       <c r="D6" t="s">
-        <v>440</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7471,16 +7451,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D7" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7488,19 +7468,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920323</v>
+        <v>19330051920330</v>
       </c>
       <c r="B8" t="s">
-        <v>432</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D8" t="s">
-        <v>281</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7508,19 +7488,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920330</v>
+        <v>19330051920337</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>341</v>
       </c>
       <c r="C9" t="s">
-        <v>436</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>441</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7528,19 +7508,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920337</v>
+        <v>19330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>338</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7548,19 +7528,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920345</v>
+        <v>19330051920351</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>414</v>
       </c>
       <c r="D11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7568,19 +7548,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920351</v>
+        <v>19330051920352</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>340</v>
       </c>
       <c r="C12" t="s">
-        <v>411</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>443</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7591,38 +7571,18 @@
         <v>19330051920352</v>
       </c>
       <c r="B13" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920352</v>
-      </c>
-      <c r="B14" t="s">
-        <v>337</v>
-      </c>
-      <c r="C14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -7661,16 +7621,16 @@
         <v>18330051920097</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D2" t="s">
         <v>447</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7681,7 +7641,7 @@
         <v>18330051920108</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
         <v>445</v>
@@ -7690,7 +7650,7 @@
         <v>448</v>
       </c>
       <c r="E3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7710,7 +7670,7 @@
         <v>449</v>
       </c>
       <c r="E4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7730,7 +7690,7 @@
         <v>449</v>
       </c>
       <c r="E5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7741,7 +7701,7 @@
         <v>19330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C6" t="s">
         <v>52</v>
@@ -7750,7 +7710,7 @@
         <v>450</v>
       </c>
       <c r="E6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7761,7 +7721,7 @@
         <v>19330051920369</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C7" t="s">
         <v>52</v>
@@ -7770,7 +7730,7 @@
         <v>450</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7784,13 +7744,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
         <v>451</v>
       </c>
       <c r="E8" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7810,7 +7770,7 @@
         <v>452</v>
       </c>
       <c r="E9" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7824,13 +7784,13 @@
         <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
         <v>453</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7844,13 +7804,13 @@
         <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D11" t="s">
         <v>453</v>
       </c>
       <c r="E11" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7870,7 +7830,7 @@
         <v>454</v>
       </c>
       <c r="E12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7890,7 +7850,7 @@
         <v>454</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7934,13 +7894,13 @@
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
         <v>467</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7960,7 +7920,7 @@
         <v>468</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7980,7 +7940,7 @@
         <v>469</v>
       </c>
       <c r="E4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -8000,7 +7960,7 @@
         <v>469</v>
       </c>
       <c r="E5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8014,13 +7974,13 @@
         <v>456</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
         <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -8040,7 +8000,7 @@
         <v>470</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8060,7 +8020,7 @@
         <v>471</v>
       </c>
       <c r="E8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8080,7 +8040,7 @@
         <v>472</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8094,13 +8054,13 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8120,7 +8080,7 @@
         <v>473</v>
       </c>
       <c r="E11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8134,13 +8094,13 @@
         <v>457</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D12" t="s">
         <v>474</v>
       </c>
       <c r="E12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8157,10 +8117,10 @@
         <v>462</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8180,7 +8140,7 @@
         <v>475</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -8200,7 +8160,7 @@
         <v>475</v>
       </c>
       <c r="E15" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8220,7 +8180,7 @@
         <v>476</v>
       </c>
       <c r="E16" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -8240,7 +8200,7 @@
         <v>477</v>
       </c>
       <c r="E17" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -8254,13 +8214,13 @@
         <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
         <v>478</v>
       </c>
       <c r="E18" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -8280,7 +8240,7 @@
         <v>479</v>
       </c>
       <c r="E19" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -8300,7 +8260,7 @@
         <v>479</v>
       </c>
       <c r="E20" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -8923,7 +8883,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8957,10 +8917,10 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8974,13 +8934,13 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8994,13 +8954,13 @@
         <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9014,13 +8974,13 @@
         <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9028,21 +8988,101 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920035</v>
+        <v>20330051920025</v>
       </c>
       <c r="B6" t="s">
         <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>20330051920025</v>
+      </c>
+      <c r="B7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>20330051920035</v>
+      </c>
+      <c r="B8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>20330051920363</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>20330051920363</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10">
         <v>5</v>
       </c>
     </row>
@@ -9087,10 +9127,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9107,10 +9147,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9121,16 +9161,16 @@
         <v>20330051920224</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9144,13 +9184,13 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9161,16 +9201,16 @@
         <v>20330051920234</v>
       </c>
       <c r="B6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" t="s">
         <v>129</v>
-      </c>
-      <c r="C6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" t="s">
-        <v>125</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9181,16 +9221,16 @@
         <v>20330051920234</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9207,10 +9247,10 @@
         <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9221,16 +9261,16 @@
         <v>20330051920252</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9241,16 +9281,16 @@
         <v>20330051920375</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9291,16 +9331,16 @@
         <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9311,16 +9351,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9331,16 +9371,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9351,16 +9391,16 @@
         <v>20330051920340</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9371,16 +9411,16 @@
         <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9394,13 +9434,13 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9414,13 +9454,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9437,10 +9477,10 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F9">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="447">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -417,979 +417,955 @@
     <t>QUIRIZ</t>
   </si>
   <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>ELELYN IVETH</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
+  </si>
+  <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>BENY ALEXANDER</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>FERNANDO DE JESUS</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>AYELEN</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>CITLAHUA</t>
+  </si>
+  <si>
+    <t>CONDADO</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>RAUL ARTURO</t>
+  </si>
+  <si>
+    <t>JOSUE ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>IRIS VIANNEY</t>
-  </si>
-  <si>
-    <t>ELELYN IVETH</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>ANASTACIO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>BENY ALEXANDER</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VALDERRAMA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>YAMIL ELIEL</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>FERNANDO DE JESUS</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>AYELEN</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
-  </si>
-  <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>KAROL</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>LICEA</t>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>EBER</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>PAOLA JAZMIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>FERGIE PAULETTE</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>JAZMIN ADALI</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MOSTRANZO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ZALAVA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CARLOS URIEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>THANIA CRISTAL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>RIVADENEYRA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>DAVID OSWALDO</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>JOSIAH</t>
+  </si>
+  <si>
+    <t>OLIVER ULISES</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>CEREZO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>DAMIEN</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>KITZIA YAMILET</t>
+  </si>
+  <si>
+    <t>SHADAI COSTANTIN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>CLARET YAZMIN</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>SILVIA ANGELICA</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>BENITEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>URIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO PREVENTIVO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CARLOS ADRIAN</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>MARTI NEFTALI</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DEGANTE</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>SHARITH</t>
+  </si>
+  <si>
+    <t>JHOVANA</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>KARLA MICHEL</t>
+  </si>
+  <si>
+    <t>ROSA JATZIRI</t>
+  </si>
+  <si>
+    <t>CECILIA ARLETH</t>
+  </si>
+  <si>
+    <t>LAISHA STEFANY</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
+  </si>
+  <si>
+    <t>ANALIZA Y FRACCIONA SANGRE CON FINES TRANSFUSIONALES</t>
   </si>
   <si>
     <t>CARDENAS</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CITLAHUA</t>
-  </si>
-  <si>
-    <t>CONDADO</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>RAUL ARTURO</t>
-  </si>
-  <si>
-    <t>JOSUE ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>JUAN ANTONIO</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
+    <t>VILLA</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>GUILLERMO UBALDO</t>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>BRENDA ELENA</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
+    <t>WENDY</t>
   </si>
   <si>
     <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>MONFIL</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>EBER</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>PAOLA JAZMIN</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>CABALLERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>FERGIE PAULETTE</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>JAZMIN ADALI</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MOSTRANZO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ZALAVA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CARLOS URIEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>THANIA CRISTAL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>RIVADENEYRA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>DAVID OSWALDO</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>JOSIAH</t>
-  </si>
-  <si>
-    <t>OLIVER ULISES</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>CEREZO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
-    <t>DAMIEN</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>KITZIA YAMILET</t>
-  </si>
-  <si>
-    <t>SHADAI COSTANTIN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>CLARET YAZMIN</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>SILVIA ANGELICA</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>BENITEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>URIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO PREVENTIVO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARLOS ADRIAN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>LUIS ARIEL</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>MARTI NEFTALI</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DEGANTE</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>SHARITH</t>
-  </si>
-  <si>
-    <t>JHOVANA</t>
-  </si>
-  <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>KARLA MICHEL</t>
-  </si>
-  <si>
-    <t>ROSA JATZIRI</t>
-  </si>
-  <si>
-    <t>CECILIA ARLETH</t>
-  </si>
-  <si>
-    <t>LAISHA STEFANY</t>
-  </si>
-  <si>
-    <t>ASHLEY ZURELY</t>
-  </si>
-  <si>
-    <t>ANALIZA Y FRACCIONA SANGRE CON FINES TRANSFUSIONALES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>VALDES</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CORDOBA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>BRENDA ELENA</t>
-  </si>
-  <si>
-    <t>EVELYN AISHA</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>WENDY</t>
   </si>
   <si>
     <t>JAVIER FERNANDO</t>
@@ -1938,7 +1914,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1972,7 +1948,7 @@
         <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>84</v>
@@ -1989,10 +1965,10 @@
         <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>83</v>
@@ -2009,10 +1985,10 @@
         <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -2029,10 +2005,10 @@
         <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
         <v>83</v>
@@ -2043,19 +2019,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920181</v>
+        <v>20330051920183</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2069,13 +2045,13 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2083,41 +2059,21 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920183</v>
+        <v>20330051920306</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920306</v>
-      </c>
-      <c r="B9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -2156,13 +2112,13 @@
         <v>20330051920042</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
         <v>83</v>
@@ -2179,7 +2135,7 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
         <v>116</v>
@@ -2196,13 +2152,13 @@
         <v>20330051920097</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
         <v>84</v>
@@ -2216,10 +2172,10 @@
         <v>20330051920099</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
         <v>83</v>
@@ -2233,13 +2189,13 @@
         <v>20330051920100</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -2253,13 +2209,13 @@
         <v>20330051920100</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
         <v>83</v>
@@ -2273,13 +2229,13 @@
         <v>20330051920109</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
         <v>83</v>
@@ -2293,13 +2249,13 @@
         <v>20330051920109</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
         <v>84</v>
@@ -2313,13 +2269,13 @@
         <v>20330051920366</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
         <v>84</v>
@@ -2333,13 +2289,13 @@
         <v>20330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E11" t="s">
         <v>84</v>
@@ -2355,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2380,19 +2336,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920296</v>
+        <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>160</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2400,16 +2356,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920307</v>
+        <v>20330051920286</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
         <v>84</v>
@@ -2420,19 +2376,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920307</v>
+        <v>20330051920296</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2440,21 +2396,61 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
+        <v>20330051920307</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>20330051920307</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
         <v>20330051920309</v>
       </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
         <v>159</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="F5">
+      <c r="F7">
         <v>5</v>
       </c>
     </row>
@@ -2496,13 +2492,13 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2516,13 +2512,13 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2536,13 +2532,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2553,16 +2549,16 @@
         <v>19330051920032</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2573,16 +2569,16 @@
         <v>19330051920036</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2593,16 +2589,16 @@
         <v>19330051920039</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2613,16 +2609,16 @@
         <v>19330051920039</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2633,16 +2629,16 @@
         <v>19330051920417</v>
       </c>
       <c r="B9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C9" t="s">
         <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2686,13 +2682,13 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2703,16 +2699,16 @@
         <v>19330051920155</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2723,16 +2719,16 @@
         <v>19330051920155</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2743,16 +2739,16 @@
         <v>19330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2769,10 +2765,10 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2789,10 +2785,10 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2805,7 +2801,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2839,10 +2835,10 @@
         <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2850,141 +2846,21 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920235</v>
+        <v>19330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920236</v>
-      </c>
-      <c r="B4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920237</v>
-      </c>
-      <c r="B5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" t="s">
-        <v>194</v>
-      </c>
-      <c r="E5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920244</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" t="s">
-        <v>174</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920245</v>
-      </c>
-      <c r="B7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E7" t="s">
-        <v>174</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920429</v>
-      </c>
-      <c r="B8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920430</v>
-      </c>
-      <c r="B9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" t="s">
-        <v>174</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -3053,16 +2929,16 @@
         <v>19330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3073,16 +2949,16 @@
         <v>19330051920091</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3093,16 +2969,16 @@
         <v>19330051920091</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3113,16 +2989,16 @@
         <v>19330051920093</v>
       </c>
       <c r="B5" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="E5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3136,13 +3012,13 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3159,10 +3035,10 @@
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3179,10 +3055,10 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3193,16 +3069,16 @@
         <v>19330051920109</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
         <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3213,16 +3089,16 @@
         <v>19330051920109</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3235,7 +3111,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3260,19 +3136,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920201</v>
+        <v>19330051920194</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3280,41 +3156,21 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920203</v>
+        <v>19330051920204</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920207</v>
-      </c>
-      <c r="B4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F4">
         <v>5</v>
       </c>
     </row>
@@ -3353,13 +3209,13 @@
         <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
         <v>33</v>
@@ -3373,13 +3229,13 @@
         <v>21330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C3" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D3" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
@@ -3399,7 +3255,7 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
@@ -3419,7 +3275,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -3453,13 +3309,13 @@
         <v>21330051920020</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
@@ -3473,13 +3329,13 @@
         <v>21330051920024</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="C8" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D8" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -3493,13 +3349,13 @@
         <v>21330051920025</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D9" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -3513,13 +3369,13 @@
         <v>21330051920355</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="D10" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -3536,10 +3392,10 @@
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
@@ -3553,13 +3409,13 @@
         <v>21330051920380</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="D12" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -3573,13 +3429,13 @@
         <v>21330051920385</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -3593,13 +3449,13 @@
         <v>21330051920393</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="E14" t="s">
         <v>33</v>
@@ -3796,10 +3652,10 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -3813,13 +3669,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
@@ -3833,13 +3689,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -3856,10 +3712,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -3876,10 +3732,10 @@
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -3893,13 +3749,13 @@
         <v>21330051920052</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="D7" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -3919,7 +3775,7 @@
         <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -3933,13 +3789,13 @@
         <v>21330051920059</v>
       </c>
       <c r="B9" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="D9" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -3953,13 +3809,13 @@
         <v>21330051920061</v>
       </c>
       <c r="B10" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -3973,13 +3829,13 @@
         <v>21330051920065</v>
       </c>
       <c r="B11" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="C11" t="s">
         <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -3993,13 +3849,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -4013,13 +3869,13 @@
         <v>21330051920069</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -4033,13 +3889,13 @@
         <v>21330051920070</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" t="s">
         <v>257</v>
-      </c>
-      <c r="D14" t="s">
-        <v>270</v>
       </c>
       <c r="E14" t="s">
         <v>20</v>
@@ -4053,13 +3909,13 @@
         <v>21330051920388</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
+        <v>245</v>
+      </c>
+      <c r="D15" t="s">
         <v>258</v>
-      </c>
-      <c r="D15" t="s">
-        <v>271</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
@@ -4073,13 +3929,13 @@
         <v>21330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
+        <v>245</v>
+      </c>
+      <c r="D16" t="s">
         <v>258</v>
-      </c>
-      <c r="D16" t="s">
-        <v>271</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -4123,13 +3979,13 @@
         <v>21330051920073</v>
       </c>
       <c r="B2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D2" t="s">
         <v>272</v>
-      </c>
-      <c r="C2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D2" t="s">
-        <v>283</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -4143,13 +3999,13 @@
         <v>21330051920078</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
@@ -4166,10 +4022,10 @@
         <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -4183,13 +4039,13 @@
         <v>21330051920088</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>260</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -4209,7 +4065,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -4226,10 +4082,10 @@
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -4246,10 +4102,10 @@
         <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D8" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -4263,13 +4119,13 @@
         <v>21330051920097</v>
       </c>
       <c r="B9" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C9" t="s">
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -4283,13 +4139,13 @@
         <v>21330051920097</v>
       </c>
       <c r="B10" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C10" t="s">
         <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4309,7 +4165,7 @@
         <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -4323,13 +4179,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B12" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
         <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
@@ -4343,13 +4199,13 @@
         <v>21330051920107</v>
       </c>
       <c r="B13" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C13" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="D13" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -4363,13 +4219,13 @@
         <v>21330051920107</v>
       </c>
       <c r="B14" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -4383,13 +4239,13 @@
         <v>21330051920108</v>
       </c>
       <c r="B15" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
@@ -4403,13 +4259,13 @@
         <v>21330051920108</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C16" t="s">
         <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -4423,13 +4279,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C17" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D17" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="E17" t="s">
         <v>20</v>
@@ -4443,13 +4299,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C18" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D18" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
@@ -4463,13 +4319,13 @@
         <v>21330051920383</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="D19" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="E19" t="s">
         <v>20</v>
@@ -4486,10 +4342,10 @@
         <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D20" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="E20" t="s">
         <v>20</v>
@@ -4506,10 +4362,10 @@
         <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D21" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="E21" t="s">
         <v>18</v>
@@ -4553,13 +4409,13 @@
         <v>21330051920110</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -4573,13 +4429,13 @@
         <v>21330051920110</v>
       </c>
       <c r="B3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
@@ -4593,13 +4449,13 @@
         <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
         <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -4613,13 +4469,13 @@
         <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
         <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -4633,13 +4489,13 @@
         <v>21330051920128</v>
       </c>
       <c r="B6" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
@@ -4653,13 +4509,13 @@
         <v>21330051920128</v>
       </c>
       <c r="B7" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C7" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
@@ -4673,13 +4529,13 @@
         <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C8" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
@@ -4693,13 +4549,13 @@
         <v>21330051920133</v>
       </c>
       <c r="B9" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C9" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D9" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="E9" t="s">
         <v>33</v>
@@ -4743,13 +4599,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -4769,7 +4625,7 @@
         <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -4786,10 +4642,10 @@
         <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -4806,10 +4662,10 @@
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="D5" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -4826,10 +4682,10 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -4849,7 +4705,7 @@
         <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -4869,7 +4725,7 @@
         <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="E8" t="s">
         <v>33</v>
@@ -4883,13 +4739,13 @@
         <v>21330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="C9" t="s">
         <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -4903,13 +4759,13 @@
         <v>21330051920384</v>
       </c>
       <c r="B10" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
@@ -4923,13 +4779,13 @@
         <v>21330051920384</v>
       </c>
       <c r="B11" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -4943,13 +4799,13 @@
         <v>21330051920395</v>
       </c>
       <c r="B12" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C12" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D12" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -4963,13 +4819,13 @@
         <v>21330051920395</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C13" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D13" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -5019,7 +4875,7 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="E2" t="s">
         <v>85</v>
@@ -5039,10 +4895,10 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="E3" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5056,10 +4912,10 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E4" t="s">
         <v>85</v>
@@ -5073,13 +4929,13 @@
         <v>20330051920065</v>
       </c>
       <c r="B5" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="E5" t="s">
         <v>86</v>
@@ -5093,13 +4949,13 @@
         <v>20330051920065</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D6" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -5119,7 +4975,7 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -5133,16 +4989,16 @@
         <v>20330051920074</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E8" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5153,13 +5009,13 @@
         <v>20330051920074</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D9" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E9" t="s">
         <v>85</v>
@@ -5173,13 +5029,13 @@
         <v>20330051920082</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="E10" t="s">
         <v>85</v>
@@ -5223,13 +5079,13 @@
         <v>19330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="C2" t="s">
         <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="E2" t="s">
         <v>86</v>
@@ -5243,13 +5099,13 @@
         <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="C3" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="D3" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="E3" t="s">
         <v>86</v>
@@ -5269,7 +5125,7 @@
         <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="E4" t="s">
         <v>83</v>
@@ -5289,7 +5145,7 @@
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="E5" t="s">
         <v>86</v>
@@ -5303,13 +5159,13 @@
         <v>20330051920194</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="E6" t="s">
         <v>83</v>
@@ -5323,13 +5179,13 @@
         <v>20330051920194</v>
       </c>
       <c r="B7" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -5349,7 +5205,7 @@
         <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="E8" t="s">
         <v>86</v>
@@ -5369,7 +5225,7 @@
         <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="E9" t="s">
         <v>83</v>
@@ -5386,10 +5242,10 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="D10" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="E10" t="s">
         <v>86</v>
@@ -5406,10 +5262,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="D11" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="E11" t="s">
         <v>83</v>
@@ -5423,13 +5279,13 @@
         <v>20330051920205</v>
       </c>
       <c r="B12" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="C12" t="s">
         <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="E12" t="s">
         <v>86</v>
@@ -5446,10 +5302,10 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D13" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="E13" t="s">
         <v>86</v>
@@ -5466,10 +5322,10 @@
         <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D14" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="E14" t="s">
         <v>83</v>
@@ -5483,13 +5339,13 @@
         <v>20330051920214</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="C15" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D15" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="E15" t="s">
         <v>86</v>
@@ -5503,13 +5359,13 @@
         <v>20330051920215</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="C16" t="s">
         <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="E16" t="s">
         <v>86</v>
@@ -5523,13 +5379,13 @@
         <v>20330051920392</v>
       </c>
       <c r="B17" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="C17" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D17" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="E17" t="s">
         <v>83</v>
@@ -5543,13 +5399,13 @@
         <v>20330051920392</v>
       </c>
       <c r="B18" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="C18" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D18" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="E18" t="s">
         <v>86</v>
@@ -5565,7 +5421,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5593,16 +5449,16 @@
         <v>19330051920425</v>
       </c>
       <c r="B2" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5610,16 +5466,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920261</v>
+        <v>19330051920425</v>
       </c>
       <c r="B3" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C3" t="s">
-        <v>348</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="E3" t="s">
         <v>86</v>
@@ -5633,16 +5489,16 @@
         <v>20330051920261</v>
       </c>
       <c r="B4" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="C4" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D4" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5650,19 +5506,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920264</v>
+        <v>20330051920261</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>336</v>
       </c>
       <c r="C5" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="D5" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5670,16 +5526,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920267</v>
+        <v>20330051920264</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D6" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -5693,13 +5549,13 @@
         <v>20330051920267</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="D7" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E7" t="s">
         <v>83</v>
@@ -5710,19 +5566,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920274</v>
+        <v>20330051920267</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>339</v>
       </c>
       <c r="D8" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5730,19 +5586,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920278</v>
+        <v>20330051920274</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5753,16 +5609,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5770,16 +5626,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920281</v>
+        <v>20330051920278</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="E11" t="s">
         <v>83</v>
@@ -5793,16 +5649,16 @@
         <v>20330051920281</v>
       </c>
       <c r="B12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5810,21 +5666,41 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920282</v>
+        <v>20330051920281</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>242</v>
+        <v>346</v>
       </c>
       <c r="E13" t="s">
         <v>86</v>
       </c>
       <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>20330051920282</v>
+      </c>
+      <c r="B14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -5869,7 +5745,7 @@
         <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="E2" t="s">
         <v>83</v>
@@ -5886,10 +5762,10 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="D3" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="E3" t="s">
         <v>86</v>
@@ -5906,13 +5782,13 @@
         <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="E4" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5926,10 +5802,10 @@
         <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="E5" t="s">
         <v>86</v>
@@ -5943,13 +5819,13 @@
         <v>20330051920136</v>
       </c>
       <c r="B6" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E6" t="s">
         <v>85</v>
@@ -5963,13 +5839,13 @@
         <v>20330051920148</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="C7" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="E7" t="s">
         <v>85</v>
@@ -5983,13 +5859,13 @@
         <v>20330051920387</v>
       </c>
       <c r="B8" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C8" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="E8" t="s">
         <v>86</v>
@@ -6036,10 +5912,10 @@
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="D2" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="E2" t="s">
         <v>86</v>
@@ -6053,13 +5929,13 @@
         <v>20330051920321</v>
       </c>
       <c r="B3" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="C3" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="D3" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="E3" t="s">
         <v>83</v>
@@ -6076,10 +5952,10 @@
         <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="D4" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="E4" t="s">
         <v>86</v>
@@ -6093,13 +5969,13 @@
         <v>20330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="E5" t="s">
         <v>83</v>
@@ -6113,13 +5989,13 @@
         <v>20330051920328</v>
       </c>
       <c r="B6" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -6133,13 +6009,13 @@
         <v>20330051920330</v>
       </c>
       <c r="B7" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C7" t="s">
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="E7" t="s">
         <v>83</v>
@@ -6153,13 +6029,13 @@
         <v>20330051920330</v>
       </c>
       <c r="B8" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C8" t="s">
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="E8" t="s">
         <v>86</v>
@@ -6176,10 +6052,10 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="D9" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="E9" t="s">
         <v>86</v>
@@ -6193,16 +6069,16 @@
         <v>20330051920396</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6213,13 +6089,13 @@
         <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="E11" t="s">
         <v>86</v>
@@ -6233,13 +6109,13 @@
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
@@ -6286,13 +6162,13 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6303,16 +6179,16 @@
         <v>18330051920022</v>
       </c>
       <c r="B3" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="C3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D3" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6323,16 +6199,16 @@
         <v>19330051920045</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6346,13 +6222,13 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="D5" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6363,16 +6239,16 @@
         <v>19330051920050</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6386,13 +6262,13 @@
         <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6409,10 +6285,10 @@
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6429,10 +6305,10 @@
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6449,10 +6325,10 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="E10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6469,10 +6345,10 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="E11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6483,16 +6359,16 @@
         <v>19330051920418</v>
       </c>
       <c r="B12" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D12" t="s">
         <v>382</v>
       </c>
-      <c r="C12" t="s">
-        <v>384</v>
-      </c>
-      <c r="D12" t="s">
-        <v>393</v>
-      </c>
       <c r="E12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6503,16 +6379,16 @@
         <v>19330051920418</v>
       </c>
       <c r="B13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C13" t="s">
+        <v>373</v>
+      </c>
+      <c r="D13" t="s">
         <v>382</v>
       </c>
-      <c r="C13" t="s">
-        <v>384</v>
-      </c>
-      <c r="D13" t="s">
-        <v>393</v>
-      </c>
       <c r="E13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6743,16 +6619,16 @@
         <v>18330051920242</v>
       </c>
       <c r="B2" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="C2" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="D2" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6763,16 +6639,16 @@
         <v>18330051920319</v>
       </c>
       <c r="B3" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="C3" t="s">
         <v>56</v>
       </c>
       <c r="D3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E3" t="s">
         <v>407</v>
-      </c>
-      <c r="E3" t="s">
-        <v>418</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6789,10 +6665,10 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6803,16 +6679,16 @@
         <v>19330051920269</v>
       </c>
       <c r="B5" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="D5" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6823,16 +6699,16 @@
         <v>19330051920273</v>
       </c>
       <c r="B6" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C6" t="s">
         <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="E6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6843,16 +6719,16 @@
         <v>19330051920278</v>
       </c>
       <c r="B7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="D7" t="s">
         <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6866,13 +6742,13 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="D8" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6883,16 +6759,16 @@
         <v>19330051920286</v>
       </c>
       <c r="B9" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="D9" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6903,16 +6779,16 @@
         <v>19330051920286</v>
       </c>
       <c r="B10" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C10" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="D10" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="E10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6926,13 +6802,13 @@
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D11" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="E11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6943,16 +6819,16 @@
         <v>19330051920292</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>267</v>
       </c>
       <c r="C12" t="s">
         <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6969,10 +6845,10 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6983,16 +6859,16 @@
         <v>19330051920299</v>
       </c>
       <c r="B14" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C14" t="s">
+        <v>393</v>
+      </c>
+      <c r="D14" t="s">
         <v>404</v>
       </c>
-      <c r="D14" t="s">
-        <v>415</v>
-      </c>
       <c r="E14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7006,13 +6882,13 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
+        <v>394</v>
+      </c>
+      <c r="D15" t="s">
         <v>405</v>
       </c>
-      <c r="D15" t="s">
-        <v>416</v>
-      </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7029,10 +6905,10 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -7049,10 +6925,10 @@
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -7096,13 +6972,13 @@
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>410</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7113,16 +6989,16 @@
         <v>19330051920312</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>408</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7133,16 +7009,16 @@
         <v>19330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7153,16 +7029,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B5" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="C5" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="D5" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7173,16 +7049,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B6" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="C6" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="D6" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7193,16 +7069,16 @@
         <v>19330051920338</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C7" t="s">
         <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7219,10 +7095,10 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7233,7 +7109,7 @@
         <v>19330051920352</v>
       </c>
       <c r="B9" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C9" t="s">
         <v>105</v>
@@ -7242,7 +7118,7 @@
         <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7255,7 +7131,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7286,13 +7162,13 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E2" t="s">
         <v>427</v>
-      </c>
-      <c r="D2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E2" t="s">
-        <v>436</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7303,16 +7179,16 @@
         <v>18330051920188</v>
       </c>
       <c r="B3" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C3" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D3" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E3" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7323,16 +7199,16 @@
         <v>18330051920188</v>
       </c>
       <c r="B4" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C4" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D4" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7346,13 +7222,13 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D5" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7366,13 +7242,13 @@
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D6" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7383,16 +7259,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D7" t="s">
         <v>425</v>
       </c>
-      <c r="C7" t="s">
-        <v>430</v>
-      </c>
-      <c r="D7" t="s">
-        <v>434</v>
-      </c>
       <c r="E7" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7403,16 +7279,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B8" t="s">
+        <v>416</v>
+      </c>
+      <c r="C8" t="s">
+        <v>421</v>
+      </c>
+      <c r="D8" t="s">
         <v>425</v>
       </c>
-      <c r="C8" t="s">
-        <v>430</v>
-      </c>
-      <c r="D8" t="s">
-        <v>434</v>
-      </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7423,16 +7299,16 @@
         <v>19330051920366</v>
       </c>
       <c r="B9" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="C9" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D9" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7440,16 +7316,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920366</v>
+        <v>19330051920436</v>
       </c>
       <c r="B10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
         <v>426</v>
-      </c>
-      <c r="C10" t="s">
-        <v>258</v>
-      </c>
-      <c r="D10" t="s">
-        <v>265</v>
       </c>
       <c r="E10" t="s">
         <v>174</v>
@@ -7460,41 +7336,21 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920367</v>
+        <v>19330051920436</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E11" t="s">
-        <v>174</v>
+        <v>427</v>
       </c>
       <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920369</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>174</v>
-      </c>
-      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -7533,16 +7389,16 @@
         <v>19330051920248</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7553,16 +7409,16 @@
         <v>19330051920250</v>
       </c>
       <c r="B3" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C3" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="D3" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7579,10 +7435,10 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7599,10 +7455,10 @@
         <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7619,10 +7475,10 @@
         <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7639,10 +7495,10 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7659,10 +7515,10 @@
         <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>439</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7679,10 +7535,10 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7696,13 +7552,13 @@
         <v>112</v>
       </c>
       <c r="C10" t="s">
+        <v>432</v>
+      </c>
+      <c r="D10" t="s">
         <v>441</v>
       </c>
-      <c r="D10" t="s">
-        <v>449</v>
-      </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7716,13 +7572,13 @@
         <v>112</v>
       </c>
       <c r="C11" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" t="s">
         <v>441</v>
       </c>
-      <c r="D11" t="s">
-        <v>449</v>
-      </c>
       <c r="E11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7733,16 +7589,16 @@
         <v>19330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="C12" t="s">
         <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="E12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7756,13 +7612,13 @@
         <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D13" t="s">
         <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7773,16 +7629,16 @@
         <v>19330051920400</v>
       </c>
       <c r="B14" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C14" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="D14" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7796,13 +7652,13 @@
         <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7813,16 +7669,16 @@
         <v>19330051920405</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="E16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -7833,16 +7689,16 @@
         <v>19330051920414</v>
       </c>
       <c r="B17" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="D17" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F17">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3442" uniqueCount="792">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -2341,9 +2341,6 @@
   </si>
   <si>
     <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES MÓVILES PARA IOS</t>
   </si>
   <si>
     <t>CRISTOBAL</t>
@@ -14130,7 +14127,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -14295,19 +14292,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920334</v>
+        <v>19330051920337</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>618</v>
+        <v>761</v>
       </c>
       <c r="E9" t="s">
-        <v>765</v>
+        <v>455</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -14315,16 +14312,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920337</v>
+        <v>19330051920345</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E10" t="s">
         <v>455</v>
@@ -14335,101 +14332,61 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920345</v>
+        <v>19330051920352</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>570</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E11" t="s">
-        <v>455</v>
+        <v>745</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B12" t="s">
-        <v>570</v>
+        <v>755</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="D12" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E12" t="s">
-        <v>745</v>
+        <v>455</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B13" t="s">
-        <v>570</v>
+        <v>755</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="D13" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E13" t="s">
-        <v>765</v>
+        <v>454</v>
       </c>
       <c r="F13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920353</v>
-      </c>
-      <c r="B14" t="s">
-        <v>755</v>
-      </c>
-      <c r="C14" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" t="s">
-        <v>764</v>
-      </c>
-      <c r="E14" t="s">
-        <v>455</v>
-      </c>
-      <c r="F14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920353</v>
-      </c>
-      <c r="B15" t="s">
-        <v>755</v>
-      </c>
-      <c r="C15" t="s">
-        <v>201</v>
-      </c>
-      <c r="D15" t="s">
-        <v>764</v>
-      </c>
-      <c r="E15" t="s">
-        <v>454</v>
-      </c>
-      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -14468,7 +14425,7 @@
         <v>19330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C2" t="s">
         <v>647</v>
@@ -14477,7 +14434,7 @@
         <v>376</v>
       </c>
       <c r="E2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -14488,7 +14445,7 @@
         <v>19330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C3" t="s">
         <v>647</v>
@@ -14514,7 +14471,7 @@
         <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E4" t="s">
         <v>520</v>
@@ -14534,10 +14491,10 @@
         <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E5" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -14571,13 +14528,13 @@
         <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D7" t="s">
         <v>391</v>
       </c>
       <c r="E7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -14594,7 +14551,7 @@
         <v>190</v>
       </c>
       <c r="D8" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E8" t="s">
         <v>520</v>
@@ -14614,10 +14571,10 @@
         <v>190</v>
       </c>
       <c r="D9" t="s">
+        <v>768</v>
+      </c>
+      <c r="E9" t="s">
         <v>769</v>
-      </c>
-      <c r="E9" t="s">
-        <v>770</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -14637,7 +14594,7 @@
         <v>152</v>
       </c>
       <c r="E10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -14677,7 +14634,7 @@
         <v>651</v>
       </c>
       <c r="E12" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -14758,13 +14715,13 @@
         <v>19330051920246</v>
       </c>
       <c r="B2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C2" t="s">
         <v>408</v>
       </c>
       <c r="D2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E2" t="s">
         <v>455</v>
@@ -14784,7 +14741,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E3" t="s">
         <v>455</v>
@@ -14798,13 +14755,13 @@
         <v>19330051920249</v>
       </c>
       <c r="B4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C4" t="s">
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E4" t="s">
         <v>455</v>
@@ -14824,7 +14781,7 @@
         <v>646</v>
       </c>
       <c r="D5" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E5" t="s">
         <v>745</v>
@@ -14838,7 +14795,7 @@
         <v>19330051920260</v>
       </c>
       <c r="B6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C6" t="s">
         <v>495</v>
@@ -14858,16 +14815,16 @@
         <v>19330051920261</v>
       </c>
       <c r="B7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C7" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D7" t="s">
         <v>400</v>
       </c>
       <c r="E7" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -14918,13 +14875,13 @@
         <v>19330051920266</v>
       </c>
       <c r="B10" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C10" t="s">
         <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E10" t="s">
         <v>745</v>
@@ -14938,13 +14895,13 @@
         <v>19330051920400</v>
       </c>
       <c r="B11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C11" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D11" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E11" t="s">
         <v>455</v>
@@ -14964,7 +14921,7 @@
         <v>273</v>
       </c>
       <c r="D12" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E12" t="s">
         <v>455</v>
@@ -14984,7 +14941,7 @@
         <v>194</v>
       </c>
       <c r="D13" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E13" t="s">
         <v>745</v>
@@ -15004,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E14" t="s">
         <v>455</v>
@@ -15024,7 +14981,7 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E15" t="s">
         <v>745</v>
@@ -15041,10 +14998,10 @@
         <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D16" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E16" t="s">
         <v>745</v>
@@ -15064,7 +15021,7 @@
         <v>626</v>
       </c>
       <c r="D17" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E17" t="s">
         <v>745</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2203" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="653">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -9673,7 +9673,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9778,19 +9778,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>585</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -9810,7 +9810,7 @@
         <v>592</v>
       </c>
       <c r="E7" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -9818,19 +9818,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920322</v>
+        <v>20330051920323</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -9850,7 +9850,7 @@
         <v>593</v>
       </c>
       <c r="E9" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -9858,19 +9858,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E10" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -9890,7 +9890,7 @@
         <v>594</v>
       </c>
       <c r="E11" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -9898,19 +9898,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>586</v>
       </c>
       <c r="D12" t="s">
-        <v>594</v>
+        <v>430</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -9930,7 +9930,7 @@
         <v>430</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -9938,16 +9938,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>438</v>
       </c>
       <c r="C14" t="s">
-        <v>586</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>430</v>
+        <v>595</v>
       </c>
       <c r="E14" t="s">
         <v>192</v>
@@ -9970,7 +9970,7 @@
         <v>595</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -9978,16 +9978,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B16" t="s">
-        <v>438</v>
+        <v>582</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E16" t="s">
         <v>165</v>
@@ -10010,7 +10010,7 @@
         <v>596</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -10018,16 +10018,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B18" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>329</v>
       </c>
       <c r="D18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E18" t="s">
         <v>192</v>
@@ -10050,7 +10050,7 @@
         <v>597</v>
       </c>
       <c r="E19" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -10058,16 +10058,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920330</v>
+        <v>20330051920331</v>
       </c>
       <c r="B20" t="s">
-        <v>583</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>329</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E20" t="s">
         <v>165</v>
@@ -10078,16 +10078,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920331</v>
+        <v>20330051920333</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>598</v>
+        <v>391</v>
       </c>
       <c r="E21" t="s">
         <v>165</v>
@@ -10110,7 +10110,7 @@
         <v>391</v>
       </c>
       <c r="E22" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -10118,19 +10118,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>587</v>
       </c>
       <c r="D23" t="s">
-        <v>391</v>
+        <v>599</v>
       </c>
       <c r="E23" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -10150,7 +10150,7 @@
         <v>599</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -10158,41 +10158,21 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920335</v>
+        <v>20330051920380</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>584</v>
       </c>
       <c r="C25" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D25" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E25" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="F25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920380</v>
-      </c>
-      <c r="B26" t="s">
-        <v>584</v>
-      </c>
-      <c r="C26" t="s">
-        <v>588</v>
-      </c>
-      <c r="D26" t="s">
-        <v>600</v>
-      </c>
-      <c r="E26" t="s">
-        <v>165</v>
-      </c>
-      <c r="F26">
         <v>-1</v>
       </c>
     </row>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="640">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -816,798 +816,795 @@
     <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>VALERIA ANGELY</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>PROBABILIDAD Y ESTADÍSTICA</t>
+  </si>
+  <si>
+    <t>TEMAS DE FILOSOFÍA</t>
+  </si>
+  <si>
+    <t>TEMAS DE FÍSICA</t>
+  </si>
+  <si>
+    <t>MATEMÁTICAS APLICADAS</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO EN SUBESTACIONES ELÉCTRICAS</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>COUDER</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESE YAEL</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>KATHERINE AZUL</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>MARIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
+  </si>
+  <si>
+    <t>ANALIZA SANGRE MEDIANTE PRUEBAS HORMONALES, TOXICOLÓGICAS Y DE MARCADORES TUMORALES</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MARIA DE JESUS</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
+  </si>
+  <si>
+    <t>YESUA ISIDRO</t>
+  </si>
+  <si>
+    <t>RENZO JHOVANI</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES MÓVILES PARA IOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>DENISSE MERARY</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>DETERMINA LA NÓMINA DEL PERSONAL DE LA ORGANIZACIÓN TOMANDO EN CUENTA LA NORMATIVIDAD LABORAL</t>
+  </si>
+  <si>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>OCTAVIANO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JUAN LUIS</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>YARITZI</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>ROSARIO DOLORES</t>
+  </si>
+  <si>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>INGLÉS II</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>MARCOS JESUS</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>DISTINGUE LOS DIFERENTES TIPOS DE EMPRESA POR SU GIRO, ÁREAS FUNCIONALES, DOCUMENTACIÓN ADMINISTRATIVA Y RECURSOS</t>
+  </si>
+  <si>
+    <t>ELABORA ESTRATEGIAS PARA REALIZAR LAS ACTIVIDADES DE SU ÁREA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>ENSAMBLA E INSTALA CONTROLADORES Y DISPOSITIVOS PERIFÉRICOS</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
     <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTROMAGNÉTICO</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>PROBABILIDAD Y ESTADÍSTICA</t>
-  </si>
-  <si>
-    <t>TEMAS DE FILOSOFÍA</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
-  </si>
-  <si>
-    <t>MATEMÁTICAS APLICADAS</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO EN SUBESTACIONES ELÉCTRICAS</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESE YAEL</t>
-  </si>
-  <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>KATHERINE AZUL</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>KAROL</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
-    <t>MARIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
-  </si>
-  <si>
-    <t>ANALIZA SANGRE MEDIANTE PRUEBAS HORMONALES, TOXICOLÓGICAS Y DE MARCADORES TUMORALES</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MARIA DE JESUS</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>RENZO JHOVANI</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES MÓVILES PARA IOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>ROCIO</t>
-  </si>
-  <si>
-    <t>DETERMINA LA NÓMINA DEL PERSONAL DE LA ORGANIZACIÓN TOMANDO EN CUENTA LA NORMATIVIDAD LABORAL</t>
-  </si>
-  <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>OCTAVIANO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
-    <t>GROTH</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ROSARIO DOLORES</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>CABALLERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>INGLÉS II</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>MARCOS JESUS</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>DISTINGUE LOS DIFERENTES TIPOS DE EMPRESA POR SU GIRO, ÁREAS FUNCIONALES, DOCUMENTACIÓN ADMINISTRATIVA Y RECURSOS</t>
-  </si>
-  <si>
-    <t>ELABORA ESTRATEGIAS PARA REALIZAR LAS ACTIVIDADES DE SU ÁREA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>ENSAMBLA E INSTALA CONTROLADORES Y DISPOSITIVOS PERIFÉRICOS</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
     <t>ASCENCION</t>
   </si>
   <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
     <t>GALVEZ</t>
   </si>
   <si>
@@ -1650,9 +1647,6 @@
     <t>ERICK DE JESUS</t>
   </si>
   <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
     <t>AMARELY GUADALUPE</t>
   </si>
   <si>
@@ -1680,6 +1674,9 @@
     <t>SUSANA</t>
   </si>
   <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
     <t>AMADA ARELY</t>
   </si>
   <si>
@@ -1716,9 +1713,6 @@
     <t>AXEL YAEL</t>
   </si>
   <si>
-    <t>LIMON</t>
-  </si>
-  <si>
     <t>MARCIAL</t>
   </si>
   <si>
@@ -1728,15 +1722,9 @@
     <t>OSORIO</t>
   </si>
   <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
     <t>NOYOLA</t>
   </si>
   <si>
@@ -1752,18 +1740,9 @@
     <t>MELANIE NAOMI</t>
   </si>
   <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
     <t>YAZMIN</t>
   </si>
   <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
     <t>ABDIEL</t>
   </si>
   <si>
@@ -1779,169 +1758,151 @@
     <t>KARLA</t>
   </si>
   <si>
-    <t>INGRID YALITH</t>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>BRINDA SOPORTE TÉCNICO DE MANERA PRESENCIAL</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>BERNAL</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>DIEGO OLLIN</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>GWINETH</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>AGUILA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
   </si>
   <si>
     <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>BRINDA SOPORTE TÉCNICO DE MANERA PRESENCIAL</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>BERNAL</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>DIEGO OLLIN</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>ASHLEY ZURELY</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>AGUILA</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
   </si>
   <si>
     <t>DETERMINA REMUNERACIONES DEL PERSONAL EN SITUACIONES EXTRAORDINARIAS</t>
@@ -2742,7 +2703,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2916,7 +2877,7 @@
         <v>247</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -2933,7 +2894,7 @@
         <v>247</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>192</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -2973,24 +2934,24 @@
         <v>249</v>
       </c>
       <c r="E12" t="s">
-        <v>256</v>
+        <v>163</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920102</v>
+        <v>20330051920107</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E13" t="s">
         <v>163</v>
@@ -3001,16 +2962,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920107</v>
+        <v>20330051920109</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E14" t="s">
         <v>163</v>
@@ -3021,16 +2982,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920109</v>
+        <v>20330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E15" t="s">
         <v>163</v>
@@ -3041,16 +3002,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920112</v>
+        <v>20330051920113</v>
       </c>
       <c r="B16" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E16" t="s">
         <v>163</v>
@@ -3061,41 +3022,21 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920113</v>
+        <v>20330051920365</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>218</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920365</v>
-      </c>
-      <c r="B18" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" t="s">
-        <v>139</v>
-      </c>
-      <c r="D18" t="s">
-        <v>254</v>
-      </c>
-      <c r="E18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F18">
         <v>5</v>
       </c>
     </row>
@@ -3134,13 +3075,13 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
         <v>193</v>
@@ -3154,13 +3095,13 @@
         <v>20330051920287</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E3" t="s">
         <v>192</v>
@@ -3177,10 +3118,10 @@
         <v>221</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E4" t="s">
         <v>192</v>
@@ -3194,13 +3135,13 @@
         <v>20330051920298</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C5" t="s">
         <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E5" t="s">
         <v>166</v>
@@ -3297,10 +3238,10 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
         <v>193</v>
@@ -3317,10 +3258,10 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E11" t="s">
         <v>166</v>
@@ -3340,7 +3281,7 @@
         <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E12" t="s">
         <v>166</v>
@@ -3354,10 +3295,10 @@
         <v>20330051920311</v>
       </c>
       <c r="B13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
         <v>61</v>
@@ -3377,10 +3318,10 @@
         <v>213</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E14" t="s">
         <v>166</v>
@@ -3397,10 +3338,10 @@
         <v>213</v>
       </c>
       <c r="C15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E15" t="s">
         <v>165</v>
@@ -3444,16 +3385,16 @@
         <v>18330061460390</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
         <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -3467,13 +3408,13 @@
         <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D3" t="s">
         <v>245</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -3487,13 +3428,13 @@
         <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D4" t="s">
         <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3510,10 +3451,10 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3530,13 +3471,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E6" t="s">
         <v>289</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3550,13 +3491,13 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3567,13 +3508,13 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -3587,13 +3528,13 @@
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -3604,16 +3545,16 @@
         <v>19330051920023</v>
       </c>
       <c r="B10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -3624,16 +3565,16 @@
         <v>19330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -3650,10 +3591,10 @@
         <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -3670,10 +3611,10 @@
         <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -3684,16 +3625,16 @@
         <v>19330051920039</v>
       </c>
       <c r="B14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -3704,16 +3645,16 @@
         <v>19330051920039</v>
       </c>
       <c r="B15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3724,7 +3665,7 @@
         <v>19330051920040</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -3744,7 +3685,7 @@
         <v>19330051920040</v>
       </c>
       <c r="B17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
@@ -3753,7 +3694,7 @@
         <v>249</v>
       </c>
       <c r="E17" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -3794,16 +3735,16 @@
         <v>19330051920149</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3820,10 +3761,10 @@
         <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3837,13 +3778,13 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -3857,13 +3798,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3874,19 +3815,19 @@
         <v>19330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C6" t="s">
         <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3894,19 +3835,19 @@
         <v>19330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
         <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E7" t="s">
         <v>289</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3917,13 +3858,13 @@
         <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -3940,10 +3881,10 @@
         <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -3960,10 +3901,10 @@
         <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3980,10 +3921,10 @@
         <v>178</v>
       </c>
       <c r="D11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -4000,10 +3941,10 @@
         <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4014,16 +3955,16 @@
         <v>19330051920276</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C13" t="s">
         <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -4034,16 +3975,16 @@
         <v>19330051920276</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C14" t="s">
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4060,10 +4001,10 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -4077,13 +4018,13 @@
         <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4127,13 +4068,13 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D2" t="s">
         <v>253</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -4144,16 +4085,16 @@
         <v>19330051920227</v>
       </c>
       <c r="B3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C3" t="s">
         <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4164,16 +4105,16 @@
         <v>19330051920227</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C4" t="s">
         <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4184,16 +4125,16 @@
         <v>19330051920240</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4210,10 +4151,10 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4230,10 +4171,10 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -4244,16 +4185,16 @@
         <v>19330051920245</v>
       </c>
       <c r="B8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -4264,16 +4205,16 @@
         <v>19330051920404</v>
       </c>
       <c r="B9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -4287,13 +4228,13 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -4334,16 +4275,16 @@
         <v>19330051920130</v>
       </c>
       <c r="B2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C2" t="s">
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -4354,16 +4295,16 @@
         <v>19330051920130</v>
       </c>
       <c r="B3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
         <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4380,10 +4321,10 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4400,10 +4341,10 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -4414,16 +4355,16 @@
         <v>19330051920136</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
         <v>92</v>
       </c>
       <c r="D6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E6" t="s">
         <v>332</v>
-      </c>
-      <c r="E6" t="s">
-        <v>333</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -4443,7 +4384,7 @@
         <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -4490,10 +4431,10 @@
         <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E2" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -4510,10 +4451,10 @@
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>357</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -4527,13 +4468,13 @@
         <v>196</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D4" t="s">
         <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -4547,13 +4488,13 @@
         <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D5" t="s">
         <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -4564,16 +4505,16 @@
         <v>19330051920097</v>
       </c>
       <c r="B6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -4590,10 +4531,10 @@
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -4607,13 +4548,13 @@
         <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -4627,13 +4568,13 @@
         <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4644,16 +4585,16 @@
         <v>19330051920105</v>
       </c>
       <c r="B10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -4664,16 +4605,16 @@
         <v>19330051920105</v>
       </c>
       <c r="B11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -4684,16 +4625,16 @@
         <v>19330051920106</v>
       </c>
       <c r="B12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -4710,13 +4651,13 @@
         <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4730,13 +4671,13 @@
         <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E14" t="s">
         <v>289</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4744,16 +4685,16 @@
         <v>19330051920115</v>
       </c>
       <c r="B15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -4764,16 +4705,16 @@
         <v>19330051920116</v>
       </c>
       <c r="B16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D16" t="s">
         <v>162</v>
       </c>
       <c r="E16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -4784,16 +4725,16 @@
         <v>19330051920117</v>
       </c>
       <c r="B17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C17" t="s">
         <v>196</v>
       </c>
       <c r="D17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -4804,16 +4745,16 @@
         <v>19330051920117</v>
       </c>
       <c r="B18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C18" t="s">
         <v>196</v>
       </c>
       <c r="D18" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -4824,16 +4765,16 @@
         <v>19330051920118</v>
       </c>
       <c r="B19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -4844,16 +4785,16 @@
         <v>19330051920118</v>
       </c>
       <c r="B20" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E20" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -4864,16 +4805,16 @@
         <v>19330051920119</v>
       </c>
       <c r="B21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C21" t="s">
         <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -4884,16 +4825,16 @@
         <v>19330051920120</v>
       </c>
       <c r="B22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D22" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -4934,16 +4875,16 @@
         <v>18330051920351</v>
       </c>
       <c r="B2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C2" t="s">
         <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4954,16 +4895,16 @@
         <v>19330051920194</v>
       </c>
       <c r="B3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4974,16 +4915,16 @@
         <v>19330051920195</v>
       </c>
       <c r="B4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4994,16 +4935,16 @@
         <v>19330051920195</v>
       </c>
       <c r="B5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5020,10 +4961,10 @@
         <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -5064,13 +5005,13 @@
         <v>20330051920022</v>
       </c>
       <c r="B2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C2" t="s">
         <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E2" t="s">
         <v>84</v>
@@ -5084,13 +5025,13 @@
         <v>20330051920022</v>
       </c>
       <c r="B3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C3" t="s">
         <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -5107,10 +5048,10 @@
         <v>198</v>
       </c>
       <c r="C4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E4" t="s">
         <v>84</v>
@@ -5127,10 +5068,10 @@
         <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -5150,7 +5091,7 @@
         <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -5167,10 +5108,10 @@
         <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E7" t="s">
         <v>84</v>
@@ -5184,13 +5125,13 @@
         <v>21330051920003</v>
       </c>
       <c r="B8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C8" t="s">
         <v>241</v>
       </c>
       <c r="D8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E8" t="s">
         <v>84</v>
@@ -5210,7 +5151,7 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -5230,7 +5171,7 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E10" t="s">
         <v>84</v>
@@ -5244,13 +5185,13 @@
         <v>21330051920008</v>
       </c>
       <c r="B11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E11" t="s">
         <v>84</v>
@@ -5267,10 +5208,10 @@
         <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E12" t="s">
         <v>84</v>
@@ -5287,7 +5228,7 @@
         <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D13" t="s">
         <v>119</v>
@@ -5304,7 +5245,7 @@
         <v>21330051920013</v>
       </c>
       <c r="B14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -5330,7 +5271,7 @@
         <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E15" t="s">
         <v>84</v>
@@ -5344,13 +5285,13 @@
         <v>21330051920016</v>
       </c>
       <c r="B16" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E16" t="s">
         <v>84</v>
@@ -5364,13 +5305,13 @@
         <v>21330051920016</v>
       </c>
       <c r="B17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D17" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
@@ -5384,13 +5325,13 @@
         <v>21330051920018</v>
       </c>
       <c r="B18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C18" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D18" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E18" t="s">
         <v>106</v>
@@ -5404,13 +5345,13 @@
         <v>21330051920018</v>
       </c>
       <c r="B19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E19" t="s">
         <v>84</v>
@@ -5424,10 +5365,10 @@
         <v>21330051920021</v>
       </c>
       <c r="B20" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C20" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D20" t="s">
         <v>52</v>
@@ -5444,13 +5385,13 @@
         <v>21330051920025</v>
       </c>
       <c r="B21" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C21" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D21" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E21" t="s">
         <v>84</v>
@@ -5464,13 +5405,13 @@
         <v>21330051920025</v>
       </c>
       <c r="B22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C22" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D22" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
@@ -5490,7 +5431,7 @@
         <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E23" t="s">
         <v>84</v>
@@ -5510,7 +5451,7 @@
         <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E24" t="s">
         <v>21</v>
@@ -5527,7 +5468,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D25" t="s">
         <v>158</v>
@@ -5550,7 +5491,7 @@
         <v>171</v>
       </c>
       <c r="D26" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E26" t="s">
         <v>84</v>
@@ -5567,10 +5508,10 @@
         <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D27" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E27" t="s">
         <v>21</v>
@@ -5587,10 +5528,10 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D28" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E28" t="s">
         <v>84</v>
@@ -5610,7 +5551,7 @@
         <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E29" t="s">
         <v>84</v>
@@ -6050,7 +5991,7 @@
         <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E2" t="s">
         <v>63</v>
@@ -6070,7 +6011,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E3" t="s">
         <v>84</v>
@@ -6090,7 +6031,7 @@
         <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -6104,13 +6045,13 @@
         <v>21330051920072</v>
       </c>
       <c r="B5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -6130,7 +6071,7 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -6150,7 +6091,7 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E7" t="s">
         <v>84</v>
@@ -6167,10 +6108,10 @@
         <v>221</v>
       </c>
       <c r="C8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E8" t="s">
         <v>84</v>
@@ -6187,10 +6128,10 @@
         <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -6207,10 +6148,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E10" t="s">
         <v>63</v>
@@ -6227,10 +6168,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E11" t="s">
         <v>84</v>
@@ -6247,10 +6188,10 @@
         <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E12" t="s">
         <v>84</v>
@@ -6270,10 +6211,10 @@
         <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -6287,10 +6228,10 @@
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E14" t="s">
         <v>63</v>
@@ -6304,10 +6245,10 @@
         <v>21330051920092</v>
       </c>
       <c r="B15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D15" t="s">
         <v>155</v>
@@ -6324,10 +6265,10 @@
         <v>21330051920092</v>
       </c>
       <c r="B16" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D16" t="s">
         <v>155</v>
@@ -6347,13 +6288,13 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D17" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -6367,10 +6308,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E18" t="s">
         <v>63</v>
@@ -6387,10 +6328,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D19" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E19" t="s">
         <v>84</v>
@@ -6404,7 +6345,7 @@
         <v>21330051920097</v>
       </c>
       <c r="B20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C20" t="s">
         <v>143</v>
@@ -6424,7 +6365,7 @@
         <v>21330051920097</v>
       </c>
       <c r="B21" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C21" t="s">
         <v>143</v>
@@ -6444,13 +6385,13 @@
         <v>21330051920098</v>
       </c>
       <c r="B22" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E22" t="s">
         <v>84</v>
@@ -6464,13 +6405,13 @@
         <v>21330051920098</v>
       </c>
       <c r="B23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E23" t="s">
         <v>21</v>
@@ -6484,13 +6425,13 @@
         <v>21330051920099</v>
       </c>
       <c r="B24" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C24" t="s">
         <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E24" t="s">
         <v>84</v>
@@ -6504,13 +6445,13 @@
         <v>21330051920100</v>
       </c>
       <c r="B25" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D25" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E25" t="s">
         <v>21</v>
@@ -6524,13 +6465,13 @@
         <v>21330051920100</v>
       </c>
       <c r="B26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D26" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E26" t="s">
         <v>84</v>
@@ -6550,7 +6491,7 @@
         <v>196</v>
       </c>
       <c r="D27" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E27" t="s">
         <v>63</v>
@@ -6570,7 +6511,7 @@
         <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E28" t="s">
         <v>21</v>
@@ -6584,13 +6525,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B29" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C29" t="s">
         <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E29" t="s">
         <v>21</v>
@@ -6604,13 +6545,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B30" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C30" t="s">
         <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E30" t="s">
         <v>84</v>
@@ -6627,10 +6568,10 @@
         <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D31" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E31" t="s">
         <v>84</v>
@@ -6647,10 +6588,10 @@
         <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D32" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E32" t="s">
         <v>21</v>
@@ -6664,13 +6605,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B33" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D33" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E33" t="s">
         <v>21</v>
@@ -6684,13 +6625,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B34" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D34" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E34" t="s">
         <v>84</v>
@@ -6704,13 +6645,13 @@
         <v>21330051920383</v>
       </c>
       <c r="B35" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C35" t="s">
         <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E35" t="s">
         <v>84</v>
@@ -6754,13 +6695,13 @@
         <v>21330051920111</v>
       </c>
       <c r="B2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E2" t="s">
         <v>78</v>
@@ -6774,13 +6715,13 @@
         <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C3" t="s">
         <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E3" t="s">
         <v>84</v>
@@ -6797,7 +6738,7 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
         <v>187</v>
@@ -6817,10 +6758,10 @@
         <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -6834,13 +6775,13 @@
         <v>21330051920117</v>
       </c>
       <c r="B6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C6" t="s">
         <v>217</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E6" t="s">
         <v>78</v>
@@ -6860,7 +6801,7 @@
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E7" t="s">
         <v>78</v>
@@ -6880,7 +6821,7 @@
         <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E8" t="s">
         <v>84</v>
@@ -6900,7 +6841,7 @@
         <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E9" t="s">
         <v>78</v>
@@ -6914,13 +6855,13 @@
         <v>21330051920124</v>
       </c>
       <c r="B10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C10" t="s">
         <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E10" t="s">
         <v>78</v>
@@ -6934,13 +6875,13 @@
         <v>21330051920127</v>
       </c>
       <c r="B11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D11" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E11" t="s">
         <v>84</v>
@@ -6954,13 +6895,13 @@
         <v>21330051920127</v>
       </c>
       <c r="B12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E12" t="s">
         <v>78</v>
@@ -6974,13 +6915,13 @@
         <v>21330051920130</v>
       </c>
       <c r="B13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E13" t="s">
         <v>78</v>
@@ -6994,13 +6935,13 @@
         <v>21330051920130</v>
       </c>
       <c r="B14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E14" t="s">
         <v>84</v>
@@ -7017,10 +6958,10 @@
         <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -7040,10 +6981,10 @@
         <v>173</v>
       </c>
       <c r="D16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -7060,7 +7001,7 @@
         <v>173</v>
       </c>
       <c r="D17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E17" t="s">
         <v>78</v>
@@ -7104,13 +7045,13 @@
         <v>21330051920029</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E2" t="s">
         <v>84</v>
@@ -7130,7 +7071,7 @@
         <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E3" t="s">
         <v>84</v>
@@ -7144,16 +7085,16 @@
         <v>21330051920032</v>
       </c>
       <c r="B4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7164,13 +7105,13 @@
         <v>21330051920032</v>
       </c>
       <c r="B5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -7187,10 +7128,10 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -7204,13 +7145,13 @@
         <v>21330051920035</v>
       </c>
       <c r="B7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E7" t="s">
         <v>84</v>
@@ -7224,13 +7165,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E8" t="s">
         <v>84</v>
@@ -7250,10 +7191,10 @@
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7270,7 +7211,7 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E10" t="s">
         <v>84</v>
@@ -7290,7 +7231,7 @@
         <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -7310,7 +7251,7 @@
         <v>213</v>
       </c>
       <c r="D12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E12" t="s">
         <v>84</v>
@@ -7327,10 +7268,10 @@
         <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E13" t="s">
         <v>84</v>
@@ -7347,10 +7288,10 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D14" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E14" t="s">
         <v>84</v>
@@ -7370,7 +7311,7 @@
         <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
@@ -7390,7 +7331,7 @@
         <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E16" t="s">
         <v>84</v>
@@ -7404,13 +7345,13 @@
         <v>21330051920046</v>
       </c>
       <c r="B17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E17" t="s">
         <v>84</v>
@@ -7427,13 +7368,13 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E18" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -7447,13 +7388,13 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D19" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -7464,13 +7405,13 @@
         <v>21330051920053</v>
       </c>
       <c r="B20" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E20" t="s">
         <v>84</v>
@@ -7484,16 +7425,16 @@
         <v>21330051920053</v>
       </c>
       <c r="B21" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C21" t="s">
         <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E21" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -7507,10 +7448,10 @@
         <v>236</v>
       </c>
       <c r="C22" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D22" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E22" t="s">
         <v>84</v>
@@ -7524,7 +7465,7 @@
         <v>21330051920058</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C23" t="s">
         <v>27</v>
@@ -7544,10 +7485,10 @@
         <v>21330051920059</v>
       </c>
       <c r="B24" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C24" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D24" t="s">
         <v>229</v>
@@ -7567,10 +7508,10 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D25" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E25" t="s">
         <v>84</v>
@@ -7584,13 +7525,13 @@
         <v>21330051920062</v>
       </c>
       <c r="B26" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E26" t="s">
         <v>84</v>
@@ -7604,16 +7545,16 @@
         <v>21330051920062</v>
       </c>
       <c r="B27" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E27" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F27">
         <v>-1</v>
@@ -7630,7 +7571,7 @@
         <v>175</v>
       </c>
       <c r="D28" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E28" t="s">
         <v>84</v>
@@ -7664,13 +7605,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E30" t="s">
         <v>84</v>
@@ -7684,13 +7625,13 @@
         <v>21330051920388</v>
       </c>
       <c r="B31" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C31" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D31" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E31" t="s">
         <v>84</v>
@@ -7707,10 +7648,10 @@
         <v>221</v>
       </c>
       <c r="C32" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D32" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E32" t="s">
         <v>84</v>
@@ -7757,10 +7698,10 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -7777,10 +7718,10 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -7794,13 +7735,13 @@
         <v>21330051920145</v>
       </c>
       <c r="B4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E4" t="s">
         <v>84</v>
@@ -7814,16 +7755,16 @@
         <v>21330051920145</v>
       </c>
       <c r="B5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7834,13 +7775,13 @@
         <v>21330051920147</v>
       </c>
       <c r="B6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -7854,16 +7795,16 @@
         <v>21330051920147</v>
       </c>
       <c r="B7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7877,10 +7818,10 @@
         <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -7894,16 +7835,16 @@
         <v>21330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
+        <v>498</v>
+      </c>
+      <c r="E9" t="s">
         <v>499</v>
-      </c>
-      <c r="E9" t="s">
-        <v>500</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7950,13 +7891,13 @@
         <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E2" t="s">
-        <v>255</v>
+        <v>192</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7970,13 +7911,13 @@
         <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E3" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7990,7 +7931,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E4" t="s">
         <v>192</v>
@@ -8007,10 +7948,10 @@
         <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E5" t="s">
         <v>192</v>
@@ -8024,13 +7965,13 @@
         <v>20330051920064</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" t="s">
         <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E6" t="s">
         <v>192</v>
@@ -8044,13 +7985,13 @@
         <v>20330051920065</v>
       </c>
       <c r="B7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E7" t="s">
         <v>192</v>
@@ -8064,13 +8005,13 @@
         <v>20330051920065</v>
       </c>
       <c r="B8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E8" t="s">
         <v>165</v>
@@ -8090,7 +8031,7 @@
         <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -8110,7 +8051,7 @@
         <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E10" t="s">
         <v>192</v>
@@ -8130,7 +8071,7 @@
         <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E11" t="s">
         <v>192</v>
@@ -8150,10 +8091,10 @@
         <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E12" t="s">
-        <v>256</v>
+        <v>516</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -8170,7 +8111,7 @@
         <v>212</v>
       </c>
       <c r="D13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E13" t="s">
         <v>192</v>
@@ -8190,7 +8131,7 @@
         <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E14" t="s">
         <v>192</v>
@@ -8204,13 +8145,13 @@
         <v>20330051920087</v>
       </c>
       <c r="B15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E15" t="s">
         <v>165</v>
@@ -8224,13 +8165,13 @@
         <v>20330051920087</v>
       </c>
       <c r="B16" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E16" t="s">
         <v>192</v>
@@ -8287,10 +8228,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D19" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E19" t="s">
         <v>192</v>
@@ -8310,7 +8251,7 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E20" t="s">
         <v>163</v>
@@ -8326,7 +8267,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8360,10 +8301,10 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -8371,19 +8312,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920177</v>
+        <v>19330051920280</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>522</v>
       </c>
       <c r="D3" t="s">
         <v>527</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -8391,13 +8332,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920280</v>
+        <v>19330051920290</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>523</v>
+        <v>337</v>
       </c>
       <c r="D4" t="s">
         <v>528</v>
@@ -8411,19 +8352,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920280</v>
+        <v>20330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>517</v>
       </c>
       <c r="C5" t="s">
-        <v>523</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -8431,16 +8372,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920290</v>
+        <v>20330051920191</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>338</v>
+        <v>435</v>
       </c>
       <c r="D6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E6" t="s">
         <v>192</v>
@@ -8451,16 +8392,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920190</v>
+        <v>20330051920193</v>
       </c>
       <c r="B7" t="s">
-        <v>517</v>
+        <v>409</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E7" t="s">
         <v>192</v>
@@ -8471,16 +8412,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920191</v>
+        <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>518</v>
       </c>
       <c r="C8" t="s">
-        <v>436</v>
+        <v>256</v>
       </c>
       <c r="D8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E8" t="s">
         <v>192</v>
@@ -8491,16 +8432,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920193</v>
+        <v>20330051920198</v>
       </c>
       <c r="B9" t="s">
-        <v>410</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>523</v>
       </c>
       <c r="D9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E9" t="s">
         <v>192</v>
@@ -8511,16 +8452,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920196</v>
+        <v>20330051920199</v>
       </c>
       <c r="B10" t="s">
-        <v>518</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="D10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E10" t="s">
         <v>192</v>
@@ -8531,19 +8472,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920197</v>
+        <v>20330051920200</v>
       </c>
       <c r="B11" t="s">
         <v>519</v>
       </c>
       <c r="C11" t="s">
-        <v>380</v>
+        <v>524</v>
       </c>
       <c r="D11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E11" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -8551,16 +8492,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920198</v>
+        <v>20330051920201</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>524</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>535</v>
+        <v>355</v>
       </c>
       <c r="E12" t="s">
         <v>192</v>
@@ -8571,16 +8512,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920199</v>
+        <v>20330051920202</v>
       </c>
       <c r="B13" t="s">
-        <v>221</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>536</v>
+        <v>188</v>
       </c>
       <c r="E13" t="s">
         <v>192</v>
@@ -8591,19 +8532,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920200</v>
+        <v>20330051920202</v>
       </c>
       <c r="B14" t="s">
-        <v>520</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>525</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>537</v>
+        <v>188</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -8611,16 +8552,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920201</v>
+        <v>20330051920206</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>275</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>356</v>
+        <v>536</v>
       </c>
       <c r="E15" t="s">
         <v>192</v>
@@ -8631,19 +8572,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920202</v>
+        <v>20330051920208</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>520</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>188</v>
+        <v>537</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -8651,16 +8592,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920202</v>
+        <v>20330051920209</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>521</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>525</v>
       </c>
       <c r="D17" t="s">
-        <v>188</v>
+        <v>538</v>
       </c>
       <c r="E17" t="s">
         <v>192</v>
@@ -8671,16 +8612,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920206</v>
+        <v>20330051920210</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E18" t="s">
         <v>192</v>
@@ -8691,19 +8632,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920206</v>
+        <v>20330051920212</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>328</v>
       </c>
       <c r="D19" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -8711,16 +8652,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920208</v>
+        <v>20330051920213</v>
       </c>
       <c r="B20" t="s">
-        <v>521</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>464</v>
       </c>
       <c r="D20" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E20" t="s">
         <v>192</v>
@@ -8731,16 +8672,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920209</v>
+        <v>20330051920214</v>
       </c>
       <c r="B21" t="s">
-        <v>522</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>526</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E21" t="s">
         <v>192</v>
@@ -8751,19 +8692,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920209</v>
+        <v>20330051920214</v>
       </c>
       <c r="B22" t="s">
-        <v>522</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>526</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E22" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -8771,16 +8712,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920210</v>
+        <v>20330051920215</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E23" t="s">
         <v>192</v>
@@ -8791,121 +8732,21 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920212</v>
+        <v>20330051920217</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>329</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E24" t="s">
         <v>192</v>
       </c>
       <c r="F24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920213</v>
-      </c>
-      <c r="B25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" t="s">
-        <v>465</v>
-      </c>
-      <c r="D25" t="s">
-        <v>543</v>
-      </c>
-      <c r="E25" t="s">
-        <v>192</v>
-      </c>
-      <c r="F25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920213</v>
-      </c>
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" t="s">
-        <v>465</v>
-      </c>
-      <c r="D26" t="s">
-        <v>543</v>
-      </c>
-      <c r="E26" t="s">
-        <v>165</v>
-      </c>
-      <c r="F26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920215</v>
-      </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" t="s">
-        <v>544</v>
-      </c>
-      <c r="E27" t="s">
-        <v>192</v>
-      </c>
-      <c r="F27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920217</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s">
-        <v>545</v>
-      </c>
-      <c r="E28" t="s">
-        <v>165</v>
-      </c>
-      <c r="F28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920217</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" t="s">
-        <v>545</v>
-      </c>
-      <c r="E29" t="s">
-        <v>192</v>
-      </c>
-      <c r="F29">
         <v>-1</v>
       </c>
     </row>
@@ -8950,7 +8791,7 @@
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E2" t="s">
         <v>192</v>
@@ -8964,13 +8805,13 @@
         <v>20330051920269</v>
       </c>
       <c r="B3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E3" t="s">
         <v>192</v>
@@ -8990,7 +8831,7 @@
         <v>218</v>
       </c>
       <c r="D4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E4" t="s">
         <v>166</v>
@@ -9010,7 +8851,7 @@
         <v>218</v>
       </c>
       <c r="D5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E5" t="s">
         <v>192</v>
@@ -9027,10 +8868,10 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E6" t="s">
         <v>166</v>
@@ -9047,10 +8888,10 @@
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E7" t="s">
         <v>192</v>
@@ -9067,10 +8908,10 @@
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D8" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E8" t="s">
         <v>192</v>
@@ -9084,13 +8925,13 @@
         <v>20330051920273</v>
       </c>
       <c r="B9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C9" t="s">
         <v>221</v>
       </c>
       <c r="D9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E9" t="s">
         <v>192</v>
@@ -9104,13 +8945,13 @@
         <v>20330051920276</v>
       </c>
       <c r="B10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E10" t="s">
         <v>166</v>
@@ -9124,13 +8965,13 @@
         <v>20330051920276</v>
       </c>
       <c r="B11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D11" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E11" t="s">
         <v>192</v>
@@ -9144,13 +8985,13 @@
         <v>20330051920279</v>
       </c>
       <c r="B12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E12" t="s">
         <v>192</v>
@@ -9164,13 +9005,13 @@
         <v>20330051920279</v>
       </c>
       <c r="B13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E13" t="s">
         <v>165</v>
@@ -9186,7 +9027,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9214,13 +9055,13 @@
         <v>20330051920115</v>
       </c>
       <c r="B2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C2" t="s">
         <v>221</v>
       </c>
       <c r="D2" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E2" t="s">
         <v>192</v>
@@ -9231,19 +9072,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920115</v>
+        <v>20330051920129</v>
       </c>
       <c r="B3" t="s">
-        <v>462</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
-        <v>221</v>
+        <v>558</v>
       </c>
       <c r="D3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -9251,76 +9092,76 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920116</v>
+        <v>20330051920132</v>
       </c>
       <c r="B4" t="s">
-        <v>410</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>458</v>
+        <v>559</v>
       </c>
       <c r="D4" t="s">
-        <v>568</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>571</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920128</v>
+        <v>20330051920133</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>339</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920129</v>
+        <v>20330051920134</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D6" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>571</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920129</v>
+        <v>20330051920136</v>
       </c>
       <c r="B7" t="s">
-        <v>328</v>
+        <v>555</v>
       </c>
       <c r="C7" t="s">
-        <v>561</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E7" t="s">
         <v>165</v>
@@ -9331,19 +9172,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920131</v>
+        <v>20330051920137</v>
       </c>
       <c r="B8" t="s">
         <v>556</v>
       </c>
       <c r="C8" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D8" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -9351,19 +9192,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920132</v>
+        <v>20330051920137</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>556</v>
       </c>
       <c r="C9" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>568</v>
       </c>
       <c r="E9" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9371,298 +9212,101 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920133</v>
+        <v>20330051920141</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>557</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>562</v>
       </c>
       <c r="D10" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E10" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920134</v>
+        <v>20330051920141</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>557</v>
       </c>
       <c r="C11" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D11" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E11" t="s">
         <v>165</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920134</v>
+        <v>20330051920145</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>564</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E12" t="s">
-        <v>581</v>
+        <v>166</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920136</v>
+        <v>20330051920387</v>
       </c>
       <c r="B13" t="s">
-        <v>557</v>
+        <v>374</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>491</v>
       </c>
       <c r="D13" t="s">
-        <v>574</v>
+        <v>310</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>571</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920137</v>
+        <v>20330051920387</v>
       </c>
       <c r="B14" t="s">
-        <v>558</v>
+        <v>374</v>
       </c>
       <c r="C14" t="s">
-        <v>565</v>
+        <v>491</v>
       </c>
       <c r="D14" t="s">
-        <v>575</v>
+        <v>310</v>
       </c>
       <c r="E14" t="s">
-        <v>581</v>
+        <v>192</v>
       </c>
       <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920137</v>
-      </c>
-      <c r="B15" t="s">
-        <v>558</v>
-      </c>
-      <c r="C15" t="s">
-        <v>565</v>
-      </c>
-      <c r="D15" t="s">
-        <v>575</v>
-      </c>
-      <c r="E15" t="s">
-        <v>192</v>
-      </c>
-      <c r="F15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920140</v>
-      </c>
-      <c r="B16" t="s">
-        <v>405</v>
-      </c>
-      <c r="C16" t="s">
-        <v>335</v>
-      </c>
-      <c r="D16" t="s">
-        <v>311</v>
-      </c>
-      <c r="E16" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920141</v>
-      </c>
-      <c r="B17" t="s">
-        <v>559</v>
-      </c>
-      <c r="C17" t="s">
-        <v>566</v>
-      </c>
-      <c r="D17" t="s">
-        <v>576</v>
-      </c>
-      <c r="E17" t="s">
-        <v>165</v>
-      </c>
-      <c r="F17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920141</v>
-      </c>
-      <c r="B18" t="s">
-        <v>559</v>
-      </c>
-      <c r="C18" t="s">
-        <v>566</v>
-      </c>
-      <c r="D18" t="s">
-        <v>576</v>
-      </c>
-      <c r="E18" t="s">
-        <v>192</v>
-      </c>
-      <c r="F18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920142</v>
-      </c>
-      <c r="B19" t="s">
-        <v>315</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" t="s">
-        <v>577</v>
-      </c>
-      <c r="E19" t="s">
-        <v>165</v>
-      </c>
-      <c r="F19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920143</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>436</v>
-      </c>
-      <c r="D20" t="s">
-        <v>578</v>
-      </c>
-      <c r="E20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920144</v>
-      </c>
-      <c r="B21" t="s">
-        <v>560</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>579</v>
-      </c>
-      <c r="E21" t="s">
-        <v>165</v>
-      </c>
-      <c r="F21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920145</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>580</v>
-      </c>
-      <c r="E22" t="s">
-        <v>166</v>
-      </c>
-      <c r="F22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920145</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>580</v>
-      </c>
-      <c r="E23" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920153</v>
-      </c>
-      <c r="B24" t="s">
-        <v>222</v>
-      </c>
-      <c r="D24" t="s">
-        <v>434</v>
-      </c>
-      <c r="E24" t="s">
-        <v>165</v>
-      </c>
-      <c r="F24">
         <v>-1</v>
       </c>
     </row>
@@ -9673,7 +9317,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9707,13 +9351,13 @@
         <v>518</v>
       </c>
       <c r="D2" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="E2" t="s">
         <v>165</v>
       </c>
       <c r="F2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -9727,10 +9371,10 @@
         <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E3" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9738,19 +9382,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920318</v>
+        <v>20330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>574</v>
       </c>
       <c r="D4" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -9758,16 +9402,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>585</v>
+        <v>221</v>
       </c>
       <c r="D5" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="E5" t="s">
         <v>192</v>
@@ -9787,10 +9431,10 @@
         <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -9798,19 +9442,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920322</v>
+        <v>20330051920323</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -9818,19 +9462,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -9838,16 +9482,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920323</v>
+        <v>20330051920325</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>575</v>
       </c>
       <c r="D9" t="s">
-        <v>593</v>
+        <v>429</v>
       </c>
       <c r="E9" t="s">
         <v>192</v>
@@ -9858,19 +9502,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920324</v>
+        <v>20330051920326</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>437</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="E10" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -9878,16 +9522,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920324</v>
+        <v>20330051920327</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>572</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="E11" t="s">
         <v>192</v>
@@ -9898,19 +9542,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920325</v>
+        <v>20330051920330</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>573</v>
       </c>
       <c r="C12" t="s">
-        <v>586</v>
+        <v>328</v>
       </c>
       <c r="D12" t="s">
-        <v>430</v>
+        <v>585</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -9918,16 +9562,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920325</v>
+        <v>20330051920333</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>586</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="E13" t="s">
         <v>192</v>
@@ -9938,241 +9582,21 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920326</v>
+        <v>20330051920335</v>
       </c>
       <c r="B14" t="s">
-        <v>438</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>576</v>
       </c>
       <c r="D14" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="E14" t="s">
         <v>192</v>
       </c>
       <c r="F14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920326</v>
-      </c>
-      <c r="B15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>595</v>
-      </c>
-      <c r="E15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920327</v>
-      </c>
-      <c r="B16" t="s">
-        <v>582</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>596</v>
-      </c>
-      <c r="E16" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920327</v>
-      </c>
-      <c r="B17" t="s">
-        <v>582</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
-        <v>596</v>
-      </c>
-      <c r="E17" t="s">
-        <v>192</v>
-      </c>
-      <c r="F17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920330</v>
-      </c>
-      <c r="B18" t="s">
-        <v>583</v>
-      </c>
-      <c r="C18" t="s">
-        <v>329</v>
-      </c>
-      <c r="D18" t="s">
-        <v>597</v>
-      </c>
-      <c r="E18" t="s">
-        <v>192</v>
-      </c>
-      <c r="F18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920330</v>
-      </c>
-      <c r="B19" t="s">
-        <v>583</v>
-      </c>
-      <c r="C19" t="s">
-        <v>329</v>
-      </c>
-      <c r="D19" t="s">
-        <v>597</v>
-      </c>
-      <c r="E19" t="s">
-        <v>165</v>
-      </c>
-      <c r="F19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920331</v>
-      </c>
-      <c r="B20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>598</v>
-      </c>
-      <c r="E20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920333</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>391</v>
-      </c>
-      <c r="E21" t="s">
-        <v>165</v>
-      </c>
-      <c r="F21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920333</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>391</v>
-      </c>
-      <c r="E22" t="s">
-        <v>192</v>
-      </c>
-      <c r="F22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920335</v>
-      </c>
-      <c r="B23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" t="s">
-        <v>587</v>
-      </c>
-      <c r="D23" t="s">
-        <v>599</v>
-      </c>
-      <c r="E23" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920335</v>
-      </c>
-      <c r="B24" t="s">
-        <v>139</v>
-      </c>
-      <c r="C24" t="s">
-        <v>587</v>
-      </c>
-      <c r="D24" t="s">
-        <v>599</v>
-      </c>
-      <c r="E24" t="s">
-        <v>192</v>
-      </c>
-      <c r="F24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920380</v>
-      </c>
-      <c r="B25" t="s">
-        <v>584</v>
-      </c>
-      <c r="C25" t="s">
-        <v>588</v>
-      </c>
-      <c r="D25" t="s">
-        <v>600</v>
-      </c>
-      <c r="E25" t="s">
-        <v>165</v>
-      </c>
-      <c r="F25">
         <v>-1</v>
       </c>
     </row>
@@ -10211,16 +9635,16 @@
         <v>18330051920022</v>
       </c>
       <c r="B2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D2" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -10231,16 +9655,16 @@
         <v>18330051920022</v>
       </c>
       <c r="B3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D3" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -10251,16 +9675,16 @@
         <v>18330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D4" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -10271,16 +9695,16 @@
         <v>18330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D5" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -10291,16 +9715,16 @@
         <v>19330051920045</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
         <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -10311,16 +9735,16 @@
         <v>19330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" t="s">
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -10337,10 +9761,10 @@
         <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -10357,10 +9781,10 @@
         <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -10374,13 +9798,13 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D10" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -10397,10 +9821,10 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="E11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -10414,13 +9838,13 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="D12" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -10434,13 +9858,13 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="D13" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="E13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -10457,10 +9881,10 @@
         <v>176</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -10480,7 +9904,7 @@
         <v>249</v>
       </c>
       <c r="E15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -10500,7 +9924,7 @@
         <v>249</v>
       </c>
       <c r="E16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -10514,13 +9938,13 @@
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D17" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="E17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -10774,13 +10198,13 @@
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="D2" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="E2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10794,13 +10218,13 @@
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D3" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10814,13 +10238,13 @@
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D4" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -10834,13 +10258,13 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D5" t="s">
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10854,13 +10278,13 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D6" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10871,16 +10295,16 @@
         <v>19330051920286</v>
       </c>
       <c r="B7" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="C7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D7" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -10891,16 +10315,16 @@
         <v>19330051920286</v>
       </c>
       <c r="B8" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="C8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D8" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10911,16 +10335,16 @@
         <v>19330051920292</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C9" t="s">
         <v>221</v>
       </c>
       <c r="D9" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10934,13 +10358,13 @@
         <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="D10" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -10981,16 +10405,16 @@
         <v>19330051920308</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D2" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -11001,16 +10425,16 @@
         <v>19330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D3" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="E3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -11021,16 +10445,16 @@
         <v>19330051920312</v>
       </c>
       <c r="B4" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="C4" t="s">
         <v>232</v>
       </c>
       <c r="D4" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -11041,16 +10465,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C5" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="D5" t="s">
         <v>246</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -11067,10 +10491,10 @@
         <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -11087,10 +10511,10 @@
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="E7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -11101,16 +10525,16 @@
         <v>19330051920352</v>
       </c>
       <c r="B8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D8" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -11121,16 +10545,16 @@
         <v>19330051920353</v>
       </c>
       <c r="B9" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -11171,16 +10595,16 @@
         <v>19330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="C2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D2" t="s">
         <v>229</v>
       </c>
       <c r="E2" t="s">
-        <v>632</v>
+        <v>332</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -11191,16 +10615,16 @@
         <v>19330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="C3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D3" t="s">
         <v>229</v>
       </c>
       <c r="E3" t="s">
-        <v>333</v>
+        <v>619</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -11217,10 +10641,10 @@
         <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="E4" t="s">
-        <v>632</v>
+        <v>332</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -11237,10 +10661,10 @@
         <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="E5" t="s">
-        <v>333</v>
+        <v>619</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -11257,10 +10681,10 @@
         <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -11274,13 +10698,13 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="D7" t="s">
         <v>245</v>
       </c>
       <c r="E7" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -11297,10 +10721,10 @@
         <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="E8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -11317,10 +10741,10 @@
         <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="E9" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -11337,10 +10761,10 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>578</v>
+        <v>618</v>
       </c>
       <c r="E10" t="s">
-        <v>333</v>
+        <v>619</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -11357,10 +10781,10 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>578</v>
+        <v>618</v>
       </c>
       <c r="E11" t="s">
-        <v>632</v>
+        <v>332</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -11374,13 +10798,13 @@
         <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -11394,13 +10818,13 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D13" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E13" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -11411,16 +10835,16 @@
         <v>19330051920398</v>
       </c>
       <c r="B14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -11461,16 +10885,16 @@
         <v>19330051920246</v>
       </c>
       <c r="B2" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D2" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -11487,10 +10911,10 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -11501,16 +10925,16 @@
         <v>19330051920249</v>
       </c>
       <c r="B4" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="C4" t="s">
         <v>199</v>
       </c>
       <c r="D4" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="E4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -11527,10 +10951,10 @@
         <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -11547,10 +10971,10 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -11567,10 +10991,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E7" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -11581,16 +11005,16 @@
         <v>19330051920260</v>
       </c>
       <c r="B8" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="C8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D8" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -11601,16 +11025,16 @@
         <v>19330051920261</v>
       </c>
       <c r="B9" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="C9" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="D9" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="E9" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -11624,13 +11048,13 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D10" t="s">
         <v>202</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -11647,10 +11071,10 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="E11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -11661,16 +11085,16 @@
         <v>19330051920406</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D12" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -11681,16 +11105,16 @@
         <v>19330051920407</v>
       </c>
       <c r="B13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C13" t="s">
         <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="E13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -11707,10 +11131,10 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -11724,13 +11148,13 @@
         <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="D15" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="E15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -11744,13 +11168,13 @@
         <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D16" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="E16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F16">
         <v>-1</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1859" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="582">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -729,171 +729,183 @@
     <t>MONSERRATH YARETZY</t>
   </si>
   <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>BENY ALEXANDER</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CARAZA</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>ARENZANO</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>KAREN ESTEPHANY</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>VALERIA ANGELY</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>IKER</t>
+  </si>
+  <si>
+    <t>IVONNE SHERLINE</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>JOSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>LAURA IVETTE</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
+    <t>JARED URIEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>BENY ALEXANDER</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CARAZA</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ARENZANO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>KAREN ESTEPHANY</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>IKER</t>
-  </si>
-  <si>
-    <t>IVONNE SHERLINE</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>JOSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>LAURA IVETTE</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>JARED URIEL</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
@@ -927,9 +939,6 @@
     <t>ALEX SAUL</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
@@ -1005,9 +1014,6 @@
     <t>CASTAÑEDA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>ALEXANDER</t>
   </si>
   <si>
@@ -1341,9 +1347,6 @@
     <t>DEL ROSARIO</t>
   </si>
   <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
     <t>LEPE</t>
   </si>
   <si>
@@ -1368,9 +1371,6 @@
     <t>GIOVANI</t>
   </si>
   <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
     <t>MICHEL</t>
   </si>
   <si>
@@ -1420,9 +1420,6 @@
   </si>
   <si>
     <t>ENSAMBLA E INSTALA CONTROLADORES Y DISPOSITIVOS PERIFÉRICOS</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
   </si>
   <si>
     <t>SILVESTRE</t>
@@ -2692,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2717,16 +2714,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920039</v>
+        <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
         <v>227</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E2" t="s">
         <v>160</v>
@@ -2737,19 +2734,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920039</v>
+        <v>20330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2757,19 +2754,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920044</v>
+        <v>20330051920099</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2783,7 +2777,7 @@
         <v>229</v>
       </c>
       <c r="D5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E5" t="s">
         <v>158</v>
@@ -2794,16 +2788,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920099</v>
+        <v>20330051920101</v>
       </c>
       <c r="B6" t="s">
-        <v>229</v>
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>234</v>
       </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2811,19 +2808,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920109</v>
+        <v>20330051920107</v>
       </c>
       <c r="B7" t="s">
-        <v>230</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2831,19 +2828,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920111</v>
+        <v>20330051920109</v>
       </c>
       <c r="B8" t="s">
         <v>231</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2851,19 +2848,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920111</v>
+        <v>20330051920109</v>
       </c>
       <c r="B9" t="s">
         <v>231</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2871,21 +2868,61 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
+        <v>20330051920111</v>
+      </c>
+      <c r="B10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" t="s">
+        <v>242</v>
+      </c>
+      <c r="E10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>20330051920111</v>
+      </c>
+      <c r="B11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
         <v>20330051920365</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>212</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="D10" t="s">
-        <v>240</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" t="s">
         <v>160</v>
       </c>
-      <c r="F10">
+      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -2924,13 +2961,13 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
         <v>157</v>
@@ -2944,13 +2981,13 @@
         <v>20330051920283</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
         <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E3" t="s">
         <v>158</v>
@@ -2970,7 +3007,7 @@
         <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E4" t="s">
         <v>158</v>
@@ -2984,13 +3021,13 @@
         <v>20330051920285</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C5" t="s">
         <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E5" t="s">
         <v>157</v>
@@ -3004,13 +3041,13 @@
         <v>20330051920285</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
         <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E6" t="s">
         <v>160</v>
@@ -3024,13 +3061,13 @@
         <v>20330051920286</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
         <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E7" t="s">
         <v>160</v>
@@ -3044,13 +3081,13 @@
         <v>20330051920286</v>
       </c>
       <c r="B8" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
         <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E8" t="s">
         <v>158</v>
@@ -3064,13 +3101,13 @@
         <v>20330051920287</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E9" t="s">
         <v>158</v>
@@ -3084,13 +3121,13 @@
         <v>20330051920287</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E10" t="s">
         <v>157</v>
@@ -3107,10 +3144,10 @@
         <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D11" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E11" t="s">
         <v>158</v>
@@ -3124,13 +3161,13 @@
         <v>20330051920293</v>
       </c>
       <c r="B12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C12" t="s">
         <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E12" t="s">
         <v>160</v>
@@ -3144,13 +3181,13 @@
         <v>20330051920293</v>
       </c>
       <c r="B13" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
         <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -3167,10 +3204,10 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D14" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E14" t="s">
         <v>158</v>
@@ -3184,13 +3221,13 @@
         <v>20330051920298</v>
       </c>
       <c r="B15" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D15" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E15" t="s">
         <v>158</v>
@@ -3204,13 +3241,13 @@
         <v>20330051920298</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
         <v>157</v>
@@ -3227,10 +3264,10 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E17" t="s">
         <v>158</v>
@@ -3244,13 +3281,13 @@
         <v>20330051920300</v>
       </c>
       <c r="B18" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E18" t="s">
         <v>158</v>
@@ -3264,13 +3301,13 @@
         <v>20330051920303</v>
       </c>
       <c r="B19" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D19" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E19" t="s">
         <v>158</v>
@@ -3290,7 +3327,7 @@
         <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E20" t="s">
         <v>158</v>
@@ -3310,7 +3347,7 @@
         <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E21" t="s">
         <v>160</v>
@@ -3330,7 +3367,7 @@
         <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E22" t="s">
         <v>157</v>
@@ -3344,13 +3381,13 @@
         <v>20330051920312</v>
       </c>
       <c r="B23" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C23" t="s">
         <v>211</v>
       </c>
       <c r="D23" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E23" t="s">
         <v>158</v>
@@ -3364,13 +3401,13 @@
         <v>20330051920312</v>
       </c>
       <c r="B24" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C24" t="s">
         <v>211</v>
       </c>
       <c r="D24" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E24" t="s">
         <v>160</v>
@@ -3384,13 +3421,13 @@
         <v>20330051920313</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C25" t="s">
         <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E25" t="s">
         <v>158</v>
@@ -3407,10 +3444,10 @@
         <v>180</v>
       </c>
       <c r="C26" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E26" t="s">
         <v>158</v>
@@ -3430,7 +3467,7 @@
         <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E27" t="s">
         <v>158</v>
@@ -3444,13 +3481,13 @@
         <v>20330051920379</v>
       </c>
       <c r="B28" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D28" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E28" t="s">
         <v>157</v>
@@ -3464,13 +3501,13 @@
         <v>20330051920379</v>
       </c>
       <c r="B29" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D29" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E29" t="s">
         <v>158</v>
@@ -3484,13 +3521,13 @@
         <v>20330051920390</v>
       </c>
       <c r="B30" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C30" t="s">
         <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E30" t="s">
         <v>158</v>
@@ -3510,7 +3547,7 @@
         <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E31" t="s">
         <v>158</v>
@@ -3560,10 +3597,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3580,10 +3617,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3600,10 +3637,10 @@
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3614,16 +3651,16 @@
         <v>19330051920003</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>285</v>
       </c>
       <c r="C5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
         <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3640,10 +3677,10 @@
         <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3657,13 +3694,13 @@
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D7" t="s">
-        <v>293</v>
+        <v>237</v>
       </c>
       <c r="E7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3677,13 +3714,13 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D8" t="s">
-        <v>293</v>
+        <v>237</v>
       </c>
       <c r="E8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3700,10 +3737,10 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3714,16 +3751,16 @@
         <v>19330051920016</v>
       </c>
       <c r="B10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3737,13 +3774,13 @@
         <v>184</v>
       </c>
       <c r="C11" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3754,16 +3791,16 @@
         <v>19330051920018</v>
       </c>
       <c r="B12" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C12" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D12" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E12" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3777,13 +3814,13 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3797,13 +3834,13 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E14" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3820,10 +3857,10 @@
         <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3840,10 +3877,10 @@
         <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E16" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3857,13 +3894,13 @@
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E17" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3883,7 +3920,7 @@
         <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3903,7 +3940,7 @@
         <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -3950,10 +3987,10 @@
         <v>209</v>
       </c>
       <c r="D2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3964,16 +4001,16 @@
         <v>19330051920168</v>
       </c>
       <c r="B3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
         <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3984,16 +4021,16 @@
         <v>19330051920168</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4004,16 +4041,16 @@
         <v>19330051920276</v>
       </c>
       <c r="B5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C5" t="s">
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4024,16 +4061,16 @@
         <v>19330051920276</v>
       </c>
       <c r="B6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4077,13 +4114,13 @@
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4097,13 +4134,13 @@
         <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4114,16 +4151,16 @@
         <v>19330051920223</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C4" t="s">
         <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4134,16 +4171,16 @@
         <v>19330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C5" t="s">
         <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4154,16 +4191,16 @@
         <v>19330051920227</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4174,16 +4211,16 @@
         <v>19330051920227</v>
       </c>
       <c r="B7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4194,16 +4231,16 @@
         <v>19330051920230</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4214,16 +4251,16 @@
         <v>19330051920233</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C9" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D9" t="s">
         <v>236</v>
       </c>
       <c r="E9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4234,16 +4271,16 @@
         <v>19330051920233</v>
       </c>
       <c r="B10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D10" t="s">
         <v>236</v>
       </c>
       <c r="E10" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4254,7 +4291,7 @@
         <v>19330051920236</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -4263,7 +4300,7 @@
         <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4277,13 +4314,13 @@
         <v>209</v>
       </c>
       <c r="C12" t="s">
-        <v>319</v>
+        <v>230</v>
       </c>
       <c r="D12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E12" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4300,10 +4337,10 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4320,10 +4357,10 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E14" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4334,16 +4371,16 @@
         <v>19330051920430</v>
       </c>
       <c r="B15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4384,16 +4421,16 @@
         <v>19330051920125</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4404,16 +4441,16 @@
         <v>19330051920125</v>
       </c>
       <c r="B3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -4427,13 +4464,13 @@
         <v>188</v>
       </c>
       <c r="C4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4450,10 +4487,10 @@
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4470,10 +4507,10 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4484,16 +4521,16 @@
         <v>19330051920133</v>
       </c>
       <c r="B7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4504,7 +4541,7 @@
         <v>19330051920431</v>
       </c>
       <c r="B8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C8" t="s">
         <v>76</v>
@@ -4513,7 +4550,7 @@
         <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4524,7 +4561,7 @@
         <v>19330051920431</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
         <v>76</v>
@@ -4533,7 +4570,7 @@
         <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4574,16 +4611,16 @@
         <v>19330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4594,16 +4631,16 @@
         <v>19330051920001</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4620,10 +4657,10 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4634,16 +4671,16 @@
         <v>19330051920088</v>
       </c>
       <c r="B5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4657,13 +4694,13 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4677,13 +4714,13 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4697,13 +4734,13 @@
         <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4717,13 +4754,13 @@
         <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4740,10 +4777,10 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4757,13 +4794,13 @@
         <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4777,13 +4814,13 @@
         <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4800,10 +4837,10 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4814,16 +4851,16 @@
         <v>19330051920118</v>
       </c>
       <c r="B14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E14" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4834,16 +4871,16 @@
         <v>19330051920118</v>
       </c>
       <c r="B15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E15" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4854,16 +4891,16 @@
         <v>19330051920119</v>
       </c>
       <c r="B16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C16" t="s">
         <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E16" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4874,16 +4911,16 @@
         <v>19330051920119</v>
       </c>
       <c r="B17" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C17" t="s">
         <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E17" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -4894,16 +4931,16 @@
         <v>19330051920120</v>
       </c>
       <c r="B18" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C18" t="s">
         <v>207</v>
       </c>
       <c r="D18" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -4914,16 +4951,16 @@
         <v>19330051920122</v>
       </c>
       <c r="B19" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C19" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E19" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -4964,16 +5001,16 @@
         <v>19330051920194</v>
       </c>
       <c r="B2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4987,13 +5024,13 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -5007,13 +5044,13 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5054,13 +5091,13 @@
         <v>20330051920022</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C2" t="s">
         <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E2" t="s">
         <v>69</v>
@@ -5074,13 +5111,13 @@
         <v>20330051920049</v>
       </c>
       <c r="B3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
@@ -5094,13 +5131,13 @@
         <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -5120,7 +5157,7 @@
         <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E5" t="s">
         <v>69</v>
@@ -5140,7 +5177,7 @@
         <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -5157,10 +5194,10 @@
         <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E7" t="s">
         <v>69</v>
@@ -5200,7 +5237,7 @@
         <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E9" t="s">
         <v>69</v>
@@ -5214,13 +5251,13 @@
         <v>21330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -5234,13 +5271,13 @@
         <v>21330051920018</v>
       </c>
       <c r="B11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
@@ -5257,7 +5294,7 @@
         <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
@@ -5277,10 +5314,10 @@
         <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -5297,10 +5334,10 @@
         <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E14" t="s">
         <v>69</v>
@@ -5317,10 +5354,10 @@
         <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D15" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E15" t="s">
         <v>69</v>
@@ -5337,10 +5374,10 @@
         <v>117</v>
       </c>
       <c r="C16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D16" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -5631,13 +5668,13 @@
         <v>21330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C3" t="s">
         <v>211</v>
       </c>
       <c r="D3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
@@ -5651,13 +5688,13 @@
         <v>21330051920072</v>
       </c>
       <c r="B4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C4" t="s">
         <v>211</v>
       </c>
       <c r="D4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -5674,10 +5711,10 @@
         <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E5" t="s">
         <v>69</v>
@@ -5697,7 +5734,7 @@
         <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -5714,10 +5751,10 @@
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -5734,10 +5771,10 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E8" t="s">
         <v>69</v>
@@ -5754,13 +5791,13 @@
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5771,13 +5808,13 @@
         <v>21330051920098</v>
       </c>
       <c r="B10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C10" t="s">
         <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -5791,13 +5828,13 @@
         <v>21330051920098</v>
       </c>
       <c r="B11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C11" t="s">
         <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E11" t="s">
         <v>69</v>
@@ -5811,13 +5848,13 @@
         <v>21330051920100</v>
       </c>
       <c r="B12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E12" t="s">
         <v>69</v>
@@ -5831,13 +5868,13 @@
         <v>21330051920100</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -5857,7 +5894,7 @@
         <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -5871,13 +5908,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C15" t="s">
         <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -5891,13 +5928,13 @@
         <v>21330051920104</v>
       </c>
       <c r="B16" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C16" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D16" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -5911,13 +5948,13 @@
         <v>21330051920108</v>
       </c>
       <c r="B17" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -5931,13 +5968,13 @@
         <v>21330051920108</v>
       </c>
       <c r="B18" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C18" t="s">
         <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -5951,13 +5988,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D19" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -5971,13 +6008,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B20" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D20" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -5991,13 +6028,13 @@
         <v>21330051920383</v>
       </c>
       <c r="B21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C21" t="s">
         <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E21" t="s">
         <v>69</v>
@@ -6047,7 +6084,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E2" t="s">
         <v>69</v>
@@ -6064,10 +6101,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E3" t="s">
         <v>27</v>
@@ -6084,10 +6121,10 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -6124,13 +6161,13 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6144,10 +6181,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E7" t="s">
         <v>69</v>
@@ -6167,7 +6204,7 @@
         <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E8" t="s">
         <v>69</v>
@@ -6181,7 +6218,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -6190,7 +6227,7 @@
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6201,7 +6238,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -6221,13 +6258,13 @@
         <v>21330051920127</v>
       </c>
       <c r="B11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E11" t="s">
         <v>69</v>
@@ -6241,13 +6278,13 @@
         <v>21330051920130</v>
       </c>
       <c r="B12" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D12" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E12" t="s">
         <v>69</v>
@@ -6261,16 +6298,16 @@
         <v>21330051920134</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C13" t="s">
         <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E13" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -6281,13 +6318,13 @@
         <v>21330051920134</v>
       </c>
       <c r="B14" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C14" t="s">
         <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E14" t="s">
         <v>69</v>
@@ -6303,7 +6340,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6331,13 +6368,13 @@
         <v>21330051920029</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E2" t="s">
         <v>69</v>
@@ -6351,16 +6388,16 @@
         <v>21330051920032</v>
       </c>
       <c r="B3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6371,13 +6408,13 @@
         <v>21330051920032</v>
       </c>
       <c r="B4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E4" t="s">
         <v>70</v>
@@ -6391,13 +6428,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C5" t="s">
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E5" t="s">
         <v>69</v>
@@ -6414,10 +6451,10 @@
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E6" t="s">
         <v>446</v>
@@ -6434,10 +6471,10 @@
         <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E7" t="s">
         <v>69</v>
@@ -6454,10 +6491,10 @@
         <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E8" t="s">
         <v>70</v>
@@ -6474,10 +6511,10 @@
         <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E9" t="s">
         <v>69</v>
@@ -6494,13 +6531,13 @@
         <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6514,10 +6551,10 @@
         <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E11" t="s">
         <v>69</v>
@@ -6528,56 +6565,56 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920046</v>
+        <v>21330051920048</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>431</v>
+        <v>131</v>
       </c>
       <c r="D12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>433</v>
       </c>
       <c r="D13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920054</v>
+        <v>21330051920058</v>
       </c>
       <c r="B14" t="s">
-        <v>319</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>432</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>442</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
         <v>69</v>
@@ -6588,16 +6625,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920058</v>
+        <v>21330051920062</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>429</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>443</v>
       </c>
       <c r="E15" t="s">
         <v>69</v>
@@ -6608,16 +6645,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B16" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>390</v>
       </c>
       <c r="D16" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E16" t="s">
         <v>69</v>
@@ -6628,41 +6665,21 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920067</v>
+        <v>21330051920388</v>
       </c>
       <c r="B17" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C17" t="s">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="D17" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E17" t="s">
         <v>69</v>
       </c>
       <c r="F17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920388</v>
-      </c>
-      <c r="B18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C18" t="s">
-        <v>433</v>
-      </c>
-      <c r="D18" t="s">
-        <v>445</v>
-      </c>
-      <c r="E18" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18">
         <v>5</v>
       </c>
     </row>
@@ -6701,7 +6718,7 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
         <v>207</v>
@@ -6721,7 +6738,7 @@
         <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
         <v>207</v>
@@ -6821,10 +6838,10 @@
         <v>21330051920147</v>
       </c>
       <c r="B8" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D8" t="s">
         <v>454</v>
@@ -6917,7 +6934,7 @@
         <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -6937,7 +6954,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E3" t="s">
         <v>157</v>
@@ -6957,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E4" t="s">
         <v>158</v>
@@ -6971,13 +6988,13 @@
         <v>20330051920063</v>
       </c>
       <c r="B5" t="s">
-        <v>458</v>
+        <v>234</v>
       </c>
       <c r="C5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E5" t="s">
         <v>158</v>
@@ -6991,13 +7008,13 @@
         <v>20330051920065</v>
       </c>
       <c r="B6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E6" t="s">
         <v>158</v>
@@ -7011,13 +7028,13 @@
         <v>20330051920065</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E7" t="s">
         <v>160</v>
@@ -7031,16 +7048,16 @@
         <v>20330051920066</v>
       </c>
       <c r="B8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7051,16 +7068,16 @@
         <v>20330051920066</v>
       </c>
       <c r="B9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7077,7 +7094,7 @@
         <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E10" t="s">
         <v>160</v>
@@ -7091,13 +7108,13 @@
         <v>20330051920087</v>
       </c>
       <c r="B11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E11" t="s">
         <v>160</v>
@@ -7111,13 +7128,13 @@
         <v>20330051920087</v>
       </c>
       <c r="B12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E12" t="s">
         <v>158</v>
@@ -7131,16 +7148,16 @@
         <v>20330051920090</v>
       </c>
       <c r="B13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D13" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7157,7 +7174,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E14" t="s">
         <v>160</v>
@@ -7207,10 +7224,10 @@
         <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7224,10 +7241,10 @@
         <v>216</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E3" t="s">
         <v>158</v>
@@ -7244,10 +7261,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E4" t="s">
         <v>159</v>
@@ -7264,13 +7281,13 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7284,13 +7301,13 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7301,13 +7318,13 @@
         <v>20330051920218</v>
       </c>
       <c r="B7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E7" t="s">
         <v>158</v>
@@ -7321,16 +7338,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C8" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7347,7 +7364,7 @@
         <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E9" t="s">
         <v>157</v>
@@ -7363,7 +7380,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7391,13 +7408,13 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -7408,39 +7425,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19220030050208</v>
+        <v>19330051920238</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="C3" t="s">
-        <v>256</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>486</v>
       </c>
       <c r="E3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920238</v>
+        <v>20330051920270</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>212</v>
       </c>
       <c r="D4" t="s">
         <v>487</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7448,13 +7465,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920270</v>
+        <v>20330051920271</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="D5" t="s">
         <v>488</v>
@@ -7468,141 +7485,61 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920270</v>
+        <v>20330051920273</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>347</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920271</v>
+        <v>20330051920276</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>484</v>
       </c>
       <c r="C7" t="s">
-        <v>259</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920271</v>
+        <v>20330051920278</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>259</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920273</v>
-      </c>
-      <c r="B9" t="s">
-        <v>345</v>
-      </c>
-      <c r="C9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" t="s">
-        <v>490</v>
-      </c>
-      <c r="E9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920276</v>
-      </c>
-      <c r="B10" t="s">
-        <v>485</v>
-      </c>
-      <c r="C10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" t="s">
-        <v>491</v>
-      </c>
-      <c r="E10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920276</v>
-      </c>
-      <c r="B11" t="s">
-        <v>485</v>
-      </c>
-      <c r="C11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" t="s">
-        <v>491</v>
-      </c>
-      <c r="E11" t="s">
-        <v>157</v>
-      </c>
-      <c r="F11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920278</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" t="s">
-        <v>492</v>
-      </c>
-      <c r="E12" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12">
         <v>-1</v>
       </c>
     </row>
@@ -7644,10 +7581,10 @@
         <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E2" t="s">
         <v>159</v>
@@ -7667,10 +7604,10 @@
         <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7687,7 +7624,7 @@
         <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E4" t="s">
         <v>158</v>
@@ -7704,10 +7641,10 @@
         <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E5" t="s">
         <v>157</v>
@@ -7724,7 +7661,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -7744,13 +7681,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7764,10 +7701,10 @@
         <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E8" t="s">
         <v>160</v>
@@ -7784,10 +7721,10 @@
         <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E9" t="s">
         <v>158</v>
@@ -7801,13 +7738,13 @@
         <v>20330051920145</v>
       </c>
       <c r="B10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E10" t="s">
         <v>157</v>
@@ -7821,13 +7758,13 @@
         <v>20330051920145</v>
       </c>
       <c r="B11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E11" t="s">
         <v>158</v>
@@ -7844,10 +7781,10 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D12" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E12" t="s">
         <v>160</v>
@@ -7864,10 +7801,10 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D13" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E13" t="s">
         <v>158</v>
@@ -7887,7 +7824,7 @@
         <v>448</v>
       </c>
       <c r="D14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E14" t="s">
         <v>158</v>
@@ -7937,7 +7874,7 @@
         <v>216</v>
       </c>
       <c r="D2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E2" t="s">
         <v>160</v>
@@ -7954,13 +7891,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7977,7 +7914,7 @@
         <v>189</v>
       </c>
       <c r="D4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E4" t="s">
         <v>158</v>
@@ -7994,13 +7931,13 @@
         <v>449</v>
       </c>
       <c r="C5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8014,10 +7951,10 @@
         <v>449</v>
       </c>
       <c r="C6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E6" t="s">
         <v>158</v>
@@ -8037,7 +7974,7 @@
         <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E7" t="s">
         <v>158</v>
@@ -8054,13 +7991,13 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8074,10 +8011,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E9" t="s">
         <v>158</v>
@@ -8091,16 +8028,16 @@
         <v>20330051920396</v>
       </c>
       <c r="B10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
+        <v>514</v>
+      </c>
+      <c r="E10" t="s">
         <v>515</v>
-      </c>
-      <c r="E10" t="s">
-        <v>516</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8141,16 +8078,16 @@
         <v>18330051920022</v>
       </c>
       <c r="B2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C2" t="s">
         <v>517</v>
       </c>
-      <c r="C2" t="s">
-        <v>518</v>
-      </c>
       <c r="D2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8161,16 +8098,16 @@
         <v>19330051920045</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8184,13 +8121,13 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8204,13 +8141,13 @@
         <v>132</v>
       </c>
       <c r="C5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8224,13 +8161,13 @@
         <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8244,13 +8181,13 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8264,13 +8201,13 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8287,10 +8224,10 @@
         <v>167</v>
       </c>
       <c r="D9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8307,10 +8244,10 @@
         <v>167</v>
       </c>
       <c r="D10" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8461,16 +8398,16 @@
         <v>19330051920269</v>
       </c>
       <c r="B2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8487,10 +8424,10 @@
         <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -8507,10 +8444,10 @@
         <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8524,13 +8461,13 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D5" t="s">
         <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8544,13 +8481,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8561,16 +8498,16 @@
         <v>19330051920286</v>
       </c>
       <c r="B7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8587,10 +8524,10 @@
         <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8607,10 +8544,10 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8654,13 +8591,13 @@
         <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8671,16 +8608,16 @@
         <v>19330051920312</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C3" t="s">
+        <v>540</v>
+      </c>
+      <c r="D3" t="s">
         <v>541</v>
       </c>
-      <c r="D3" t="s">
-        <v>542</v>
-      </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8691,16 +8628,16 @@
         <v>19330051920316</v>
       </c>
       <c r="B4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C4" t="s">
         <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8720,7 +8657,7 @@
         <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8740,7 +8677,7 @@
         <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8751,16 +8688,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8774,13 +8711,13 @@
         <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8797,10 +8734,10 @@
         <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8811,16 +8748,16 @@
         <v>19330051920337</v>
       </c>
       <c r="B10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8834,13 +8771,13 @@
         <v>449</v>
       </c>
       <c r="C11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8854,13 +8791,13 @@
         <v>449</v>
       </c>
       <c r="C12" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D12" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E12" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8871,7 +8808,7 @@
         <v>19330051920352</v>
       </c>
       <c r="B13" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C13" t="s">
         <v>127</v>
@@ -8880,7 +8817,7 @@
         <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8891,16 +8828,16 @@
         <v>19330051920353</v>
       </c>
       <c r="B14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C14" t="s">
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E14" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8911,16 +8848,16 @@
         <v>19330051920353</v>
       </c>
       <c r="B15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E15" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8961,16 +8898,16 @@
         <v>19330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8987,10 +8924,10 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9007,10 +8944,10 @@
         <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9027,10 +8964,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9044,13 +8981,13 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>319</v>
+        <v>230</v>
       </c>
       <c r="D6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9067,10 +9004,10 @@
         <v>188</v>
       </c>
       <c r="D7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9081,16 +9018,16 @@
         <v>19330051920398</v>
       </c>
       <c r="B8" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D8" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9131,16 +9068,16 @@
         <v>19330051920246</v>
       </c>
       <c r="B2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9157,10 +9094,10 @@
         <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9171,16 +9108,16 @@
         <v>19330051920250</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9197,10 +9134,10 @@
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9217,10 +9154,10 @@
         <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9237,10 +9174,10 @@
         <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9257,10 +9194,10 @@
         <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9274,13 +9211,13 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9297,10 +9234,10 @@
         <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9317,10 +9254,10 @@
         <v>166</v>
       </c>
       <c r="D11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E11" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -9331,16 +9268,16 @@
         <v>19330051920261</v>
       </c>
       <c r="B12" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C12" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D12" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E12" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -9351,16 +9288,16 @@
         <v>19330051920265</v>
       </c>
       <c r="B13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C13" t="s">
         <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -9371,16 +9308,16 @@
         <v>19330051920400</v>
       </c>
       <c r="B14" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C14" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D14" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E14" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -9391,16 +9328,16 @@
         <v>19330051920400</v>
       </c>
       <c r="B15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C15" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D15" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -9411,16 +9348,16 @@
         <v>19330051920402</v>
       </c>
       <c r="B16" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C16" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E16" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -9431,16 +9368,16 @@
         <v>19330051920402</v>
       </c>
       <c r="B17" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C17" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D17" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E17" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -9451,16 +9388,16 @@
         <v>19330051920405</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C18" t="s">
         <v>212</v>
       </c>
       <c r="D18" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E18" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -9477,10 +9414,10 @@
         <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E19" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -9494,13 +9431,13 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D20" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E20" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -9514,13 +9451,13 @@
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D21" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E21" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -9531,16 +9468,16 @@
         <v>19330051920414</v>
       </c>
       <c r="B22" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D22" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E22" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -9554,13 +9491,13 @@
         <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D23" t="s">
+        <v>580</v>
+      </c>
+      <c r="E23" t="s">
         <v>581</v>
-      </c>
-      <c r="E23" t="s">
-        <v>582</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -9574,13 +9511,13 @@
         <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F24">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="582">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -129,12 +129,12 @@
     <t>ANGEL FIDEL</t>
   </si>
   <si>
+    <t>QUÍMICA II</t>
+  </si>
+  <si>
     <t>GEOMETRÍA Y TRIGONOMETRÍA</t>
   </si>
   <si>
-    <t>QUÍMICA II</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -957,18 +957,18 @@
     <t>ERICK ORLANDO</t>
   </si>
   <si>
+    <t>MATEMÁTICAS APLICADAS</t>
+  </si>
+  <si>
     <t>TEMAS DE FÍSICA</t>
   </si>
   <si>
-    <t>MATEMÁTICAS APLICADAS</t>
+    <t>PROBABILIDAD Y ESTADÍSTICA</t>
   </si>
   <si>
     <t>TEMAS DE FILOSOFÍA</t>
   </si>
   <si>
-    <t>PROBABILIDAD Y ESTADÍSTICA</t>
-  </si>
-  <si>
     <t>MIXCOAC</t>
   </si>
   <si>
@@ -1425,6 +1425,9 @@
     <t>SILVESTRE</t>
   </si>
   <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
@@ -1452,18 +1455,12 @@
     <t>YAIR</t>
   </si>
   <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
     <t>DIEGO IVAN</t>
   </si>
   <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
     <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
   </si>
   <si>
@@ -1509,6 +1506,9 @@
     <t>IRVING JAIR</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
     <t>ELIAS ALONSO</t>
   </si>
   <si>
@@ -1566,6 +1566,9 @@
     <t>EVALÚA EL DESEMPEÑO DE LA ORGANIZACIÓN UTILIZANDO HERRAMIENTAS DE CALIDAD</t>
   </si>
   <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -1620,12 +1623,12 @@
     <t>ALEXIS ARMANDO</t>
   </si>
   <si>
+    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
+  </si>
+  <si>
     <t>REALIZA MANTENIMIENTO EN SUBESTACIONES ELÉCTRICAS</t>
   </si>
   <si>
-    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
-  </si>
-  <si>
     <t>AJACTLE</t>
   </si>
   <si>
@@ -1711,9 +1714,6 @@
   </si>
   <si>
     <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
   <si>
     <t>DETERMINA REMUNERACIONES DEL PERSONAL EN SITUACIONES EXTRAORDINARIAS</t>
@@ -2226,7 +2226,7 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2286,7 +2286,7 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2306,7 +2306,7 @@
         <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2366,7 +2366,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2386,7 +2386,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2516,7 +2516,7 @@
         <v>221</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2536,7 +2536,7 @@
         <v>221</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2656,7 +2656,7 @@
         <v>226</v>
       </c>
       <c r="E13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2676,7 +2676,7 @@
         <v>226</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2763,7 +2763,7 @@
         <v>238</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2780,7 +2780,7 @@
         <v>238</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2840,7 +2840,7 @@
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2860,7 +2860,7 @@
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3030,7 +3030,7 @@
         <v>266</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3050,7 +3050,7 @@
         <v>266</v>
       </c>
       <c r="E6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3070,7 +3070,7 @@
         <v>267</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3090,7 +3090,7 @@
         <v>267</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3390,7 +3390,7 @@
         <v>278</v>
       </c>
       <c r="E23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -3410,7 +3410,7 @@
         <v>278</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -3490,7 +3490,7 @@
         <v>282</v>
       </c>
       <c r="E28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -3510,7 +3510,7 @@
         <v>282</v>
       </c>
       <c r="E29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -3640,7 +3640,7 @@
         <v>295</v>
       </c>
       <c r="E4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3660,7 +3660,7 @@
         <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3680,7 +3680,7 @@
         <v>296</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3740,7 +3740,7 @@
         <v>297</v>
       </c>
       <c r="E9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3760,7 +3760,7 @@
         <v>298</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3780,7 +3780,7 @@
         <v>299</v>
       </c>
       <c r="E11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3800,7 +3800,7 @@
         <v>300</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3820,7 +3820,7 @@
         <v>265</v>
       </c>
       <c r="E13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3840,7 +3840,7 @@
         <v>265</v>
       </c>
       <c r="E14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3860,7 +3860,7 @@
         <v>301</v>
       </c>
       <c r="E15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3880,7 +3880,7 @@
         <v>301</v>
       </c>
       <c r="E16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3900,7 +3900,7 @@
         <v>302</v>
       </c>
       <c r="E17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3920,7 +3920,7 @@
         <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3940,7 +3940,7 @@
         <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -3990,7 +3990,7 @@
         <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4010,7 +4010,7 @@
         <v>310</v>
       </c>
       <c r="E3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4030,7 +4030,7 @@
         <v>310</v>
       </c>
       <c r="E4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4050,7 +4050,7 @@
         <v>311</v>
       </c>
       <c r="E5" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4070,7 +4070,7 @@
         <v>311</v>
       </c>
       <c r="E6" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4120,7 +4120,7 @@
         <v>322</v>
       </c>
       <c r="E2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4140,7 +4140,7 @@
         <v>322</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4160,7 +4160,7 @@
         <v>323</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4180,7 +4180,7 @@
         <v>324</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4220,7 +4220,7 @@
         <v>325</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4240,7 +4240,7 @@
         <v>326</v>
       </c>
       <c r="E8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4260,7 +4260,7 @@
         <v>236</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4280,7 +4280,7 @@
         <v>236</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4300,7 +4300,7 @@
         <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4320,7 +4320,7 @@
         <v>327</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4340,7 +4340,7 @@
         <v>328</v>
       </c>
       <c r="E13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4360,7 +4360,7 @@
         <v>329</v>
       </c>
       <c r="E14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4380,7 +4380,7 @@
         <v>330</v>
       </c>
       <c r="E15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4430,7 +4430,7 @@
         <v>336</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4450,7 +4450,7 @@
         <v>336</v>
       </c>
       <c r="E3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -4510,7 +4510,7 @@
         <v>338</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4530,7 +4530,7 @@
         <v>339</v>
       </c>
       <c r="E7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4570,7 +4570,7 @@
         <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4620,7 +4620,7 @@
         <v>353</v>
       </c>
       <c r="E2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4640,7 +4640,7 @@
         <v>353</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4660,7 +4660,7 @@
         <v>354</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4680,7 +4680,7 @@
         <v>355</v>
       </c>
       <c r="E5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4700,7 +4700,7 @@
         <v>356</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4720,7 +4720,7 @@
         <v>356</v>
       </c>
       <c r="E7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4740,7 +4740,7 @@
         <v>357</v>
       </c>
       <c r="E8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4760,7 +4760,7 @@
         <v>357</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4780,7 +4780,7 @@
         <v>358</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4800,7 +4800,7 @@
         <v>359</v>
       </c>
       <c r="E11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4820,7 +4820,7 @@
         <v>359</v>
       </c>
       <c r="E12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4840,7 +4840,7 @@
         <v>360</v>
       </c>
       <c r="E13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4860,7 +4860,7 @@
         <v>361</v>
       </c>
       <c r="E14" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4880,7 +4880,7 @@
         <v>361</v>
       </c>
       <c r="E15" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4900,7 +4900,7 @@
         <v>362</v>
       </c>
       <c r="E16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4920,7 +4920,7 @@
         <v>362</v>
       </c>
       <c r="E17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -4940,7 +4940,7 @@
         <v>363</v>
       </c>
       <c r="E18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -4960,7 +4960,7 @@
         <v>364</v>
       </c>
       <c r="E19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -5010,7 +5010,7 @@
         <v>367</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5033,7 +5033,7 @@
         <v>306</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5053,7 +5053,7 @@
         <v>305</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -5120,7 +5120,7 @@
         <v>380</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5180,7 +5180,7 @@
         <v>382</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5260,7 +5260,7 @@
         <v>385</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5320,10 +5320,10 @@
         <v>386</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5340,10 +5340,10 @@
         <v>386</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -5380,7 +5380,7 @@
         <v>387</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5430,7 +5430,7 @@
         <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5450,7 +5450,7 @@
         <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5510,7 +5510,7 @@
         <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5530,7 +5530,7 @@
         <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5550,7 +5550,7 @@
         <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5570,7 +5570,7 @@
         <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5587,7 +5587,7 @@
         <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5607,7 +5607,7 @@
         <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5657,7 +5657,7 @@
         <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5677,10 +5677,10 @@
         <v>400</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5697,10 +5697,10 @@
         <v>400</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5737,7 +5737,7 @@
         <v>402</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5757,7 +5757,7 @@
         <v>403</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5817,7 +5817,7 @@
         <v>405</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5857,10 +5857,10 @@
         <v>406</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5877,10 +5877,10 @@
         <v>406</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5897,7 +5897,7 @@
         <v>407</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5917,7 +5917,7 @@
         <v>408</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5937,7 +5937,7 @@
         <v>409</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5957,7 +5957,7 @@
         <v>410</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5977,7 +5977,7 @@
         <v>410</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -5997,10 +5997,10 @@
         <v>411</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -6017,10 +6017,10 @@
         <v>411</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -6107,7 +6107,7 @@
         <v>419</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6167,7 +6167,7 @@
         <v>420</v>
       </c>
       <c r="E6" t="s">
-        <v>425</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6187,7 +6187,7 @@
         <v>420</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>425</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6227,7 +6227,7 @@
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>413</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6247,7 +6247,7 @@
         <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>413</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6307,10 +6307,10 @@
         <v>424</v>
       </c>
       <c r="E13" t="s">
-        <v>426</v>
+        <v>69</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6327,10 +6327,10 @@
         <v>424</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>426</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -6457,10 +6457,10 @@
         <v>437</v>
       </c>
       <c r="E6" t="s">
-        <v>446</v>
+        <v>69</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6477,10 +6477,10 @@
         <v>437</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>446</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6537,10 +6537,10 @@
         <v>440</v>
       </c>
       <c r="E10" t="s">
-        <v>413</v>
+        <v>69</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6557,10 +6557,10 @@
         <v>440</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>413</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6727,7 +6727,7 @@
         <v>451</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6747,7 +6747,7 @@
         <v>451</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6767,7 +6767,7 @@
         <v>452</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6787,7 +6787,7 @@
         <v>442</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6807,10 +6807,10 @@
         <v>453</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>457</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6827,10 +6827,10 @@
         <v>453</v>
       </c>
       <c r="E7" t="s">
-        <v>457</v>
+        <v>69</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6847,7 +6847,7 @@
         <v>454</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6867,7 +6867,7 @@
         <v>455</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6887,7 +6887,7 @@
         <v>456</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6934,7 +6934,7 @@
         <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -6954,7 +6954,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E3" t="s">
         <v>157</v>
@@ -6974,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E4" t="s">
         <v>158</v>
@@ -6991,10 +6991,10 @@
         <v>234</v>
       </c>
       <c r="C5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E5" t="s">
         <v>158</v>
@@ -7011,16 +7011,16 @@
         <v>343</v>
       </c>
       <c r="C6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7031,16 +7031,16 @@
         <v>343</v>
       </c>
       <c r="C7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7054,7 +7054,7 @@
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E8" t="s">
         <v>157</v>
@@ -7074,7 +7074,7 @@
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E9" t="s">
         <v>158</v>
@@ -7085,42 +7085,42 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920068</v>
+        <v>20330051920073</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>459</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>468</v>
+        <v>265</v>
       </c>
       <c r="E10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920087</v>
+        <v>20330051920073</v>
       </c>
       <c r="B11" t="s">
         <v>459</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>469</v>
+        <v>265</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>471</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7128,7 +7128,7 @@
         <v>20330051920087</v>
       </c>
       <c r="B12" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -7137,27 +7137,27 @@
         <v>469</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920090</v>
+        <v>20330051920087</v>
       </c>
       <c r="B13" t="s">
-        <v>287</v>
+        <v>460</v>
       </c>
       <c r="C13" t="s">
-        <v>462</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E13" t="s">
-        <v>472</v>
+        <v>158</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7165,19 +7165,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920091</v>
+        <v>20330051920090</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>287</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>463</v>
       </c>
       <c r="D14" t="s">
+        <v>470</v>
+      </c>
+      <c r="E14" t="s">
         <v>471</v>
-      </c>
-      <c r="E14" t="s">
-        <v>160</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7224,10 +7224,10 @@
         <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7244,7 +7244,7 @@
         <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E3" t="s">
         <v>158</v>
@@ -7261,10 +7261,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E4" t="s">
         <v>159</v>
@@ -7281,13 +7281,13 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7301,13 +7301,13 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7318,13 +7318,13 @@
         <v>20330051920218</v>
       </c>
       <c r="B7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C7" t="s">
         <v>389</v>
       </c>
       <c r="D7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E7" t="s">
         <v>158</v>
@@ -7338,16 +7338,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C8" t="s">
         <v>389</v>
       </c>
       <c r="D8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7364,7 +7364,7 @@
         <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E9" t="s">
         <v>157</v>
@@ -7380,7 +7380,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7414,7 +7414,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -7434,7 +7434,7 @@
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E3" t="s">
         <v>159</v>
@@ -7445,36 +7445,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920270</v>
+        <v>20330051920267</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>320</v>
       </c>
       <c r="D4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E4" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920271</v>
+        <v>20330051920267</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E5" t="s">
         <v>158</v>
@@ -7485,16 +7485,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920273</v>
+        <v>20330051920270</v>
       </c>
       <c r="B6" t="s">
-        <v>347</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="D6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E6" t="s">
         <v>158</v>
@@ -7505,16 +7505,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920276</v>
+        <v>20330051920271</v>
       </c>
       <c r="B7" t="s">
-        <v>484</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="D7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E7" t="s">
         <v>158</v>
@@ -7525,21 +7525,61 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
+        <v>20330051920273</v>
+      </c>
+      <c r="B8" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>20330051920276</v>
+      </c>
+      <c r="B9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
         <v>20330051920278</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>125</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>491</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E10" t="s">
         <v>159</v>
       </c>
-      <c r="F8">
+      <c r="F10">
         <v>-1</v>
       </c>
     </row>
@@ -7550,7 +7590,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7667,7 +7707,7 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>505</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7687,7 +7727,7 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>505</v>
+        <v>158</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7707,7 +7747,7 @@
         <v>501</v>
       </c>
       <c r="E8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7715,16 +7755,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920141</v>
+        <v>20330051920145</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>492</v>
       </c>
       <c r="C9" t="s">
-        <v>496</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E9" t="s">
         <v>158</v>
@@ -7755,16 +7795,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920145</v>
+        <v>20330051920148</v>
       </c>
       <c r="B11" t="s">
-        <v>492</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>497</v>
       </c>
       <c r="D11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E11" t="s">
         <v>158</v>
@@ -7775,61 +7815,21 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920148</v>
+        <v>20330051920387</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>497</v>
+        <v>448</v>
       </c>
       <c r="D12" t="s">
-        <v>503</v>
+        <v>401</v>
       </c>
       <c r="E12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920148</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>497</v>
-      </c>
-      <c r="D13" t="s">
-        <v>503</v>
-      </c>
-      <c r="E13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920387</v>
-      </c>
-      <c r="B14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" t="s">
-        <v>448</v>
-      </c>
-      <c r="D14" t="s">
-        <v>401</v>
-      </c>
-      <c r="E14" t="s">
-        <v>158</v>
-      </c>
-      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7874,7 +7874,7 @@
         <v>216</v>
       </c>
       <c r="D2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E2" t="s">
         <v>160</v>
@@ -7891,13 +7891,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7914,7 +7914,7 @@
         <v>189</v>
       </c>
       <c r="D4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E4" t="s">
         <v>158</v>
@@ -7931,13 +7931,13 @@
         <v>449</v>
       </c>
       <c r="C5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E5" t="s">
-        <v>515</v>
+        <v>158</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7951,13 +7951,13 @@
         <v>449</v>
       </c>
       <c r="C6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>516</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7974,7 +7974,7 @@
         <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E7" t="s">
         <v>158</v>
@@ -7991,13 +7991,13 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8011,10 +8011,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E9" t="s">
         <v>158</v>
@@ -8034,12 +8034,52 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>20330051920397</v>
+      </c>
+      <c r="B11" t="s">
+        <v>506</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>297</v>
+      </c>
+      <c r="E11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>20330051920397</v>
+      </c>
+      <c r="B12" t="s">
+        <v>506</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>297</v>
+      </c>
+      <c r="E12" t="s">
+        <v>516</v>
+      </c>
+      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -8078,16 +8118,16 @@
         <v>18330051920022</v>
       </c>
       <c r="B2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8104,10 +8144,10 @@
         <v>392</v>
       </c>
       <c r="D3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8121,13 +8161,13 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8144,10 +8184,10 @@
         <v>392</v>
       </c>
       <c r="D5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8164,10 +8204,10 @@
         <v>392</v>
       </c>
       <c r="D6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8184,7 +8224,7 @@
         <v>292</v>
       </c>
       <c r="D7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E7" t="s">
         <v>304</v>
@@ -8204,7 +8244,7 @@
         <v>292</v>
       </c>
       <c r="D8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E8" t="s">
         <v>303</v>
@@ -8297,7 +8337,7 @@
         <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8317,7 +8357,7 @@
         <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8337,7 +8377,7 @@
         <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8357,7 +8397,7 @@
         <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8398,16 +8438,16 @@
         <v>19330051920269</v>
       </c>
       <c r="B2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8424,13 +8464,13 @@
         <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E3" t="s">
         <v>305</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8444,13 +8484,13 @@
         <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E4" t="s">
         <v>306</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8461,13 +8501,13 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D5" t="s">
         <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8481,13 +8521,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8498,16 +8538,16 @@
         <v>19330051920286</v>
       </c>
       <c r="B7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C7" t="s">
         <v>320</v>
       </c>
       <c r="D7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8527,7 +8567,7 @@
         <v>501</v>
       </c>
       <c r="E8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8544,10 +8584,10 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8597,7 +8637,7 @@
         <v>265</v>
       </c>
       <c r="E2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8611,13 +8651,13 @@
         <v>319</v>
       </c>
       <c r="C3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8628,16 +8668,16 @@
         <v>19330051920316</v>
       </c>
       <c r="B4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C4" t="s">
         <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8657,7 +8697,7 @@
         <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8677,7 +8717,7 @@
         <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8688,16 +8728,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C7" t="s">
         <v>245</v>
       </c>
       <c r="D7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8717,7 +8757,7 @@
         <v>367</v>
       </c>
       <c r="E8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8737,7 +8777,7 @@
         <v>419</v>
       </c>
       <c r="E9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8748,16 +8788,16 @@
         <v>19330051920337</v>
       </c>
       <c r="B10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C10" t="s">
         <v>390</v>
       </c>
       <c r="D10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8774,7 +8814,7 @@
         <v>317</v>
       </c>
       <c r="D11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E11" t="s">
         <v>304</v>
@@ -8794,7 +8834,7 @@
         <v>317</v>
       </c>
       <c r="D12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E12" t="s">
         <v>303</v>
@@ -8808,7 +8848,7 @@
         <v>19330051920352</v>
       </c>
       <c r="B13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C13" t="s">
         <v>127</v>
@@ -8817,7 +8857,7 @@
         <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8828,16 +8868,16 @@
         <v>19330051920353</v>
       </c>
       <c r="B14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C14" t="s">
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8848,16 +8888,16 @@
         <v>19330051920353</v>
       </c>
       <c r="B15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8898,13 +8938,13 @@
         <v>19330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C2" t="s">
         <v>434</v>
       </c>
       <c r="D2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E2" t="s">
         <v>556</v>
@@ -8924,7 +8964,7 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E3" t="s">
         <v>340</v>
@@ -8944,7 +8984,7 @@
         <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E4" t="s">
         <v>340</v>
@@ -8964,7 +9004,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E5" t="s">
         <v>556</v>
@@ -8984,10 +9024,10 @@
         <v>230</v>
       </c>
       <c r="D6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9004,7 +9044,7 @@
         <v>188</v>
       </c>
       <c r="D7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E7" t="s">
         <v>340</v>
@@ -9018,13 +9058,13 @@
         <v>19330051920398</v>
       </c>
       <c r="B8" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C8" t="s">
         <v>287</v>
       </c>
       <c r="D8" t="s">
-        <v>555</v>
+        <v>486</v>
       </c>
       <c r="E8" t="s">
         <v>340</v>
@@ -9077,7 +9117,7 @@
         <v>568</v>
       </c>
       <c r="E2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9097,7 +9137,7 @@
         <v>569</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9117,7 +9157,7 @@
         <v>570</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9134,10 +9174,10 @@
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>555</v>
+        <v>486</v>
       </c>
       <c r="E5" t="s">
-        <v>581</v>
+        <v>303</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9154,10 +9194,10 @@
         <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>555</v>
+        <v>486</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>581</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9177,7 +9217,7 @@
         <v>571</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9237,7 +9277,7 @@
         <v>368</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9297,7 +9337,7 @@
         <v>501</v>
       </c>
       <c r="E13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -9357,7 +9397,7 @@
         <v>576</v>
       </c>
       <c r="E16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -9417,7 +9457,7 @@
         <v>578</v>
       </c>
       <c r="E19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -9457,7 +9497,7 @@
         <v>579</v>
       </c>
       <c r="E21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -9474,10 +9514,10 @@
         <v>567</v>
       </c>
       <c r="D22" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E22" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -9497,7 +9537,7 @@
         <v>580</v>
       </c>
       <c r="E23" t="s">
-        <v>581</v>
+        <v>303</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -9517,7 +9557,7 @@
         <v>580</v>
       </c>
       <c r="E24" t="s">
-        <v>304</v>
+        <v>581</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -9587,7 +9627,7 @@
         <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9607,7 +9647,7 @@
         <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9627,7 +9667,7 @@
         <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9647,7 +9687,7 @@
         <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9697,7 +9737,7 @@
         <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9737,7 +9777,7 @@
         <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9757,7 +9797,7 @@
         <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9777,7 +9817,7 @@
         <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9837,7 +9877,7 @@
         <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9857,7 +9897,7 @@
         <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9897,7 +9937,7 @@
         <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -9947,7 +9987,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9967,7 +10007,7 @@
         <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9987,7 +10027,7 @@
         <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10007,7 +10047,7 @@
         <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10047,7 +10087,7 @@
         <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10067,7 +10107,7 @@
         <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10087,7 +10127,7 @@
         <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10107,7 +10147,7 @@
         <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -10127,7 +10167,7 @@
         <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -10147,7 +10187,7 @@
         <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -10167,7 +10207,7 @@
         <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -10477,7 +10517,7 @@
         <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -10497,7 +10537,7 @@
         <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -10617,7 +10657,7 @@
         <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -10637,7 +10677,7 @@
         <v>151</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -10697,7 +10737,7 @@
         <v>153</v>
       </c>
       <c r="E25" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -10717,7 +10757,7 @@
         <v>153</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -10927,7 +10967,7 @@
         <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10947,7 +10987,7 @@
         <v>176</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -11237,7 +11277,7 @@
         <v>198</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -11257,7 +11297,7 @@
         <v>198</v>
       </c>
       <c r="E12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -11297,7 +11337,7 @@
         <v>199</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -11317,7 +11357,7 @@
         <v>199</v>
       </c>
       <c r="E15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -11337,7 +11377,7 @@
         <v>200</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -11357,7 +11397,7 @@
         <v>200</v>
       </c>
       <c r="E17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F17">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="453">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -342,808 +342,748 @@
     <t>ARROYO</t>
   </si>
   <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
+  </si>
+  <si>
+    <t>INGLÉS IV</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
+    <t>ELIDETH</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>TEMAS DE FÍSICA</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
+  </si>
+  <si>
+    <t>PROBABILIDAD Y ESTADÍSTICA</t>
+  </si>
+  <si>
+    <t>TEMAS DE FILOSOFÍA</t>
+  </si>
+  <si>
+    <t>MATEMÁTICAS APLICADAS</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>CESAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>QADMIEL TAMARA</t>
+  </si>
+  <si>
+    <t>NADYA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANGEL EDUARDO</t>
+  </si>
+  <si>
+    <t>ABDIEL ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES MÓVILES PARA IOS</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES MÓVILES PARA ANDROID</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>YATZIRI NAOMI</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>DETERMINA LA NÓMINA DEL PERSONAL DE LA ORGANIZACIÓN TOMANDO EN CUENTA LA NORMATIVIDAD LABORAL</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>ADOLFO</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>DISEÑA INSTALACIONES ELÉCTRICAS</t>
+  </si>
+  <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>INGLÉS II</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>APLICA ESTRUCTURAS DE DATOS CON UN LENGUAJE DE PROGRAMACIÓN</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>DISTINGUE LOS DIFERENTES TIPOS DE EMPRESA POR SU GIRO, ÁREAS FUNCIONALES, DOCUMENTACIÓN ADMINISTRATIVA Y RECURSOS</t>
+  </si>
+  <si>
+    <t>ELABORA ESTRATEGIAS PARA REALIZAR LAS ACTIVIDADES DE SU ÁREA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>ENSAMBLA E INSTALA CONTROLADORES Y DISPOSITIVOS PERIFÉRICOS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>FÍSICA I</t>
+  </si>
+  <si>
+    <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTROMAGNÉTICO</t>
+  </si>
+  <si>
+    <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EVELYN IVETH</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>INGLÉS IV</t>
-  </si>
-  <si>
-    <t>FÍSICA I</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>ELIDETH</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
-  </si>
-  <si>
-    <t>PROBABILIDAD Y ESTADÍSTICA</t>
-  </si>
-  <si>
-    <t>TEMAS DE FILOSOFÍA</t>
-  </si>
-  <si>
-    <t>MATEMÁTICAS APLICADAS</t>
-  </si>
-  <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
-    <t>NADYA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANGEL EDUARDO</t>
-  </si>
-  <si>
-    <t>ABDIEL ANTONIO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES MÓVILES PARA IOS</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES MÓVILES PARA ANDROID</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>YATZIRI NAOMI</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>DETERMINA LA NÓMINA DEL PERSONAL DE LA ORGANIZACIÓN TOMANDO EN CUENTA LA NORMATIVIDAD LABORAL</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>JUAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ADRIANA</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>DISEÑA INSTALACIONES ELÉCTRICAS</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>CABALLERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>INGLÉS II</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>APLICA ESTRUCTURAS DE DATOS CON UN LENGUAJE DE PROGRAMACIÓN</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>DISTINGUE LOS DIFERENTES TIPOS DE EMPRESA POR SU GIRO, ÁREAS FUNCIONALES, DOCUMENTACIÓN ADMINISTRATIVA Y RECURSOS</t>
-  </si>
-  <si>
-    <t>ELABORA ESTRATEGIAS PARA REALIZAR LAS ACTIVIDADES DE SU ÁREA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>ENSAMBLA E INSTALA CONTROLADORES Y DISPOSITIVOS PERIFÉRICOS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTROMAGNÉTICO</t>
-  </si>
-  <si>
-    <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
   </si>
   <si>
     <t>DE LA LUZ</t>
@@ -1852,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1883,10 +1823,10 @@
         <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>65</v>
@@ -1903,13 +1843,13 @@
         <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -1923,10 +1863,10 @@
         <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
@@ -1937,16 +1877,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920162</v>
+        <v>20330051920172</v>
       </c>
       <c r="B5" t="s">
         <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
         <v>65</v>
@@ -1957,16 +1897,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920167</v>
+        <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
         <v>65</v>
@@ -1977,19 +1917,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920172</v>
+        <v>20330051920174</v>
       </c>
       <c r="B7" t="s">
         <v>99</v>
       </c>
       <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
         <v>112</v>
       </c>
-      <c r="D7" t="s">
-        <v>124</v>
-      </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1997,19 +1937,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920173</v>
+        <v>20330051920373</v>
       </c>
       <c r="B8" t="s">
         <v>100</v>
       </c>
       <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" t="s">
         <v>113</v>
       </c>
-      <c r="D8" t="s">
-        <v>125</v>
-      </c>
       <c r="E8" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2017,19 +1957,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920173</v>
+        <v>20330051920388</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2037,19 +1977,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920174</v>
+        <v>20330051920388</v>
       </c>
       <c r="B10" t="s">
         <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2057,181 +1997,21 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920174</v>
+        <v>20330051920393</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920177</v>
-      </c>
-      <c r="B12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920180</v>
-      </c>
-      <c r="B13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920183</v>
-      </c>
-      <c r="B14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920369</v>
-      </c>
-      <c r="B15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920373</v>
-      </c>
-      <c r="B16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920388</v>
-      </c>
-      <c r="B17" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" t="s">
-        <v>132</v>
-      </c>
-      <c r="E17" t="s">
-        <v>134</v>
-      </c>
-      <c r="F17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920388</v>
-      </c>
-      <c r="B18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920393</v>
-      </c>
-      <c r="B19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" t="s">
-        <v>133</v>
-      </c>
-      <c r="E19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19">
         <v>5</v>
       </c>
     </row>
@@ -2270,13 +2050,13 @@
         <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
         <v>65</v>
@@ -2290,13 +2070,13 @@
         <v>20330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>65</v>
@@ -2310,13 +2090,13 @@
         <v>20330051920101</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
@@ -2330,13 +2110,13 @@
         <v>20330051920107</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
         <v>65</v>
@@ -2350,13 +2130,13 @@
         <v>20330051920111</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
         <v>65</v>
@@ -2400,13 +2180,13 @@
         <v>20330051920287</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
         <v>65</v>
@@ -2423,10 +2203,10 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
         <v>65</v>
@@ -2440,13 +2220,13 @@
         <v>20330051920310</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
@@ -2460,13 +2240,13 @@
         <v>20330051920379</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
         <v>65</v>
@@ -2482,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2516,10 +2296,10 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2530,16 +2310,16 @@
         <v>19330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2556,10 +2336,10 @@
         <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2567,19 +2347,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920010</v>
+        <v>19330051920014</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2587,19 +2367,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920016</v>
+        <v>19330051920014</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2607,19 +2387,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920017</v>
+        <v>19330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2627,19 +2407,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920018</v>
+        <v>19330051920017</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2647,19 +2427,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920024</v>
+        <v>19330051920018</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D9" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2667,19 +2447,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920026</v>
+        <v>19330051920024</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2687,19 +2467,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920034</v>
+        <v>19330051920026</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2710,16 +2490,16 @@
         <v>19330051920034</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2727,19 +2507,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920037</v>
+        <v>19330051920034</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" t="s">
         <v>169</v>
-      </c>
-      <c r="D13" t="s">
-        <v>181</v>
-      </c>
-      <c r="E13" t="s">
-        <v>185</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2747,19 +2527,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920038</v>
+        <v>19330051920037</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2767,19 +2547,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920039</v>
+        <v>19330051920038</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="C15" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2787,19 +2567,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920040</v>
+        <v>19330051920039</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" t="s">
         <v>169</v>
-      </c>
-      <c r="D16" t="s">
-        <v>184</v>
-      </c>
-      <c r="E16" t="s">
-        <v>187</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -2810,18 +2590,38 @@
         <v>19330051920040</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="D17" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>19330051920040</v>
+      </c>
+      <c r="B18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18">
         <v>5</v>
       </c>
     </row>
@@ -2860,16 +2660,16 @@
         <v>19330051920168</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2910,16 +2710,16 @@
         <v>19330051420227</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2930,16 +2730,16 @@
         <v>19330051920223</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2950,16 +2750,16 @@
         <v>19330051920225</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2970,16 +2770,16 @@
         <v>19330051920227</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2990,16 +2790,16 @@
         <v>19330051920227</v>
       </c>
       <c r="B6" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
         <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3010,16 +2810,16 @@
         <v>19330051920230</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3030,16 +2830,16 @@
         <v>19330051920233</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3050,16 +2850,16 @@
         <v>19330051920235</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3070,16 +2870,16 @@
         <v>19330051920235</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3090,16 +2890,16 @@
         <v>19330051920236</v>
       </c>
       <c r="B11" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C11" t="s">
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="E11" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3110,16 +2910,16 @@
         <v>19330051920237</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3130,16 +2930,16 @@
         <v>19330051920237</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3150,16 +2950,16 @@
         <v>19330051920239</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3170,16 +2970,16 @@
         <v>19330051920242</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3190,16 +2990,16 @@
         <v>19330051920243</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D16" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3210,16 +3010,16 @@
         <v>19330051920243</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" t="s">
         <v>204</v>
-      </c>
-      <c r="D17" t="s">
-        <v>216</v>
-      </c>
-      <c r="E17" t="s">
-        <v>218</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3230,16 +3030,16 @@
         <v>19330051920430</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="E18" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3280,16 +3080,16 @@
         <v>19330051920125</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -3303,13 +3103,13 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="E3" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3320,16 +3120,16 @@
         <v>19330051920130</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3340,16 +3140,16 @@
         <v>19330051920431</v>
       </c>
       <c r="B5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s">
         <v>107</v>
       </c>
-      <c r="C5" t="s">
-        <v>118</v>
-      </c>
       <c r="D5" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3390,16 +3190,16 @@
         <v>19330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="D2" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3416,10 +3216,10 @@
         <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3433,13 +3233,13 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D4" t="s">
         <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3450,16 +3250,16 @@
         <v>19330051920095</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3473,13 +3273,13 @@
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3493,13 +3293,13 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3513,13 +3313,13 @@
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D8" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3533,13 +3333,13 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3556,10 +3356,10 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3573,13 +3373,13 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="E11" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3593,13 +3393,13 @@
         <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3613,13 +3413,13 @@
         <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3630,16 +3430,16 @@
         <v>19330051920118</v>
       </c>
       <c r="B14" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C14" t="s">
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3650,16 +3450,16 @@
         <v>19330051920119</v>
       </c>
       <c r="B15" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3670,16 +3470,16 @@
         <v>19330051920120</v>
       </c>
       <c r="B16" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3690,16 +3490,16 @@
         <v>19330051920122</v>
       </c>
       <c r="B17" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3773,13 +3573,13 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D2" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>283</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -3793,13 +3593,13 @@
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3" t="s">
         <v>267</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -3810,13 +3610,13 @@
         <v>20330051920022</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C4" t="s">
         <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -3833,10 +3633,10 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -3850,13 +3650,13 @@
         <v>21330051920003</v>
       </c>
       <c r="B6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" t="s">
         <v>254</v>
-      </c>
-      <c r="C6" t="s">
-        <v>260</v>
-      </c>
-      <c r="D6" t="s">
-        <v>270</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -3870,13 +3670,13 @@
         <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" t="s">
         <v>255</v>
-      </c>
-      <c r="C7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D7" t="s">
-        <v>271</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -3890,19 +3690,19 @@
         <v>21330051920006</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3910,19 +3710,19 @@
         <v>21330051920006</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3930,13 +3730,13 @@
         <v>21330051920007</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C10" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -3950,13 +3750,13 @@
         <v>21330051920007</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C11" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -3973,10 +3773,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -3993,10 +3793,10 @@
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -4016,7 +3816,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -4033,10 +3833,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -4050,13 +3850,13 @@
         <v>21330051920023</v>
       </c>
       <c r="B16" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -4076,7 +3876,7 @@
         <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -4096,7 +3896,7 @@
         <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -4110,13 +3910,13 @@
         <v>21330051920028</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="D19" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E19" t="s">
         <v>23</v>
@@ -4130,13 +3930,13 @@
         <v>21330051920355</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
@@ -4150,13 +3950,13 @@
         <v>21330051920385</v>
       </c>
       <c r="B21" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="E21" t="s">
         <v>23</v>
@@ -4170,13 +3970,13 @@
         <v>21330051920393</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D22" t="s">
         <v>266</v>
-      </c>
-      <c r="D22" t="s">
-        <v>282</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
@@ -4290,13 +4090,13 @@
         <v>21330051920072</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -4313,10 +4113,10 @@
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -4333,10 +4133,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="D4" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -4353,13 +4153,13 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="D5" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="E5" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4373,10 +4173,10 @@
         <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="D6" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -4390,13 +4190,13 @@
         <v>21330051920098</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
         <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -4410,13 +4210,13 @@
         <v>21330051920098</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
         <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -4430,13 +4230,13 @@
         <v>21330051920100</v>
       </c>
       <c r="B9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" t="s">
         <v>285</v>
-      </c>
-      <c r="C9" t="s">
-        <v>293</v>
-      </c>
-      <c r="D9" t="s">
-        <v>301</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -4450,13 +4250,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B10" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C10" t="s">
         <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -4470,13 +4270,13 @@
         <v>21330051920107</v>
       </c>
       <c r="B11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C11" t="s">
+        <v>278</v>
+      </c>
+      <c r="D11" t="s">
         <v>287</v>
-      </c>
-      <c r="C11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D11" t="s">
-        <v>303</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -4490,13 +4290,13 @@
         <v>21330051920107</v>
       </c>
       <c r="B12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D12" t="s">
         <v>287</v>
-      </c>
-      <c r="C12" t="s">
-        <v>294</v>
-      </c>
-      <c r="D12" t="s">
-        <v>303</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -4510,13 +4310,13 @@
         <v>21330051920109</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
         <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -4530,13 +4330,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="C14" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -4550,13 +4350,13 @@
         <v>21330051920357</v>
       </c>
       <c r="B15" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="C15" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D15" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -4570,13 +4370,13 @@
         <v>21330051920383</v>
       </c>
       <c r="B16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" t="s">
         <v>289</v>
-      </c>
-      <c r="C16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" t="s">
-        <v>305</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -4620,16 +4420,16 @@
         <v>21330051920112</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4640,16 +4440,16 @@
         <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4660,13 +4460,13 @@
         <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -4686,7 +4486,7 @@
         <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -4700,16 +4500,16 @@
         <v>21330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="E6" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4720,13 +4520,13 @@
         <v>21330051920126</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -4740,16 +4540,16 @@
         <v>21330051920134</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="C8" t="s">
         <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="E8" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4760,16 +4560,16 @@
         <v>21330051920391</v>
       </c>
       <c r="B9" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="D9" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>290</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4780,16 +4580,16 @@
         <v>21330051920391</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="D10" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="E10" t="s">
-        <v>306</v>
+        <v>12</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4830,13 +4630,13 @@
         <v>21330051920029</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -4850,16 +4650,16 @@
         <v>21330051920032</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C3" t="s">
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="E3" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4870,13 +4670,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -4890,19 +4690,19 @@
         <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="E5" t="s">
-        <v>338</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4910,19 +4710,19 @@
         <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D6" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>322</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4933,16 +4733,16 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="E7" t="s">
-        <v>306</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4953,16 +4753,16 @@
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>290</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4970,13 +4770,13 @@
         <v>21330051920054</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -4996,13 +4796,13 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="E10" t="s">
-        <v>337</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5016,13 +4816,13 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5030,13 +4830,13 @@
         <v>21330051920058</v>
       </c>
       <c r="B12" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -5050,13 +4850,13 @@
         <v>21330051920062</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="C13" t="s">
         <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -5070,13 +4870,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -5090,16 +4890,16 @@
         <v>21330051920388</v>
       </c>
       <c r="B15" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="C15" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D15" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="E15" t="s">
-        <v>306</v>
+        <v>23</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5110,16 +4910,16 @@
         <v>21330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="C16" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D16" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>290</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5160,13 +4960,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -5183,10 +4983,10 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="D3" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -5203,10 +5003,10 @@
         <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D4" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -5220,16 +5020,16 @@
         <v>21330051920145</v>
       </c>
       <c r="B5" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="C5" t="s">
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="E5" t="s">
-        <v>347</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5240,16 +5040,16 @@
         <v>21330051920145</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>331</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5260,13 +5060,13 @@
         <v>21330051920147</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -5283,10 +5083,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D8" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -5302,7 +5102,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5330,16 +5130,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="E2" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5350,16 +5150,16 @@
         <v>20330051920059</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -5370,13 +5170,13 @@
         <v>20330051920065</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="D4" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
@@ -5390,13 +5190,13 @@
         <v>20330051920070</v>
       </c>
       <c r="B5" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
         <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -5410,16 +5210,16 @@
         <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="C6" t="s">
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E6" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -5427,39 +5227,39 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920073</v>
+        <v>20330051920075</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C7" t="s">
-        <v>353</v>
+        <v>152</v>
       </c>
       <c r="D7" t="s">
-        <v>179</v>
+        <v>339</v>
       </c>
       <c r="E7" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B8" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>336</v>
       </c>
       <c r="D8" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="E8" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5467,102 +5267,22 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>336</v>
       </c>
       <c r="D9" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="E9" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="F9">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920077</v>
-      </c>
-      <c r="B10" t="s">
-        <v>351</v>
-      </c>
-      <c r="C10" t="s">
-        <v>354</v>
-      </c>
-      <c r="D10" t="s">
-        <v>360</v>
-      </c>
-      <c r="E10" t="s">
-        <v>363</v>
-      </c>
-      <c r="F10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920077</v>
-      </c>
-      <c r="B11" t="s">
-        <v>351</v>
-      </c>
-      <c r="C11" t="s">
-        <v>354</v>
-      </c>
-      <c r="D11" t="s">
-        <v>360</v>
-      </c>
-      <c r="E11" t="s">
-        <v>364</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920080</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>355</v>
-      </c>
-      <c r="D12" t="s">
-        <v>361</v>
-      </c>
-      <c r="E12" t="s">
-        <v>364</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920090</v>
-      </c>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" t="s">
-        <v>356</v>
-      </c>
-      <c r="D13" t="s">
-        <v>362</v>
-      </c>
-      <c r="E13" t="s">
-        <v>364</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5600,16 +5320,16 @@
         <v>20330051920191</v>
       </c>
       <c r="B2" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="D2" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="E2" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5620,16 +5340,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>345</v>
       </c>
       <c r="C3" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="D3" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5640,16 +5360,16 @@
         <v>20330051920204</v>
       </c>
       <c r="B4" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C4" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="D4" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="E4" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5660,13 +5380,13 @@
         <v>20330051920204</v>
       </c>
       <c r="B5" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="D5" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -5680,16 +5400,16 @@
         <v>20330051920214</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="E6" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5700,16 +5420,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B7" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D7" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="E7" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5720,16 +5440,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B8" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5746,10 +5466,10 @@
         <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="E9" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5766,7 +5486,7 @@
         <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="E10" t="s">
         <v>65</v>
@@ -5810,16 +5530,16 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C2" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="D2" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="E2" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -5830,13 +5550,13 @@
         <v>19330051920238</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="E3" t="s">
         <v>66</v>
@@ -5850,19 +5570,19 @@
         <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5870,19 +5590,19 @@
         <v>19330051920314</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>341</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5893,13 +5613,13 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D6" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5913,13 +5633,13 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5930,16 +5650,16 @@
         <v>20330051920273</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5953,10 +5673,10 @@
         <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="E9" t="s">
         <v>66</v>
@@ -5973,13 +5693,13 @@
         <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="E10" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -5990,16 +5710,16 @@
         <v>20330051920276</v>
       </c>
       <c r="B11" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="C11" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6016,7 +5736,7 @@
         <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="E12" t="s">
         <v>66</v>
@@ -6033,13 +5753,13 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>341</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6053,13 +5773,13 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6103,10 +5823,10 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="D2" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
@@ -6126,10 +5846,10 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="E3" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6146,10 +5866,10 @@
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="E4" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6166,10 +5886,10 @@
         <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="E5" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6183,13 +5903,13 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="E6" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6200,16 +5920,16 @@
         <v>20330051920151</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="E7" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6220,16 +5940,16 @@
         <v>20330051920151</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="E8" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6273,13 +5993,13 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" t="s">
         <v>116</v>
-      </c>
-      <c r="D2" t="s">
-        <v>404</v>
-      </c>
-      <c r="E2" t="s">
-        <v>134</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6290,13 +6010,13 @@
         <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C3" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="D3" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="E3" t="s">
         <v>66</v>
@@ -6310,16 +6030,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C4" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="D4" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6330,16 +6050,16 @@
         <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="C5" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="D5" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6350,13 +6070,13 @@
         <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="E6" t="s">
         <v>66</v>
@@ -6370,16 +6090,16 @@
         <v>20330051920322</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -6390,16 +6110,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6413,13 +6133,13 @@
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="D9" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="E9" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6430,16 +6150,16 @@
         <v>20330051920335</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="D10" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="E10" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6450,16 +6170,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>341</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -6470,16 +6190,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D12" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="E12" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6520,16 +6240,16 @@
         <v>18330051920022</v>
       </c>
       <c r="B2" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="D2" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6540,16 +6260,16 @@
         <v>19330051920045</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="D3" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6560,16 +6280,16 @@
         <v>19330051920055</v>
       </c>
       <c r="B4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" t="s">
         <v>169</v>
-      </c>
-      <c r="C4" t="s">
-        <v>415</v>
-      </c>
-      <c r="D4" t="s">
-        <v>418</v>
-      </c>
-      <c r="E4" t="s">
-        <v>185</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6583,13 +6303,13 @@
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="D5" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="E5" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6603,13 +6323,13 @@
         <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="D6" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>170</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6623,13 +6343,13 @@
         <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="E7" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6643,13 +6363,13 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6663,13 +6383,13 @@
         <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="D9" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6683,13 +6403,13 @@
         <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6780,16 +6500,16 @@
         <v>19330051920269</v>
       </c>
       <c r="B2" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6800,16 +6520,16 @@
         <v>19330051920273</v>
       </c>
       <c r="B3" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="C3" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="D3" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="E3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6820,16 +6540,16 @@
         <v>19330051920278</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="D4" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6843,13 +6563,13 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="D5" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6860,16 +6580,16 @@
         <v>19330051920286</v>
       </c>
       <c r="B6" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D6" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6880,16 +6600,16 @@
         <v>19330051920292</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6900,16 +6620,16 @@
         <v>19330051920443</v>
       </c>
       <c r="B8" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="C8" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="D8" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6956,10 +6676,10 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6970,16 +6690,16 @@
         <v>19330051920312</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
         <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6990,16 +6710,16 @@
         <v>19330051920316</v>
       </c>
       <c r="B4" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="C4" t="s">
         <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7010,16 +6730,16 @@
         <v>19330051920323</v>
       </c>
       <c r="B5" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="C5" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="D5" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="E5" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7033,13 +6753,13 @@
         <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="D6" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7053,13 +6773,13 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="D7" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7070,16 +6790,16 @@
         <v>19330051920337</v>
       </c>
       <c r="B8" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="C8" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="D8" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7090,16 +6810,16 @@
         <v>19330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>361</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7110,16 +6830,16 @@
         <v>19330051920338</v>
       </c>
       <c r="B10" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>361</v>
+        <v>158</v>
       </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7130,16 +6850,16 @@
         <v>19330051920352</v>
       </c>
       <c r="B11" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="C11" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="D11" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7150,16 +6870,16 @@
         <v>19330051920353</v>
       </c>
       <c r="B12" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7170,16 +6890,16 @@
         <v>19330051920353</v>
       </c>
       <c r="B13" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7220,16 +6940,16 @@
         <v>19330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7246,10 +6966,10 @@
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="E3" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7266,10 +6986,10 @@
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="E4" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7286,10 +7006,10 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="E5" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7303,13 +7023,13 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7320,16 +7040,16 @@
         <v>19330051920396</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="E7" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7346,10 +7066,10 @@
         <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="E8" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7390,16 +7110,16 @@
         <v>19330051920246</v>
       </c>
       <c r="B2" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D2" t="s">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7410,16 +7130,16 @@
         <v>19330051920247</v>
       </c>
       <c r="B3" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="C3" t="s">
         <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7430,16 +7150,16 @@
         <v>19330051920247</v>
       </c>
       <c r="B4" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="C4" t="s">
         <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="E4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7450,16 +7170,16 @@
         <v>19330051920248</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" t="s">
+        <v>445</v>
+      </c>
+      <c r="E5" t="s">
         <v>169</v>
-      </c>
-      <c r="D5" t="s">
-        <v>465</v>
-      </c>
-      <c r="E5" t="s">
-        <v>185</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7470,16 +7190,16 @@
         <v>19330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="D6" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7496,10 +7216,10 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="E7" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7516,10 +7236,10 @@
         <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7533,13 +7253,13 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="D9" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7550,16 +7270,16 @@
         <v>19330051920265</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
         <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7570,16 +7290,16 @@
         <v>19330051920265</v>
       </c>
       <c r="B11" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C11" t="s">
         <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7590,16 +7310,16 @@
         <v>19330051920400</v>
       </c>
       <c r="B12" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="C12" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="D12" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7613,13 +7333,13 @@
         <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="D13" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7633,13 +7353,13 @@
         <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7650,16 +7370,16 @@
         <v>19330051920409</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" t="s">
+        <v>452</v>
+      </c>
+      <c r="E15" t="s">
         <v>169</v>
-      </c>
-      <c r="D15" t="s">
-        <v>472</v>
-      </c>
-      <c r="E15" t="s">
-        <v>185</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7670,16 +7390,16 @@
         <v>19330051920414</v>
       </c>
       <c r="B16" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C16" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="D16" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -7799,7 +7519,7 @@
         <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7819,7 +7539,7 @@
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8459,7 +8179,7 @@
         <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8479,7 +8199,7 @@
         <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F7">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="694">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -1773,13 +1773,22 @@
     <t>FLOR GUADALUPE</t>
   </si>
   <si>
-    <t>TLAXCALTECA</t>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>QUERO</t>
   </si>
   <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
-    <t>CLAUDIA</t>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>APLICA LA METODOLOGÍA DE DESARROLLO RÁPIDO DE APLICACIONES CON PROGRAMACIÓN ORIENTADA A EVENTOS</t>
   </si>
   <si>
     <t>ANDRADE</t>
@@ -2028,9 +2037,6 @@
     <t>TIBURCIO</t>
   </si>
   <si>
-    <t>PAZOS</t>
-  </si>
-  <si>
     <t>VERGEL</t>
   </si>
   <si>
@@ -2041,9 +2047,6 @@
   </si>
   <si>
     <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>CARLA DANIELA</t>
   </si>
   <si>
     <t>TANIA</t>
@@ -9382,7 +9385,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9407,19 +9410,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>18330051920377</v>
+        <v>20330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>268</v>
       </c>
       <c r="C2" t="s">
-        <v>575</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
-        <v>194</v>
+        <v>290</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -9427,19 +9430,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>268</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>576</v>
+        <v>218</v>
       </c>
       <c r="E3" t="s">
-        <v>194</v>
+        <v>580</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -9456,7 +9459,7 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E4" t="s">
         <v>290</v>
@@ -9467,21 +9470,81 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920122</v>
+        <v>21330051920117</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>575</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>354</v>
       </c>
       <c r="D5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>21330051920117</v>
+      </c>
+      <c r="B6" t="s">
+        <v>575</v>
+      </c>
+      <c r="C6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" t="s">
+        <v>578</v>
+      </c>
+      <c r="E6" t="s">
+        <v>580</v>
+      </c>
+      <c r="F6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>21330051920130</v>
+      </c>
+      <c r="B7" t="s">
+        <v>576</v>
+      </c>
+      <c r="C7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" t="s">
+        <v>579</v>
+      </c>
+      <c r="E7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>21330051920130</v>
+      </c>
+      <c r="B8" t="s">
+        <v>576</v>
+      </c>
+      <c r="C8" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" t="s">
+        <v>579</v>
+      </c>
+      <c r="E8" t="s">
+        <v>580</v>
+      </c>
+      <c r="F8">
         <v>-1</v>
       </c>
     </row>
@@ -9520,7 +9583,7 @@
         <v>21330051920029</v>
       </c>
       <c r="B2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
@@ -9546,7 +9609,7 @@
         <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E3" t="s">
         <v>194</v>
@@ -9566,7 +9629,7 @@
         <v>431</v>
       </c>
       <c r="D4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E4" t="s">
         <v>194</v>
@@ -9580,13 +9643,13 @@
         <v>21330051920035</v>
       </c>
       <c r="B5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E5" t="s">
         <v>194</v>
@@ -9606,7 +9669,7 @@
         <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E6" t="s">
         <v>194</v>
@@ -9626,7 +9689,7 @@
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E7" t="s">
         <v>194</v>
@@ -9646,7 +9709,7 @@
         <v>433</v>
       </c>
       <c r="D8" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E8" t="s">
         <v>194</v>
@@ -9666,7 +9729,7 @@
         <v>241</v>
       </c>
       <c r="D9" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E9" t="s">
         <v>194</v>
@@ -9686,7 +9749,7 @@
         <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E10" t="s">
         <v>194</v>
@@ -9703,10 +9766,10 @@
         <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D11" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E11" t="s">
         <v>195</v>
@@ -9723,10 +9786,10 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D12" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E12" t="s">
         <v>194</v>
@@ -9746,7 +9809,7 @@
         <v>266</v>
       </c>
       <c r="D13" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E13" t="s">
         <v>194</v>
@@ -9766,7 +9829,7 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E14" t="s">
         <v>194</v>
@@ -9783,7 +9846,7 @@
         <v>475</v>
       </c>
       <c r="C15" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D15" t="s">
         <v>459</v>
@@ -9803,10 +9866,10 @@
         <v>118</v>
       </c>
       <c r="C16" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D16" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E16" t="s">
         <v>194</v>
@@ -9823,10 +9886,10 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D17" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E17" t="s">
         <v>194</v>
@@ -9840,13 +9903,13 @@
         <v>21330051920055</v>
       </c>
       <c r="B18" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C18" t="s">
         <v>493</v>
       </c>
       <c r="D18" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E18" t="s">
         <v>194</v>
@@ -9863,10 +9926,10 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D19" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E19" t="s">
         <v>194</v>
@@ -9886,7 +9949,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E20" t="s">
         <v>194</v>
@@ -9900,7 +9963,7 @@
         <v>21330051920059</v>
       </c>
       <c r="B21" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C21" t="s">
         <v>448</v>
@@ -9923,10 +9986,10 @@
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D22" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E22" t="s">
         <v>194</v>
@@ -9940,13 +10003,13 @@
         <v>21330051920062</v>
       </c>
       <c r="B23" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E23" t="s">
         <v>194</v>
@@ -9966,7 +10029,7 @@
         <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E24" t="s">
         <v>194</v>
@@ -10006,7 +10069,7 @@
         <v>156</v>
       </c>
       <c r="D26" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E26" t="s">
         <v>194</v>
@@ -10023,10 +10086,10 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D27" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E27" t="s">
         <v>194</v>
@@ -10073,10 +10136,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E2" t="s">
         <v>191</v>
@@ -10096,7 +10159,7 @@
         <v>509</v>
       </c>
       <c r="D3" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="E3" t="s">
         <v>191</v>
@@ -10116,7 +10179,7 @@
         <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E4" t="s">
         <v>191</v>
@@ -10136,7 +10199,7 @@
         <v>471</v>
       </c>
       <c r="D5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E5" t="s">
         <v>191</v>
@@ -10156,7 +10219,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E6" t="s">
         <v>194</v>
@@ -10176,7 +10239,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E7" t="s">
         <v>191</v>
@@ -10196,7 +10259,7 @@
         <v>296</v>
       </c>
       <c r="D8" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E8" t="s">
         <v>191</v>
@@ -10213,10 +10276,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D9" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E9" t="s">
         <v>194</v>
@@ -10233,10 +10296,10 @@
         <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D10" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E10" t="s">
         <v>191</v>
@@ -10276,7 +10339,7 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E12" t="s">
         <v>191</v>
@@ -10326,7 +10389,7 @@
         <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E2" t="s">
         <v>319</v>
@@ -10340,13 +10403,13 @@
         <v>20330051920041</v>
       </c>
       <c r="B3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C3" t="s">
         <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E3" t="s">
         <v>319</v>
@@ -10366,7 +10429,7 @@
         <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E4" t="s">
         <v>319</v>
@@ -10386,7 +10449,7 @@
         <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E5" t="s">
         <v>319</v>
@@ -10406,7 +10469,7 @@
         <v>442</v>
       </c>
       <c r="D6" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E6" t="s">
         <v>318</v>
@@ -10426,7 +10489,7 @@
         <v>442</v>
       </c>
       <c r="D7" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E7" t="s">
         <v>319</v>
@@ -10446,7 +10509,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E8" t="s">
         <v>318</v>
@@ -10466,7 +10529,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E9" t="s">
         <v>319</v>
@@ -10480,7 +10543,7 @@
         <v>20330051920073</v>
       </c>
       <c r="B10" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C10" t="s">
         <v>414</v>
@@ -10546,7 +10609,7 @@
         <v>538</v>
       </c>
       <c r="D13" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E13" t="s">
         <v>319</v>
@@ -10566,7 +10629,7 @@
         <v>538</v>
       </c>
       <c r="D14" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E14" t="s">
         <v>318</v>
@@ -10586,7 +10649,7 @@
         <v>241</v>
       </c>
       <c r="D15" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E15" t="s">
         <v>319</v>
@@ -10606,7 +10669,7 @@
         <v>241</v>
       </c>
       <c r="D16" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E16" t="s">
         <v>318</v>
@@ -10620,7 +10683,7 @@
         <v>20330051920091</v>
       </c>
       <c r="B17" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C17" t="s">
         <v>127</v>
@@ -10640,7 +10703,7 @@
         <v>20330051920091</v>
       </c>
       <c r="B18" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C18" t="s">
         <v>127</v>
@@ -10666,7 +10729,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E19" t="s">
         <v>319</v>
@@ -11106,7 +11169,7 @@
         <v>496</v>
       </c>
       <c r="D2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E2" t="s">
         <v>318</v>
@@ -11120,13 +11183,13 @@
         <v>20330051920192</v>
       </c>
       <c r="B3" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C3" t="s">
         <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E3" t="s">
         <v>320</v>
@@ -11140,13 +11203,13 @@
         <v>20330051920197</v>
       </c>
       <c r="B4" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E4" t="s">
         <v>318</v>
@@ -11163,10 +11226,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E5" t="s">
         <v>318</v>
@@ -11186,7 +11249,7 @@
         <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E6" t="s">
         <v>318</v>
@@ -11206,7 +11269,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E7" t="s">
         <v>318</v>
@@ -11226,7 +11289,7 @@
         <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E8" t="s">
         <v>320</v>
@@ -11246,7 +11309,7 @@
         <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E9" t="s">
         <v>318</v>
@@ -11263,7 +11326,7 @@
         <v>542</v>
       </c>
       <c r="C10" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -11283,7 +11346,7 @@
         <v>542</v>
       </c>
       <c r="C11" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -11306,7 +11369,7 @@
         <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E12" t="s">
         <v>318</v>
@@ -11323,10 +11386,10 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D13" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E13" t="s">
         <v>320</v>
@@ -11343,10 +11406,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D14" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E14" t="s">
         <v>318</v>
@@ -11366,7 +11429,7 @@
         <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E15" t="s">
         <v>318</v>
@@ -11386,7 +11449,7 @@
         <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E16" t="s">
         <v>320</v>
@@ -11406,7 +11469,7 @@
         <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E17" t="s">
         <v>318</v>
@@ -11426,7 +11489,7 @@
         <v>183</v>
       </c>
       <c r="D18" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E18" t="s">
         <v>318</v>
@@ -11470,13 +11533,13 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C2" t="s">
         <v>533</v>
       </c>
       <c r="D2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E2" t="s">
         <v>318</v>
@@ -11490,13 +11553,13 @@
         <v>19220030050208</v>
       </c>
       <c r="B3" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C3" t="s">
         <v>533</v>
       </c>
       <c r="D3" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E3" t="s">
         <v>320</v>
@@ -11510,13 +11573,13 @@
         <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C4" t="s">
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E4" t="s">
         <v>320</v>
@@ -11530,13 +11593,13 @@
         <v>20330051920260</v>
       </c>
       <c r="B5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C5" t="s">
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E5" t="s">
         <v>318</v>
@@ -11556,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E6" t="s">
         <v>318</v>
@@ -11576,7 +11639,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E7" t="s">
         <v>320</v>
@@ -11596,7 +11659,7 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E8" t="s">
         <v>318</v>
@@ -11616,7 +11679,7 @@
         <v>223</v>
       </c>
       <c r="D9" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E9" t="s">
         <v>320</v>
@@ -11636,7 +11699,7 @@
         <v>223</v>
       </c>
       <c r="D10" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E10" t="s">
         <v>318</v>
@@ -11656,7 +11719,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E11" t="s">
         <v>320</v>
@@ -11676,7 +11739,7 @@
         <v>338</v>
       </c>
       <c r="D12" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E12" t="s">
         <v>318</v>
@@ -11696,7 +11759,7 @@
         <v>338</v>
       </c>
       <c r="D13" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E13" t="s">
         <v>320</v>
@@ -11710,13 +11773,13 @@
         <v>20330051920282</v>
       </c>
       <c r="B14" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C14" t="s">
         <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E14" t="s">
         <v>318</v>
@@ -11732,7 +11795,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -11757,19 +11820,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>18330051920189</v>
+        <v>18330051920393</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>660</v>
+        <v>374</v>
       </c>
       <c r="D2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E2" t="s">
-        <v>676</v>
+        <v>318</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -11777,22 +11840,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>18330051920393</v>
+        <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>541</v>
       </c>
       <c r="C3" t="s">
-        <v>374</v>
+        <v>204</v>
       </c>
       <c r="D3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E3" t="s">
-        <v>318</v>
+        <v>677</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -11806,30 +11869,30 @@
         <v>204</v>
       </c>
       <c r="D4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E4" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920360</v>
+        <v>19330051920383</v>
       </c>
       <c r="B5" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>471</v>
       </c>
       <c r="D5" t="s">
-        <v>667</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -11849,7 +11912,7 @@
         <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>677</v>
+        <v>318</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -11857,19 +11920,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920383</v>
+        <v>19330051920387</v>
       </c>
       <c r="B7" t="s">
-        <v>538</v>
+        <v>323</v>
       </c>
       <c r="C7" t="s">
-        <v>471</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>669</v>
       </c>
       <c r="E7" t="s">
-        <v>318</v>
+        <v>678</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -11886,10 +11949,10 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E8" t="s">
-        <v>677</v>
+        <v>319</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -11897,19 +11960,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920387</v>
+        <v>19330051920399</v>
       </c>
       <c r="B9" t="s">
-        <v>323</v>
+        <v>273</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>663</v>
       </c>
       <c r="D9" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E9" t="s">
-        <v>319</v>
+        <v>677</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -11923,13 +11986,13 @@
         <v>273</v>
       </c>
       <c r="C10" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D10" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -11937,19 +12000,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920399</v>
+        <v>20330051920115</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>588</v>
       </c>
       <c r="C11" t="s">
-        <v>661</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E11" t="s">
-        <v>676</v>
+        <v>319</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -11957,16 +12020,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920115</v>
+        <v>20330051920118</v>
       </c>
       <c r="B12" t="s">
-        <v>585</v>
+        <v>661</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E12" t="s">
         <v>319</v>
@@ -11977,16 +12040,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920118</v>
+        <v>20330051920121</v>
       </c>
       <c r="B13" t="s">
-        <v>658</v>
+        <v>340</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>664</v>
       </c>
       <c r="D13" t="s">
-        <v>671</v>
+        <v>324</v>
       </c>
       <c r="E13" t="s">
         <v>319</v>
@@ -12003,13 +12066,13 @@
         <v>340</v>
       </c>
       <c r="C14" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D14" t="s">
         <v>324</v>
       </c>
       <c r="E14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -12017,19 +12080,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920121</v>
+        <v>20330051920128</v>
       </c>
       <c r="B15" t="s">
-        <v>340</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D15" t="s">
-        <v>324</v>
+        <v>673</v>
       </c>
       <c r="E15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -12043,13 +12106,13 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D16" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E16" t="s">
-        <v>319</v>
+        <v>678</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -12057,19 +12120,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920128</v>
+        <v>20330051920139</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D17" t="s">
-        <v>672</v>
+        <v>604</v>
       </c>
       <c r="E17" t="s">
-        <v>677</v>
+        <v>319</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -12083,13 +12146,13 @@
         <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D18" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E18" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -12097,16 +12160,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920139</v>
+        <v>20330051920142</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>664</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>601</v>
+        <v>674</v>
       </c>
       <c r="E19" t="s">
         <v>319</v>
@@ -12117,22 +12180,22 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920142</v>
+        <v>20330051920143</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>335</v>
       </c>
       <c r="D20" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -12146,52 +12209,32 @@
         <v>335</v>
       </c>
       <c r="D21" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920143</v>
+        <v>20330051920150</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>662</v>
       </c>
       <c r="C22" t="s">
-        <v>335</v>
+        <v>161</v>
       </c>
       <c r="D22" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E22" t="s">
         <v>319</v>
       </c>
       <c r="F22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920150</v>
-      </c>
-      <c r="B23" t="s">
-        <v>659</v>
-      </c>
-      <c r="C23" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" t="s">
-        <v>675</v>
-      </c>
-      <c r="E23" t="s">
-        <v>319</v>
-      </c>
-      <c r="F23">
         <v>-1</v>
       </c>
     </row>
@@ -12236,10 +12279,10 @@
         <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -12250,16 +12293,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -12276,10 +12319,10 @@
         <v>399</v>
       </c>
       <c r="D4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -12296,7 +12339,7 @@
         <v>399</v>
       </c>
       <c r="D5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E5" t="s">
         <v>319</v>
@@ -12319,7 +12362,7 @@
         <v>478</v>
       </c>
       <c r="E6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -12356,10 +12399,10 @@
         <v>473</v>
       </c>
       <c r="D8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E8" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -12376,10 +12419,10 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E9" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -12399,7 +12442,7 @@
         <v>568</v>
       </c>
       <c r="E10" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -12430,16 +12473,16 @@
         <v>20330051920327</v>
       </c>
       <c r="B12" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E12" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -12450,16 +12493,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B13" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C13" t="s">
         <v>354</v>
       </c>
       <c r="D13" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E13" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -12470,13 +12513,13 @@
         <v>20330051920329</v>
       </c>
       <c r="B14" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C14" t="s">
         <v>354</v>
       </c>
       <c r="D14" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E14" t="s">
         <v>318</v>
@@ -12499,7 +12542,7 @@
         <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -12513,10 +12556,10 @@
         <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D16" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E16" t="s">
         <v>318</v>
@@ -12533,13 +12576,13 @@
         <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D17" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E17" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -12553,13 +12596,13 @@
         <v>376</v>
       </c>
       <c r="C18" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D18" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E18" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -12579,7 +12622,7 @@
         <v>357</v>
       </c>
       <c r="E19" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F19">
         <v>-1</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="594">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -711,9 +711,6 @@
     <t>YAEL</t>
   </si>
   <si>
-    <t>LORENA</t>
-  </si>
-  <si>
     <t>LIZBETH JOSELYN</t>
   </si>
   <si>
@@ -1293,9 +1290,6 @@
     <t>BONILLA</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>TEPOLE</t>
   </si>
   <si>
@@ -1320,9 +1314,6 @@
     <t>FERNANDA MARGARITA</t>
   </si>
   <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
     <t>MARIA ANGELES</t>
   </si>
   <si>
@@ -1800,10 +1791,10 @@
     <t>TAILY</t>
   </si>
   <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
     <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
   </si>
   <si>
     <t>NAJERA</t>
@@ -2311,10 +2302,10 @@
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2331,10 +2322,10 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2391,10 +2382,10 @@
         <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2411,10 +2402,10 @@
         <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2444,7 +2435,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2589,19 +2580,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
         <v>221</v>
       </c>
       <c r="E8" t="s">
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2609,19 +2600,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
         <v>221</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2629,13 +2620,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920235</v>
+        <v>21330051920239</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>222</v>
@@ -2649,19 +2640,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>214</v>
       </c>
       <c r="D11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2669,13 +2660,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920239</v>
+        <v>21330051920240</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>214</v>
       </c>
       <c r="D12" t="s">
         <v>223</v>
@@ -2689,13 +2680,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920240</v>
+        <v>21330051920247</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
         <v>224</v>
@@ -2709,61 +2700,21 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920240</v>
+        <v>21330051920250</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E14" t="s">
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920247</v>
-      </c>
-      <c r="B15" t="s">
-        <v>212</v>
-      </c>
-      <c r="C15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" t="s">
-        <v>225</v>
-      </c>
-      <c r="E15" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920250</v>
-      </c>
-      <c r="B16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" t="s">
-        <v>215</v>
-      </c>
-      <c r="D16" t="s">
-        <v>226</v>
-      </c>
-      <c r="E16" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16">
         <v>5</v>
       </c>
     </row>
@@ -2805,13 +2756,13 @@
         <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2825,13 +2776,13 @@
         <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2842,13 +2793,13 @@
         <v>21330051920192</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E4" t="s">
         <v>159</v>
@@ -2865,10 +2816,10 @@
         <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E5" t="s">
         <v>159</v>
@@ -2888,7 +2839,7 @@
         <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E6" t="s">
         <v>159</v>
@@ -2902,13 +2853,13 @@
         <v>21330051920201</v>
       </c>
       <c r="B7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E7" t="s">
         <v>159</v>
@@ -2925,13 +2876,13 @@
         <v>214</v>
       </c>
       <c r="C8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2945,13 +2896,13 @@
         <v>214</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2968,7 +2919,7 @@
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
         <v>159</v>
@@ -2982,10 +2933,10 @@
         <v>21330051920213</v>
       </c>
       <c r="B11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D11" t="s">
         <v>135</v>
@@ -3002,13 +2953,13 @@
         <v>21330051920386</v>
       </c>
       <c r="B12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E12" t="s">
         <v>159</v>
@@ -3052,16 +3003,16 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
         <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3078,10 +3029,10 @@
         <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3092,16 +3043,16 @@
         <v>21330051920298</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3118,7 +3069,7 @@
         <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
         <v>199</v>
@@ -3132,13 +3083,13 @@
         <v>21330051920304</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E6" t="s">
         <v>160</v>
@@ -3152,16 +3103,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3178,7 +3129,7 @@
         <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E8" t="s">
         <v>199</v>
@@ -3192,13 +3143,13 @@
         <v>21330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
         <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E9" t="s">
         <v>199</v>
@@ -3212,7 +3163,7 @@
         <v>21330051920316</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C10" t="s">
         <v>144</v>
@@ -3238,10 +3189,10 @@
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3252,16 +3203,16 @@
         <v>21330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
         <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3272,16 +3223,16 @@
         <v>21330051920328</v>
       </c>
       <c r="B13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3292,13 +3243,13 @@
         <v>21330051920330</v>
       </c>
       <c r="B14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E14" t="s">
         <v>160</v>
@@ -3342,16 +3293,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C2" t="s">
         <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3362,16 +3313,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C3" t="s">
         <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3382,16 +3333,16 @@
         <v>20330051920011</v>
       </c>
       <c r="B4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3402,16 +3353,16 @@
         <v>20330051920012</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3425,7 +3376,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D6" t="s">
         <v>131</v>
@@ -3445,13 +3396,13 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
         <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3468,10 +3419,10 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3488,10 +3439,10 @@
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3502,16 +3453,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3522,16 +3473,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3542,16 +3493,16 @@
         <v>20330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C12" t="s">
         <v>170</v>
       </c>
       <c r="D12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3568,10 +3519,10 @@
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3588,10 +3539,10 @@
         <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3605,13 +3556,13 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -3628,10 +3579,10 @@
         <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3645,13 +3596,13 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s">
+        <v>289</v>
+      </c>
+      <c r="E17" t="s">
         <v>290</v>
-      </c>
-      <c r="E17" t="s">
-        <v>291</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3692,16 +3643,16 @@
         <v>20330051920221</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -3715,13 +3666,13 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3732,13 +3683,13 @@
         <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C4" t="s">
         <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E4" t="s">
         <v>291</v>
@@ -3752,16 +3703,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3781,10 +3732,10 @@
         <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3801,10 +3752,10 @@
         <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3815,13 +3766,13 @@
         <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3835,13 +3786,13 @@
         <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3852,16 +3803,16 @@
         <v>20330051920243</v>
       </c>
       <c r="B10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C10" t="s">
         <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3872,16 +3823,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3892,16 +3843,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3912,16 +3863,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3932,16 +3883,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3952,16 +3903,16 @@
         <v>20330051920374</v>
       </c>
       <c r="B15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4002,16 +3953,16 @@
         <v>19330050470596</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
         <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -4022,16 +3973,16 @@
         <v>20330051920336</v>
       </c>
       <c r="B3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -4042,16 +3993,16 @@
         <v>20330051920336</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4062,16 +4013,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -4082,16 +4033,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4102,16 +4053,16 @@
         <v>20330051920340</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -4125,16 +4076,16 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E8" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4145,16 +4096,16 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E9" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4168,10 +4119,10 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -4182,16 +4133,16 @@
         <v>20330051920349</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C11" t="s">
         <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -4202,16 +4153,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4225,13 +4176,13 @@
         <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D13" t="s">
         <v>203</v>
       </c>
       <c r="E13" t="s">
-        <v>333</v>
+        <v>292</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -4245,13 +4196,13 @@
         <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D14" t="s">
         <v>203</v>
       </c>
       <c r="E14" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -4268,10 +4219,10 @@
         <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -4282,16 +4233,16 @@
         <v>20330051920383</v>
       </c>
       <c r="B16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C16" t="s">
         <v>94</v>
       </c>
       <c r="D16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E16" t="s">
         <v>331</v>
-      </c>
-      <c r="E16" t="s">
-        <v>332</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4302,16 +4253,16 @@
         <v>20330051920383</v>
       </c>
       <c r="B17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C17" t="s">
         <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -4358,10 +4309,10 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -4372,19 +4323,19 @@
         <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4392,19 +4343,19 @@
         <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E4" t="s">
         <v>292</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4418,10 +4369,10 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4438,10 +4389,10 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -4458,13 +4409,13 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4478,13 +4429,13 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E8" t="s">
         <v>292</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4492,19 +4443,19 @@
         <v>20330051920168</v>
       </c>
       <c r="B9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E9" t="s">
         <v>292</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4512,19 +4463,19 @@
         <v>20330051920168</v>
       </c>
       <c r="B10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C10" t="s">
         <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4532,19 +4483,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4552,19 +4503,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E12" t="s">
         <v>292</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4572,16 +4523,16 @@
         <v>20330051920178</v>
       </c>
       <c r="B13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C13" t="s">
         <v>179</v>
       </c>
       <c r="D13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -4592,16 +4543,16 @@
         <v>20330051920178</v>
       </c>
       <c r="B14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C14" t="s">
         <v>179</v>
       </c>
       <c r="D14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -4618,10 +4569,10 @@
         <v>148</v>
       </c>
       <c r="D15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -4635,7 +4586,7 @@
         <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D16" t="s">
         <v>75</v>
@@ -4644,7 +4595,7 @@
         <v>292</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4655,16 +4606,16 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D17" t="s">
         <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4672,16 +4623,16 @@
         <v>20330051920373</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -4692,7 +4643,7 @@
         <v>20330051920388</v>
       </c>
       <c r="B19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="s">
         <v>37</v>
@@ -4701,7 +4652,7 @@
         <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -4712,7 +4663,7 @@
         <v>20330051920388</v>
       </c>
       <c r="B20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
         <v>37</v>
@@ -4721,7 +4672,7 @@
         <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -4762,16 +4713,16 @@
         <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4782,16 +4733,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C3" t="s">
         <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4805,13 +4756,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4825,13 +4776,13 @@
         <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4845,13 +4796,13 @@
         <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4868,10 +4819,10 @@
         <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4885,13 +4836,13 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4905,10 +4856,10 @@
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E9" t="s">
         <v>291</v>
@@ -4925,13 +4876,13 @@
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4948,10 +4899,10 @@
         <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4962,16 +4913,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4982,16 +4933,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5008,10 +4959,10 @@
         <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5028,10 +4979,10 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5044,7 +4995,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5078,10 +5029,10 @@
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -5092,19 +5043,19 @@
         <v>20330051920286</v>
       </c>
       <c r="B3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E3" t="s">
         <v>291</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5112,19 +5063,19 @@
         <v>20330051920286</v>
       </c>
       <c r="B4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5138,10 +5089,10 @@
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -5158,10 +5109,10 @@
         <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -5178,10 +5129,10 @@
         <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5198,10 +5149,10 @@
         <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -5215,13 +5166,13 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -5238,13 +5189,13 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5258,13 +5209,13 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E11" t="s">
         <v>291</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5278,10 +5229,10 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -5298,10 +5249,10 @@
         <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -5318,10 +5269,10 @@
         <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5341,7 +5292,7 @@
         <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -5349,16 +5300,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920312</v>
+        <v>20330051920311</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>379</v>
+        <v>196</v>
       </c>
       <c r="E16" t="s">
         <v>292</v>
@@ -5369,21 +5320,41 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920394</v>
+        <v>20330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="D17" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E17" t="s">
         <v>291</v>
       </c>
       <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>20330051920394</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" t="s">
+        <v>379</v>
+      </c>
+      <c r="E18" t="s">
+        <v>290</v>
+      </c>
+      <c r="F18">
         <v>-1</v>
       </c>
     </row>
@@ -5422,13 +5393,13 @@
         <v>22330051920180</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -5445,10 +5416,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
@@ -5462,19 +5433,19 @@
         <v>22330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5482,19 +5453,19 @@
         <v>22330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5502,13 +5473,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
@@ -5522,13 +5493,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E7" t="s">
         <v>76</v>
@@ -5545,10 +5516,10 @@
         <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E8" t="s">
         <v>76</v>
@@ -5565,13 +5536,13 @@
         <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5585,13 +5556,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5602,13 +5573,13 @@
         <v>22330051920358</v>
       </c>
       <c r="B11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -5622,13 +5593,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
@@ -5645,10 +5616,10 @@
         <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -5665,10 +5636,10 @@
         <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E14" t="s">
         <v>76</v>
@@ -5682,7 +5653,7 @@
         <v>22330051920390</v>
       </c>
       <c r="B15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C15" t="s">
         <v>65</v>
@@ -5691,10 +5662,10 @@
         <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -5702,7 +5673,7 @@
         <v>22330051920390</v>
       </c>
       <c r="B16" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C16" t="s">
         <v>65</v>
@@ -5711,10 +5682,10 @@
         <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5761,10 +5732,10 @@
         <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5781,10 +5752,10 @@
         <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5961,7 +5932,7 @@
         <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5981,7 +5952,7 @@
         <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6028,7 +5999,7 @@
         <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E2" t="s">
         <v>76</v>
@@ -6048,13 +6019,13 @@
         <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6068,13 +6039,13 @@
         <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6082,13 +6053,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E5" t="s">
         <v>76</v>
@@ -6108,7 +6079,7 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -6122,13 +6093,13 @@
         <v>22330051920221</v>
       </c>
       <c r="B7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E7" t="s">
         <v>52</v>
@@ -6148,7 +6119,7 @@
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
         <v>76</v>
@@ -6162,13 +6133,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E9" t="s">
         <v>76</v>
@@ -6182,13 +6153,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
@@ -6202,13 +6173,13 @@
         <v>22330051920229</v>
       </c>
       <c r="B11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C11" t="s">
         <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -6222,19 +6193,19 @@
         <v>22330051920362</v>
       </c>
       <c r="B12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C12" t="s">
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6242,19 +6213,19 @@
         <v>22330051920362</v>
       </c>
       <c r="B13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C13" t="s">
         <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6262,7 +6233,7 @@
         <v>22330051920393</v>
       </c>
       <c r="B14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C14" t="s">
         <v>212</v>
@@ -6302,13 +6273,13 @@
         <v>22330051920421</v>
       </c>
       <c r="B16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E16" t="s">
         <v>52</v>
@@ -6324,7 +6295,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6355,10 +6326,10 @@
         <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -6375,10 +6346,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -6392,13 +6363,13 @@
         <v>22330051920233</v>
       </c>
       <c r="B4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
@@ -6409,39 +6380,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920236</v>
+        <v>22330051920243</v>
       </c>
       <c r="B5" t="s">
-        <v>415</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920236</v>
+        <v>22330051920256</v>
       </c>
       <c r="B6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>418</v>
       </c>
       <c r="D6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6449,19 +6420,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920243</v>
+        <v>22330051920366</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6469,81 +6440,41 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920256</v>
+        <v>22330051920366</v>
       </c>
       <c r="B8" t="s">
-        <v>416</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>420</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920366</v>
+        <v>22330051920368</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920366</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>427</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920368</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>428</v>
-      </c>
-      <c r="E11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -6585,10 +6516,10 @@
         <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E2" t="s">
         <v>52</v>
@@ -6602,13 +6533,13 @@
         <v>22330051920261</v>
       </c>
       <c r="B3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C3" t="s">
         <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
@@ -6622,13 +6553,13 @@
         <v>22330051920261</v>
       </c>
       <c r="B4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C4" t="s">
         <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E4" t="s">
         <v>76</v>
@@ -6645,10 +6576,10 @@
         <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E5" t="s">
         <v>52</v>
@@ -6668,7 +6599,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
@@ -6685,10 +6616,10 @@
         <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E7" t="s">
         <v>52</v>
@@ -6708,7 +6639,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E8" t="s">
         <v>52</v>
@@ -6725,10 +6656,10 @@
         <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D9" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E9" t="s">
         <v>52</v>
@@ -6745,10 +6676,10 @@
         <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D10" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E10" t="s">
         <v>76</v>
@@ -6762,13 +6693,13 @@
         <v>22330051920288</v>
       </c>
       <c r="B11" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C11" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
@@ -6788,13 +6719,13 @@
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6808,13 +6739,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6825,7 +6756,7 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -6848,7 +6779,7 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -6892,13 +6823,13 @@
         <v>22330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -6918,7 +6849,7 @@
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E3" t="s">
         <v>52</v>
@@ -6932,13 +6863,13 @@
         <v>22330051920293</v>
       </c>
       <c r="B4" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C4" t="s">
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
@@ -6958,7 +6889,7 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E5" t="s">
         <v>52</v>
@@ -6975,10 +6906,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E6" t="s">
         <v>30</v>
@@ -6992,13 +6923,13 @@
         <v>22330051920298</v>
       </c>
       <c r="B7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C7" t="s">
         <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E7" t="s">
         <v>52</v>
@@ -7018,7 +6949,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E8" t="s">
         <v>76</v>
@@ -7038,13 +6969,13 @@
         <v>177</v>
       </c>
       <c r="D9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7058,13 +6989,13 @@
         <v>177</v>
       </c>
       <c r="D10" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7075,10 +7006,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D11" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -7092,7 +7023,7 @@
         <v>22330051920308</v>
       </c>
       <c r="B12" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
@@ -7112,13 +7043,13 @@
         <v>22330051920309</v>
       </c>
       <c r="B13" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -7132,10 +7063,10 @@
         <v>22330051920311</v>
       </c>
       <c r="B14" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E14" t="s">
         <v>30</v>
@@ -7149,13 +7080,13 @@
         <v>22330051920312</v>
       </c>
       <c r="B15" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C15" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D15" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E15" t="s">
         <v>30</v>
@@ -7169,13 +7100,13 @@
         <v>22330051920312</v>
       </c>
       <c r="B16" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C16" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D16" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -7192,10 +7123,10 @@
         <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D17" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E17" t="s">
         <v>76</v>
@@ -7209,13 +7140,13 @@
         <v>22330051920315</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C18" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D18" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
@@ -7229,13 +7160,13 @@
         <v>22330051920315</v>
       </c>
       <c r="B19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C19" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D19" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
@@ -7249,10 +7180,10 @@
         <v>22330051920360</v>
       </c>
       <c r="B20" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C20" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D20" t="s">
         <v>131</v>
@@ -7269,19 +7200,19 @@
         <v>22330051920397</v>
       </c>
       <c r="B21" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C21" t="s">
         <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7289,19 +7220,19 @@
         <v>22330051920397</v>
       </c>
       <c r="B22" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C22" t="s">
         <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7312,7 +7243,7 @@
         <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D23" t="s">
         <v>75</v>
@@ -7329,13 +7260,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B24" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C24" t="s">
         <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
@@ -7399,16 +7330,16 @@
         <v>20330051920005</v>
       </c>
       <c r="B2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C2" t="s">
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7419,16 +7350,16 @@
         <v>20330051920005</v>
       </c>
       <c r="B3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7442,13 +7373,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D4" t="s">
         <v>477</v>
       </c>
-      <c r="D4" t="s">
-        <v>480</v>
-      </c>
       <c r="E4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7459,16 +7390,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -7479,13 +7410,13 @@
         <v>20330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
         <v>162</v>
@@ -7505,7 +7436,7 @@
         <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E7" t="s">
         <v>159</v>
@@ -7519,13 +7450,13 @@
         <v>21330051920028</v>
       </c>
       <c r="B8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C8" t="s">
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E8" t="s">
         <v>161</v>
@@ -7545,7 +7476,7 @@
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E9" t="s">
         <v>160</v>
@@ -7559,13 +7490,13 @@
         <v>21330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C10" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D10" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E10" t="s">
         <v>162</v>
@@ -7579,13 +7510,13 @@
         <v>21330051920393</v>
       </c>
       <c r="B11" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C11" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D11" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E11" t="s">
         <v>159</v>
@@ -7632,7 +7563,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D2" t="s">
         <v>106</v>
@@ -7652,13 +7583,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D3" t="s">
         <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7675,7 +7606,7 @@
         <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E4" t="s">
         <v>159</v>
@@ -7718,7 +7649,7 @@
         <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>271</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7738,7 +7669,7 @@
         <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>159</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7752,10 +7683,10 @@
         <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D8" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E8" t="s">
         <v>160</v>
@@ -7772,16 +7703,16 @@
         <v>95</v>
       </c>
       <c r="C9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D9" t="s">
         <v>487</v>
-      </c>
-      <c r="D9" t="s">
-        <v>490</v>
       </c>
       <c r="E9" t="s">
         <v>271</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7792,16 +7723,16 @@
         <v>95</v>
       </c>
       <c r="C10" t="s">
+        <v>484</v>
+      </c>
+      <c r="D10" t="s">
         <v>487</v>
       </c>
-      <c r="D10" t="s">
-        <v>490</v>
-      </c>
       <c r="E10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7842,10 +7773,10 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E2" t="s">
         <v>160</v>
@@ -7859,7 +7790,7 @@
         <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C3" t="s">
         <v>180</v>
@@ -7868,7 +7799,7 @@
         <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -7879,16 +7810,16 @@
         <v>21330051920111</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -7899,19 +7830,19 @@
         <v>21330051920113</v>
       </c>
       <c r="B5" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7919,19 +7850,19 @@
         <v>21330051920113</v>
       </c>
       <c r="B6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E6" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7939,16 +7870,16 @@
         <v>21330051920117</v>
       </c>
       <c r="B7" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7959,16 +7890,16 @@
         <v>21330051920117</v>
       </c>
       <c r="B8" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D8" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7985,7 +7916,7 @@
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E9" t="s">
         <v>207</v>
@@ -8005,10 +7936,10 @@
         <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -8025,10 +7956,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E11" t="s">
-        <v>272</v>
+        <v>207</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -8045,10 +7976,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E12" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -8059,16 +7990,16 @@
         <v>21330051920126</v>
       </c>
       <c r="B13" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C13" t="s">
         <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E13" t="s">
-        <v>272</v>
+        <v>207</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -8079,16 +8010,16 @@
         <v>21330051920126</v>
       </c>
       <c r="B14" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C14" t="s">
         <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E14" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -8099,13 +8030,13 @@
         <v>21330051920130</v>
       </c>
       <c r="B15" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D15" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E15" t="s">
         <v>160</v>
@@ -8149,16 +8080,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C2" t="s">
         <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8169,13 +8100,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C3" t="s">
         <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E3" t="s">
         <v>159</v>
@@ -8192,13 +8123,13 @@
         <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D4" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8212,10 +8143,10 @@
         <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E5" t="s">
         <v>159</v>
@@ -8265,7 +8196,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E2" t="s">
         <v>160</v>
@@ -8282,13 +8213,13 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8302,13 +8233,13 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D4" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8352,13 +8283,13 @@
         <v>121</v>
       </c>
       <c r="C2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D2" t="s">
         <v>509</v>
       </c>
-      <c r="D2" t="s">
-        <v>512</v>
-      </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -8375,10 +8306,10 @@
         <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -8395,10 +8326,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -8409,16 +8340,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8432,13 +8363,13 @@
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -8452,13 +8383,13 @@
         <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -8472,13 +8403,13 @@
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D8" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -8492,13 +8423,13 @@
         <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D9" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -8509,16 +8440,16 @@
         <v>20330051920087</v>
       </c>
       <c r="B10" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8529,16 +8460,16 @@
         <v>20330051920087</v>
       </c>
       <c r="B11" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -8552,13 +8483,13 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -8572,13 +8503,13 @@
         <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D13" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8768,7 +8699,7 @@
         <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8788,7 +8719,7 @@
         <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8889,16 +8820,16 @@
         <v>19330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D2" t="s">
         <v>523</v>
       </c>
-      <c r="D2" t="s">
-        <v>526</v>
-      </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -8909,19 +8840,19 @@
         <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C3" t="s">
         <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E3" t="s">
         <v>291</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8929,19 +8860,19 @@
         <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C4" t="s">
         <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8952,13 +8883,13 @@
         <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -8975,13 +8906,13 @@
         <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E6" t="s">
         <v>291</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8995,13 +8926,13 @@
         <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9009,19 +8940,19 @@
         <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D8" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9029,19 +8960,19 @@
         <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D9" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E9" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9049,16 +8980,16 @@
         <v>20330051920197</v>
       </c>
       <c r="B10" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C10" t="s">
         <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -9072,13 +9003,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D11" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -9095,10 +9026,10 @@
         <v>127</v>
       </c>
       <c r="D12" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -9115,10 +9046,10 @@
         <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -9135,10 +9066,10 @@
         <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -9155,10 +9086,10 @@
         <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -9172,13 +9103,13 @@
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D16" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -9192,13 +9123,13 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D17" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -9215,13 +9146,13 @@
         <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -9235,13 +9166,13 @@
         <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E19" t="s">
         <v>291</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -9255,10 +9186,10 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -9272,13 +9203,13 @@
         <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D21" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -9289,19 +9220,19 @@
         <v>20330051920218</v>
       </c>
       <c r="B22" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C22" t="s">
         <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E22" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -9309,19 +9240,19 @@
         <v>20330051920218</v>
       </c>
       <c r="B23" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C23" t="s">
         <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E23" t="s">
         <v>291</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -9359,16 +9290,16 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C2" t="s">
         <v>541</v>
       </c>
-      <c r="C2" t="s">
-        <v>544</v>
-      </c>
       <c r="D2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9379,16 +9310,16 @@
         <v>19330051920425</v>
       </c>
       <c r="B3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9399,16 +9330,16 @@
         <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C4" t="s">
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9425,10 +9356,10 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -9445,10 +9376,10 @@
         <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9462,16 +9393,16 @@
         <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E7" t="s">
         <v>291</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9482,16 +9413,16 @@
         <v>179</v>
       </c>
       <c r="C8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D8" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -9535,10 +9466,10 @@
         <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -9549,19 +9480,19 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C3" t="s">
         <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E3" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -9569,19 +9500,19 @@
         <v>19330051920360</v>
       </c>
       <c r="B4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C4" t="s">
         <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E4" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9589,16 +9520,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D5" t="s">
         <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -9609,16 +9540,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D6" t="s">
         <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -9629,16 +9560,16 @@
         <v>19330051920387</v>
       </c>
       <c r="B7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C7" t="s">
         <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -9652,13 +9583,13 @@
         <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D8" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E8" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -9672,13 +9603,13 @@
         <v>128</v>
       </c>
       <c r="C9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D9" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E9" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9692,13 +9623,13 @@
         <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D10" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E10" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -9712,13 +9643,13 @@
         <v>145</v>
       </c>
       <c r="C11" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D11" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -9729,16 +9660,16 @@
         <v>20330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C12" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -9752,13 +9683,13 @@
         <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E13" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -9772,13 +9703,13 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D14" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -9795,10 +9726,10 @@
         <v>201</v>
       </c>
       <c r="D15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E15" t="s">
-        <v>292</v>
+        <v>582</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -9815,10 +9746,10 @@
         <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E16" t="s">
-        <v>584</v>
+        <v>291</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -9835,10 +9766,10 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -9855,10 +9786,10 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E18" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -9875,10 +9806,10 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E19" t="s">
-        <v>292</v>
+        <v>582</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -9895,10 +9826,10 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E20" t="s">
-        <v>584</v>
+        <v>291</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -9912,13 +9843,13 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D21" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E21" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -9929,16 +9860,16 @@
         <v>20330051920131</v>
       </c>
       <c r="B22" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C22" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D22" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -9949,16 +9880,16 @@
         <v>20330051920131</v>
       </c>
       <c r="B23" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C23" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D23" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E23" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -9972,13 +9903,13 @@
         <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D24" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E24" t="s">
-        <v>292</v>
+        <v>582</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -9992,13 +9923,13 @@
         <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D25" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E25" t="s">
-        <v>584</v>
+        <v>291</v>
       </c>
       <c r="F25">
         <v>-1</v>
@@ -10009,16 +9940,16 @@
         <v>20330051920137</v>
       </c>
       <c r="B26" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C26" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D26" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E26" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F26">
         <v>-1</v>
@@ -10029,16 +9960,16 @@
         <v>20330051920137</v>
       </c>
       <c r="B27" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C27" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D27" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E27" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F27">
         <v>-1</v>
@@ -10052,13 +9983,13 @@
         <v>170</v>
       </c>
       <c r="C28" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D28" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E28" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -10069,7 +10000,7 @@
         <v>20330051920140</v>
       </c>
       <c r="B29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C29" t="s">
         <v>33</v>
@@ -10078,7 +10009,7 @@
         <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>292</v>
+        <v>582</v>
       </c>
       <c r="F29">
         <v>-1</v>
@@ -10089,7 +10020,7 @@
         <v>20330051920140</v>
       </c>
       <c r="B30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -10098,7 +10029,7 @@
         <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>584</v>
+        <v>291</v>
       </c>
       <c r="F30">
         <v>-1</v>
@@ -10109,16 +10040,16 @@
         <v>20330051920141</v>
       </c>
       <c r="B31" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C31" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D31" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E31" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F31">
         <v>-1</v>
@@ -10129,16 +10060,16 @@
         <v>20330051920141</v>
       </c>
       <c r="B32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C32" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D32" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F32">
         <v>-1</v>
@@ -10149,16 +10080,16 @@
         <v>20330051920144</v>
       </c>
       <c r="B33" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C33" t="s">
         <v>180</v>
       </c>
       <c r="D33" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E33" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F33">
         <v>-1</v>
@@ -10172,13 +10103,13 @@
         <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D34" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E34" t="s">
-        <v>292</v>
+        <v>582</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -10192,13 +10123,13 @@
         <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D35" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E35" t="s">
-        <v>584</v>
+        <v>291</v>
       </c>
       <c r="F35">
         <v>-1</v>
@@ -10209,13 +10140,13 @@
         <v>20330051920153</v>
       </c>
       <c r="B36" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D36" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F36">
         <v>-1</v>
@@ -10226,13 +10157,13 @@
         <v>20330051920153</v>
       </c>
       <c r="B37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D37" t="s">
+        <v>579</v>
+      </c>
+      <c r="E37" t="s">
         <v>582</v>
-      </c>
-      <c r="E37" t="s">
-        <v>584</v>
       </c>
       <c r="F37">
         <v>-1</v>
@@ -10243,16 +10174,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B38" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C38" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D38" t="s">
         <v>106</v>
       </c>
       <c r="E38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F38">
         <v>-1</v>
@@ -10263,16 +10194,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C39" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D39" t="s">
         <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F39">
         <v>-1</v>
@@ -10283,16 +10214,16 @@
         <v>20330051920389</v>
       </c>
       <c r="B40" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D40" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E40" t="s">
-        <v>292</v>
+        <v>582</v>
       </c>
       <c r="F40">
         <v>-1</v>
@@ -10303,16 +10234,16 @@
         <v>20330051920389</v>
       </c>
       <c r="B41" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D41" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E41" t="s">
-        <v>584</v>
+        <v>291</v>
       </c>
       <c r="F41">
         <v>-1</v>
@@ -10356,13 +10287,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D2" t="s">
         <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -10376,13 +10307,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D3" t="s">
         <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10396,13 +10327,13 @@
         <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D4" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10419,10 +10350,10 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -10439,10 +10370,10 @@
         <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -10459,10 +10390,10 @@
         <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10479,10 +10410,10 @@
         <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -10493,19 +10424,19 @@
         <v>20330051920329</v>
       </c>
       <c r="B9" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D9" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E9" t="s">
         <v>291</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -10513,19 +10444,19 @@
         <v>20330051920329</v>
       </c>
       <c r="B10" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D10" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -10533,19 +10464,19 @@
         <v>20330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C11" t="s">
         <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E11" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -10553,19 +10484,19 @@
         <v>20330051920330</v>
       </c>
       <c r="B12" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C12" t="s">
         <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E12" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -10579,10 +10510,10 @@
         <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -10596,13 +10527,13 @@
         <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D14" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -10613,16 +10544,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B15" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C15" t="s">
         <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -10633,16 +10564,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B16" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C16" t="s">
         <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -10732,7 +10663,7 @@
         <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10752,7 +10683,7 @@
         <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10882,7 +10813,7 @@
         <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10902,7 +10833,7 @@
         <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10982,7 +10913,7 @@
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -11002,7 +10933,7 @@
         <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -11142,7 +11073,7 @@
         <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -11162,7 +11093,7 @@
         <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -11272,7 +11203,7 @@
         <v>130</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -11292,7 +11223,7 @@
         <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -11352,7 +11283,7 @@
         <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -11372,7 +11303,7 @@
         <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -11412,7 +11343,7 @@
         <v>135</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -11432,7 +11363,7 @@
         <v>135</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -11502,7 +11433,7 @@
         <v>151</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -11522,7 +11453,7 @@
         <v>151</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -11642,7 +11573,7 @@
         <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -11662,7 +11593,7 @@
         <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -11702,7 +11633,7 @@
         <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -11722,7 +11653,7 @@
         <v>157</v>
       </c>
       <c r="E14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -12009,7 +11940,7 @@
         <v>192</v>
       </c>
       <c r="E13" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -12029,7 +11960,7 @@
         <v>192</v>
       </c>
       <c r="E14" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="F14">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="609">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -933,12 +933,12 @@
     <t>ANDRES NOEL</t>
   </si>
   <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
     <t>CÁLCULO INTEGRAL</t>
   </si>
   <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
     <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
   </si>
   <si>
@@ -963,708 +963,723 @@
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>JOSSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>LISBETH ESMERALDA</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSE ISAIAS</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>OMAR ALDAIR</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>ANGELA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>CONSTRUYE BASES DE DATOS PARA APLICACIONES WEB</t>
+  </si>
+  <si>
+    <t>DESARROLLA APLICACIONES WEB CON CONEXIÓN A BASES DE DATOS</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>CAZARES</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>ABDIEL NOE</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>CHONKOA</t>
+  </si>
+  <si>
+    <t>RONZON</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>CRISTIAN LEOBARDO</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ARAWY</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>MARIA ANGELES</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>UREÑA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>GERMAN</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>JULISSA</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>AYALA</t>
+  </si>
+  <si>
+    <t>CANTE</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VALDEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>TOMAS RAFAEL</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ISAI</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>MOISES ALBERTO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>XOCHITL JOSELINE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
   </si>
   <si>
     <t>ITZEL</t>
   </si>
   <si>
-    <t>LISBETH ESMERALDA</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>CONSTRUYE BASES DE DATOS PARA APLICACIONES WEB</t>
-  </si>
-  <si>
-    <t>DESARROLLA APLICACIONES WEB CON CONEXIÓN A BASES DE DATOS</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>CAZARES</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>RONZON</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ARAWY</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>GERMAN</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>AYALA</t>
-  </si>
-  <si>
-    <t>CANTE</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>TOMAS RAFAEL</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAVIER</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>XOCHITL JOSELINE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
     <t>JULIO CESAR</t>
   </si>
   <si>
@@ -1818,7 +1833,7 @@
     <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
   </si>
   <si>
-    <t>NAJERA</t>
+    <t>CANTELLAN</t>
   </si>
   <si>
     <t>OCAÑA</t>
@@ -1827,7 +1842,13 @@
     <t>IBAÑEZ</t>
   </si>
   <si>
+    <t>LARA</t>
+  </si>
+  <si>
     <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
     <t>SURISADAY</t>
@@ -2756,7 +2777,7 @@
         <v>224</v>
       </c>
       <c r="E8" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2776,7 +2797,7 @@
         <v>224</v>
       </c>
       <c r="E9" t="s">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2816,7 +2837,7 @@
         <v>226</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2836,7 +2857,7 @@
         <v>226</v>
       </c>
       <c r="E12" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2926,7 +2947,7 @@
         <v>241</v>
       </c>
       <c r="E2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2946,7 +2967,7 @@
         <v>241</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3086,7 +3107,7 @@
         <v>247</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3106,7 +3127,7 @@
         <v>247</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3586,7 +3607,7 @@
         <v>285</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3606,7 +3627,7 @@
         <v>286</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3626,7 +3647,7 @@
         <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3646,7 +3667,7 @@
         <v>136</v>
       </c>
       <c r="E7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3686,7 +3707,7 @@
         <v>287</v>
       </c>
       <c r="E9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3706,7 +3727,7 @@
         <v>288</v>
       </c>
       <c r="E10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3726,7 +3747,7 @@
         <v>288</v>
       </c>
       <c r="E11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3746,7 +3767,7 @@
         <v>289</v>
       </c>
       <c r="E12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3766,7 +3787,7 @@
         <v>290</v>
       </c>
       <c r="E13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3786,7 +3807,7 @@
         <v>291</v>
       </c>
       <c r="E14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3806,7 +3827,7 @@
         <v>292</v>
       </c>
       <c r="E15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -3826,7 +3847,7 @@
         <v>293</v>
       </c>
       <c r="E16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3846,7 +3867,7 @@
         <v>294</v>
       </c>
       <c r="E17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3859,7 +3880,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3893,10 +3914,10 @@
         <v>303</v>
       </c>
       <c r="D2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -3913,10 +3934,10 @@
         <v>304</v>
       </c>
       <c r="D3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3933,7 +3954,7 @@
         <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E4" t="s">
         <v>295</v>
@@ -3953,7 +3974,7 @@
         <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E5" t="s">
         <v>296</v>
@@ -3976,7 +3997,7 @@
         <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3996,7 +4017,7 @@
         <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -4004,19 +4025,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920241</v>
+        <v>20330051920243</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4024,19 +4045,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920241</v>
+        <v>20330051920244</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>301</v>
       </c>
       <c r="C9" t="s">
-        <v>305</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
         <v>310</v>
       </c>
       <c r="E9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4044,19 +4065,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920243</v>
+        <v>20330051920244</v>
       </c>
       <c r="B10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4064,16 +4085,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B11" t="s">
-        <v>301</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
-        <v>234</v>
+        <v>305</v>
       </c>
       <c r="D11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E11" t="s">
         <v>295</v>
@@ -4084,16 +4105,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B12" t="s">
-        <v>301</v>
+        <v>239</v>
       </c>
       <c r="C12" t="s">
-        <v>234</v>
+        <v>305</v>
       </c>
       <c r="D12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E12" t="s">
         <v>296</v>
@@ -4104,61 +4125,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920251</v>
+        <v>20330051920374</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
       <c r="C13" t="s">
-        <v>306</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920251</v>
-      </c>
-      <c r="B14" t="s">
-        <v>239</v>
-      </c>
-      <c r="C14" t="s">
-        <v>306</v>
-      </c>
-      <c r="D14" t="s">
-        <v>313</v>
-      </c>
-      <c r="E14" t="s">
-        <v>296</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920374</v>
-      </c>
-      <c r="B15" t="s">
-        <v>302</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s">
-        <v>314</v>
-      </c>
-      <c r="E15" t="s">
-        <v>295</v>
-      </c>
-      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -4169,7 +4150,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4203,7 +4184,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E2" t="s">
         <v>297</v>
@@ -4217,39 +4198,39 @@
         <v>20330051920336</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4257,13 +4238,13 @@
         <v>20330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E5" t="s">
         <v>297</v>
@@ -4274,42 +4255,42 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920337</v>
+        <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920340</v>
+        <v>20330051920341</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4320,13 +4301,13 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4340,10 +4321,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E9" t="s">
         <v>297</v>
@@ -4363,7 +4344,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E10" t="s">
         <v>297</v>
@@ -4374,39 +4355,39 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920349</v>
+        <v>20330051920347</v>
       </c>
       <c r="B11" t="s">
-        <v>319</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920354</v>
+        <v>20330051920349</v>
       </c>
       <c r="B12" t="s">
-        <v>257</v>
+        <v>317</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4414,19 +4395,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920356</v>
+        <v>20330051920349</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>317</v>
       </c>
       <c r="C13" t="s">
-        <v>325</v>
+        <v>145</v>
       </c>
       <c r="D13" t="s">
-        <v>207</v>
+        <v>331</v>
       </c>
       <c r="E13" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -4434,22 +4415,22 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920356</v>
+        <v>20330051920354</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="C14" t="s">
-        <v>325</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>332</v>
       </c>
       <c r="E14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4463,7 +4444,7 @@
         <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E15" t="s">
         <v>297</v>
@@ -4474,19 +4455,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920383</v>
+        <v>20330051920381</v>
       </c>
       <c r="B16" t="s">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E16" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4497,19 +4478,39 @@
         <v>20330051920383</v>
       </c>
       <c r="B17" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C17" t="s">
         <v>100</v>
       </c>
       <c r="D17" t="s">
+        <v>334</v>
+      </c>
+      <c r="E17" t="s">
+        <v>336</v>
+      </c>
+      <c r="F17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>20330051920383</v>
+      </c>
+      <c r="B18" t="s">
+        <v>318</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>334</v>
+      </c>
+      <c r="E18" t="s">
         <v>335</v>
       </c>
-      <c r="E17" t="s">
-        <v>337</v>
-      </c>
-      <c r="F17">
-        <v>-1</v>
+      <c r="F18">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4553,7 +4554,7 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E2" t="s">
         <v>297</v>
@@ -4567,13 +4568,13 @@
         <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E3" t="s">
         <v>297</v>
@@ -4587,16 +4588,16 @@
         <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4613,7 +4614,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E5" t="s">
         <v>297</v>
@@ -4633,10 +4634,10 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4653,10 +4654,10 @@
         <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4673,7 +4674,7 @@
         <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E8" t="s">
         <v>297</v>
@@ -4687,16 +4688,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4707,13 +4708,13 @@
         <v>20330051920168</v>
       </c>
       <c r="B10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E10" t="s">
         <v>297</v>
@@ -4727,19 +4728,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
         <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4747,19 +4748,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C12" t="s">
         <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4767,16 +4768,16 @@
         <v>20330051920178</v>
       </c>
       <c r="B13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C13" t="s">
         <v>183</v>
       </c>
       <c r="D13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -4787,16 +4788,16 @@
         <v>20330051920178</v>
       </c>
       <c r="B14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C14" t="s">
         <v>183</v>
       </c>
       <c r="D14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -4813,7 +4814,7 @@
         <v>152</v>
       </c>
       <c r="D15" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E15" t="s">
         <v>297</v>
@@ -4830,16 +4831,16 @@
         <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D16" t="s">
         <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4850,16 +4851,16 @@
         <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D17" t="s">
         <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4873,7 +4874,7 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E18" t="s">
         <v>297</v>
@@ -4890,16 +4891,16 @@
         <v>258</v>
       </c>
       <c r="C19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D19" t="s">
         <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4910,16 +4911,16 @@
         <v>258</v>
       </c>
       <c r="C20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D20" t="s">
         <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -4957,16 +4958,16 @@
         <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4977,16 +4978,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C3" t="s">
         <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5000,13 +5001,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5020,13 +5021,13 @@
         <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E5" t="s">
-        <v>373</v>
+        <v>313</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5040,13 +5041,13 @@
         <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5063,10 +5064,10 @@
         <v>148</v>
       </c>
       <c r="D7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5080,13 +5081,13 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5100,13 +5101,13 @@
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5120,13 +5121,13 @@
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5143,10 +5144,10 @@
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5157,16 +5158,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E12" t="s">
-        <v>373</v>
+        <v>313</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5177,16 +5178,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E13" t="s">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5203,10 +5204,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5223,10 +5224,10 @@
         <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5273,10 +5274,10 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -5287,19 +5288,19 @@
         <v>20330051920286</v>
       </c>
       <c r="B3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C3" t="s">
         <v>261</v>
       </c>
       <c r="D3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E3" t="s">
         <v>295</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5307,19 +5308,19 @@
         <v>20330051920286</v>
       </c>
       <c r="B4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="s">
         <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E4" t="s">
         <v>296</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5333,7 +5334,7 @@
         <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E5" t="s">
         <v>297</v>
@@ -5353,10 +5354,10 @@
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -5373,10 +5374,10 @@
         <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5393,10 +5394,10 @@
         <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -5410,13 +5411,13 @@
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -5433,13 +5434,13 @@
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E10" t="s">
         <v>295</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5453,13 +5454,13 @@
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E11" t="s">
         <v>296</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5473,10 +5474,10 @@
         <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -5493,13 +5494,13 @@
         <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E13" t="s">
         <v>295</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5513,13 +5514,13 @@
         <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E14" t="s">
         <v>296</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -5556,7 +5557,7 @@
         <v>200</v>
       </c>
       <c r="E16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -5573,10 +5574,10 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5593,10 +5594,10 @@
         <v>183</v>
       </c>
       <c r="D18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -5643,7 +5644,7 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E2" t="s">
         <v>43</v>
@@ -5660,10 +5661,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E3" t="s">
         <v>41</v>
@@ -5677,13 +5678,13 @@
         <v>22330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E4" t="s">
         <v>44</v>
@@ -5697,13 +5698,13 @@
         <v>22330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E5" t="s">
         <v>123</v>
@@ -5717,13 +5718,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E6" t="s">
         <v>41</v>
@@ -5737,13 +5738,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E7" t="s">
         <v>44</v>
@@ -5760,10 +5761,10 @@
         <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E8" t="s">
         <v>44</v>
@@ -5780,10 +5781,10 @@
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E9" t="s">
         <v>41</v>
@@ -5800,10 +5801,10 @@
         <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E10" t="s">
         <v>44</v>
@@ -5817,13 +5818,13 @@
         <v>22330051920358</v>
       </c>
       <c r="B11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E11" t="s">
         <v>41</v>
@@ -5837,13 +5838,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E12" t="s">
         <v>43</v>
@@ -5863,7 +5864,7 @@
         <v>301</v>
       </c>
       <c r="D13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E13" t="s">
         <v>41</v>
@@ -5883,7 +5884,7 @@
         <v>301</v>
       </c>
       <c r="D14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E14" t="s">
         <v>44</v>
@@ -5897,7 +5898,7 @@
         <v>22330051920390</v>
       </c>
       <c r="B15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C15" t="s">
         <v>72</v>
@@ -5917,7 +5918,7 @@
         <v>22330051920390</v>
       </c>
       <c r="B16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C16" t="s">
         <v>72</v>
@@ -6203,7 +6204,7 @@
         <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E2" t="s">
         <v>44</v>
@@ -6223,7 +6224,7 @@
         <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E3" t="s">
         <v>44</v>
@@ -6243,7 +6244,7 @@
         <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -6257,13 +6258,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C5" t="s">
         <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E5" t="s">
         <v>44</v>
@@ -6277,13 +6278,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C6" t="s">
         <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
@@ -6303,7 +6304,7 @@
         <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E7" t="s">
         <v>42</v>
@@ -6323,7 +6324,7 @@
         <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E8" t="s">
         <v>44</v>
@@ -6337,13 +6338,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E9" t="s">
         <v>44</v>
@@ -6357,13 +6358,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
@@ -6377,13 +6378,13 @@
         <v>22330051920229</v>
       </c>
       <c r="B11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C11" t="s">
         <v>128</v>
       </c>
       <c r="D11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E11" t="s">
         <v>42</v>
@@ -6403,7 +6404,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E12" t="s">
         <v>62</v>
@@ -6417,7 +6418,7 @@
         <v>22330051920393</v>
       </c>
       <c r="B13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C13" t="s">
         <v>215</v>
@@ -6457,13 +6458,13 @@
         <v>22330051920421</v>
       </c>
       <c r="B15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E15" t="s">
         <v>62</v>
@@ -6510,10 +6511,10 @@
         <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E2" t="s">
         <v>43</v>
@@ -6530,10 +6531,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E3" t="s">
         <v>42</v>
@@ -6547,13 +6548,13 @@
         <v>22330051920238</v>
       </c>
       <c r="B4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E4" t="s">
         <v>62</v>
@@ -6570,7 +6571,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D5" t="s">
         <v>76</v>
@@ -6593,7 +6594,7 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>
@@ -6607,13 +6608,13 @@
         <v>22330051920256</v>
       </c>
       <c r="B7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
@@ -6633,7 +6634,7 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E8" t="s">
         <v>62</v>
@@ -6653,7 +6654,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E9" t="s">
         <v>44</v>
@@ -6673,7 +6674,7 @@
         <v>233</v>
       </c>
       <c r="D10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E10" t="s">
         <v>62</v>
@@ -6720,7 +6721,7 @@
         <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D2" t="s">
         <v>286</v>
@@ -6734,56 +6735,56 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920261</v>
+        <v>22330051920265</v>
       </c>
       <c r="B3" t="s">
-        <v>430</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>432</v>
       </c>
       <c r="D3" t="s">
         <v>437</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920261</v>
+        <v>22330051920270</v>
       </c>
       <c r="B4" t="s">
-        <v>430</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920272</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
         <v>433</v>
       </c>
       <c r="D5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E5" t="s">
         <v>62</v>
@@ -6794,19 +6795,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920270</v>
+        <v>22330051920274</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6814,16 +6815,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920272</v>
+        <v>22330051920279</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
         <v>434</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
@@ -6834,30 +6835,30 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920274</v>
+        <v>22330051920279</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>434</v>
       </c>
       <c r="D8" t="s">
         <v>441</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920279</v>
+        <v>22330051920283</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>429</v>
       </c>
       <c r="C9" t="s">
         <v>435</v>
@@ -6866,27 +6867,27 @@
         <v>442</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920279</v>
+        <v>22330051920288</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>430</v>
       </c>
       <c r="C10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D10" t="s">
-        <v>442</v>
+        <v>381</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6894,16 +6895,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920288</v>
+        <v>22330051920402</v>
       </c>
       <c r="B11" t="s">
-        <v>431</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>436</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>382</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
         <v>41</v>
@@ -6926,64 +6927,64 @@
         <v>443</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920402</v>
+        <v>22330051920404</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="D13" t="s">
-        <v>443</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
         <v>44</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920404</v>
+        <v>22330051920405</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>444</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920404</v>
+        <v>22330051920406</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>358</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>445</v>
       </c>
       <c r="E15" t="s">
         <v>62</v>
@@ -6994,22 +6995,22 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920405</v>
+        <v>22330051920411</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7047,13 +7048,13 @@
         <v>22330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>456</v>
       </c>
       <c r="D2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E2" t="s">
         <v>42</v>
@@ -7073,7 +7074,7 @@
         <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E3" t="s">
         <v>62</v>
@@ -7093,7 +7094,7 @@
         <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E4" t="s">
         <v>42</v>
@@ -7107,13 +7108,13 @@
         <v>22330051920293</v>
       </c>
       <c r="B5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -7130,10 +7131,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D6" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>
@@ -7147,13 +7148,13 @@
         <v>22330051920298</v>
       </c>
       <c r="B7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C7" t="s">
         <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
@@ -7173,7 +7174,7 @@
         <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E8" t="s">
         <v>42</v>
@@ -7193,7 +7194,7 @@
         <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E9" t="s">
         <v>44</v>
@@ -7213,7 +7214,7 @@
         <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E10" t="s">
         <v>43</v>
@@ -7233,7 +7234,7 @@
         <v>181</v>
       </c>
       <c r="D11" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E11" t="s">
         <v>42</v>
@@ -7250,10 +7251,10 @@
         <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D12" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E12" t="s">
         <v>42</v>
@@ -7270,10 +7271,10 @@
         <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D13" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E13" t="s">
         <v>62</v>
@@ -7287,7 +7288,7 @@
         <v>22330051920308</v>
       </c>
       <c r="B14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
@@ -7296,7 +7297,7 @@
         <v>205</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -7307,7 +7308,7 @@
         <v>22330051920308</v>
       </c>
       <c r="B15" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
@@ -7316,7 +7317,7 @@
         <v>205</v>
       </c>
       <c r="E15" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -7327,13 +7328,13 @@
         <v>22330051920309</v>
       </c>
       <c r="B16" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E16" t="s">
         <v>42</v>
@@ -7347,7 +7348,7 @@
         <v>22330051920311</v>
       </c>
       <c r="B17" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D17" t="s">
         <v>285</v>
@@ -7364,13 +7365,13 @@
         <v>22330051920312</v>
       </c>
       <c r="B18" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C18" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D18" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E18" t="s">
         <v>43</v>
@@ -7384,13 +7385,13 @@
         <v>22330051920312</v>
       </c>
       <c r="B19" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C19" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D19" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E19" t="s">
         <v>42</v>
@@ -7407,10 +7408,10 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D20" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E20" t="s">
         <v>62</v>
@@ -7427,10 +7428,10 @@
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D21" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E21" t="s">
         <v>44</v>
@@ -7450,7 +7451,7 @@
         <v>436</v>
       </c>
       <c r="D22" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E22" t="s">
         <v>41</v>
@@ -7470,7 +7471,7 @@
         <v>436</v>
       </c>
       <c r="D23" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -7484,10 +7485,10 @@
         <v>22330051920360</v>
       </c>
       <c r="B24" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C24" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -7504,13 +7505,13 @@
         <v>22330051920397</v>
       </c>
       <c r="B25" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E25" t="s">
         <v>41</v>
@@ -7524,13 +7525,13 @@
         <v>22330051920397</v>
       </c>
       <c r="B26" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E26" t="s">
         <v>62</v>
@@ -7547,7 +7548,7 @@
         <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D27" t="s">
         <v>82</v>
@@ -7564,13 +7565,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B28" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C28" t="s">
         <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E28" t="s">
         <v>43</v>
@@ -7584,13 +7585,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B29" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C29" t="s">
         <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E29" t="s">
         <v>62</v>
@@ -7646,7 +7647,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7671,19 +7672,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920005</v>
+        <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
-        <v>475</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>480</v>
       </c>
       <c r="D2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7691,39 +7692,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920005</v>
+        <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>359</v>
       </c>
       <c r="D3" t="s">
-        <v>480</v>
+        <v>285</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>487</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920018</v>
+        <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>478</v>
       </c>
       <c r="C4" t="s">
-        <v>478</v>
+        <v>359</v>
       </c>
       <c r="D4" t="s">
-        <v>481</v>
+        <v>285</v>
       </c>
       <c r="E4" t="s">
-        <v>276</v>
+        <v>166</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7731,59 +7732,59 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920089</v>
+        <v>21330051920005</v>
       </c>
       <c r="B5" t="s">
-        <v>476</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>285</v>
+        <v>483</v>
       </c>
       <c r="E5" t="s">
-        <v>486</v>
+        <v>163</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920089</v>
+        <v>21330051920028</v>
       </c>
       <c r="B6" t="s">
-        <v>476</v>
+        <v>257</v>
       </c>
       <c r="C6" t="s">
-        <v>360</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
-        <v>285</v>
+        <v>484</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920005</v>
+        <v>21330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>487</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7791,39 +7792,39 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920028</v>
+        <v>21330051920195</v>
       </c>
       <c r="B8" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920195</v>
+        <v>21330051920393</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>479</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>481</v>
       </c>
       <c r="D9" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7834,38 +7835,18 @@
         <v>21330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920393</v>
-      </c>
-      <c r="B11" t="s">
-        <v>477</v>
-      </c>
-      <c r="C11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D11" t="s">
-        <v>485</v>
-      </c>
-      <c r="E11" t="s">
-        <v>163</v>
-      </c>
-      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -7907,7 +7888,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D2" t="s">
         <v>112</v>
@@ -7927,7 +7908,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D3" t="s">
         <v>112</v>
@@ -7950,7 +7931,7 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E4" t="s">
         <v>163</v>
@@ -8027,10 +8008,10 @@
         <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D8" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E8" t="s">
         <v>164</v>
@@ -8047,10 +8028,10 @@
         <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E9" t="s">
         <v>275</v>
@@ -8067,10 +8048,10 @@
         <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E10" t="s">
         <v>276</v>
@@ -8117,10 +8098,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E2" t="s">
         <v>164</v>
@@ -8154,13 +8135,13 @@
         <v>21330051920111</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C4" t="s">
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E4" t="s">
         <v>276</v>
@@ -8174,13 +8155,13 @@
         <v>21330051920113</v>
       </c>
       <c r="B5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E5" t="s">
         <v>163</v>
@@ -8194,13 +8175,13 @@
         <v>21330051920113</v>
       </c>
       <c r="B6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E6" t="s">
         <v>210</v>
@@ -8214,13 +8195,13 @@
         <v>21330051920117</v>
       </c>
       <c r="B7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E7" t="s">
         <v>163</v>
@@ -8234,13 +8215,13 @@
         <v>21330051920117</v>
       </c>
       <c r="B8" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E8" t="s">
         <v>164</v>
@@ -8260,7 +8241,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E9" t="s">
         <v>210</v>
@@ -8280,7 +8261,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E10" t="s">
         <v>276</v>
@@ -8300,7 +8281,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E11" t="s">
         <v>210</v>
@@ -8320,7 +8301,7 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E12" t="s">
         <v>276</v>
@@ -8334,7 +8315,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C13" t="s">
         <v>65</v>
@@ -8354,7 +8335,7 @@
         <v>21330051920126</v>
       </c>
       <c r="B14" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C14" t="s">
         <v>65</v>
@@ -8374,13 +8355,13 @@
         <v>21330051920130</v>
       </c>
       <c r="B15" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E15" t="s">
         <v>164</v>
@@ -8427,10 +8408,10 @@
         <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E2" t="s">
         <v>163</v>
@@ -8447,13 +8428,13 @@
         <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8464,13 +8445,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C4" t="s">
         <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E4" t="s">
         <v>163</v>
@@ -8484,13 +8465,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C5" t="s">
         <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E5" t="s">
         <v>276</v>
@@ -8510,7 +8491,7 @@
         <v>237</v>
       </c>
       <c r="D6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E6" t="s">
         <v>163</v>
@@ -8530,7 +8511,7 @@
         <v>237</v>
       </c>
       <c r="D7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E7" t="s">
         <v>276</v>
@@ -8577,10 +8558,10 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E2" t="s">
         <v>163</v>
@@ -8600,7 +8581,7 @@
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E3" t="s">
         <v>164</v>
@@ -8620,7 +8601,7 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E4" t="s">
         <v>163</v>
@@ -8637,10 +8618,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E5" t="s">
         <v>164</v>
@@ -8656,7 +8637,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8681,59 +8662,59 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920064</v>
+        <v>18330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>514</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920068</v>
+        <v>20330051920063</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>360</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>515</v>
       </c>
       <c r="D3" t="s">
-        <v>427</v>
+        <v>519</v>
       </c>
       <c r="E3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920071</v>
+        <v>20330051920064</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>516</v>
       </c>
       <c r="D4" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -8741,39 +8722,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920073</v>
+        <v>20330051920068</v>
       </c>
       <c r="B5" t="s">
-        <v>512</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>403</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="E5" t="s">
-        <v>522</v>
+        <v>295</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920080</v>
+        <v>20330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>305</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="E6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -8781,59 +8762,59 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920081</v>
+        <v>20330051920073</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>513</v>
       </c>
       <c r="C7" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="D7" t="s">
-        <v>518</v>
+        <v>375</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920082</v>
+        <v>20330051920073</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>513</v>
       </c>
       <c r="C8" t="s">
-        <v>232</v>
+        <v>402</v>
       </c>
       <c r="D8" t="s">
-        <v>519</v>
+        <v>375</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>526</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920082</v>
+        <v>20330051920080</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>232</v>
+        <v>456</v>
       </c>
       <c r="D9" t="s">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="E9" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -8841,19 +8822,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920087</v>
+        <v>20330051920081</v>
       </c>
       <c r="B10" t="s">
-        <v>513</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="D10" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -8861,62 +8842,122 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920087</v>
+        <v>20330051920082</v>
       </c>
       <c r="B11" t="s">
-        <v>513</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="D11" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E11" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920093</v>
+        <v>20330051920082</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>515</v>
+        <v>232</v>
       </c>
       <c r="D12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E12" t="s">
-        <v>373</v>
+        <v>295</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
+        <v>20330051920087</v>
+      </c>
+      <c r="B13" t="s">
+        <v>514</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>524</v>
+      </c>
+      <c r="E13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>20330051920087</v>
+      </c>
+      <c r="B14" t="s">
+        <v>514</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
+        <v>524</v>
+      </c>
+      <c r="E14" t="s">
+        <v>296</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
         <v>20330051920093</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
-        <v>515</v>
-      </c>
-      <c r="D13" t="s">
-        <v>521</v>
-      </c>
-      <c r="E13" t="s">
-        <v>296</v>
-      </c>
-      <c r="F13">
-        <v>-1</v>
+      <c r="C15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D15" t="s">
+        <v>525</v>
+      </c>
+      <c r="E15" t="s">
+        <v>295</v>
+      </c>
+      <c r="F15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>20330051920093</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>517</v>
+      </c>
+      <c r="D16" t="s">
+        <v>525</v>
+      </c>
+      <c r="E16" t="s">
+        <v>372</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9227,13 +9268,13 @@
         <v>232</v>
       </c>
       <c r="C2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -9244,16 +9285,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C3" t="s">
         <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9264,16 +9305,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C4" t="s">
         <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -9287,13 +9328,13 @@
         <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D5" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -9310,10 +9351,10 @@
         <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9330,10 +9371,10 @@
         <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -9344,16 +9385,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C8" t="s">
         <v>250</v>
       </c>
       <c r="D8" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9364,16 +9405,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C9" t="s">
         <v>250</v>
       </c>
       <c r="D9" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -9384,16 +9425,16 @@
         <v>20330051920197</v>
       </c>
       <c r="B10" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C10" t="s">
         <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="E10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -9407,13 +9448,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D11" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -9430,10 +9471,10 @@
         <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -9450,10 +9491,10 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -9470,10 +9511,10 @@
         <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>310</v>
+        <v>543</v>
       </c>
       <c r="E14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -9484,16 +9525,16 @@
         <v>20330051920210</v>
       </c>
       <c r="B15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C15" t="s">
         <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -9507,13 +9548,13 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D16" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -9527,13 +9568,13 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D17" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -9550,10 +9591,10 @@
         <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="E18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -9570,10 +9611,10 @@
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="E19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -9590,10 +9631,10 @@
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -9610,10 +9651,10 @@
         <v>256</v>
       </c>
       <c r="D21" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="E21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -9624,16 +9665,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B22" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C22" t="s">
         <v>128</v>
       </c>
       <c r="D22" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="E22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -9644,16 +9685,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B23" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C23" t="s">
         <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="E23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -9694,16 +9735,16 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D2" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9714,13 +9755,13 @@
         <v>19330051920425</v>
       </c>
       <c r="B3" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E3" t="s">
         <v>297</v>
@@ -9734,16 +9775,16 @@
         <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9760,10 +9801,10 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -9780,10 +9821,10 @@
         <v>205</v>
       </c>
       <c r="D6" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="E6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9797,13 +9838,13 @@
         <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D7" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -9817,13 +9858,13 @@
         <v>183</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D8" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9870,10 +9911,10 @@
         <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -9884,16 +9925,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C3" t="s">
         <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="E3" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9904,16 +9945,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B4" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C4" t="s">
         <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="E4" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -9924,16 +9965,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C5" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D5" t="s">
         <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -9944,16 +9985,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D6" t="s">
         <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -9970,10 +10011,10 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="E7" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -9987,16 +10028,16 @@
         <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D8" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E8" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10007,16 +10048,16 @@
         <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D9" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E9" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -10027,16 +10068,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D10" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E10" t="s">
-        <v>589</v>
+        <v>296</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -10047,16 +10088,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D11" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E11" t="s">
-        <v>295</v>
+        <v>594</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -10064,16 +10105,16 @@
         <v>20330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D12" t="s">
         <v>303</v>
       </c>
       <c r="E12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -10090,10 +10131,10 @@
         <v>252</v>
       </c>
       <c r="D13" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E13" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -10110,10 +10151,10 @@
         <v>252</v>
       </c>
       <c r="D14" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -10130,10 +10171,10 @@
         <v>205</v>
       </c>
       <c r="D15" t="s">
-        <v>310</v>
+        <v>543</v>
       </c>
       <c r="E15" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -10150,10 +10191,10 @@
         <v>205</v>
       </c>
       <c r="D16" t="s">
-        <v>310</v>
+        <v>543</v>
       </c>
       <c r="E16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -10170,10 +10211,10 @@
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="E17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -10190,10 +10231,10 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="E18" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -10210,10 +10251,10 @@
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E19" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -10230,10 +10271,10 @@
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F20">
         <v>-1</v>
@@ -10247,13 +10288,13 @@
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D21" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E21" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -10264,16 +10305,16 @@
         <v>20330051920131</v>
       </c>
       <c r="B22" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C22" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D22" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E22" t="s">
-        <v>296</v>
+        <v>594</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -10284,16 +10325,16 @@
         <v>20330051920131</v>
       </c>
       <c r="B23" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C23" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D23" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E23" t="s">
-        <v>589</v>
+        <v>295</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -10307,13 +10348,13 @@
         <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D24" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E24" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -10327,13 +10368,13 @@
         <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D25" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E25" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F25">
         <v>-1</v>
@@ -10344,16 +10385,16 @@
         <v>20330051920137</v>
       </c>
       <c r="B26" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C26" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D26" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F26">
         <v>-1</v>
@@ -10364,16 +10405,16 @@
         <v>20330051920137</v>
       </c>
       <c r="B27" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C27" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D27" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E27" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F27">
         <v>-1</v>
@@ -10387,13 +10428,13 @@
         <v>174</v>
       </c>
       <c r="C28" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D28" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="E28" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -10404,7 +10445,7 @@
         <v>20330051920140</v>
       </c>
       <c r="B29" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -10413,7 +10454,7 @@
         <v>112</v>
       </c>
       <c r="E29" t="s">
-        <v>589</v>
+        <v>295</v>
       </c>
       <c r="F29">
         <v>-1</v>
@@ -10424,7 +10465,7 @@
         <v>20330051920140</v>
       </c>
       <c r="B30" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -10433,7 +10474,7 @@
         <v>112</v>
       </c>
       <c r="E30" t="s">
-        <v>296</v>
+        <v>594</v>
       </c>
       <c r="F30">
         <v>-1</v>
@@ -10447,13 +10488,13 @@
         <v>261</v>
       </c>
       <c r="C31" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D31" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E31" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F31">
         <v>-1</v>
@@ -10467,13 +10508,13 @@
         <v>261</v>
       </c>
       <c r="C32" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D32" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E32" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F32">
         <v>-1</v>
@@ -10484,16 +10525,16 @@
         <v>20330051920144</v>
       </c>
       <c r="B33" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C33" t="s">
         <v>184</v>
       </c>
       <c r="D33" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F33">
         <v>-1</v>
@@ -10507,13 +10548,13 @@
         <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D34" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E34" t="s">
-        <v>589</v>
+        <v>295</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -10527,13 +10568,13 @@
         <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D35" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E35" t="s">
-        <v>296</v>
+        <v>594</v>
       </c>
       <c r="F35">
         <v>-1</v>
@@ -10547,10 +10588,10 @@
         <v>257</v>
       </c>
       <c r="D36" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="E36" t="s">
-        <v>296</v>
+        <v>594</v>
       </c>
       <c r="F36">
         <v>-1</v>
@@ -10564,10 +10605,10 @@
         <v>257</v>
       </c>
       <c r="D37" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="E37" t="s">
-        <v>589</v>
+        <v>295</v>
       </c>
       <c r="F37">
         <v>-1</v>
@@ -10578,16 +10619,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C38" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D38" t="s">
         <v>112</v>
       </c>
       <c r="E38" t="s">
-        <v>296</v>
+        <v>594</v>
       </c>
       <c r="F38">
         <v>-1</v>
@@ -10598,16 +10639,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B39" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C39" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D39" t="s">
         <v>112</v>
       </c>
       <c r="E39" t="s">
-        <v>589</v>
+        <v>295</v>
       </c>
       <c r="F39">
         <v>-1</v>
@@ -10618,16 +10659,16 @@
         <v>20330051920389</v>
       </c>
       <c r="B40" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C40" t="s">
         <v>279</v>
       </c>
       <c r="D40" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E40" t="s">
-        <v>589</v>
+        <v>295</v>
       </c>
       <c r="F40">
         <v>-1</v>
@@ -10638,16 +10679,16 @@
         <v>20330051920389</v>
       </c>
       <c r="B41" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C41" t="s">
         <v>279</v>
       </c>
       <c r="D41" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E41" t="s">
-        <v>296</v>
+        <v>594</v>
       </c>
       <c r="F41">
         <v>-1</v>
@@ -10660,7 +10701,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -10691,13 +10732,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D2" t="s">
         <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -10711,13 +10752,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D3" t="s">
         <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10725,16 +10766,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920321</v>
+        <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>595</v>
       </c>
       <c r="C4" t="s">
-        <v>389</v>
+        <v>598</v>
       </c>
       <c r="D4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="E4" t="s">
         <v>295</v>
@@ -10745,39 +10786,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920322</v>
+        <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>388</v>
       </c>
       <c r="D5" t="s">
-        <v>460</v>
+        <v>601</v>
       </c>
       <c r="E5" t="s">
         <v>296</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920325</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>595</v>
+        <v>463</v>
       </c>
       <c r="E6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -10785,19 +10826,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920326</v>
+        <v>20330051920325</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -10814,30 +10855,30 @@
         <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="E8" t="s">
         <v>295</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920329</v>
+        <v>20330051920326</v>
       </c>
       <c r="B9" t="s">
-        <v>590</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="E9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10848,36 +10889,36 @@
         <v>20330051920329</v>
       </c>
       <c r="B10" t="s">
-        <v>590</v>
+        <v>435</v>
       </c>
       <c r="C10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D10" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="E10" t="s">
         <v>296</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920330</v>
+        <v>20330051920329</v>
       </c>
       <c r="B11" t="s">
-        <v>591</v>
+        <v>435</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>341</v>
       </c>
       <c r="D11" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="E11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -10888,56 +10929,56 @@
         <v>20330051920330</v>
       </c>
       <c r="B12" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C12" t="s">
         <v>128</v>
       </c>
       <c r="D12" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="E12" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920331</v>
+        <v>20330051920330</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>596</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E13" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920335</v>
+        <v>20330051920331</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>593</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="E14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -10945,22 +10986,22 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920397</v>
+        <v>20330051920335</v>
       </c>
       <c r="B15" t="s">
-        <v>592</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>599</v>
       </c>
       <c r="D15" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="E15" t="s">
         <v>295</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -10968,18 +11009,38 @@
         <v>20330051920397</v>
       </c>
       <c r="B16" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C16" t="s">
         <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="E16" t="s">
         <v>296</v>
       </c>
       <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>20330051920397</v>
+      </c>
+      <c r="B17" t="s">
+        <v>597</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>608</v>
+      </c>
+      <c r="E17" t="s">
+        <v>295</v>
+      </c>
+      <c r="F17">
         <v>-1</v>
       </c>
     </row>
@@ -11937,7 +11998,7 @@
         <v>158</v>
       </c>
       <c r="E8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -11957,7 +12018,7 @@
         <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -11977,7 +12038,7 @@
         <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -11997,7 +12058,7 @@
         <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -12037,7 +12098,7 @@
         <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -12057,7 +12118,7 @@
         <v>161</v>
       </c>
       <c r="E14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F14">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="552">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -1113,12 +1113,12 @@
     <t>BRUNO AZAEL</t>
   </si>
   <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
     <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
   </si>
   <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
@@ -1146,21 +1146,36 @@
     <t>ROSAS</t>
   </si>
   <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t>TETLA</t>
   </si>
   <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
     <t>CAZARES</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
     <t>SERRANO</t>
   </si>
   <si>
+    <t>TIZA</t>
+  </si>
+  <si>
     <t>JOSE ALONSO</t>
   </si>
   <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
@@ -1170,18 +1185,33 @@
     <t>NAHUM HIRAM</t>
   </si>
   <si>
+    <t>ERIK</t>
+  </si>
+  <si>
     <t>JOSUE GUSTAVO</t>
   </si>
   <si>
     <t>CRISTOPHER</t>
   </si>
   <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
     <t>LUIS</t>
   </si>
   <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
@@ -1386,9 +1416,6 @@
     <t>ISAI</t>
   </si>
   <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
     <t>JOSUE ISRAEL</t>
   </si>
   <si>
@@ -1531,9 +1558,6 @@
   </si>
   <si>
     <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
   </si>
   <si>
     <t>SAID ANDRES</t>
@@ -3062,7 +3086,7 @@
         <v>264</v>
       </c>
       <c r="E9" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3082,7 +3106,7 @@
         <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4532,7 +4556,7 @@
         <v>350</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4552,7 +4576,7 @@
         <v>350</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4815,7 +4839,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4846,10 +4870,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -4860,39 +4884,39 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920193</v>
+        <v>22330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>363</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>370</v>
       </c>
       <c r="D3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920193</v>
+        <v>22330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>363</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>370</v>
       </c>
       <c r="D4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4900,22 +4924,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920199</v>
+        <v>22330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C5" t="s">
-        <v>368</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4926,10 +4950,10 @@
         <v>364</v>
       </c>
       <c r="C6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D6" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
@@ -4946,30 +4970,30 @@
         <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D7" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920356</v>
+        <v>22330051920201</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>306</v>
       </c>
       <c r="C8" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D8" t="s">
-        <v>374</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
         <v>35</v>
@@ -4980,16 +5004,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920356</v>
+        <v>22330051920201</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>306</v>
       </c>
       <c r="C9" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
-        <v>374</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
@@ -5000,16 +5024,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920358</v>
+        <v>22330051920202</v>
       </c>
       <c r="B10" t="s">
-        <v>365</v>
+        <v>306</v>
       </c>
       <c r="C10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -5020,19 +5044,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920378</v>
+        <v>22330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>357</v>
       </c>
       <c r="D11" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5040,61 +5064,261 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920378</v>
+        <v>22330051920356</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>294</v>
+        <v>357</v>
       </c>
       <c r="D12" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920390</v>
+        <v>22330051920358</v>
       </c>
       <c r="B13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>372</v>
       </c>
       <c r="D13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920390</v>
+        <v>22330051920359</v>
       </c>
       <c r="B14" t="s">
         <v>366</v>
       </c>
       <c r="C14" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14" t="s">
+        <v>382</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>22330051920359</v>
+      </c>
+      <c r="B15" t="s">
+        <v>366</v>
+      </c>
+      <c r="C15" t="s">
+        <v>373</v>
+      </c>
+      <c r="D15" t="s">
+        <v>382</v>
+      </c>
+      <c r="E15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>22330051920371</v>
+      </c>
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>383</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>22330051920378</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D17" t="s">
+        <v>384</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>22330051920378</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>294</v>
+      </c>
+      <c r="D18" t="s">
+        <v>384</v>
+      </c>
+      <c r="E18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>22330051920388</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" t="s">
+        <v>385</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>22330051920388</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" t="s">
+        <v>385</v>
+      </c>
+      <c r="E20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>22330051920390</v>
+      </c>
+      <c r="B21" t="s">
+        <v>367</v>
+      </c>
+      <c r="C21" t="s">
         <v>66</v>
       </c>
-      <c r="D14" t="s">
-        <v>377</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D21" t="s">
+        <v>386</v>
+      </c>
+      <c r="E21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>22330051920390</v>
+      </c>
+      <c r="B22" t="s">
+        <v>367</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" t="s">
+        <v>386</v>
+      </c>
+      <c r="E22" t="s">
         <v>117</v>
       </c>
-      <c r="F14">
+      <c r="F22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>22330051920413</v>
+      </c>
+      <c r="B23" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>387</v>
+      </c>
+      <c r="E23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22330051920413</v>
+      </c>
+      <c r="B24" t="s">
+        <v>368</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>387</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24">
         <v>5</v>
       </c>
     </row>
@@ -5349,7 +5573,7 @@
         <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E2" t="s">
         <v>37</v>
@@ -5369,7 +5593,7 @@
         <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="E3" t="s">
         <v>37</v>
@@ -5383,13 +5607,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="E4" t="s">
         <v>56</v>
@@ -5403,13 +5627,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="E5" t="s">
         <v>37</v>
@@ -5426,10 +5650,10 @@
         <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="D6" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="E6" t="s">
         <v>56</v>
@@ -5446,10 +5670,10 @@
         <v>167</v>
       </c>
       <c r="C7" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="D7" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -5469,7 +5693,7 @@
         <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
@@ -5483,13 +5707,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D9" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
@@ -5503,13 +5727,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C10" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D10" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -5526,10 +5750,10 @@
         <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="D11" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
@@ -5546,10 +5770,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="D12" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -5566,10 +5790,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="D13" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -5616,10 +5840,10 @@
         <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="D2" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -5636,13 +5860,13 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="D3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="E3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5653,13 +5877,13 @@
         <v>22330051920238</v>
       </c>
       <c r="B4" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="E4" t="s">
         <v>56</v>
@@ -5699,10 +5923,10 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="E6" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5713,13 +5937,13 @@
         <v>22330051920256</v>
       </c>
       <c r="B7" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C7" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="D7" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="E7" t="s">
         <v>56</v>
@@ -5739,7 +5963,7 @@
         <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
@@ -5759,7 +5983,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
@@ -5779,7 +6003,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="E10" t="s">
         <v>56</v>
@@ -5799,7 +6023,7 @@
         <v>227</v>
       </c>
       <c r="D11" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
@@ -5846,7 +6070,7 @@
         <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D2" t="s">
         <v>280</v>
@@ -5866,10 +6090,10 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="D3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="E3" t="s">
         <v>56</v>
@@ -5886,13 +6110,13 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="D4" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="E4" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5906,10 +6130,10 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="D5" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="E5" t="s">
         <v>56</v>
@@ -5929,7 +6153,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
@@ -5946,10 +6170,10 @@
         <v>167</v>
       </c>
       <c r="C7" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="E7" t="s">
         <v>56</v>
@@ -5969,7 +6193,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
@@ -5986,10 +6210,10 @@
         <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="D9" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="E9" t="s">
         <v>56</v>
@@ -6006,10 +6230,10 @@
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="D10" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="E10" t="s">
         <v>37</v>
@@ -6023,13 +6247,13 @@
         <v>22330051920283</v>
       </c>
       <c r="B11" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C11" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D11" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
@@ -6043,13 +6267,13 @@
         <v>22330051920288</v>
       </c>
       <c r="B12" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="C12" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="D12" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -6069,7 +6293,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
@@ -6109,10 +6333,10 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="E15" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6129,7 +6353,7 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="E16" t="s">
         <v>56</v>
@@ -6149,7 +6373,7 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="E17" t="s">
         <v>56</v>
@@ -6193,16 +6417,16 @@
         <v>22330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C2" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D2" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="E2" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6219,7 +6443,7 @@
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E3" t="s">
         <v>56</v>
@@ -6239,10 +6463,10 @@
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E4" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6256,13 +6480,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="E5" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6273,13 +6497,13 @@
         <v>22330051920298</v>
       </c>
       <c r="B6" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C6" t="s">
         <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="E6" t="s">
         <v>56</v>
@@ -6299,10 +6523,10 @@
         <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="E7" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6319,10 +6543,10 @@
         <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>446</v>
+        <v>385</v>
       </c>
       <c r="E8" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6339,7 +6563,7 @@
         <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>446</v>
+        <v>385</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -6356,10 +6580,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D10" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="E10" t="s">
         <v>56</v>
@@ -6376,13 +6600,13 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D11" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="E11" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6393,7 +6617,7 @@
         <v>22330051920308</v>
       </c>
       <c r="B12" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -6413,7 +6637,7 @@
         <v>22330051920308</v>
       </c>
       <c r="B13" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -6433,16 +6657,16 @@
         <v>22330051920309</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="E14" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6453,13 +6677,13 @@
         <v>22330051920311</v>
       </c>
       <c r="B15" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="D15" t="s">
         <v>279</v>
       </c>
       <c r="E15" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6470,13 +6694,13 @@
         <v>22330051920312</v>
       </c>
       <c r="B16" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C16" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D16" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="E16" t="s">
         <v>36</v>
@@ -6493,10 +6717,10 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D17" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="E17" t="s">
         <v>37</v>
@@ -6513,10 +6737,10 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D18" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="E18" t="s">
         <v>56</v>
@@ -6533,10 +6757,10 @@
         <v>227</v>
       </c>
       <c r="C19" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="D19" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E19" t="s">
         <v>35</v>
@@ -6553,13 +6777,13 @@
         <v>227</v>
       </c>
       <c r="C20" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="D20" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E20" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -6570,16 +6794,16 @@
         <v>22330051920360</v>
       </c>
       <c r="B21" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="C21" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -6593,10 +6817,10 @@
         <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="D22" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E22" t="s">
         <v>56</v>
@@ -6610,13 +6834,13 @@
         <v>22330051920397</v>
       </c>
       <c r="B23" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C23" t="s">
         <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
@@ -6630,13 +6854,13 @@
         <v>22330051920397</v>
       </c>
       <c r="B24" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C24" t="s">
         <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="E24" t="s">
         <v>56</v>
@@ -6653,7 +6877,7 @@
         <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="D25" t="s">
         <v>76</v>
@@ -6670,13 +6894,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B26" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C26" t="s">
         <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E26" t="s">
         <v>56</v>
@@ -6690,13 +6914,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B27" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C27" t="s">
         <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E27" t="s">
         <v>36</v>
@@ -6739,7 +6963,7 @@
         <v>76</v>
       </c>
       <c r="E29" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -6783,10 +7007,10 @@
         <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="D2" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E2" t="s">
         <v>270</v>
@@ -6800,7 +7024,7 @@
         <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C3" t="s">
         <v>341</v>
@@ -6820,7 +7044,7 @@
         <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C4" t="s">
         <v>341</v>
@@ -6829,7 +7053,7 @@
         <v>279</v>
       </c>
       <c r="E4" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6846,7 +7070,7 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="E5" t="s">
         <v>155</v>
@@ -6866,10 +7090,10 @@
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="E6" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6886,7 +7110,7 @@
         <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="E7" t="s">
         <v>156</v>
@@ -6933,13 +7157,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D2" t="s">
         <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>270</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6953,13 +7177,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D3" t="s">
         <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>270</v>
+        <v>155</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6976,7 +7200,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="E4" t="s">
         <v>155</v>
@@ -7010,13 +7234,13 @@
         <v>21330051920103</v>
       </c>
       <c r="B6" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C6" t="s">
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="E6" t="s">
         <v>156</v>
@@ -7033,10 +7257,10 @@
         <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="D7" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="E7" t="s">
         <v>269</v>
@@ -7056,7 +7280,7 @@
         <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="E8" t="s">
         <v>269</v>
@@ -7076,7 +7300,7 @@
         <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="E9" t="s">
         <v>156</v>
@@ -7123,10 +7347,10 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="D2" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="E2" t="s">
         <v>156</v>
@@ -7160,13 +7384,13 @@
         <v>21330051920113</v>
       </c>
       <c r="B4" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="E4" t="s">
         <v>155</v>
@@ -7180,13 +7404,13 @@
         <v>21330051920117</v>
       </c>
       <c r="B5" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C5" t="s">
         <v>325</v>
       </c>
       <c r="D5" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E5" t="s">
         <v>156</v>
@@ -7200,13 +7424,13 @@
         <v>21330051920117</v>
       </c>
       <c r="B6" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C6" t="s">
         <v>325</v>
       </c>
       <c r="D6" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E6" t="s">
         <v>155</v>
@@ -7226,7 +7450,7 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="E7" t="s">
         <v>156</v>
@@ -7246,7 +7470,7 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="E8" t="s">
         <v>155</v>
@@ -7266,7 +7490,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E9" t="s">
         <v>270</v>
@@ -7280,13 +7504,13 @@
         <v>21330051920130</v>
       </c>
       <c r="B10" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D10" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="E10" t="s">
         <v>156</v>
@@ -7333,10 +7557,10 @@
         <v>206</v>
       </c>
       <c r="C2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D2" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E2" t="s">
         <v>155</v>
@@ -7353,13 +7577,13 @@
         <v>206</v>
       </c>
       <c r="C3" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D3" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E3" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7370,13 +7594,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="E4" t="s">
         <v>270</v>
@@ -7390,13 +7614,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="E5" t="s">
         <v>155</v>
@@ -7416,7 +7640,7 @@
         <v>231</v>
       </c>
       <c r="D6" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="E6" t="s">
         <v>270</v>
@@ -7436,7 +7660,7 @@
         <v>231</v>
       </c>
       <c r="D7" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="E7" t="s">
         <v>155</v>
@@ -7486,7 +7710,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="E2" t="s">
         <v>156</v>
@@ -7506,7 +7730,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="E3" t="s">
         <v>155</v>
@@ -7523,10 +7747,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D4" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="E4" t="s">
         <v>155</v>
@@ -7543,10 +7767,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D5" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="E5" t="s">
         <v>156</v>
@@ -7563,10 +7787,10 @@
         <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D6" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="E6" t="s">
         <v>155</v>
@@ -7586,7 +7810,7 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E7" t="s">
         <v>155</v>
@@ -7606,7 +7830,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E8" t="s">
         <v>156</v>
@@ -7623,10 +7847,10 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="D9" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="E9" t="s">
         <v>156</v>
@@ -7676,7 +7900,7 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E2" t="s">
         <v>289</v>
@@ -7693,10 +7917,10 @@
         <v>342</v>
       </c>
       <c r="C3" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="D3" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="E3" t="s">
         <v>289</v>
@@ -7716,7 +7940,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="E4" t="s">
         <v>289</v>
@@ -7730,16 +7954,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B5" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="C5" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="D5" t="s">
-        <v>495</v>
+        <v>383</v>
       </c>
       <c r="E5" t="s">
-        <v>289</v>
+        <v>507</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7750,16 +7974,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B6" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="C6" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="D6" t="s">
-        <v>495</v>
+        <v>383</v>
       </c>
       <c r="E6" t="s">
-        <v>499</v>
+        <v>289</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7773,10 +7997,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D7" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="E7" t="s">
         <v>289</v>
@@ -7796,10 +8020,10 @@
         <v>226</v>
       </c>
       <c r="D8" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>355</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7816,10 +8040,10 @@
         <v>226</v>
       </c>
       <c r="D9" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E9" t="s">
-        <v>356</v>
+        <v>289</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7830,13 +8054,13 @@
         <v>20330051920087</v>
       </c>
       <c r="B10" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E10" t="s">
         <v>290</v>
@@ -7853,13 +8077,13 @@
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D11" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8170,13 +8394,13 @@
         <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="C2" t="s">
         <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E2" t="s">
         <v>289</v>
@@ -8190,13 +8414,13 @@
         <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E3" t="s">
         <v>290</v>
@@ -8216,7 +8440,7 @@
         <v>304</v>
       </c>
       <c r="D4" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="E4" t="s">
         <v>289</v>
@@ -8236,7 +8460,7 @@
         <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="E5" t="s">
         <v>290</v>
@@ -8250,13 +8474,13 @@
         <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C6" t="s">
         <v>244</v>
       </c>
       <c r="D6" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E6" t="s">
         <v>289</v>
@@ -8270,16 +8494,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C7" t="s">
         <v>244</v>
       </c>
       <c r="D7" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8293,10 +8517,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="E8" t="s">
         <v>289</v>
@@ -8313,10 +8537,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D9" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E9" t="s">
         <v>290</v>
@@ -8336,7 +8560,7 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E10" t="s">
         <v>289</v>
@@ -8356,7 +8580,7 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E11" t="s">
         <v>290</v>
@@ -8376,7 +8600,7 @@
         <v>250</v>
       </c>
       <c r="D12" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="E12" t="s">
         <v>289</v>
@@ -8390,13 +8614,13 @@
         <v>20330051920218</v>
       </c>
       <c r="B13" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C13" t="s">
         <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E13" t="s">
         <v>290</v>
@@ -8440,13 +8664,13 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C2" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D2" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="E2" t="s">
         <v>290</v>
@@ -8460,13 +8684,13 @@
         <v>19330051920425</v>
       </c>
       <c r="B3" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E3" t="s">
         <v>291</v>
@@ -8480,13 +8704,13 @@
         <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="E4" t="s">
         <v>290</v>
@@ -8506,7 +8730,7 @@
         <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="E5" t="s">
         <v>290</v>
@@ -8526,7 +8750,7 @@
         <v>306</v>
       </c>
       <c r="D6" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E6" t="s">
         <v>290</v>
@@ -8546,7 +8770,7 @@
         <v>306</v>
       </c>
       <c r="D7" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E7" t="s">
         <v>289</v>
@@ -8590,16 +8814,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C2" t="s">
         <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E2" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8610,16 +8834,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C3" t="s">
         <v>169</v>
       </c>
       <c r="D3" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E3" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8633,13 +8857,13 @@
         <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D4" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E4" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8653,10 +8877,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D5" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="E5" t="s">
         <v>290</v>
@@ -8676,7 +8900,7 @@
         <v>246</v>
       </c>
       <c r="D6" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="E6" t="s">
         <v>290</v>
@@ -8696,7 +8920,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="E7" t="s">
         <v>290</v>
@@ -8743,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="D2" t="s">
         <v>75</v>
@@ -8763,13 +8987,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="D3" t="s">
         <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8780,13 +9004,13 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C4" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D4" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="E4" t="s">
         <v>289</v>
@@ -8803,10 +9027,10 @@
         <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D5" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="E5" t="s">
         <v>290</v>
@@ -8826,7 +9050,7 @@
         <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="E6" t="s">
         <v>289</v>
@@ -8846,7 +9070,7 @@
         <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="E7" t="s">
         <v>290</v>
@@ -8860,13 +9084,13 @@
         <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C8" t="s">
         <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E8" t="s">
         <v>289</v>
@@ -8880,13 +9104,13 @@
         <v>20330051920329</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C9" t="s">
         <v>325</v>
       </c>
       <c r="D9" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E9" t="s">
         <v>290</v>
@@ -8900,16 +9124,16 @@
         <v>20330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C10" t="s">
         <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="E10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8920,13 +9144,13 @@
         <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C11" t="s">
         <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="E11" t="s">
         <v>290</v>
@@ -8940,13 +9164,13 @@
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C12" t="s">
         <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="E12" t="s">
         <v>289</v>
@@ -10296,7 +10520,7 @@
         <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -10316,7 +10540,7 @@
         <v>189</v>
       </c>
       <c r="E14" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="F14">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="534">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -477,9 +477,6 @@
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -504,9 +501,6 @@
     <t>YAHIR</t>
   </si>
   <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
     <t>ANGEL FIDEL</t>
   </si>
   <si>
@@ -534,6 +528,9 @@
     <t>ESPINOZA</t>
   </si>
   <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -567,6 +564,9 @@
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
     <t>SORIANO</t>
   </si>
   <si>
@@ -603,6 +603,9 @@
     <t>LIZBETH</t>
   </si>
   <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
     <t>NADIA</t>
   </si>
   <si>
@@ -639,858 +642,795 @@
     <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
   </si>
   <si>
-    <t>ABAD</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>YARETZI VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>LAURA EVELYN</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>AMERICA PAOLA</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>CITLALI</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>IVANNA DANIELA</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ÉTICA</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>LISBETH ESMERALDA</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSE ISAIAS</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA I</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>CADENA</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>MARIA ANGELES</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>UREÑA</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>GERMAN</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>JULISSA</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>AYALA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>VALDEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>APLICA LA METODOLOGÍA ESPIRAL CON PROGRAMACIÓN ORIENTADA A OBJETOS</t>
-  </si>
-  <si>
-    <t>APLICA LA METODOLOGÍA DE DESARROLLO RÁPIDO DE APLICACIONES CON PROGRAMACIÓN ORIENTADA A EVENTOS</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ÉTICA</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>LISBETH ESMERALDA</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>CONSTRUYE BASES DE DATOS PARA APLICACIONES WEB</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>CAZARES</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
   </si>
   <si>
     <t>SERRANO</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA I</t>
-  </si>
-  <si>
-    <t>UREÑA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>GERMAN</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>AYALA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
     <t>MARIANA</t>
   </si>
   <si>
@@ -1518,12 +1458,12 @@
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
-    <t>REALIZA EL PROCESO DE ADMISIÓN Y EMPLEO</t>
-  </si>
-  <si>
     <t>GALICIA</t>
   </si>
   <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
     <t>MILKA SARAY</t>
   </si>
   <si>
@@ -1536,6 +1476,9 @@
     <t>ALEXIS ISAI</t>
   </si>
   <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
     <t>ROGELIO</t>
   </si>
   <si>
@@ -1548,12 +1491,12 @@
     <t>SALAS</t>
   </si>
   <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
     <t>VICTOR GAEL</t>
   </si>
   <si>
@@ -1566,9 +1509,6 @@
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
     <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
   </si>
   <si>
@@ -1653,7 +1593,13 @@
     <t>AMYRA NAHOMY</t>
   </si>
   <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
     <t>PAULINA</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
   </si>
   <si>
     <t>AMARANTA DENISSE</t>
@@ -2116,7 +2062,7 @@
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2136,7 +2082,7 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2216,7 +2162,7 @@
         <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2236,7 +2182,7 @@
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2363,10 +2309,10 @@
         <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2377,16 +2323,16 @@
         <v>21330051920218</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2397,16 +2343,16 @@
         <v>21330051920219</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2423,10 +2369,10 @@
         <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2440,13 +2386,13 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2466,7 +2412,7 @@
         <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2483,10 +2429,10 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" t="s">
         <v>218</v>
-      </c>
-      <c r="E8" t="s">
-        <v>223</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2503,10 +2449,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2517,16 +2463,16 @@
         <v>21330051920239</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2537,16 +2483,16 @@
         <v>21330051920240</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2557,16 +2503,16 @@
         <v>21330051920240</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2577,16 +2523,16 @@
         <v>21330051920247</v>
       </c>
       <c r="B13" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
         <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2600,13 +2546,13 @@
         <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D14" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2619,7 +2565,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2647,16 +2593,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2667,16 +2613,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2687,16 +2633,16 @@
         <v>21330051920188</v>
       </c>
       <c r="B4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C4" t="s">
         <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2707,16 +2653,16 @@
         <v>21330051920188</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C5" t="s">
         <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2727,16 +2673,16 @@
         <v>21330051920192</v>
       </c>
       <c r="B6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" t="s">
         <v>225</v>
       </c>
-      <c r="C6" t="s">
-        <v>230</v>
-      </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2747,16 +2693,16 @@
         <v>21330051920193</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D7" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2767,16 +2713,16 @@
         <v>21330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
         <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2787,16 +2733,16 @@
         <v>21330051920201</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2807,16 +2753,16 @@
         <v>21330051920202</v>
       </c>
       <c r="B10" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C10" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2827,16 +2773,16 @@
         <v>21330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C11" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2853,10 +2799,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2864,19 +2810,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920213</v>
+        <v>21330051920203</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>234</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2884,21 +2830,41 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
+        <v>21330051920213</v>
+      </c>
+      <c r="B14" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" t="s">
+        <v>153</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
         <v>21330051920386</v>
       </c>
-      <c r="B14" t="s">
-        <v>228</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="D14" t="s">
-        <v>243</v>
-      </c>
-      <c r="E14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F14">
+      <c r="D15" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -2909,7 +2875,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2937,16 +2903,16 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E2" t="s">
         <v>257</v>
-      </c>
-      <c r="E2" t="s">
-        <v>269</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2963,10 +2929,10 @@
         <v>96</v>
       </c>
       <c r="D3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" t="s">
         <v>258</v>
-      </c>
-      <c r="E3" t="s">
-        <v>270</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2977,16 +2943,16 @@
         <v>21330051920298</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E4" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3003,10 +2969,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3014,19 +2980,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920304</v>
+        <v>21330051920305</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3034,19 +3000,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920305</v>
+        <v>21330051920306</v>
       </c>
       <c r="B7" t="s">
-        <v>247</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>254</v>
+        <v>176</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3054,19 +3020,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920306</v>
+        <v>21330051920308</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>242</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3077,16 +3043,16 @@
         <v>21330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
         <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3094,19 +3060,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920308</v>
+        <v>21330051920323</v>
       </c>
       <c r="B10" t="s">
-        <v>248</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="E10" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3114,19 +3080,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920316</v>
+        <v>21330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>249</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3134,19 +3100,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920323</v>
+        <v>21330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>258</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3154,81 +3120,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>244</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>246</v>
       </c>
       <c r="D13" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E13" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920326</v>
-      </c>
-      <c r="B14" t="s">
-        <v>250</v>
-      </c>
-      <c r="C14" t="s">
-        <v>176</v>
-      </c>
-      <c r="D14" t="s">
-        <v>266</v>
-      </c>
-      <c r="E14" t="s">
-        <v>270</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920328</v>
-      </c>
-      <c r="B15" t="s">
-        <v>251</v>
-      </c>
-      <c r="C15" t="s">
-        <v>255</v>
-      </c>
-      <c r="D15" t="s">
-        <v>267</v>
-      </c>
-      <c r="E15" t="s">
-        <v>270</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920330</v>
-      </c>
-      <c r="B16" t="s">
-        <v>252</v>
-      </c>
-      <c r="C16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" t="s">
-        <v>268</v>
-      </c>
-      <c r="E16" t="s">
-        <v>156</v>
-      </c>
-      <c r="F16">
         <v>5</v>
       </c>
     </row>
@@ -3267,16 +3173,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E2" t="s">
         <v>278</v>
-      </c>
-      <c r="E2" t="s">
-        <v>289</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3287,16 +3193,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3307,16 +3213,16 @@
         <v>20330051920011</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3327,16 +3233,16 @@
         <v>20330051920012</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="E5" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3350,13 +3256,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D6" t="s">
         <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3370,13 +3276,13 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D7" t="s">
         <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3387,16 +3293,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3407,16 +3313,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3427,16 +3333,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B10" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3447,16 +3353,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3467,16 +3373,16 @@
         <v>20330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="E12" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3493,10 +3399,10 @@
         <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E13" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3513,10 +3419,10 @@
         <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E14" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3530,13 +3436,13 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E15" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -3547,16 +3453,16 @@
         <v>20330051920362</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C16" t="s">
         <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="E16" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3570,13 +3476,13 @@
         <v>47</v>
       </c>
       <c r="C17" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" t="s">
         <v>277</v>
       </c>
-      <c r="D17" t="s">
-        <v>288</v>
-      </c>
       <c r="E17" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3620,13 +3526,13 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D2" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3637,16 +3543,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C3" t="s">
         <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3657,16 +3563,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C4" t="s">
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3686,7 +3592,7 @@
         <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3697,16 +3603,16 @@
         <v>20330051920243</v>
       </c>
       <c r="B6" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3717,16 +3623,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3737,16 +3643,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D8" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="E8" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3757,16 +3663,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="D9" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3777,16 +3683,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B10" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C10" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="D10" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3797,16 +3703,16 @@
         <v>20330051920374</v>
       </c>
       <c r="B11" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3819,7 +3725,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3847,16 +3753,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="D2" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3870,13 +3776,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D3" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3890,13 +3796,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D4" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="E4" t="s">
-        <v>319</v>
+        <v>280</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3904,19 +3810,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920345</v>
+        <v>20330051920347</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>309</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3924,19 +3830,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920347</v>
+        <v>20330051920349</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>294</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3944,19 +3850,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920349</v>
+        <v>20330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3964,19 +3870,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920354</v>
+        <v>20330051920356</v>
       </c>
       <c r="B8" t="s">
-        <v>251</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="D8" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3984,61 +3890,21 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920356</v>
+        <v>20330051920381</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920381</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" t="s">
-        <v>317</v>
-      </c>
-      <c r="E10" t="s">
-        <v>289</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920383</v>
-      </c>
-      <c r="B11" t="s">
-        <v>306</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>318</v>
-      </c>
-      <c r="E11" t="s">
-        <v>319</v>
-      </c>
-      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -4077,16 +3943,16 @@
         <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4097,16 +3963,16 @@
         <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D3" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4123,10 +3989,10 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4143,10 +4009,10 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4163,10 +4029,10 @@
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4177,16 +4043,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4197,16 +4063,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B8" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4217,16 +4083,16 @@
         <v>20330051920173</v>
       </c>
       <c r="B9" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
         <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4237,16 +4103,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4257,16 +4123,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B11" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C11" t="s">
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="E11" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4277,16 +4143,16 @@
         <v>20330051920178</v>
       </c>
       <c r="B12" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C12" t="s">
         <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="E12" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4300,13 +4166,13 @@
         <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D13" t="s">
         <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4320,13 +4186,13 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D14" t="s">
         <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -4337,16 +4203,16 @@
         <v>20330051920388</v>
       </c>
       <c r="B15" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="C15" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D15" t="s">
         <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4357,16 +4223,16 @@
         <v>20330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D16" t="s">
         <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4407,16 +4273,16 @@
         <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C2" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D2" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4427,16 +4293,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4450,13 +4316,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D4" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4470,13 +4336,13 @@
         <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="E5" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4490,13 +4356,13 @@
         <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D6" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="E6" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4513,10 +4379,10 @@
         <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4527,16 +4393,16 @@
         <v>20330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4550,13 +4416,13 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4570,13 +4436,13 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D10" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="E10" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4593,10 +4459,10 @@
         <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="E11" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4607,16 +4473,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B12" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C12" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D12" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="E12" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4627,16 +4493,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B13" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C13" t="s">
+        <v>331</v>
+      </c>
+      <c r="D13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" t="s">
         <v>343</v>
-      </c>
-      <c r="D13" t="s">
-        <v>352</v>
-      </c>
-      <c r="E13" t="s">
-        <v>355</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4653,10 +4519,10 @@
         <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="E14" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4673,10 +4539,10 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="E15" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4717,16 +4583,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4743,10 +4609,10 @@
         <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4763,10 +4629,10 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4783,10 +4649,10 @@
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="E5" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4803,10 +4669,10 @@
         <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4823,10 +4689,10 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4839,7 +4705,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4864,19 +4730,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920181</v>
+        <v>21330051920265</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E2" t="s">
         <v>369</v>
-      </c>
-      <c r="D2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E2" t="s">
-        <v>35</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4884,19 +4750,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920190</v>
+        <v>21330051920265</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>370</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4910,10 +4776,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D4" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="E4" t="s">
         <v>37</v>
@@ -4924,19 +4790,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920193</v>
+        <v>22330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>363</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="D5" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="E5" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4944,19 +4810,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920199</v>
+        <v>22330051920195</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>371</v>
+        <v>263</v>
       </c>
       <c r="D6" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4964,19 +4830,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920200</v>
+        <v>22330051920199</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>351</v>
       </c>
       <c r="C7" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D7" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4984,19 +4850,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920201</v>
+        <v>22330051920200</v>
       </c>
       <c r="B8" t="s">
-        <v>306</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>362</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5007,16 +4873,16 @@
         <v>22330051920201</v>
       </c>
       <c r="B9" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="C9" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5024,19 +4890,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920202</v>
+        <v>22330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="C10" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D10" t="s">
-        <v>379</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5050,10 +4916,10 @@
         <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D11" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="E11" t="s">
         <v>37</v>
@@ -5070,10 +4936,10 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D12" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -5084,19 +4950,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920358</v>
+        <v>22330051920359</v>
       </c>
       <c r="B13" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C13" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D13" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5104,19 +4970,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920359</v>
+        <v>22330051920371</v>
       </c>
       <c r="B14" t="s">
-        <v>366</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>373</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5124,19 +4990,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920359</v>
+        <v>22330051920378</v>
       </c>
       <c r="B15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" t="s">
+        <v>283</v>
+      </c>
+      <c r="D15" t="s">
         <v>366</v>
       </c>
-      <c r="C15" t="s">
-        <v>373</v>
-      </c>
-      <c r="D15" t="s">
-        <v>382</v>
-      </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5144,19 +5010,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920371</v>
+        <v>22330051920378</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>283</v>
       </c>
       <c r="D16" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5164,19 +5030,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920378</v>
+        <v>22330051920388</v>
       </c>
       <c r="B17" t="s">
         <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5184,141 +5050,21 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920378</v>
+        <v>22330051920390</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>354</v>
       </c>
       <c r="C18" t="s">
-        <v>294</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E18" t="s">
         <v>37</v>
       </c>
       <c r="F18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920388</v>
-      </c>
-      <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>385</v>
-      </c>
-      <c r="E19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920388</v>
-      </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>385</v>
-      </c>
-      <c r="E20" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920390</v>
-      </c>
-      <c r="B21" t="s">
-        <v>367</v>
-      </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>386</v>
-      </c>
-      <c r="E21" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920390</v>
-      </c>
-      <c r="B22" t="s">
-        <v>367</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>386</v>
-      </c>
-      <c r="E22" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920413</v>
-      </c>
-      <c r="B23" t="s">
-        <v>368</v>
-      </c>
-      <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>387</v>
-      </c>
-      <c r="E23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920413</v>
-      </c>
-      <c r="B24" t="s">
-        <v>368</v>
-      </c>
-      <c r="C24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" t="s">
-        <v>387</v>
-      </c>
-      <c r="E24" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24">
         <v>5</v>
       </c>
     </row>
@@ -5570,10 +5316,10 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="E2" t="s">
         <v>37</v>
@@ -5593,7 +5339,7 @@
         <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="E3" t="s">
         <v>37</v>
@@ -5607,16 +5353,16 @@
         <v>22330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5627,16 +5373,16 @@
         <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5647,13 +5393,13 @@
         <v>22330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D6" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="E6" t="s">
         <v>56</v>
@@ -5667,13 +5413,13 @@
         <v>22330051920218</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D7" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -5693,7 +5439,7 @@
         <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
@@ -5707,13 +5453,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C9" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="D9" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
@@ -5727,13 +5473,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C10" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="D10" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -5750,10 +5496,10 @@
         <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="D11" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
@@ -5764,16 +5510,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920423</v>
+        <v>22330051920374</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>393</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -5790,10 +5536,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="D13" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -5809,7 +5555,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5840,10 +5586,10 @@
         <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="D2" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -5860,13 +5606,13 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E3" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5877,13 +5623,13 @@
         <v>22330051920238</v>
       </c>
       <c r="B4" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="E4" t="s">
         <v>56</v>
@@ -5900,7 +5646,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="D5" t="s">
         <v>70</v>
@@ -5923,10 +5669,10 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E6" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5937,13 +5683,13 @@
         <v>22330051920256</v>
       </c>
       <c r="B7" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C7" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D7" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E7" t="s">
         <v>56</v>
@@ -5963,7 +5709,7 @@
         <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
@@ -5983,10 +5729,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6003,10 +5749,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6020,15 +5766,35 @@
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D11" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
       </c>
       <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>22330051920369</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" t="s">
+        <v>397</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -6039,7 +5805,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6070,13 +5836,13 @@
         <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6084,16 +5850,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D3" t="s">
-        <v>424</v>
+        <v>269</v>
       </c>
       <c r="E3" t="s">
         <v>56</v>
@@ -6110,13 +5876,13 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6124,16 +5890,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920263</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="D5" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="E5" t="s">
         <v>56</v>
@@ -6144,19 +5910,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920270</v>
+        <v>22330051920265</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>401</v>
       </c>
       <c r="D6" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6167,13 +5933,13 @@
         <v>22330051920272</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="D7" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="E7" t="s">
         <v>56</v>
@@ -6193,7 +5959,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
@@ -6204,19 +5970,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920279</v>
+        <v>22330051920274</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>421</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6230,13 +5996,13 @@
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D10" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6244,19 +6010,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920283</v>
+        <v>22330051920279</v>
       </c>
       <c r="B11" t="s">
-        <v>416</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="D11" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6264,19 +6030,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920288</v>
+        <v>22330051920281</v>
       </c>
       <c r="B12" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="C12" t="s">
-        <v>423</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>431</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6284,19 +6050,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920402</v>
+        <v>22330051920281</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>432</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6304,19 +6070,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920404</v>
+        <v>22330051920283</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>399</v>
       </c>
       <c r="C14" t="s">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>410</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6324,19 +6090,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920405</v>
+        <v>22330051920402</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="E15" t="s">
-        <v>415</v>
+        <v>35</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6344,19 +6110,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920406</v>
+        <v>22330051920404</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>327</v>
       </c>
       <c r="D16" t="s">
-        <v>434</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6364,21 +6130,61 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
+        <v>22330051920405</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>412</v>
+      </c>
+      <c r="E17" t="s">
+        <v>369</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>22330051920406</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>413</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
         <v>22330051920411</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C19" t="s">
         <v>14</v>
       </c>
-      <c r="D17" t="s">
-        <v>435</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D19" t="s">
+        <v>414</v>
+      </c>
+      <c r="E19" t="s">
         <v>56</v>
       </c>
-      <c r="F17">
+      <c r="F19">
         <v>5</v>
       </c>
     </row>
@@ -6389,7 +6195,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6417,16 +6223,16 @@
         <v>22330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="C2" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="D2" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="E2" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6443,7 +6249,7 @@
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="E3" t="s">
         <v>56</v>
@@ -6463,10 +6269,10 @@
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6480,13 +6286,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="D5" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="E5" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6497,13 +6303,13 @@
         <v>22330051920298</v>
       </c>
       <c r="B6" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="E6" t="s">
         <v>56</v>
@@ -6514,19 +6320,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920300</v>
+        <v>22330051920302</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="E7" t="s">
-        <v>415</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6543,10 +6349,10 @@
         <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="E8" t="s">
-        <v>415</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6563,10 +6369,10 @@
         <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>369</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6580,10 +6386,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="D10" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="E10" t="s">
         <v>56</v>
@@ -6600,13 +6406,13 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="D11" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="E11" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6617,16 +6423,16 @@
         <v>22330051920308</v>
       </c>
       <c r="B12" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>436</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6637,16 +6443,16 @@
         <v>22330051920308</v>
       </c>
       <c r="B13" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>199</v>
+        <v>436</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6654,19 +6460,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920309</v>
+        <v>22330051920311</v>
       </c>
       <c r="B14" t="s">
-        <v>439</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
+        <v>418</v>
       </c>
       <c r="D14" t="s">
-        <v>457</v>
+        <v>268</v>
       </c>
       <c r="E14" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6674,16 +6477,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920311</v>
+        <v>22330051920312</v>
       </c>
       <c r="B15" t="s">
-        <v>440</v>
+        <v>419</v>
+      </c>
+      <c r="C15" t="s">
+        <v>425</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>437</v>
       </c>
       <c r="E15" t="s">
-        <v>415</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6691,19 +6497,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920312</v>
+        <v>22330051920314</v>
       </c>
       <c r="B16" t="s">
-        <v>441</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
       <c r="D16" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6717,10 +6523,10 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="D17" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="E17" t="s">
         <v>37</v>
@@ -6731,19 +6537,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920314</v>
+        <v>22330051920315</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="C18" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="D18" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -6754,16 +6560,16 @@
         <v>22330051920315</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C19" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D19" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>369</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -6771,19 +6577,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920315</v>
+        <v>22330051920360</v>
       </c>
       <c r="B20" t="s">
-        <v>227</v>
+        <v>420</v>
       </c>
       <c r="C20" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D20" t="s">
-        <v>460</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -6791,19 +6597,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920360</v>
+        <v>22330051920373</v>
       </c>
       <c r="B21" t="s">
-        <v>442</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>449</v>
+        <v>368</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>440</v>
       </c>
       <c r="E21" t="s">
-        <v>415</v>
+        <v>56</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -6811,16 +6617,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920373</v>
+        <v>22330051920397</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>421</v>
       </c>
       <c r="C22" t="s">
-        <v>386</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="E22" t="s">
         <v>56</v>
@@ -6834,13 +6640,13 @@
         <v>22330051920397</v>
       </c>
       <c r="B23" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="C23" t="s">
         <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
@@ -6851,16 +6657,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920397</v>
+        <v>22330051920408</v>
       </c>
       <c r="B24" t="s">
-        <v>443</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>429</v>
       </c>
       <c r="D24" t="s">
-        <v>462</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
         <v>56</v>
@@ -6871,19 +6677,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920408</v>
+        <v>22330051920412</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>356</v>
       </c>
       <c r="C25" t="s">
-        <v>450</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>442</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -6894,13 +6700,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B26" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C26" t="s">
         <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="E26" t="s">
         <v>56</v>
@@ -6911,19 +6717,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920412</v>
+        <v>22330051920419</v>
       </c>
       <c r="B27" t="s">
-        <v>371</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>463</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -6943,29 +6749,9 @@
         <v>76</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>369</v>
       </c>
       <c r="F28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920419</v>
-      </c>
-      <c r="B29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" t="s">
-        <v>415</v>
-      </c>
-      <c r="F29">
         <v>5</v>
       </c>
     </row>
@@ -7004,16 +6790,16 @@
         <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="D2" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="E2" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7024,16 +6810,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B3" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="C3" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="D3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7044,16 +6830,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B4" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="E4" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7070,10 +6856,10 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7090,10 +6876,10 @@
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="E6" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7110,10 +6896,10 @@
         <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7157,13 +6943,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="D2" t="s">
         <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>270</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7177,13 +6963,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="D3" t="s">
         <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>258</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7200,10 +6986,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7223,7 +7009,7 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7234,16 +7020,16 @@
         <v>21330051920103</v>
       </c>
       <c r="B6" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="C6" t="s">
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7257,13 +7043,13 @@
         <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="D7" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7280,10 +7066,10 @@
         <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E8" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7300,10 +7086,10 @@
         <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7347,13 +7133,13 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="D2" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7364,16 +7150,16 @@
         <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
         <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7384,16 +7170,16 @@
         <v>21330051920113</v>
       </c>
       <c r="B4" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7404,16 +7190,16 @@
         <v>21330051920117</v>
       </c>
       <c r="B5" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="C5" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D5" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7424,16 +7210,16 @@
         <v>21330051920117</v>
       </c>
       <c r="B6" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="C6" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D6" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7450,10 +7236,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7470,10 +7256,10 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7490,10 +7276,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7504,16 +7290,16 @@
         <v>21330051920130</v>
       </c>
       <c r="B10" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="C10" t="s">
-        <v>372</v>
+        <v>460</v>
       </c>
       <c r="D10" t="s">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7526,7 +7312,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7554,16 +7340,16 @@
         <v>20330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C2" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="D2" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7571,19 +7357,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>466</v>
       </c>
       <c r="C3" t="s">
-        <v>403</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="E3" t="s">
-        <v>490</v>
+        <v>153</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7594,16 +7380,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="E4" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7611,19 +7397,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="D5" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>258</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7634,38 +7420,18 @@
         <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D6" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="E6" t="s">
-        <v>270</v>
+        <v>153</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920037</v>
-      </c>
-      <c r="B7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" t="s">
-        <v>231</v>
-      </c>
-      <c r="D7" t="s">
-        <v>489</v>
-      </c>
-      <c r="E7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F7">
         <v>5</v>
       </c>
     </row>
@@ -7676,7 +7442,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7701,19 +7467,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7721,19 +7487,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7741,19 +7507,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920141</v>
+        <v>21330051920140</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7761,19 +7527,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920141</v>
+        <v>21330051920140</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>422</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7781,19 +7547,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920143</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>443</v>
+        <v>404</v>
       </c>
       <c r="D6" t="s">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7801,19 +7567,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920145</v>
+        <v>21330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>404</v>
       </c>
       <c r="D7" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7821,19 +7587,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920145</v>
+        <v>21330051920143</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>421</v>
       </c>
       <c r="D8" t="s">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7841,21 +7607,101 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
+        <v>21330051920145</v>
+      </c>
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>21330051920145</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>475</v>
+      </c>
+      <c r="E10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>21330051920147</v>
+      </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>476</v>
+      </c>
+      <c r="E11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>21330051920147</v>
+      </c>
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>476</v>
+      </c>
+      <c r="E12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
         <v>21330051920148</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>491</v>
-      </c>
-      <c r="D9" t="s">
-        <v>496</v>
-      </c>
-      <c r="E9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F9">
+      <c r="C13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D13" t="s">
+        <v>477</v>
+      </c>
+      <c r="E13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -7866,7 +7712,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7900,10 +7746,10 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7911,19 +7757,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920063</v>
+        <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
-        <v>342</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>499</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="E3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7931,19 +7777,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920071</v>
+        <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>503</v>
+        <v>482</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>343</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7951,19 +7797,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920073</v>
+        <v>20330051920063</v>
       </c>
       <c r="B5" t="s">
-        <v>497</v>
+        <v>330</v>
       </c>
       <c r="C5" t="s">
-        <v>388</v>
+        <v>480</v>
       </c>
       <c r="D5" t="s">
-        <v>383</v>
+        <v>483</v>
       </c>
       <c r="E5" t="s">
-        <v>507</v>
+        <v>278</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7971,19 +7817,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920073</v>
+        <v>20330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>497</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>383</v>
+        <v>484</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7991,19 +7837,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920080</v>
+        <v>20330051920073</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>478</v>
       </c>
       <c r="C7" t="s">
-        <v>444</v>
+        <v>370</v>
       </c>
       <c r="D7" t="s">
-        <v>468</v>
+        <v>365</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>487</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8011,19 +7857,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920082</v>
+        <v>20330051920073</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>478</v>
       </c>
       <c r="C8" t="s">
-        <v>226</v>
+        <v>370</v>
       </c>
       <c r="D8" t="s">
-        <v>504</v>
+        <v>365</v>
       </c>
       <c r="E8" t="s">
-        <v>355</v>
+        <v>278</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8031,19 +7877,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920082</v>
+        <v>20330051920080</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>226</v>
+        <v>422</v>
       </c>
       <c r="D9" t="s">
-        <v>504</v>
+        <v>447</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8051,19 +7897,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920087</v>
+        <v>20330051920082</v>
       </c>
       <c r="B10" t="s">
-        <v>498</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="D10" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="E10" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8071,21 +7917,41 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920093</v>
+        <v>20330051920082</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>500</v>
+        <v>221</v>
       </c>
       <c r="D11" t="s">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="E11" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>20330051920087</v>
+      </c>
+      <c r="B12" t="s">
+        <v>479</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>486</v>
+      </c>
+      <c r="E12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -8394,16 +8260,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="C2" t="s">
         <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8414,16 +8280,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="E3" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8437,13 +8303,13 @@
         <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D4" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8460,10 +8326,10 @@
         <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8474,16 +8340,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="C6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D6" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>343</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8494,16 +8360,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D7" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="E7" t="s">
-        <v>355</v>
+        <v>278</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8517,13 +8383,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="D8" t="s">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8537,13 +8403,13 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="D9" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8560,10 +8426,10 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8580,10 +8446,10 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8597,13 +8463,13 @@
         <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D12" t="s">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="E12" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8614,16 +8480,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B13" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="C13" t="s">
         <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="E13" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8664,16 +8530,16 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="C2" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="D2" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8684,16 +8550,16 @@
         <v>19330051920425</v>
       </c>
       <c r="B3" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="E3" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8704,16 +8570,16 @@
         <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8727,13 +8593,13 @@
         <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>436</v>
       </c>
       <c r="D5" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8747,13 +8613,13 @@
         <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="D6" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8767,13 +8633,13 @@
         <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="D7" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8786,7 +8652,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8814,16 +8680,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D2" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="E2" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8834,16 +8700,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="E3" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8851,59 +8717,59 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920399</v>
+        <v>19330051920393</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>532</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="E4" t="s">
-        <v>540</v>
+        <v>521</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920116</v>
+        <v>19330051920393</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>533</v>
+        <v>144</v>
       </c>
       <c r="D5" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>522</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920123</v>
+        <v>19330051920399</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>246</v>
+        <v>512</v>
       </c>
       <c r="D6" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>522</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8911,21 +8777,101 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
+        <v>19330051920436</v>
+      </c>
+      <c r="B7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>517</v>
+      </c>
+      <c r="E7" t="s">
+        <v>522</v>
+      </c>
+      <c r="F7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>19330051920436</v>
+      </c>
+      <c r="B8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>517</v>
+      </c>
+      <c r="E8" t="s">
+        <v>521</v>
+      </c>
+      <c r="F8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>20330051920116</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>513</v>
+      </c>
+      <c r="D9" t="s">
+        <v>518</v>
+      </c>
+      <c r="E9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>20330051920123</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" t="s">
+        <v>519</v>
+      </c>
+      <c r="E10" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
         <v>20330051920133</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B11" t="s">
         <v>47</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
-        <v>538</v>
-      </c>
-      <c r="E7" t="s">
-        <v>290</v>
-      </c>
-      <c r="F7">
+      <c r="D11" t="s">
+        <v>520</v>
+      </c>
+      <c r="E11" t="s">
+        <v>279</v>
+      </c>
+      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -8967,13 +8913,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="D2" t="s">
         <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8987,13 +8933,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="D3" t="s">
         <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9004,16 +8950,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="C4" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="D4" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9027,13 +8973,13 @@
         <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="D5" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9047,13 +8993,13 @@
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9067,13 +9013,13 @@
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9084,16 +9030,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D8" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9104,16 +9050,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B9" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="C9" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D9" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9124,16 +9070,16 @@
         <v>20330051920330</v>
       </c>
       <c r="B10" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="C10" t="s">
         <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="E10" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9144,16 +9090,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="C11" t="s">
         <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -9164,16 +9110,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="C12" t="s">
         <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="E12" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -9223,7 +9169,7 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9243,7 +9189,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9513,7 +9459,7 @@
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9533,7 +9479,7 @@
         <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9956,7 +9902,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9990,10 +9936,10 @@
         <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10010,10 +9956,10 @@
         <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10030,10 +9976,10 @@
         <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10050,10 +9996,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10070,10 +10016,10 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10090,10 +10036,10 @@
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10110,10 +10056,10 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10130,10 +10076,10 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10150,10 +10096,10 @@
         <v>142</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -10161,19 +10107,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920171</v>
+        <v>21330051920177</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" t="s">
         <v>151</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -10181,81 +10127,21 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920176</v>
+        <v>21330051920181</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
         <v>152</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920177</v>
-      </c>
-      <c r="B13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" t="s">
-        <v>144</v>
-      </c>
-      <c r="D13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920177</v>
-      </c>
-      <c r="B14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920181</v>
-      </c>
-      <c r="B15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" t="s">
-        <v>155</v>
-      </c>
-      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -10266,7 +10152,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -10297,13 +10183,13 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D2" t="s">
         <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10317,13 +10203,13 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
         <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10343,7 +10229,7 @@
         <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10354,16 +10240,16 @@
         <v>21330051920251</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
         <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10374,16 +10260,16 @@
         <v>21330051920253</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10394,7 +10280,7 @@
         <v>21330051920256</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
@@ -10403,7 +10289,7 @@
         <v>183</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10417,13 +10303,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10431,19 +10317,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920263</v>
+        <v>21330051920262</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10451,19 +10337,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920264</v>
+        <v>21330051920262</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -10471,16 +10357,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920267</v>
+        <v>21330051920263</v>
       </c>
       <c r="B11" t="s">
-        <v>163</v>
+        <v>161</v>
+      </c>
+      <c r="C11" t="s">
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -10488,19 +10377,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920280</v>
+        <v>21330051920264</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -10508,19 +10397,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920282</v>
+        <v>21330051920267</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E13" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -10528,19 +10414,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920282</v>
+        <v>21330051920280</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
         <v>189</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -10548,19 +10434,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920284</v>
+        <v>21330051920282</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>190</v>
       </c>
       <c r="E15" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -10568,19 +10454,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920285</v>
+        <v>21330051920282</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C16" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -10588,19 +10474,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920286</v>
+        <v>21330051920284</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="D17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -10608,19 +10494,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920358</v>
+        <v>21330051920285</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="D18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -10628,19 +10514,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920361</v>
+        <v>21330051920286</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -10648,21 +10534,61 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
+        <v>21330051920358</v>
+      </c>
+      <c r="B20" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>21330051920361</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>195</v>
+      </c>
+      <c r="E21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
         <v>21330051920362</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B22" t="s">
         <v>59</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>177</v>
       </c>
-      <c r="D20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E20" t="s">
-        <v>155</v>
-      </c>
-      <c r="F20">
+      <c r="D22" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22">
         <v>5</v>
       </c>
     </row>
@@ -10673,7 +10599,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -10698,61 +10624,21 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920331</v>
+        <v>21330051920353</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
         <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920334</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920353</v>
-      </c>
-      <c r="B4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4">
         <v>5</v>
       </c>
     </row>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="535">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -447,9 +447,6 @@
     <t>GUSTAVO</t>
   </si>
   <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
@@ -471,9 +468,6 @@
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>MONGE</t>
-  </si>
-  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
@@ -486,9 +480,6 @@
     <t>CRISTIAN ALEXIS</t>
   </si>
   <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
     <t>ALEXANDER</t>
   </si>
   <si>
@@ -510,261 +501,258 @@
     <t>GEOMETRÍA ANALÍTICA</t>
   </si>
   <si>
+    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MADRAZO</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>KARLA GRISELL</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>YARELI</t>
+  </si>
+  <si>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>SUGHEYDI JAZMIN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>NADIA</t>
+  </si>
+  <si>
+    <t>VENUS</t>
+  </si>
+  <si>
+    <t>ANGELO RENE</t>
+  </si>
+  <si>
+    <t>BETHSABE</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>MAGDA SARAY</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>DUILIO</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>DE GANTE</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>YARETZI VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>LAURA EVELYN</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>AMERICA PAOLA</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>CITLALI</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>CHULIN</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>CESAR SAID</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
     <t>INGLÉS III</t>
   </si>
   <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>KARLA GRISELL</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>BETHSABE</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
     <t>MORENO</t>
   </si>
   <si>
@@ -1206,6 +1194,9 @@
     <t>FALFAN</t>
   </si>
   <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
     <t>TEPOLE</t>
   </si>
   <si>
@@ -1227,6 +1218,9 @@
     <t>JOSAVIA ARIDAI</t>
   </si>
   <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
     <t>MARIA ANGELES</t>
   </si>
   <si>
@@ -1383,126 +1377,126 @@
     <t>NAZARIO</t>
   </si>
   <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
     <t>EDGAR</t>
   </si>
   <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>XOCHITL JOSELINE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>XOCHITL JOSELINE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
     <t>SAID ANDRES</t>
   </si>
   <si>
@@ -1611,12 +1605,12 @@
     <t>ABDIEL</t>
   </si>
   <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
     <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
   </si>
   <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
@@ -1632,6 +1626,9 @@
     <t>TLAXCALA</t>
   </si>
   <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
     <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
@@ -1645,6 +1642,12 @@
   </si>
   <si>
     <t>OZIEL</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
   </si>
   <si>
     <t>EMMANUEL</t>
@@ -2309,10 +2312,10 @@
         <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2323,16 +2326,16 @@
         <v>21330051920218</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2343,16 +2346,16 @@
         <v>21330051920219</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2369,10 +2372,10 @@
         <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2386,13 +2389,13 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2412,7 +2415,7 @@
         <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2423,16 +2426,16 @@
         <v>21330051920235</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>150</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2443,16 +2446,16 @@
         <v>21330051920235</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2463,16 +2466,16 @@
         <v>21330051920239</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2483,16 +2486,16 @@
         <v>21330051920240</v>
       </c>
       <c r="B11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" t="s">
         <v>203</v>
       </c>
-      <c r="C11" t="s">
-        <v>206</v>
-      </c>
       <c r="D11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" t="s">
         <v>215</v>
-      </c>
-      <c r="E11" t="s">
-        <v>218</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2503,16 +2506,16 @@
         <v>21330051920240</v>
       </c>
       <c r="B12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" t="s">
         <v>203</v>
       </c>
-      <c r="C12" t="s">
-        <v>206</v>
-      </c>
       <c r="D12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2523,16 +2526,16 @@
         <v>21330051920247</v>
       </c>
       <c r="B13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
         <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2546,13 +2549,13 @@
         <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2565,7 +2568,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2593,16 +2596,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2613,16 +2616,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>234</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2630,19 +2633,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920188</v>
+        <v>21330051920192</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>221</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2650,19 +2653,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920188</v>
+        <v>21330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>222</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2670,19 +2673,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920192</v>
+        <v>21330051920199</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2690,19 +2693,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920193</v>
+        <v>21330051920201</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2710,19 +2713,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920199</v>
+        <v>21330051920202</v>
       </c>
       <c r="B8" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
       <c r="D8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E8" t="s">
         <v>234</v>
-      </c>
-      <c r="E8" t="s">
-        <v>153</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2730,19 +2733,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920201</v>
+        <v>21330051920202</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2750,19 +2753,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>228</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2770,19 +2773,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2790,19 +2793,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920203</v>
+        <v>21330051920213</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>218</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>225</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2810,61 +2813,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920203</v>
+        <v>21330051920386</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920213</v>
-      </c>
-      <c r="B14" t="s">
-        <v>222</v>
-      </c>
-      <c r="C14" t="s">
-        <v>229</v>
-      </c>
-      <c r="D14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" t="s">
-        <v>153</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920386</v>
-      </c>
-      <c r="B15" t="s">
-        <v>223</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>238</v>
-      </c>
-      <c r="E15" t="s">
-        <v>153</v>
-      </c>
-      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -2903,16 +2866,16 @@
         <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2929,10 +2892,10 @@
         <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2943,16 +2906,16 @@
         <v>21330051920298</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2969,10 +2932,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2983,16 +2946,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" t="s">
-        <v>245</v>
-      </c>
       <c r="D6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3006,13 +2969,13 @@
         <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3023,16 +2986,16 @@
         <v>21330051920308</v>
       </c>
       <c r="B8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
         <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E8" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3043,16 +3006,16 @@
         <v>21330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C9" t="s">
         <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3069,10 +3032,10 @@
         <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3089,10 +3052,10 @@
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3103,16 +3066,16 @@
         <v>21330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3123,16 +3086,16 @@
         <v>21330051920328</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D13" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E13" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3173,16 +3136,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3193,16 +3156,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3213,16 +3176,16 @@
         <v>20330051920011</v>
       </c>
       <c r="B4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3233,16 +3196,16 @@
         <v>20330051920012</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3256,13 +3219,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D6" t="s">
         <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3276,13 +3239,13 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D7" t="s">
         <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3293,16 +3256,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E8" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3313,16 +3276,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3333,16 +3296,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3353,16 +3316,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3373,16 +3336,16 @@
         <v>20330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E12" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3399,10 +3362,10 @@
         <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E13" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3419,10 +3382,10 @@
         <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E14" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3436,13 +3399,13 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E15" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -3453,16 +3416,16 @@
         <v>20330051920362</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C16" t="s">
         <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -3476,13 +3439,13 @@
         <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E17" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -3526,13 +3489,13 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3543,16 +3506,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C3" t="s">
         <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3563,16 +3526,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3592,7 +3555,7 @@
         <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3603,16 +3566,16 @@
         <v>20330051920243</v>
       </c>
       <c r="B6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3623,16 +3586,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D7" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3643,16 +3606,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3663,16 +3626,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3683,16 +3646,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D10" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3703,16 +3666,16 @@
         <v>20330051920374</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3753,16 +3716,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" t="s">
         <v>295</v>
       </c>
-      <c r="D2" t="s">
-        <v>299</v>
-      </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3776,13 +3739,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" t="s">
         <v>296</v>
       </c>
-      <c r="D3" t="s">
-        <v>300</v>
-      </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3796,13 +3759,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D4" t="s">
         <v>297</v>
       </c>
-      <c r="D4" t="s">
-        <v>301</v>
-      </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3816,13 +3779,13 @@
         <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3833,16 +3796,16 @@
         <v>20330051920349</v>
       </c>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3853,16 +3816,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3876,13 +3839,13 @@
         <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3899,10 +3862,10 @@
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3943,16 +3906,16 @@
         <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3963,16 +3926,16 @@
         <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3989,10 +3952,10 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4009,10 +3972,10 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4029,10 +3992,10 @@
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4043,16 +4006,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4063,16 +4026,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B8" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E8" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4083,16 +4046,16 @@
         <v>20330051920173</v>
       </c>
       <c r="B9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C9" t="s">
         <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4103,16 +4066,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B10" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E10" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4123,16 +4086,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B11" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C11" t="s">
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4143,16 +4106,16 @@
         <v>20330051920178</v>
       </c>
       <c r="B12" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E12" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4166,16 +4129,16 @@
         <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D13" t="s">
         <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4186,16 +4149,16 @@
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D14" t="s">
         <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4203,16 +4166,16 @@
         <v>20330051920388</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C15" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D15" t="s">
         <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4223,16 +4186,16 @@
         <v>20330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C16" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D16" t="s">
         <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4273,16 +4236,16 @@
         <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4293,16 +4256,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4316,13 +4279,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4336,13 +4299,13 @@
         <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E5" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4356,13 +4319,13 @@
         <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4376,13 +4339,13 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4393,16 +4356,16 @@
         <v>20330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4416,13 +4379,13 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D9" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4436,13 +4399,13 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D10" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4459,10 +4422,10 @@
         <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4473,16 +4436,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B12" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C12" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D12" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E12" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4493,16 +4456,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B13" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C13" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D13" t="s">
+        <v>336</v>
+      </c>
+      <c r="E13" t="s">
         <v>340</v>
-      </c>
-      <c r="E13" t="s">
-        <v>343</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4519,10 +4482,10 @@
         <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E14" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4539,10 +4502,10 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E15" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4583,16 +4546,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4609,10 +4572,10 @@
         <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4629,10 +4592,10 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4649,10 +4612,10 @@
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4669,10 +4632,10 @@
         <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4689,10 +4652,10 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4739,10 +4702,10 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E2" t="s">
-        <v>369</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4759,10 +4722,10 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>365</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4776,10 +4739,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D4" t="s">
         <v>355</v>
-      </c>
-      <c r="D4" t="s">
-        <v>359</v>
       </c>
       <c r="E4" t="s">
         <v>37</v>
@@ -4796,10 +4759,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" t="s">
         <v>355</v>
-      </c>
-      <c r="D5" t="s">
-        <v>359</v>
       </c>
       <c r="E5" t="s">
         <v>35</v>
@@ -4816,10 +4779,10 @@
         <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -4833,13 +4796,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B7" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
@@ -4856,10 +4819,10 @@
         <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
@@ -4873,13 +4836,13 @@
         <v>22330051920201</v>
       </c>
       <c r="B9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C9" t="s">
         <v>352</v>
       </c>
-      <c r="C9" t="s">
-        <v>356</v>
-      </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
         <v>35</v>
@@ -4893,13 +4856,13 @@
         <v>22330051920201</v>
       </c>
       <c r="B10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C10" t="s">
         <v>352</v>
       </c>
-      <c r="C10" t="s">
-        <v>356</v>
-      </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
         <v>37</v>
@@ -4916,13 +4879,13 @@
         <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D11" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4936,13 +4899,13 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D12" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4953,13 +4916,13 @@
         <v>22330051920359</v>
       </c>
       <c r="B13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C13" t="s">
         <v>353</v>
       </c>
-      <c r="C13" t="s">
-        <v>357</v>
-      </c>
       <c r="D13" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E13" t="s">
         <v>37</v>
@@ -4979,7 +4942,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -4996,10 +4959,10 @@
         <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D15" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
@@ -5016,10 +4979,10 @@
         <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D16" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
@@ -5039,7 +5002,7 @@
         <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E17" t="s">
         <v>37</v>
@@ -5053,13 +5016,13 @@
         <v>22330051920390</v>
       </c>
       <c r="B18" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C18" t="s">
         <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E18" t="s">
         <v>37</v>
@@ -5132,7 +5095,7 @@
         <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5152,7 +5115,7 @@
         <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5316,10 +5279,10 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
         <v>37</v>
@@ -5339,7 +5302,7 @@
         <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E3" t="s">
         <v>37</v>
@@ -5353,13 +5316,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E4" t="s">
         <v>37</v>
@@ -5373,13 +5336,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E5" t="s">
         <v>56</v>
@@ -5393,13 +5356,13 @@
         <v>22330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E6" t="s">
         <v>56</v>
@@ -5413,13 +5376,13 @@
         <v>22330051920218</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D7" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -5433,13 +5396,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
         <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
@@ -5453,13 +5416,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C9" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D9" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
@@ -5473,13 +5436,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C10" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D10" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -5496,10 +5459,10 @@
         <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D11" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
@@ -5519,7 +5482,7 @@
         <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E12" t="s">
         <v>35</v>
@@ -5536,10 +5499,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D13" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -5555,7 +5518,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5583,13 +5546,13 @@
         <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D2" t="s">
         <v>387</v>
-      </c>
-      <c r="D2" t="s">
-        <v>390</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -5606,13 +5569,13 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
+        <v>385</v>
+      </c>
+      <c r="D3" t="s">
         <v>388</v>
       </c>
-      <c r="D3" t="s">
-        <v>391</v>
-      </c>
       <c r="E3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5623,13 +5586,13 @@
         <v>22330051920238</v>
       </c>
       <c r="B4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E4" t="s">
         <v>56</v>
@@ -5640,16 +5603,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920242</v>
+        <v>22330051920239</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>382</v>
       </c>
       <c r="C5" t="s">
-        <v>309</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>390</v>
       </c>
       <c r="E5" t="s">
         <v>56</v>
@@ -5660,19 +5623,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920243</v>
+        <v>22330051920239</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>382</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E6" t="s">
-        <v>369</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5680,16 +5643,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920256</v>
+        <v>22330051920242</v>
       </c>
       <c r="B7" t="s">
-        <v>386</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>389</v>
+        <v>305</v>
       </c>
       <c r="D7" t="s">
-        <v>394</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>56</v>
@@ -5700,19 +5663,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920357</v>
+        <v>22330051920243</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>365</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5720,16 +5683,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920366</v>
+        <v>22330051920256</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>383</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>386</v>
       </c>
       <c r="D9" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E9" t="s">
         <v>56</v>
@@ -5740,19 +5703,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920366</v>
+        <v>22330051920357</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5760,19 +5723,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920369</v>
+        <v>22330051920366</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>222</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5780,21 +5743,61 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
+        <v>22330051920366</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>394</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
         <v>22330051920369</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D12" t="s">
-        <v>397</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D13" t="s">
+        <v>395</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>22330051920369</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D14" t="s">
+        <v>395</v>
+      </c>
+      <c r="E14" t="s">
         <v>35</v>
       </c>
-      <c r="F12">
+      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -5836,13 +5839,13 @@
         <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5856,13 +5859,13 @@
         <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5876,13 +5879,13 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E4" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5896,10 +5899,10 @@
         <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E5" t="s">
         <v>56</v>
@@ -5916,10 +5919,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E6" t="s">
         <v>56</v>
@@ -5933,13 +5936,13 @@
         <v>22330051920272</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E7" t="s">
         <v>56</v>
@@ -5959,10 +5962,10 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5979,10 +5982,10 @@
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5996,13 +5999,13 @@
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6016,13 +6019,13 @@
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D11" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6033,7 +6036,7 @@
         <v>22330051920281</v>
       </c>
       <c r="B12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C12" t="s">
         <v>87</v>
@@ -6042,7 +6045,7 @@
         <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6053,7 +6056,7 @@
         <v>22330051920281</v>
       </c>
       <c r="B13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C13" t="s">
         <v>87</v>
@@ -6062,7 +6065,7 @@
         <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6073,13 +6076,13 @@
         <v>22330051920283</v>
       </c>
       <c r="B14" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C14" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -6099,7 +6102,7 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E15" t="s">
         <v>35</v>
@@ -6116,7 +6119,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D16" t="s">
         <v>127</v>
@@ -6139,10 +6142,10 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E17" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -6159,7 +6162,7 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E18" t="s">
         <v>56</v>
@@ -6179,7 +6182,7 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E19" t="s">
         <v>56</v>
@@ -6223,16 +6226,16 @@
         <v>22330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6249,7 +6252,7 @@
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E3" t="s">
         <v>56</v>
@@ -6269,10 +6272,10 @@
         <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E4" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6286,13 +6289,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6303,13 +6306,13 @@
         <v>22330051920298</v>
       </c>
       <c r="B6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E6" t="s">
         <v>56</v>
@@ -6329,7 +6332,7 @@
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
@@ -6346,13 +6349,13 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>365</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6366,13 +6369,13 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E9" t="s">
-        <v>369</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6386,13 +6389,13 @@
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>365</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6406,13 +6409,13 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E11" t="s">
-        <v>369</v>
+        <v>56</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6423,16 +6426,16 @@
         <v>22330051920308</v>
       </c>
       <c r="B12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6443,16 +6446,16 @@
         <v>22330051920308</v>
       </c>
       <c r="B13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6463,13 +6466,13 @@
         <v>22330051920311</v>
       </c>
       <c r="B14" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D14" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E14" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6480,13 +6483,13 @@
         <v>22330051920312</v>
       </c>
       <c r="B15" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C15" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D15" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -6503,10 +6506,10 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D16" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E16" t="s">
         <v>56</v>
@@ -6523,10 +6526,10 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D17" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E17" t="s">
         <v>37</v>
@@ -6540,16 +6543,16 @@
         <v>22330051920315</v>
       </c>
       <c r="B18" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D18" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>365</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -6560,16 +6563,16 @@
         <v>22330051920315</v>
       </c>
       <c r="B19" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C19" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D19" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E19" t="s">
-        <v>369</v>
+        <v>35</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -6580,16 +6583,16 @@
         <v>22330051920360</v>
       </c>
       <c r="B20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C20" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D20" t="s">
         <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -6603,10 +6606,10 @@
         <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D21" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E21" t="s">
         <v>56</v>
@@ -6620,16 +6623,16 @@
         <v>22330051920397</v>
       </c>
       <c r="B22" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C22" t="s">
         <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -6640,16 +6643,16 @@
         <v>22330051920397</v>
       </c>
       <c r="B23" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C23" t="s">
         <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -6663,7 +6666,7 @@
         <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D24" t="s">
         <v>76</v>
@@ -6680,13 +6683,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B25" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C25" t="s">
         <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E25" t="s">
         <v>36</v>
@@ -6700,13 +6703,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B26" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C26" t="s">
         <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E26" t="s">
         <v>56</v>
@@ -6729,7 +6732,7 @@
         <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>365</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -6749,7 +6752,7 @@
         <v>76</v>
       </c>
       <c r="E28" t="s">
-        <v>369</v>
+        <v>56</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -6790,16 +6793,16 @@
         <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D2" t="s">
         <v>444</v>
       </c>
-      <c r="D2" t="s">
-        <v>445</v>
-      </c>
       <c r="E2" t="s">
-        <v>258</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6807,19 +6810,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920089</v>
+        <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
-        <v>443</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>329</v>
+        <v>442</v>
       </c>
       <c r="D3" t="s">
-        <v>268</v>
+        <v>444</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6827,19 +6830,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920089</v>
+        <v>20330051920019</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
         <v>443</v>
       </c>
-      <c r="C4" t="s">
-        <v>329</v>
-      </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>448</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6847,19 +6850,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>441</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>325</v>
       </c>
       <c r="D5" t="s">
-        <v>446</v>
+        <v>264</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6867,19 +6870,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920195</v>
+        <v>20330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>441</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>325</v>
       </c>
       <c r="D6" t="s">
-        <v>447</v>
+        <v>264</v>
       </c>
       <c r="E6" t="s">
-        <v>448</v>
+        <v>153</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6887,19 +6890,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920195</v>
+        <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6943,13 +6946,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D2" t="s">
         <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6963,13 +6966,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D3" t="s">
         <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>258</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6986,10 +6989,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7009,7 +7012,7 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7020,16 +7023,16 @@
         <v>21330051920103</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C6" t="s">
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7043,13 +7046,13 @@
         <v>95</v>
       </c>
       <c r="C7" t="s">
+        <v>448</v>
+      </c>
+      <c r="D7" t="s">
         <v>451</v>
       </c>
-      <c r="D7" t="s">
-        <v>454</v>
-      </c>
       <c r="E7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7066,10 +7069,10 @@
         <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E8" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7086,10 +7089,10 @@
         <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>253</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7133,13 +7136,13 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7150,16 +7153,16 @@
         <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7170,16 +7173,16 @@
         <v>21330051920113</v>
       </c>
       <c r="B4" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7190,16 +7193,16 @@
         <v>21330051920117</v>
       </c>
       <c r="B5" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7210,16 +7213,16 @@
         <v>21330051920117</v>
       </c>
       <c r="B6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7236,10 +7239,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7256,10 +7259,10 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7276,10 +7279,10 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7290,16 +7293,16 @@
         <v>21330051920130</v>
       </c>
       <c r="B10" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C10" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D10" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7340,16 +7343,16 @@
         <v>20330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7360,16 +7363,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C3" t="s">
         <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7380,16 +7383,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>150</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7400,16 +7403,16 @@
         <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D5" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7420,16 +7423,16 @@
         <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7442,7 +7445,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7476,10 +7479,10 @@
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7496,10 +7499,10 @@
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>234</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7516,10 +7519,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7536,10 +7539,10 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7553,13 +7556,13 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7573,13 +7576,13 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E7" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7593,13 +7596,13 @@
         <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D8" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7616,10 +7619,10 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>234</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7636,10 +7639,10 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7656,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>234</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7676,10 +7679,10 @@
         <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7693,15 +7696,55 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D13" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>21330051920382</v>
+      </c>
+      <c r="B14" t="s">
+        <v>467</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>476</v>
+      </c>
+      <c r="E14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>21330051920382</v>
+      </c>
+      <c r="B15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>476</v>
+      </c>
+      <c r="E15" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -7712,7 +7755,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7746,10 +7789,10 @@
         <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7760,16 +7803,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7780,16 +7823,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7797,19 +7840,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920063</v>
+        <v>20330051920071</v>
       </c>
       <c r="B5" t="s">
-        <v>330</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>480</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7817,19 +7860,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920071</v>
+        <v>20330051920073</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>477</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>366</v>
       </c>
       <c r="D6" t="s">
-        <v>484</v>
+        <v>361</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>485</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7840,16 +7883,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D7" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E7" t="s">
-        <v>487</v>
+        <v>274</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7857,19 +7900,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920073</v>
+        <v>20330051920080</v>
       </c>
       <c r="B8" t="s">
-        <v>478</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>370</v>
+        <v>420</v>
       </c>
       <c r="D8" t="s">
-        <v>365</v>
+        <v>482</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7877,19 +7920,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920080</v>
+        <v>20330051920082</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>422</v>
+        <v>217</v>
       </c>
       <c r="D9" t="s">
-        <v>447</v>
+        <v>483</v>
       </c>
       <c r="E9" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7903,13 +7946,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D10" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E10" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7917,41 +7960,21 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920082</v>
+        <v>20330051920087</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>478</v>
       </c>
       <c r="C11" t="s">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E11" t="s">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920087</v>
-      </c>
-      <c r="B12" t="s">
-        <v>479</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>486</v>
-      </c>
-      <c r="E12" t="s">
-        <v>279</v>
-      </c>
-      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -8232,7 +8255,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8260,16 +8283,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C2" t="s">
         <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8280,16 +8303,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8303,13 +8326,13 @@
         <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8326,10 +8349,10 @@
         <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8337,19 +8360,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920196</v>
+        <v>20330051920193</v>
       </c>
       <c r="B6" t="s">
-        <v>489</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E6" t="s">
-        <v>343</v>
+        <v>274</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8360,16 +8383,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D7" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8377,19 +8400,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920198</v>
+        <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>487</v>
       </c>
       <c r="C8" t="s">
-        <v>491</v>
+        <v>235</v>
       </c>
       <c r="D8" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8397,19 +8420,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920213</v>
+        <v>20330051920198</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D9" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8417,19 +8440,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920214</v>
+        <v>20330051920213</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="D10" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8446,10 +8469,10 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8457,19 +8480,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920217</v>
+        <v>20330051920214</v>
       </c>
       <c r="B12" t="s">
         <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8477,21 +8500,61 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
+        <v>20330051920217</v>
+      </c>
+      <c r="B13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" t="s">
+        <v>498</v>
+      </c>
+      <c r="E13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
         <v>20330051920218</v>
       </c>
-      <c r="B13" t="s">
-        <v>490</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>488</v>
+      </c>
+      <c r="C14" t="s">
         <v>122</v>
       </c>
-      <c r="D13" t="s">
-        <v>501</v>
-      </c>
-      <c r="E13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F13">
+      <c r="D14" t="s">
+        <v>499</v>
+      </c>
+      <c r="E14" t="s">
+        <v>275</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>20330051920218</v>
+      </c>
+      <c r="B15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" t="s">
+        <v>499</v>
+      </c>
+      <c r="E15" t="s">
+        <v>274</v>
+      </c>
+      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -8530,16 +8593,16 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8550,16 +8613,16 @@
         <v>19330051920425</v>
       </c>
       <c r="B3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8570,16 +8633,16 @@
         <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8593,13 +8656,13 @@
         <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8610,16 +8673,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8630,16 +8693,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8652,7 +8715,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8680,16 +8743,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8700,16 +8763,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8717,22 +8780,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920393</v>
+        <v>19330051920383</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>305</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>419</v>
       </c>
       <c r="D4" t="s">
-        <v>515</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8743,13 +8806,13 @@
         <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -8757,42 +8820,42 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920399</v>
+        <v>19330051920393</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>512</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E6" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920436</v>
+        <v>19330051920399</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c r="D7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8800,16 +8863,16 @@
         <v>19330051920436</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -8817,39 +8880,39 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920116</v>
+        <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s">
-        <v>513</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>520</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920123</v>
+        <v>20330051920116</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>264</v>
+        <v>511</v>
       </c>
       <c r="D10" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E10" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8857,21 +8920,41 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
+        <v>20330051920123</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" t="s">
+        <v>517</v>
+      </c>
+      <c r="E11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
         <v>20330051920133</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
-        <v>520</v>
-      </c>
-      <c r="E11" t="s">
-        <v>279</v>
-      </c>
-      <c r="F11">
+      <c r="D12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E12" t="s">
+        <v>275</v>
+      </c>
+      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -8882,7 +8965,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8913,13 +8996,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D2" t="s">
         <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8933,13 +9016,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D3" t="s">
         <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8950,16 +9033,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8973,13 +9056,13 @@
         <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8987,19 +9070,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920326</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>530</v>
+        <v>428</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9013,13 +9096,13 @@
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9027,19 +9110,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920329</v>
+        <v>20330051920326</v>
       </c>
       <c r="B8" t="s">
-        <v>404</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>313</v>
+        <v>163</v>
       </c>
       <c r="D8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9050,16 +9133,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9067,19 +9150,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920330</v>
+        <v>20330051920329</v>
       </c>
       <c r="B10" t="s">
-        <v>524</v>
+        <v>402</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>309</v>
       </c>
       <c r="D10" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E10" t="s">
-        <v>343</v>
+        <v>274</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9087,19 +9170,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920397</v>
+        <v>20330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -9107,21 +9190,81 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
+        <v>20330051920331</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" t="s">
+        <v>532</v>
+      </c>
+      <c r="E12" t="s">
+        <v>274</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>20330051920335</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" t="s">
+        <v>526</v>
+      </c>
+      <c r="D13" t="s">
+        <v>533</v>
+      </c>
+      <c r="E13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
         <v>20330051920397</v>
       </c>
-      <c r="B12" t="s">
-        <v>525</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B14" t="s">
+        <v>523</v>
+      </c>
+      <c r="C14" t="s">
         <v>59</v>
       </c>
-      <c r="D12" t="s">
-        <v>533</v>
-      </c>
-      <c r="E12" t="s">
-        <v>278</v>
-      </c>
-      <c r="F12">
+      <c r="D14" t="s">
+        <v>534</v>
+      </c>
+      <c r="E14" t="s">
+        <v>275</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>20330051920397</v>
+      </c>
+      <c r="B15" t="s">
+        <v>523</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>534</v>
+      </c>
+      <c r="E15" t="s">
+        <v>274</v>
+      </c>
+      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -9499,7 +9642,7 @@
         <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -9519,7 +9662,7 @@
         <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -9539,7 +9682,7 @@
         <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -9559,7 +9702,7 @@
         <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -9619,7 +9762,7 @@
         <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -9639,7 +9782,7 @@
         <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -9749,7 +9892,7 @@
         <v>128</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9769,7 +9912,7 @@
         <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9869,7 +10012,7 @@
         <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9889,7 +10032,7 @@
         <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9902,7 +10045,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9933,13 +10076,13 @@
         <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9947,19 +10090,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920154</v>
+        <v>21330051920157</v>
       </c>
       <c r="B3" t="s">
         <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9967,19 +10110,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920154</v>
+        <v>21330051920157</v>
       </c>
       <c r="B4" t="s">
         <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9987,19 +10130,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920157</v>
+        <v>21330051920162</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10007,19 +10150,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920157</v>
+        <v>21330051920162</v>
       </c>
       <c r="B6" t="s">
         <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10027,19 +10170,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920162</v>
+        <v>21330051920164</v>
       </c>
       <c r="B7" t="s">
         <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10050,16 +10193,16 @@
         <v>21330051920164</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10067,19 +10210,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920164</v>
+        <v>21330051920171</v>
       </c>
       <c r="B9" t="s">
         <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10087,19 +10230,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920171</v>
+        <v>21330051920177</v>
       </c>
       <c r="B10" t="s">
         <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" t="s">
         <v>150</v>
-      </c>
-      <c r="E10" t="s">
-        <v>153</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -10107,41 +10250,21 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920177</v>
+        <v>21330051920181</v>
       </c>
       <c r="B11" t="s">
         <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920181</v>
-      </c>
-      <c r="B12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -10183,13 +10306,13 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -10203,13 +10326,13 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -10220,16 +10343,16 @@
         <v>21330051920088</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -10240,16 +10363,16 @@
         <v>21330051920251</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -10260,16 +10383,16 @@
         <v>21330051920253</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -10280,16 +10403,16 @@
         <v>21330051920256</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -10303,13 +10426,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -10320,16 +10443,16 @@
         <v>21330051920262</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -10340,16 +10463,16 @@
         <v>21330051920262</v>
       </c>
       <c r="B10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -10360,16 +10483,16 @@
         <v>21330051920263</v>
       </c>
       <c r="B11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -10383,13 +10506,13 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -10400,13 +10523,13 @@
         <v>21330051920267</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -10423,10 +10546,10 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -10437,16 +10560,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s">
         <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E15" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -10457,16 +10580,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
         <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -10480,13 +10603,13 @@
         <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -10497,16 +10620,16 @@
         <v>21330051920285</v>
       </c>
       <c r="B18" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E18" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -10517,16 +10640,16 @@
         <v>21330051920286</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
         <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -10537,16 +10660,16 @@
         <v>21330051920358</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D20" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E20" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -10563,10 +10686,10 @@
         <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -10580,13 +10703,13 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D22" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E22" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -10627,16 +10750,16 @@
         <v>21330051920353</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F2">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="491">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -306,6 +306,9 @@
     <t>PRADO</t>
   </si>
   <si>
+    <t>LUGO</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -318,6 +321,9 @@
     <t>ANETTE</t>
   </si>
   <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
     <t>BETSABETH</t>
   </si>
   <si>
@@ -465,6 +471,9 @@
     <t>GUSTAVO</t>
   </si>
   <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
@@ -474,1036 +483,1024 @@
     <t>LOYO</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
     <t>TZITZIHUA</t>
   </si>
   <si>
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>ADALY</t>
+  </si>
+  <si>
+    <t>GEOMETRÍA ANALÍTICA</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>INGLÉS III</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>ÉTICA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>IVANNA DANIELA</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ANGEL FIDEL</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>GEOMETRÍA ANALÍTICA</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA I</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>VALERIA DANAY</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>EVELYN ROSALIA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>ATLAHUA</t>
+  </si>
+  <si>
+    <t>UREÑA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GERMAN</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>JULISSA</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
   </si>
   <si>
     <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
   </si>
   <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MELANI PAOLA</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>CONTRIBUYE A LA INTEGRACIÓN Y DESARROLLO DEL PERSONAL EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>INGLÉS III</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ÉTICA</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>IMPLEMENTA Y MANTIENE LOS SISTEMAS DE ENERGÍA RENOVABLE</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>JESUS IVAN</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA I</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>UREÑA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>GERMAN</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>AYALA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
   </si>
   <si>
     <t>MARCOS</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>XOCHITL JOSELINE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>URIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
   </si>
   <si>
     <t>JESUS ANTONIO</t>
@@ -2016,7 +2013,7 @@
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2036,7 +2033,7 @@
         <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2116,7 +2113,7 @@
         <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2136,7 +2133,7 @@
         <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2209,7 +2206,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2240,13 +2237,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2254,19 +2251,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920218</v>
+        <v>21330051920222</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2274,19 +2271,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920219</v>
+        <v>21330051920234</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2294,19 +2291,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920220</v>
+        <v>21330051920234</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2314,19 +2311,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920222</v>
+        <v>21330051920235</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2334,19 +2331,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920230</v>
+        <v>21330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2354,19 +2351,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920235</v>
+        <v>21330051920237</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2374,19 +2371,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920235</v>
+        <v>21330051920240</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2394,19 +2391,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920239</v>
+        <v>21330051920250</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>179</v>
       </c>
       <c r="D10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2414,19 +2411,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920240</v>
+        <v>21330051920359</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2434,61 +2431,21 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920240</v>
+        <v>21330051920359</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920247</v>
-      </c>
-      <c r="B13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920250</v>
-      </c>
-      <c r="B14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" t="s">
-        <v>177</v>
-      </c>
-      <c r="D14" t="s">
-        <v>187</v>
-      </c>
-      <c r="E14" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -2499,7 +2456,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2527,16 +2484,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2547,16 +2504,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E3" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2564,19 +2521,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920192</v>
+        <v>21330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2584,19 +2541,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920193</v>
+        <v>21330051920199</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2604,19 +2561,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920199</v>
+        <v>21330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2624,19 +2581,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920201</v>
+        <v>21330051920203</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2644,19 +2601,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2664,19 +2621,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920202</v>
+        <v>21330051920213</v>
       </c>
       <c r="B9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D9" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2684,81 +2641,21 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920203</v>
+        <v>21330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920203</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>206</v>
-      </c>
-      <c r="E11" t="s">
-        <v>208</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920213</v>
-      </c>
-      <c r="B12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920386</v>
-      </c>
-      <c r="B13" t="s">
-        <v>192</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>207</v>
-      </c>
-      <c r="E13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -2800,13 +2697,13 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2817,16 +2714,16 @@
         <v>21330051920298</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2837,16 +2734,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D4" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2860,13 +2757,13 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2880,13 +2777,13 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
+        <v>163</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2897,16 +2794,16 @@
         <v>21330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2917,16 +2814,16 @@
         <v>21330051920328</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E8" t="s">
         <v>215</v>
-      </c>
-      <c r="D8" t="s">
-        <v>221</v>
-      </c>
-      <c r="E8" t="s">
-        <v>222</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2937,16 +2834,16 @@
         <v>21330051920328</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2987,16 +2884,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>221</v>
       </c>
       <c r="D2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3007,16 +2904,16 @@
         <v>20330051920011</v>
       </c>
       <c r="B3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" t="s">
         <v>233</v>
-      </c>
-      <c r="E3" t="s">
-        <v>240</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3027,16 +2924,16 @@
         <v>20330051920012</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D4" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3050,13 +2947,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3070,13 +2967,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3087,16 +2984,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E7" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3107,16 +3004,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
       </c>
       <c r="D8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" t="s">
         <v>235</v>
-      </c>
-      <c r="E8" t="s">
-        <v>241</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3127,16 +3024,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B9" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3153,10 +3050,10 @@
         <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3170,13 +3067,13 @@
         <v>45</v>
       </c>
       <c r="C11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" t="s">
         <v>231</v>
       </c>
-      <c r="D11" t="s">
-        <v>238</v>
-      </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -3187,16 +3084,16 @@
         <v>20330051920362</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C12" t="s">
         <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E12" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3237,16 +3134,16 @@
         <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3257,16 +3154,16 @@
         <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3277,16 +3174,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
         <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3297,16 +3194,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C5" t="s">
         <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3317,16 +3214,16 @@
         <v>20330051920241</v>
       </c>
       <c r="B6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" t="s">
         <v>244</v>
       </c>
-      <c r="C6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D6" t="s">
-        <v>251</v>
-      </c>
       <c r="E6" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3337,16 +3234,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" t="s">
         <v>245</v>
       </c>
-      <c r="C7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" t="s">
-        <v>252</v>
-      </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3357,16 +3254,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" t="s">
         <v>245</v>
       </c>
-      <c r="C8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D8" t="s">
-        <v>252</v>
-      </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3377,16 +3274,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D9" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E9" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3397,16 +3294,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3447,16 +3344,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3470,13 +3367,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3490,13 +3387,13 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3507,16 +3404,16 @@
         <v>20330051920349</v>
       </c>
       <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" t="s">
         <v>255</v>
       </c>
-      <c r="C5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" t="s">
-        <v>262</v>
-      </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3527,16 +3424,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E6" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3547,16 +3444,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3567,16 +3464,16 @@
         <v>20330051920356</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D8" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3590,13 +3487,13 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E9" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3637,16 +3534,16 @@
         <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" t="s">
         <v>266</v>
       </c>
-      <c r="C2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D2" t="s">
-        <v>273</v>
-      </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3663,10 +3560,10 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3683,10 +3580,10 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3697,16 +3594,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3717,16 +3614,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E6" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3737,16 +3634,16 @@
         <v>20330051920173</v>
       </c>
       <c r="B7" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
         <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3757,16 +3654,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B8" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C8" t="s">
         <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3777,19 +3674,19 @@
         <v>20330051920182</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D9" t="s">
         <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3797,19 +3694,19 @@
         <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
         <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3817,7 +3714,7 @@
         <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -3826,7 +3723,7 @@
         <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3839,7 +3736,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3867,16 +3764,16 @@
         <v>20330051920044</v>
       </c>
       <c r="B2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3887,16 +3784,16 @@
         <v>20330051920046</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3910,13 +3807,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D4" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3927,16 +3824,16 @@
         <v>20330051920058</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D5" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E5" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3944,19 +3841,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920058</v>
+        <v>20330051920096</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" t="s">
         <v>285</v>
       </c>
-      <c r="D6" t="s">
-        <v>292</v>
-      </c>
       <c r="E6" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3964,19 +3861,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920096</v>
+        <v>20330051920097</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>279</v>
       </c>
       <c r="D7" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3984,19 +3881,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920097</v>
+        <v>20330051920104</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>286</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4004,19 +3901,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920101</v>
+        <v>20330051920111</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>274</v>
       </c>
       <c r="C9" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D9" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E9" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4024,19 +3921,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920101</v>
+        <v>20330051920112</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>287</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E10" t="s">
-        <v>241</v>
+        <v>291</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4044,81 +3941,21 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920104</v>
+        <v>20330051920112</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920111</v>
-      </c>
-      <c r="B12" t="s">
-        <v>281</v>
-      </c>
-      <c r="C12" t="s">
-        <v>288</v>
-      </c>
-      <c r="D12" t="s">
-        <v>297</v>
-      </c>
-      <c r="E12" t="s">
-        <v>300</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920111</v>
-      </c>
-      <c r="B13" t="s">
-        <v>281</v>
-      </c>
-      <c r="C13" t="s">
-        <v>288</v>
-      </c>
-      <c r="D13" t="s">
-        <v>297</v>
-      </c>
-      <c r="E13" t="s">
-        <v>299</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920112</v>
-      </c>
-      <c r="B14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>298</v>
-      </c>
-      <c r="E14" t="s">
-        <v>240</v>
-      </c>
-      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -4157,16 +3994,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4180,13 +4017,13 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4197,16 +4034,16 @@
         <v>20330051920301</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4223,10 +4060,10 @@
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4237,16 +4074,16 @@
         <v>20330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E6" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4257,16 +4094,16 @@
         <v>20330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4307,13 +4144,13 @@
         <v>21330051920265</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -4327,16 +4164,16 @@
         <v>21330051920265</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E3" t="s">
         <v>314</v>
-      </c>
-      <c r="E3" t="s">
-        <v>323</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4350,13 +4187,13 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D4" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4370,13 +4207,13 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D5" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4387,16 +4224,16 @@
         <v>22330051920195</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4404,19 +4241,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920199</v>
+        <v>22330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>312</v>
+        <v>222</v>
       </c>
       <c r="D7" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4424,16 +4261,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920201</v>
+        <v>22330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>308</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
@@ -4444,19 +4281,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920204</v>
+        <v>22330051920201</v>
       </c>
       <c r="B9" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C9" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D9" t="s">
-        <v>318</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4467,16 +4304,16 @@
         <v>22330051920204</v>
       </c>
       <c r="B10" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D10" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4490,10 +4327,10 @@
         <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="D11" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
@@ -4507,13 +4344,13 @@
         <v>22330051920371</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E12" t="s">
         <v>62</v>
@@ -4527,16 +4364,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D13" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4547,16 +4384,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D14" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4567,13 +4404,13 @@
         <v>22330051920388</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E15" t="s">
         <v>82</v>
@@ -4766,7 +4603,7 @@
         <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4786,7 +4623,7 @@
         <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4870,10 +4707,10 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>221</v>
       </c>
       <c r="D2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -4887,13 +4724,13 @@
         <v>22330051920215</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
         <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="E3" t="s">
         <v>82</v>
@@ -4907,13 +4744,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E4" t="s">
         <v>82</v>
@@ -4927,13 +4764,13 @@
         <v>22330051920216</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E5" t="s">
         <v>62</v>
@@ -4947,16 +4784,16 @@
         <v>22330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D6" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4967,16 +4804,16 @@
         <v>22330051920218</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D7" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4987,13 +4824,13 @@
         <v>22330051920222</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C8" t="s">
         <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E8" t="s">
         <v>82</v>
@@ -5007,16 +4844,16 @@
         <v>22330051920224</v>
       </c>
       <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" t="s">
         <v>325</v>
       </c>
-      <c r="C9" t="s">
-        <v>327</v>
-      </c>
-      <c r="D9" t="s">
-        <v>334</v>
-      </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5027,16 +4864,16 @@
         <v>22330051920224</v>
       </c>
       <c r="B10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" t="s">
         <v>325</v>
       </c>
-      <c r="C10" t="s">
-        <v>327</v>
-      </c>
-      <c r="D10" t="s">
-        <v>334</v>
-      </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5047,13 +4884,13 @@
         <v>22330051920317</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D11" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E11" t="s">
         <v>62</v>
@@ -5067,16 +4904,16 @@
         <v>22330051920362</v>
       </c>
       <c r="B12" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5087,16 +4924,16 @@
         <v>22330051920362</v>
       </c>
       <c r="B13" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5107,13 +4944,13 @@
         <v>22330051920374</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
         <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E14" t="s">
         <v>40</v>
@@ -5129,7 +4966,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5157,13 +4994,13 @@
         <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
         <v>41</v>
@@ -5180,13 +5017,13 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="E3" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5194,16 +5031,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920238</v>
+        <v>22330051920236</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E4" t="s">
         <v>62</v>
@@ -5214,19 +5051,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920239</v>
+        <v>22330051920236</v>
       </c>
       <c r="B5" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5234,19 +5071,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920239</v>
+        <v>22330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>314</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5254,16 +5091,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920242</v>
+        <v>22330051920238</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>331</v>
       </c>
       <c r="C7" t="s">
-        <v>268</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>342</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
@@ -5274,19 +5111,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920243</v>
+        <v>22330051920239</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E8" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5294,19 +5131,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920256</v>
+        <v>22330051920239</v>
       </c>
       <c r="B9" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
         <v>343</v>
       </c>
-      <c r="D9" t="s">
-        <v>349</v>
-      </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5314,16 +5151,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920357</v>
+        <v>22330051920242</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="D10" t="s">
-        <v>350</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
         <v>62</v>
@@ -5334,19 +5171,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920366</v>
+        <v>22330051920242</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="D11" t="s">
-        <v>351</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>314</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5354,19 +5191,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920366</v>
+        <v>22330051920256</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>333</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>337</v>
       </c>
       <c r="D12" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5374,16 +5211,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920369</v>
+        <v>22330051920357</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E13" t="s">
         <v>62</v>
@@ -5394,21 +5231,61 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920369</v>
+        <v>22330051920366</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>22330051920366</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>346</v>
+      </c>
+      <c r="E15" t="s">
+        <v>314</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>22330051920400</v>
+      </c>
+      <c r="B16" t="s">
+        <v>334</v>
+      </c>
+      <c r="C16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" t="s">
+        <v>347</v>
+      </c>
+      <c r="E16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16">
         <v>5</v>
       </c>
     </row>
@@ -5419,7 +5296,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5447,13 +5324,13 @@
         <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
         <v>62</v>
@@ -5467,13 +5344,13 @@
         <v>21330051920396</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
         <v>40</v>
@@ -5484,16 +5361,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920263</v>
+        <v>22330051920261</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="D4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E4" t="s">
         <v>62</v>
@@ -5510,13 +5387,13 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E5" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5524,16 +5401,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920265</v>
+        <v>22330051920263</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="D6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
@@ -5544,16 +5421,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920272</v>
+        <v>22330051920265</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
@@ -5564,16 +5441,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920274</v>
+        <v>22330051920272</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>354</v>
       </c>
       <c r="D8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E8" t="s">
         <v>62</v>
@@ -5584,19 +5461,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920274</v>
+        <v>22330051920279</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>355</v>
       </c>
       <c r="D9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5604,19 +5481,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920279</v>
+        <v>22330051920283</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>349</v>
       </c>
       <c r="C10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D10" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5624,19 +5501,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920279</v>
+        <v>22330051920402</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>314</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5644,19 +5521,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920281</v>
+        <v>22330051920402</v>
       </c>
       <c r="B12" t="s">
-        <v>353</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>362</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5664,19 +5541,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920283</v>
+        <v>22330051920403</v>
       </c>
       <c r="B13" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C13" t="s">
-        <v>359</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5684,19 +5561,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920402</v>
+        <v>22330051920403</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5704,19 +5581,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920404</v>
+        <v>22330051920405</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>364</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5724,19 +5601,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920405</v>
+        <v>22330051920406</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E16" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5744,41 +5621,21 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920406</v>
+        <v>22330051920411</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E17" t="s">
         <v>62</v>
       </c>
       <c r="F17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920411</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" t="s">
-        <v>369</v>
-      </c>
-      <c r="E18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18">
         <v>5</v>
       </c>
     </row>
@@ -5789,7 +5646,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5814,19 +5671,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920290</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
-        <v>370</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E2" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5834,19 +5691,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920291</v>
+        <v>22330051920297</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>371</v>
       </c>
       <c r="D3" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>314</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5854,19 +5711,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920291</v>
+        <v>22330051920298</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>367</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E4" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5874,19 +5731,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920297</v>
+        <v>22330051920302</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>376</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E5" t="s">
-        <v>323</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5894,19 +5751,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920298</v>
+        <v>22330051920303</v>
       </c>
       <c r="B6" t="s">
-        <v>371</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>372</v>
       </c>
       <c r="D6" t="s">
-        <v>387</v>
+        <v>313</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>314</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5914,19 +5771,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920302</v>
+        <v>22330051920307</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>373</v>
       </c>
       <c r="D7" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5934,19 +5791,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920303</v>
+        <v>22330051920307</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D8" t="s">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="E8" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5954,19 +5811,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920307</v>
+        <v>22330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>368</v>
       </c>
       <c r="C9" t="s">
-        <v>378</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="E9" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5974,19 +5831,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920307</v>
+        <v>22330051920311</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="D10" t="s">
-        <v>389</v>
+        <v>226</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>314</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5994,16 +5848,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920308</v>
+        <v>22330051920314</v>
       </c>
       <c r="B11" t="s">
-        <v>372</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>374</v>
       </c>
       <c r="D11" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="E11" t="s">
         <v>62</v>
@@ -6014,16 +5868,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920311</v>
+        <v>22330051920314</v>
       </c>
       <c r="B12" t="s">
-        <v>373</v>
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>374</v>
       </c>
       <c r="D12" t="s">
-        <v>233</v>
+        <v>384</v>
       </c>
       <c r="E12" t="s">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6031,19 +5888,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920314</v>
+        <v>22330051920315</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D13" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6051,16 +5908,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920314</v>
+        <v>22330051920373</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D14" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E14" t="s">
         <v>62</v>
@@ -6071,16 +5928,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920315</v>
+        <v>22330051920397</v>
       </c>
       <c r="B15" t="s">
-        <v>191</v>
+        <v>370</v>
       </c>
       <c r="C15" t="s">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E15" t="s">
         <v>40</v>
@@ -6091,19 +5948,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920315</v>
+        <v>22330051920397</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>370</v>
       </c>
       <c r="C16" t="s">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E16" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6111,19 +5968,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920360</v>
+        <v>22330051920408</v>
       </c>
       <c r="B17" t="s">
-        <v>374</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>323</v>
+        <v>62</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -6131,16 +5988,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920373</v>
+        <v>22330051920412</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>303</v>
       </c>
       <c r="C18" t="s">
-        <v>382</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E18" t="s">
         <v>62</v>
@@ -6151,19 +6008,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920397</v>
+        <v>22330051920419</v>
       </c>
       <c r="B19" t="s">
-        <v>375</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -6171,101 +6028,21 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920397</v>
+        <v>22330051920419</v>
       </c>
       <c r="B20" t="s">
-        <v>375</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>314</v>
       </c>
       <c r="F20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920408</v>
-      </c>
-      <c r="B21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" t="s">
-        <v>383</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920412</v>
-      </c>
-      <c r="B22" t="s">
-        <v>312</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" t="s">
-        <v>395</v>
-      </c>
-      <c r="E22" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920419</v>
-      </c>
-      <c r="B23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>323</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920419</v>
-      </c>
-      <c r="B24" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24">
         <v>5</v>
       </c>
     </row>
@@ -6276,7 +6053,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6301,19 +6078,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920018</v>
+        <v>19330051920081</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>397</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>399</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>398</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6324,16 +6101,16 @@
         <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C3" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6347,13 +6124,13 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6364,16 +6141,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C5" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>398</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6384,16 +6161,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C6" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6404,18 +6181,78 @@
         <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>21330051920195</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>396</v>
+      </c>
+      <c r="E8" t="s">
+        <v>398</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>21330051920393</v>
+      </c>
+      <c r="B9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9" t="s">
+        <v>393</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+      <c r="E9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>21330051920393</v>
+      </c>
+      <c r="B10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D10" t="s">
+        <v>397</v>
+      </c>
+      <c r="E10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F10">
         <v>5</v>
       </c>
     </row>
@@ -6426,7 +6263,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6451,19 +6288,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920077</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>402</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>403</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6471,19 +6308,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920077</v>
+        <v>21330051920086</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>402</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6491,19 +6328,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920078</v>
+        <v>21330051920086</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>404</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6511,19 +6348,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920080</v>
+        <v>21330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>318</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>399</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>404</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6531,19 +6368,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920103</v>
+        <v>21330051920094</v>
       </c>
       <c r="B6" t="s">
-        <v>401</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D6" t="s">
         <v>405</v>
       </c>
       <c r="E6" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6551,19 +6388,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920105</v>
+        <v>21330051920094</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E7" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6571,19 +6408,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920109</v>
+        <v>21330051920105</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="D8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6594,18 +6431,58 @@
         <v>21330051920109</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>21330051920109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>21330051920260</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>402</v>
+      </c>
+      <c r="D11" t="s">
         <v>407</v>
       </c>
-      <c r="E9" t="s">
-        <v>223</v>
-      </c>
-      <c r="F9">
+      <c r="E11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -6616,7 +6493,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6647,13 +6524,13 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E2" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6664,16 +6541,16 @@
         <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6681,19 +6558,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920113</v>
+        <v>21330051920117</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6701,19 +6578,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920117</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
-        <v>409</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>271</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E5" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6721,19 +6598,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920117</v>
+        <v>21330051920125</v>
       </c>
       <c r="B6" t="s">
-        <v>409</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6741,19 +6618,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920120</v>
+        <v>21330051920130</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>410</v>
       </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6761,19 +6638,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920120</v>
+        <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>411</v>
       </c>
       <c r="D8" t="s">
         <v>417</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6781,19 +6658,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920125</v>
+        <v>21330051920133</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>411</v>
       </c>
       <c r="D9" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="E9" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6801,10 +6678,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920130</v>
+        <v>21330051920391</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
         <v>412</v>
@@ -6813,7 +6690,7 @@
         <v>418</v>
       </c>
       <c r="E10" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6824,38 +6701,18 @@
         <v>21330051920391</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E11" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920391</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" t="s">
-        <v>413</v>
-      </c>
-      <c r="D12" t="s">
-        <v>419</v>
-      </c>
-      <c r="E12" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -6866,7 +6723,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6891,19 +6748,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>419</v>
       </c>
       <c r="C2" t="s">
-        <v>340</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6911,81 +6768,21 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B3" t="s">
-        <v>420</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E3" t="s">
-        <v>222</v>
+        <v>163</v>
       </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920036</v>
-      </c>
-      <c r="B4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" t="s">
-        <v>422</v>
-      </c>
-      <c r="E4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920037</v>
-      </c>
-      <c r="B5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D5" t="s">
-        <v>423</v>
-      </c>
-      <c r="E5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920037</v>
-      </c>
-      <c r="B6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D6" t="s">
-        <v>423</v>
-      </c>
-      <c r="E6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6">
         <v>5</v>
       </c>
     </row>
@@ -7024,16 +6821,16 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E2" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7044,16 +6841,16 @@
         <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
         <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7064,16 +6861,16 @@
         <v>21330051920140</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E4" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7084,16 +6881,16 @@
         <v>21330051920140</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7107,13 +6904,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7127,13 +6924,13 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7144,16 +6941,16 @@
         <v>21330051920143</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7164,16 +6961,16 @@
         <v>21330051920145</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E9" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7184,16 +6981,16 @@
         <v>21330051920145</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7207,13 +7004,13 @@
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D11" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E11" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7224,16 +7021,16 @@
         <v>21330051920382</v>
       </c>
       <c r="B12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7244,16 +7041,16 @@
         <v>21330051920382</v>
       </c>
       <c r="B13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E13" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7266,7 +7063,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7300,10 +7097,10 @@
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7314,16 +7111,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7334,16 +7131,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>291</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7351,19 +7148,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920071</v>
+        <v>20330051920070</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>291</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7371,19 +7168,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920073</v>
+        <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>433</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>324</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>320</v>
+        <v>436</v>
       </c>
       <c r="E6" t="s">
-        <v>441</v>
+        <v>233</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7391,19 +7188,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920073</v>
+        <v>20330051920071</v>
       </c>
       <c r="B7" t="s">
-        <v>433</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>324</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>320</v>
+        <v>437</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7411,19 +7208,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920080</v>
+        <v>20330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7431,19 +7228,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920082</v>
+        <v>20330051920073</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>431</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="D9" t="s">
-        <v>439</v>
+        <v>311</v>
       </c>
       <c r="E9" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7451,19 +7248,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920082</v>
+        <v>20330051920073</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>431</v>
       </c>
       <c r="C10" t="s">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="D10" t="s">
-        <v>439</v>
+        <v>311</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>291</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7471,21 +7268,101 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
+        <v>20330051920080</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" t="s">
+        <v>396</v>
+      </c>
+      <c r="E11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>20330051920080</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E12" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>20330051920082</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>433</v>
+      </c>
+      <c r="D13" t="s">
+        <v>438</v>
+      </c>
+      <c r="E13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>20330051920082</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>433</v>
+      </c>
+      <c r="D14" t="s">
+        <v>438</v>
+      </c>
+      <c r="E14" t="s">
+        <v>291</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
         <v>20330051920087</v>
       </c>
-      <c r="B11" t="s">
-        <v>434</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
-        <v>440</v>
-      </c>
-      <c r="E11" t="s">
-        <v>241</v>
-      </c>
-      <c r="F11">
+      <c r="D15" t="s">
+        <v>439</v>
+      </c>
+      <c r="E15" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -7613,7 +7490,7 @@
         <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7633,7 +7510,7 @@
         <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7794,16 +7671,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7814,16 +7691,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7834,16 +7711,16 @@
         <v>20330051920191</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7857,13 +7734,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7877,13 +7754,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E6" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7894,16 +7771,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7914,16 +7791,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E8" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7937,13 +7814,13 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E9" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7957,13 +7834,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E10" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7974,16 +7851,16 @@
         <v>20330051920214</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7994,16 +7871,16 @@
         <v>20330051920214</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E12" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8014,16 +7891,16 @@
         <v>20330051920217</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E13" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8034,16 +7911,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E14" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8054,16 +7931,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8076,7 +7953,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8104,16 +7981,16 @@
         <v>19220030050208</v>
       </c>
       <c r="B2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8121,19 +7998,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920425</v>
+        <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8141,19 +8018,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920260</v>
+        <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>459</v>
+        <v>409</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E4" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8161,19 +8038,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920272</v>
+        <v>20330051920260</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>457</v>
       </c>
       <c r="C5" t="s">
-        <v>390</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E5" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8181,19 +8058,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920278</v>
+        <v>20330051920272</v>
       </c>
       <c r="B6" t="s">
-        <v>214</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="D6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E6" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8204,18 +8081,38 @@
         <v>20330051920278</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C7" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>20330051920278</v>
+      </c>
+      <c r="B8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D8" t="s">
+        <v>463</v>
+      </c>
+      <c r="E8" t="s">
+        <v>234</v>
+      </c>
+      <c r="F8">
         <v>5</v>
       </c>
     </row>
@@ -8254,16 +8151,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8274,16 +8171,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8294,16 +8191,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B4" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D4" t="s">
         <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8314,16 +8211,16 @@
         <v>19330051920393</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -8334,16 +8231,16 @@
         <v>19330051920393</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -8354,16 +8251,16 @@
         <v>19330051920399</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8374,16 +8271,16 @@
         <v>19330051920436</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -8394,16 +8291,16 @@
         <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E9" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -8417,13 +8314,13 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E10" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8437,13 +8334,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E11" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8460,10 +8357,10 @@
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E12" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8507,13 +8404,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D2" t="s">
         <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8527,13 +8424,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D3" t="s">
         <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>233</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8544,16 +8441,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8564,16 +8461,16 @@
         <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E5" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8590,10 +8487,10 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>384</v>
+        <v>484</v>
       </c>
       <c r="E6" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8607,13 +8504,13 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8627,13 +8524,13 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8644,16 +8541,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E9" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8664,16 +8561,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C10" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E10" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8684,16 +8581,16 @@
         <v>20330051920330</v>
       </c>
       <c r="B11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E11" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8707,13 +8604,13 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E12" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8724,16 +8621,16 @@
         <v>20330051920335</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E13" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8744,16 +8641,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B14" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C14" t="s">
         <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E14" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -8764,16 +8661,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C15" t="s">
         <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E15" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -8786,7 +8683,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8820,7 +8717,7 @@
         <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -8840,7 +8737,7 @@
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>40</v>
@@ -8851,16 +8748,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920121</v>
+        <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>82</v>
@@ -8871,16 +8768,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920121</v>
+        <v>22330051920100</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>40</v>
@@ -8891,16 +8788,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920337</v>
+        <v>22330051920121</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
         <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>82</v>
@@ -8911,13 +8808,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920340</v>
+        <v>22330051920121</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
         <v>92</v>
@@ -8926,6 +8823,46 @@
         <v>40</v>
       </c>
       <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>22330051920337</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>22330051920340</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -8964,13 +8901,13 @@
         <v>22330051920124</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -8984,13 +8921,13 @@
         <v>22330051920125</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
         <v>82</v>
@@ -9004,16 +8941,16 @@
         <v>22330051920126</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9024,16 +8961,16 @@
         <v>22330051920126</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
         <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9047,10 +8984,10 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
         <v>40</v>
@@ -9070,7 +9007,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
         <v>82</v>
@@ -9084,13 +9021,13 @@
         <v>22330051920138</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
         <v>41</v>
@@ -9104,16 +9041,16 @@
         <v>22330051920144</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9124,16 +9061,16 @@
         <v>22330051920144</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9147,7 +9084,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
@@ -9167,7 +9104,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>38</v>
@@ -9187,13 +9124,13 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -9207,13 +9144,13 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -9224,13 +9161,13 @@
         <v>22330051920342</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
         <v>41</v>
@@ -9244,13 +9181,13 @@
         <v>22330051920343</v>
       </c>
       <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" t="s">
         <v>99</v>
       </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
         <v>41</v>
@@ -9264,16 +9201,16 @@
         <v>22330051920346</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -9284,16 +9221,16 @@
         <v>22330051920346</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -9304,16 +9241,16 @@
         <v>22330051920348</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -9324,10 +9261,10 @@
         <v>22330051920354</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>33</v>
@@ -9374,16 +9311,16 @@
         <v>22330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9394,16 +9331,16 @@
         <v>22330051920160</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9414,16 +9351,16 @@
         <v>22330051920160</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9434,13 +9371,13 @@
         <v>22330051920172</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
         <v>40</v>
@@ -9454,16 +9391,16 @@
         <v>22330051920382</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9474,16 +9411,16 @@
         <v>22330051920382</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9494,13 +9431,13 @@
         <v>22330051920384</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
@@ -9514,16 +9451,16 @@
         <v>22330051920386</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9534,16 +9471,16 @@
         <v>22330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9556,7 +9493,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -9584,16 +9521,16 @@
         <v>21330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9601,19 +9538,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920157</v>
+        <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9624,16 +9561,16 @@
         <v>21330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9644,16 +9581,16 @@
         <v>21330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9664,16 +9601,16 @@
         <v>21330051920162</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9684,16 +9621,16 @@
         <v>21330051920164</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -9701,19 +9638,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920164</v>
+        <v>21330051920165</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -9721,19 +9658,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920171</v>
+        <v>21330051920165</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -9741,19 +9678,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920177</v>
+        <v>21330051920166</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -9761,21 +9698,61 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
+        <v>21330051920166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>21330051920171</v>
+      </c>
+      <c r="B12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
         <v>21330051920181</v>
       </c>
-      <c r="B11" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>156</v>
-      </c>
-      <c r="F11">
+      <c r="B13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -9817,13 +9794,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -9837,13 +9814,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" t="s">
         <v>163</v>
-      </c>
-      <c r="D3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" t="s">
-        <v>169</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -9854,16 +9831,16 @@
         <v>21330051920252</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -9874,16 +9851,16 @@
         <v>21330051920262</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -9894,16 +9871,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -9914,16 +9891,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F7">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="430">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -162,1135 +162,1102 @@
     <t>INGLÉS I</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>NICOLAS</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>QUÍMICA I</t>
+  </si>
+  <si>
+    <t>ÁLGEBRA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>LUGO</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>DAMON</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>TECNOLOGÍAS DE LA INFORMACIÓN Y LA COMUNICACIÓN</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ARZATE</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>QUÍMICA I</t>
-  </si>
-  <si>
-    <t>ÁLGEBRA</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>TECNOLOGÍAS DE LA INFORMACIÓN Y LA COMUNICACIÓN</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>ESTEFANY CELESTE</t>
+  </si>
+  <si>
+    <t>ZURI GABRIELA</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>LEONOR</t>
+  </si>
+  <si>
+    <t>LUCIANA</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>FLORENTINA ESMERALDA</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>LUIS BRANDON</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>RUFINA ISABEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>ADALY</t>
+  </si>
+  <si>
+    <t>GEOMETRÍA ANALÍTICA</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>INGLÉS III</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>ÉTICA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>USCANGA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>EMILIANO DE JESUS</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>ABRIL</t>
   </si>
   <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>LEONOR</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>LUIS BRANDON</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>RUFINA ISABEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>GEOMETRÍA ANALÍTICA</t>
-  </si>
-  <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>INGLÉS III</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MELANI PAOLA</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>ÉTICA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
   </si>
   <si>
     <t>RAMOS</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>JESUS IVAN</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>VALERIA DANAY</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN YAEL</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>FRANCISCO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>TLAXCALTECA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
   </si>
   <si>
     <t>JOSE ANTONIO</t>
@@ -1907,7 +1874,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
         <v>159</v>
@@ -2336,7 +2303,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2361,19 +2328,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920235</v>
+        <v>21330051920305</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2" t="s">
         <v>188</v>
-      </c>
-      <c r="E2" t="s">
-        <v>167</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2381,19 +2348,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920298</v>
+        <v>21330051920323</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2401,19 +2368,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920305</v>
+        <v>21330051920328</v>
       </c>
       <c r="B4" t="s">
         <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2421,81 +2388,21 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920326</v>
-      </c>
-      <c r="B6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920328</v>
-      </c>
-      <c r="B7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" t="s">
-        <v>194</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920328</v>
-      </c>
-      <c r="B8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8">
         <v>5</v>
       </c>
     </row>
@@ -2534,16 +2441,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" t="s">
         <v>205</v>
       </c>
-      <c r="D2" t="s">
-        <v>212</v>
-      </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2554,16 +2461,16 @@
         <v>20330051920011</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" t="s">
         <v>206</v>
       </c>
-      <c r="D3" t="s">
-        <v>213</v>
-      </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2574,16 +2481,16 @@
         <v>20330051920012</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D4" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2594,16 +2501,16 @@
         <v>20330051920013</v>
       </c>
       <c r="B5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2614,16 +2521,16 @@
         <v>20330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2634,16 +2541,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E7" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2654,16 +2561,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2674,16 +2581,16 @@
         <v>20330051920025</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
         <v>156</v>
       </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2697,13 +2604,13 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10" t="s">
         <v>218</v>
-      </c>
-      <c r="E10" t="s">
-        <v>225</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2717,13 +2624,13 @@
         <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D11" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2734,16 +2641,16 @@
         <v>20330051920033</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2754,16 +2661,16 @@
         <v>20330051920035</v>
       </c>
       <c r="B13" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E13" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2774,16 +2681,16 @@
         <v>20330051920035</v>
       </c>
       <c r="B14" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C14" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E14" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -2794,16 +2701,16 @@
         <v>20330051920037</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C15" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E15" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2814,16 +2721,16 @@
         <v>20330051920060</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E16" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -2834,16 +2741,16 @@
         <v>20330051920362</v>
       </c>
       <c r="B17" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E17" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -2884,16 +2791,16 @@
         <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2904,16 +2811,16 @@
         <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2924,16 +2831,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2944,16 +2851,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2964,16 +2871,16 @@
         <v>20330051920241</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D6" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2984,16 +2891,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C7" t="s">
         <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E7" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3004,16 +2911,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s">
         <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3027,13 +2934,13 @@
         <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D9" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3047,13 +2954,13 @@
         <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3094,16 +3001,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3117,13 +3024,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3137,13 +3044,13 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3154,16 +3061,16 @@
         <v>20330051920349</v>
       </c>
       <c r="B5" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C5" t="s">
         <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3174,16 +3081,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3194,16 +3101,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E7" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3217,13 +3124,13 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D8" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3240,10 +3147,10 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3284,16 +3191,16 @@
         <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3304,16 +3211,16 @@
         <v>20330051920158</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="D3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3330,10 +3237,10 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3344,16 +3251,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3364,16 +3271,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E6" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3384,16 +3291,16 @@
         <v>20330051920173</v>
       </c>
       <c r="B7" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3404,16 +3311,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B8" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3424,16 +3331,16 @@
         <v>20330051920182</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3444,16 +3351,16 @@
         <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -3464,16 +3371,16 @@
         <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3514,16 +3421,16 @@
         <v>20330051920040</v>
       </c>
       <c r="B2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3537,13 +3444,13 @@
         <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D3" t="s">
         <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3554,16 +3461,16 @@
         <v>20330051920058</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E4" t="s">
         <v>266</v>
-      </c>
-      <c r="D4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E4" t="s">
-        <v>272</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3574,16 +3481,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" t="s">
         <v>264</v>
       </c>
-      <c r="C5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D5" t="s">
-        <v>270</v>
-      </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3594,16 +3501,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" t="s">
         <v>264</v>
       </c>
-      <c r="C6" t="s">
-        <v>267</v>
-      </c>
-      <c r="D6" t="s">
-        <v>270</v>
-      </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3620,10 +3527,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E7" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3664,16 +3571,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3687,13 +3594,13 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3710,10 +3617,10 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3724,16 +3631,16 @@
         <v>20330051920310</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3744,16 +3651,16 @@
         <v>20330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E6" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3764,16 +3671,16 @@
         <v>20330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3820,10 +3727,10 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3840,7 +3747,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -3857,10 +3764,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -3877,13 +3784,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D5" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3894,16 +3801,16 @@
         <v>22330051920195</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3914,16 +3821,16 @@
         <v>22330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3934,13 +3841,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" t="s">
         <v>284</v>
-      </c>
-      <c r="D8" t="s">
-        <v>290</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -3954,10 +3861,10 @@
         <v>22330051920201</v>
       </c>
       <c r="B9" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C9" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D9" t="s">
         <v>134</v>
@@ -3974,16 +3881,16 @@
         <v>22330051920204</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" t="s">
         <v>285</v>
       </c>
-      <c r="D10" t="s">
-        <v>291</v>
-      </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3997,10 +3904,10 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D11" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -4017,10 +3924,10 @@
         <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E12" t="s">
         <v>37</v>
@@ -4037,10 +3944,10 @@
         <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -4057,13 +3964,13 @@
         <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D14" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -4077,13 +3984,13 @@
         <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D15" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4246,7 +4153,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4271,19 +4178,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920205</v>
+        <v>22330051920210</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4291,19 +4198,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920215</v>
+        <v>22330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4311,19 +4218,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920216</v>
+        <v>22330051920213</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" t="s">
         <v>296</v>
       </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>303</v>
-      </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4331,19 +4238,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920216</v>
+        <v>22330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>292</v>
       </c>
       <c r="D5" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4351,19 +4258,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920218</v>
+        <v>22330051920224</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>290</v>
       </c>
       <c r="C6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" t="s">
         <v>298</v>
       </c>
-      <c r="D6" t="s">
-        <v>304</v>
-      </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4371,19 +4278,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920218</v>
+        <v>22330051920362</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>268</v>
       </c>
       <c r="C7" t="s">
-        <v>298</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4391,19 +4298,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920222</v>
+        <v>22330051920365</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>294</v>
       </c>
       <c r="D8" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4411,19 +4318,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920224</v>
+        <v>22330051920365</v>
       </c>
       <c r="B9" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C9" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D9" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4431,101 +4338,21 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920224</v>
+        <v>22330051920374</v>
       </c>
       <c r="B10" t="s">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>299</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
       </c>
       <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920317</v>
-      </c>
-      <c r="B11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" t="s">
-        <v>300</v>
-      </c>
-      <c r="D11" t="s">
-        <v>307</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920362</v>
-      </c>
-      <c r="B12" t="s">
-        <v>274</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
-        <v>308</v>
-      </c>
-      <c r="E12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920362</v>
-      </c>
-      <c r="B13" t="s">
-        <v>274</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920374</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>309</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -4567,10 +4394,10 @@
         <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
         <v>75</v>
@@ -4584,13 +4411,13 @@
         <v>22330051920232</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D3" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -4604,13 +4431,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C4" t="s">
         <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -4624,13 +4451,13 @@
         <v>22330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D5" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -4644,16 +4471,16 @@
         <v>22330051920239</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D6" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4664,13 +4491,13 @@
         <v>22330051920242</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -4687,10 +4514,10 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -4704,13 +4531,13 @@
         <v>22330051920369</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
         <v>168</v>
       </c>
       <c r="D9" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -4724,13 +4551,13 @@
         <v>22330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>168</v>
       </c>
       <c r="D10" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4744,13 +4571,13 @@
         <v>22330051920400</v>
       </c>
       <c r="B11" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -4794,13 +4621,13 @@
         <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="D2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -4814,13 +4641,13 @@
         <v>22330051920263</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -4834,16 +4661,16 @@
         <v>22330051920281</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D4" t="s">
         <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4854,16 +4681,16 @@
         <v>22330051920281</v>
       </c>
       <c r="B5" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D5" t="s">
         <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4877,13 +4704,13 @@
         <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D6" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4897,13 +4724,13 @@
         <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4920,7 +4747,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -4940,7 +4767,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -4954,16 +4781,16 @@
         <v>22330051920403</v>
       </c>
       <c r="B10" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4974,16 +4801,16 @@
         <v>22330051920403</v>
       </c>
       <c r="B11" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5000,7 +4827,7 @@
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -5047,10 +4874,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -5064,13 +4891,13 @@
         <v>22330051920302</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -5087,10 +4914,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D4" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -5104,13 +4931,13 @@
         <v>22330051920307</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D5" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -5124,10 +4951,10 @@
         <v>22330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -5144,13 +4971,13 @@
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D7" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5164,10 +4991,10 @@
         <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>341</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -5187,7 +5014,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -5207,7 +5034,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -5221,13 +5048,13 @@
         <v>22330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>335</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -5241,16 +5068,16 @@
         <v>22330051920418</v>
       </c>
       <c r="B12" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5261,13 +5088,13 @@
         <v>22330051920418</v>
       </c>
       <c r="B13" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -5281,7 +5108,7 @@
         <v>22330051920419</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
         <v>83</v>
@@ -5340,7 +5167,7 @@
         <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5351,13 +5178,13 @@
         <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D3" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E3" t="s">
         <v>142</v>
@@ -5374,10 +5201,10 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>347</v>
       </c>
       <c r="E4" t="s">
         <v>142</v>
@@ -5391,16 +5218,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D5" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E5" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5411,13 +5238,13 @@
         <v>20330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C6" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E6" t="s">
         <v>142</v>
@@ -5431,13 +5258,13 @@
         <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E7" t="s">
         <v>141</v>
@@ -5451,16 +5278,16 @@
         <v>21330051920195</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E8" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5471,16 +5298,16 @@
         <v>21330051920393</v>
       </c>
       <c r="B9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D9" t="s">
+        <v>350</v>
+      </c>
+      <c r="E9" t="s">
         <v>351</v>
-      </c>
-      <c r="C9" t="s">
-        <v>355</v>
-      </c>
-      <c r="D9" t="s">
-        <v>359</v>
-      </c>
-      <c r="E9" t="s">
-        <v>360</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5491,13 +5318,13 @@
         <v>21330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C10" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D10" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="E10" t="s">
         <v>142</v>
@@ -5544,10 +5371,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="E2" t="s">
         <v>141</v>
@@ -5564,10 +5391,10 @@
         <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
         <v>141</v>
@@ -5584,10 +5411,10 @@
         <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>167</v>
@@ -5601,13 +5428,13 @@
         <v>21330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C5" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E5" t="s">
         <v>167</v>
@@ -5624,10 +5451,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="E6" t="s">
         <v>141</v>
@@ -5644,10 +5471,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="D7" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="E7" t="s">
         <v>153</v>
@@ -5664,13 +5491,13 @@
         <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D8" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="E8" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5690,7 +5517,7 @@
         <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5724,13 +5551,13 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D11" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5743,7 +5570,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5768,19 +5595,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>18330051920377</v>
+        <v>20330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>370</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
-        <v>374</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5788,19 +5615,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920152</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="C3" t="s">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5808,19 +5635,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920117</v>
+        <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>375</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5828,19 +5655,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>21330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5848,19 +5675,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920125</v>
+        <v>21330051920127</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="E6" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5868,19 +5695,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920130</v>
+        <v>21330051920127</v>
       </c>
       <c r="B7" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="D7" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5894,13 +5721,13 @@
         <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="D8" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5908,61 +5735,21 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920133</v>
+        <v>21330051920391</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D9" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="E9" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920391</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>373</v>
-      </c>
-      <c r="D10" t="s">
-        <v>379</v>
-      </c>
-      <c r="E10" t="s">
-        <v>141</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920391</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>373</v>
-      </c>
-      <c r="D11" t="s">
-        <v>379</v>
-      </c>
-      <c r="E11" t="s">
-        <v>143</v>
-      </c>
-      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -6001,13 +5788,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="E2" t="s">
         <v>141</v>
@@ -6027,7 +5814,7 @@
         <v>170</v>
       </c>
       <c r="D3" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="E3" t="s">
         <v>141</v>
@@ -6071,13 +5858,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
         <v>143</v>
@@ -6091,13 +5878,13 @@
         <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="E3" t="s">
         <v>141</v>
@@ -6114,10 +5901,10 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="E4" t="s">
         <v>143</v>
@@ -6134,10 +5921,10 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="E5" t="s">
         <v>141</v>
@@ -6154,10 +5941,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="D6" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="E6" t="s">
         <v>141</v>
@@ -6174,10 +5961,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="D7" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="E7" t="s">
         <v>143</v>
@@ -6194,10 +5981,10 @@
         <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>335</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="E8" t="s">
         <v>141</v>
@@ -6211,13 +5998,13 @@
         <v>21330051920145</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="E9" t="s">
         <v>143</v>
@@ -6231,13 +6018,13 @@
         <v>21330051920145</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="E10" t="s">
         <v>141</v>
@@ -6251,13 +6038,13 @@
         <v>21330051920148</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="D11" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="E11" t="s">
         <v>143</v>
@@ -6271,13 +6058,13 @@
         <v>21330051920382</v>
       </c>
       <c r="B12" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="E12" t="s">
         <v>141</v>
@@ -6291,13 +6078,13 @@
         <v>21330051920382</v>
       </c>
       <c r="B13" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="E13" t="s">
         <v>143</v>
@@ -6341,16 +6128,16 @@
         <v>18330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6367,10 +6154,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="E3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6387,10 +6174,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6401,16 +6188,16 @@
         <v>20330051920070</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="E5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6421,16 +6208,16 @@
         <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
         <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6441,16 +6228,16 @@
         <v>20330051920071</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6461,16 +6248,16 @@
         <v>20330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="E8" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6481,16 +6268,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B9" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="C9" t="s">
-        <v>296</v>
+        <v>381</v>
       </c>
       <c r="D9" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E9" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6501,16 +6288,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B10" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="C10" t="s">
-        <v>296</v>
+        <v>381</v>
       </c>
       <c r="D10" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6521,16 +6308,16 @@
         <v>20330051920080</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D11" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E11" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6541,16 +6328,16 @@
         <v>20330051920080</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D12" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6561,16 +6348,16 @@
         <v>20330051920082</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="D13" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="E13" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6581,16 +6368,16 @@
         <v>20330051920082</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="D14" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="E14" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6601,16 +6388,16 @@
         <v>20330051920091</v>
       </c>
       <c r="B15" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C15" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="E15" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6621,16 +6408,16 @@
         <v>20330051920091</v>
       </c>
       <c r="B16" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C16" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="E16" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6668,16 +6455,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920053</v>
+        <v>22330051920054</v>
       </c>
       <c r="B2" t="s">
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -6688,16 +6475,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920054</v>
+        <v>22330051920059</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -6708,16 +6495,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920059</v>
+        <v>22330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -6728,16 +6515,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920061</v>
+        <v>22330051920064</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -6748,16 +6535,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920064</v>
+        <v>22330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -6771,16 +6558,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
         <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6788,16 +6575,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920068</v>
+        <v>22330051920071</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -6811,16 +6598,16 @@
         <v>22330051920071</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6828,19 +6615,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920071</v>
+        <v>22330051920072</v>
       </c>
       <c r="B10" t="s">
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6857,10 +6644,10 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6868,19 +6655,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920079</v>
+        <v>22330051920084</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6888,16 +6675,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920084</v>
+        <v>22330051920316</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -6914,7 +6701,7 @@
         <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
@@ -6967,10 +6754,10 @@
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="E2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6987,10 +6774,10 @@
         <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7001,16 +6788,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7021,16 +6808,16 @@
         <v>20330051920191</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D5" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7044,13 +6831,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7061,16 +6848,16 @@
         <v>20330051920198</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="D7" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7084,13 +6871,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7104,13 +6891,13 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>183</v>
+        <v>393</v>
       </c>
       <c r="D9" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="E9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7121,16 +6908,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B10" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="E10" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7141,16 +6928,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B11" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7161,16 +6948,16 @@
         <v>20330051920259</v>
       </c>
       <c r="B12" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C12" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D12" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="E12" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7181,16 +6968,16 @@
         <v>20330051920259</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D13" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="E13" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7231,16 +7018,16 @@
         <v>19330051920314</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7251,16 +7038,16 @@
         <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="E3" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7271,16 +7058,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>403</v>
       </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D4" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E4" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7291,16 +7078,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>403</v>
       </c>
       <c r="C5" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D5" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7341,16 +7128,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
       </c>
       <c r="D2" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="E2" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7361,16 +7148,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="E3" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7381,16 +7168,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>335</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7401,16 +7188,16 @@
         <v>19330051920393</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>131</v>
       </c>
       <c r="D5" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="E5" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -7421,16 +7208,16 @@
         <v>19330051920393</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
         <v>131</v>
       </c>
       <c r="D6" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="E6" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -7441,16 +7228,16 @@
         <v>19330051920399</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="D7" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="E7" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7461,16 +7248,16 @@
         <v>19330051920436</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>403</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="E8" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -7481,16 +7268,16 @@
         <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>403</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="E9" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -7531,16 +7318,16 @@
         <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7551,16 +7338,16 @@
         <v>20330051920317</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C3" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7571,16 +7358,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C4" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="D4" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7591,16 +7378,16 @@
         <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D5" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="E5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7614,13 +7401,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="E6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7631,16 +7418,16 @@
         <v>20330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7651,16 +7438,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D8" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7671,16 +7458,16 @@
         <v>20330051920330</v>
       </c>
       <c r="B9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" t="s">
         <v>426</v>
       </c>
-      <c r="C9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" t="s">
-        <v>437</v>
-      </c>
       <c r="E9" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7694,13 +7481,13 @@
         <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7714,13 +7501,13 @@
         <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="D11" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7731,16 +7518,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="C12" t="s">
         <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7753,7 +7540,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7778,19 +7565,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920098</v>
+        <v>22330051920100</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7804,7 +7591,7 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
         <v>71</v>
@@ -7818,19 +7605,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920100</v>
+        <v>22330051920105</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7838,19 +7625,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920105</v>
+        <v>22330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7858,61 +7645,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920105</v>
+        <v>22330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920121</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920340</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8">
         <v>5</v>
       </c>
     </row>
@@ -7923,7 +7670,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7954,10 +7701,10 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>75</v>
@@ -7968,19 +7715,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920131</v>
+        <v>22330051920138</v>
       </c>
       <c r="B3" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7988,16 +7735,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920138</v>
+        <v>22330051920144</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>75</v>
@@ -8008,19 +7755,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920144</v>
+        <v>22330051920244</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8028,19 +7775,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920144</v>
+        <v>22330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8048,19 +7795,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920244</v>
+        <v>22330051920247</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8068,19 +7815,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920244</v>
+        <v>22330051920247</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
         <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8088,19 +7835,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920247</v>
+        <v>22330051920342</v>
       </c>
       <c r="B9" t="s">
         <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8108,13 +7855,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920247</v>
+        <v>22330051920343</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
         <v>96</v>
@@ -8128,13 +7875,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920342</v>
+        <v>22330051920346</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
         <v>97</v>
@@ -8148,19 +7895,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920343</v>
+        <v>22330051920348</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
         <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8168,81 +7915,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920346</v>
+        <v>22330051920354</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
         <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920346</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920348</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920354</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16">
         <v>5</v>
       </c>
     </row>
@@ -8253,7 +7940,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8281,16 +7968,16 @@
         <v>22330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8301,16 +7988,16 @@
         <v>22330051920160</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8318,16 +8005,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920161</v>
+        <v>22330051920160</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -8347,10 +8034,10 @@
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8358,16 +8045,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920172</v>
+        <v>22330051920161</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -8381,16 +8068,16 @@
         <v>22330051920172</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8398,16 +8085,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920382</v>
+        <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -8418,19 +8105,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920384</v>
+        <v>22330051920296</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8438,21 +8125,81 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
+        <v>22330051920296</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>22330051920382</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>22330051920384</v>
+      </c>
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
         <v>22330051920386</v>
       </c>
-      <c r="B10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
         <v>117</v>
       </c>
-      <c r="E10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10">
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -8491,7 +8238,7 @@
         <v>21330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
         <v>126</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="420">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -249,6 +249,9 @@
     <t>ÁLGEBRA</t>
   </si>
   <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
     <t>LARRACILLA</t>
   </si>
   <si>
@@ -261,928 +264,895 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
     <t>ZAYRA</t>
   </si>
   <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
     <t>DAMON</t>
   </si>
   <si>
     <t>MONSERRAT</t>
   </si>
   <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>FLORENTINA ESMERALDA</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>LUIS BRANDON</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>RUFINA ISABEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>ADALY</t>
+  </si>
+  <si>
+    <t>GEOMETRÍA ANALÍTICA</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>INGLÉS III</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ÉTICA</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>USCANGA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>EMILIANO DE JESUS</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
     <t>TECNOLOGÍAS DE LA INFORMACIÓN Y LA COMUNICACIÓN</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>BAEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>LEONOR</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>LUIS BRANDON</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>RUFINA ISABEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>GEOMETRÍA ANALÍTICA</t>
-  </si>
-  <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>INGLÉS III</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MELANI PAOLA</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>ÉTICA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>JESUS IVAN</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>USCANGA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>EMILIANO DE JESUS</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN YAEL</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>FRANCISCO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>CANUTO</t>
@@ -1843,7 +1813,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1874,13 +1844,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -1891,16 +1861,16 @@
         <v>21330051920222</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -1914,13 +1884,13 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -1928,19 +1898,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920234</v>
+        <v>21330051920235</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1948,19 +1918,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920235</v>
+        <v>21330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1971,16 +1941,16 @@
         <v>21330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1988,19 +1958,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920237</v>
+        <v>21330051920240</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2008,19 +1978,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920240</v>
+        <v>21330051920250</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" t="s">
         <v>157</v>
       </c>
-      <c r="D9" t="s">
-        <v>164</v>
-      </c>
       <c r="E9" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2028,19 +1998,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920250</v>
+        <v>21330051920359</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
         <v>158</v>
       </c>
-      <c r="D10" t="s">
-        <v>165</v>
-      </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2054,35 +2024,15 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920359</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -2121,16 +2071,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2141,16 +2091,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" t="s">
         <v>131</v>
-      </c>
-      <c r="C3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" t="s">
-        <v>143</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2161,16 +2111,16 @@
         <v>21330051920193</v>
       </c>
       <c r="B4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" t="s">
         <v>131</v>
-      </c>
-      <c r="C4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" t="s">
-        <v>141</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2181,16 +2131,16 @@
         <v>21330051920199</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2201,16 +2151,16 @@
         <v>21330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2227,10 +2177,10 @@
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2247,10 +2197,10 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2261,16 +2211,16 @@
         <v>21330051920213</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2281,16 +2231,16 @@
         <v>21330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2331,16 +2281,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2357,10 +2307,10 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2371,16 +2321,16 @@
         <v>21330051920328</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2391,16 +2341,16 @@
         <v>21330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2441,16 +2391,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2461,16 +2411,16 @@
         <v>20330051920011</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2481,16 +2431,16 @@
         <v>20330051920012</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" t="s">
         <v>199</v>
       </c>
-      <c r="D4" t="s">
-        <v>207</v>
-      </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2501,16 +2451,16 @@
         <v>20330051920013</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2521,16 +2471,16 @@
         <v>20330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2541,16 +2491,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2561,16 +2511,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" t="s">
         <v>193</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>201</v>
       </c>
-      <c r="D8" t="s">
-        <v>209</v>
-      </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2581,16 +2531,16 @@
         <v>20330051920025</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" t="s">
         <v>210</v>
-      </c>
-      <c r="E9" t="s">
-        <v>218</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2607,10 +2557,10 @@
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E10" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2624,13 +2574,13 @@
         <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2647,10 +2597,10 @@
         <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2661,16 +2611,16 @@
         <v>20330051920035</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D13" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E13" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2681,16 +2631,16 @@
         <v>20330051920035</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C14" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D14" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E14" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -2701,16 +2651,16 @@
         <v>20330051920037</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2724,13 +2674,13 @@
         <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D16" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E16" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -2741,16 +2691,16 @@
         <v>20330051920362</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E17" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -2791,16 +2741,16 @@
         <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2811,16 +2761,16 @@
         <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2831,16 +2781,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2851,16 +2801,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2874,13 +2824,13 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D6" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2891,16 +2841,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2911,16 +2861,16 @@
         <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2931,16 +2881,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D9" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2951,16 +2901,16 @@
         <v>20330051920251</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C10" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3001,16 +2951,16 @@
         <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3024,13 +2974,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3044,13 +2994,13 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3061,16 +3011,16 @@
         <v>20330051920349</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3081,16 +3031,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3101,16 +3051,16 @@
         <v>20330051920354</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3121,16 +3071,16 @@
         <v>20330051920356</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D8" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3147,10 +3097,10 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3191,16 +3141,16 @@
         <v>20330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3214,13 +3164,13 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3237,10 +3187,10 @@
         <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3251,16 +3201,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3271,16 +3221,16 @@
         <v>20330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E6" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3291,16 +3241,16 @@
         <v>20330051920173</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C7" t="s">
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3311,16 +3261,16 @@
         <v>20330051920174</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3331,16 +3281,16 @@
         <v>20330051920182</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="C9" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3351,16 +3301,16 @@
         <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -3371,7 +3321,7 @@
         <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
@@ -3380,7 +3330,7 @@
         <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -3421,16 +3371,16 @@
         <v>20330051920040</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3441,16 +3391,16 @@
         <v>20330051920050</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3461,16 +3411,16 @@
         <v>20330051920058</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E4" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3481,16 +3431,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B5" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D5" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3501,16 +3451,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D6" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E6" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3521,16 +3471,16 @@
         <v>20330051920112</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E7" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3571,16 +3521,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3594,13 +3544,13 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3611,16 +3561,16 @@
         <v>20330051920301</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3637,10 +3587,10 @@
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3651,16 +3601,16 @@
         <v>20330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E6" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3671,16 +3621,16 @@
         <v>20330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3721,13 +3671,13 @@
         <v>21330051920265</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
@@ -3741,13 +3691,13 @@
         <v>21330051920265</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -3764,10 +3714,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -3784,10 +3734,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D5" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -3804,10 +3754,10 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -3824,10 +3774,10 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E7" t="s">
         <v>66</v>
@@ -3841,13 +3791,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -3861,13 +3811,13 @@
         <v>22330051920201</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -3881,13 +3831,13 @@
         <v>22330051920204</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C10" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E10" t="s">
         <v>66</v>
@@ -3904,10 +3854,10 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D11" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -3921,13 +3871,13 @@
         <v>22330051920371</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E12" t="s">
         <v>37</v>
@@ -3941,13 +3891,13 @@
         <v>22330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -3961,13 +3911,13 @@
         <v>22330051920378</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D14" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E14" t="s">
         <v>66</v>
@@ -3981,13 +3931,13 @@
         <v>22330051920388</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D15" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E15" t="s">
         <v>66</v>
@@ -4120,7 +4070,7 @@
         <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4140,7 +4090,7 @@
         <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4181,13 +4131,13 @@
         <v>22330051920210</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -4204,10 +4154,10 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -4224,10 +4174,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E4" t="s">
         <v>66</v>
@@ -4241,13 +4191,13 @@
         <v>22330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D5" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -4261,13 +4211,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C6" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D6" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -4281,13 +4231,13 @@
         <v>22330051920362</v>
       </c>
       <c r="B7" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E7" t="s">
         <v>66</v>
@@ -4301,13 +4251,13 @@
         <v>22330051920365</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D8" t="s">
         <v>294</v>
-      </c>
-      <c r="D8" t="s">
-        <v>300</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -4321,13 +4271,13 @@
         <v>22330051920365</v>
       </c>
       <c r="B9" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D9" t="s">
         <v>294</v>
-      </c>
-      <c r="D9" t="s">
-        <v>300</v>
       </c>
       <c r="E9" t="s">
         <v>66</v>
@@ -4341,13 +4291,13 @@
         <v>22330051920374</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="C10" t="s">
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4391,16 +4341,16 @@
         <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="F2">
         <v>-1</v>
@@ -4414,10 +4364,10 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -4431,13 +4381,13 @@
         <v>22330051920236</v>
       </c>
       <c r="B4" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -4451,13 +4401,13 @@
         <v>22330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D5" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -4471,13 +4421,13 @@
         <v>22330051920239</v>
       </c>
       <c r="B6" t="s">
-        <v>304</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E6" t="s">
         <v>66</v>
@@ -4494,7 +4444,7 @@
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -4514,10 +4464,10 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -4531,13 +4481,13 @@
         <v>22330051920369</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -4551,13 +4501,13 @@
         <v>22330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D10" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4571,13 +4521,13 @@
         <v>22330051920400</v>
       </c>
       <c r="B11" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -4621,13 +4571,13 @@
         <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -4644,10 +4594,10 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -4661,13 +4611,13 @@
         <v>22330051920281</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -4681,13 +4631,13 @@
         <v>22330051920281</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C5" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -4704,10 +4654,10 @@
         <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D6" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -4724,10 +4674,10 @@
         <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -4747,7 +4697,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -4767,7 +4717,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -4781,13 +4731,13 @@
         <v>22330051920403</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4801,13 +4751,13 @@
         <v>22330051920403</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -4827,7 +4777,7 @@
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -4874,10 +4824,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -4897,7 +4847,7 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -4914,10 +4864,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -4931,13 +4881,13 @@
         <v>22330051920307</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D5" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -4951,10 +4901,10 @@
         <v>22330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -4971,10 +4921,10 @@
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D7" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E7" t="s">
         <v>66</v>
@@ -4988,13 +4938,13 @@
         <v>22330051920315</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -5014,7 +4964,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -5034,7 +4984,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -5054,7 +5004,7 @@
         <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -5068,16 +5018,16 @@
         <v>22330051920418</v>
       </c>
       <c r="B12" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5088,16 +5038,16 @@
         <v>22330051920418</v>
       </c>
       <c r="B13" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5108,10 +5058,10 @@
         <v>22330051920419</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
@@ -5158,16 +5108,16 @@
         <v>19330051920081</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5178,16 +5128,16 @@
         <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5201,13 +5151,13 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D4" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5218,16 +5168,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D5" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5238,16 +5188,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C6" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5258,16 +5208,16 @@
         <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5281,13 +5231,13 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E8" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5298,16 +5248,16 @@
         <v>21330051920393</v>
       </c>
       <c r="B9" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C9" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E9" t="s">
-        <v>351</v>
+        <v>132</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5318,16 +5268,16 @@
         <v>21330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C10" t="s">
+        <v>339</v>
+      </c>
+      <c r="D10" t="s">
+        <v>344</v>
+      </c>
+      <c r="E10" t="s">
         <v>345</v>
-      </c>
-      <c r="D10" t="s">
-        <v>350</v>
-      </c>
-      <c r="E10" t="s">
-        <v>142</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5340,7 +5290,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5374,10 +5324,10 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5388,7 +5338,7 @@
         <v>21330051920086</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>54</v>
@@ -5397,7 +5347,7 @@
         <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5408,7 +5358,7 @@
         <v>21330051920086</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
@@ -5417,7 +5367,7 @@
         <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5428,16 +5378,16 @@
         <v>21330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5445,19 +5395,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920094</v>
+        <v>21330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D6" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5465,101 +5415,21 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920094</v>
+        <v>21330051920109</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>353</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>357</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920105</v>
-      </c>
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" t="s">
-        <v>354</v>
-      </c>
-      <c r="D8" t="s">
-        <v>358</v>
-      </c>
-      <c r="E8" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920109</v>
-      </c>
-      <c r="B9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" t="s">
-        <v>188</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920109</v>
-      </c>
-      <c r="B10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10" t="s">
-        <v>141</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920260</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>355</v>
-      </c>
-      <c r="D11" t="s">
-        <v>359</v>
-      </c>
-      <c r="E11" t="s">
-        <v>188</v>
-      </c>
-      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -5598,16 +5468,16 @@
         <v>20330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5618,16 +5488,16 @@
         <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5638,16 +5508,16 @@
         <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5658,16 +5528,16 @@
         <v>21330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5678,16 +5548,16 @@
         <v>21330051920127</v>
       </c>
       <c r="B6" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5698,16 +5568,16 @@
         <v>21330051920127</v>
       </c>
       <c r="B7" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D7" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="E7" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5718,16 +5588,16 @@
         <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E8" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5738,16 +5608,16 @@
         <v>21330051920391</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="D9" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="E9" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5788,16 +5658,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5808,16 +5678,16 @@
         <v>21330051920037</v>
       </c>
       <c r="B3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" t="s">
         <v>131</v>
-      </c>
-      <c r="C3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" t="s">
-        <v>368</v>
-      </c>
-      <c r="E3" t="s">
-        <v>141</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5830,7 +5700,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5858,16 +5728,16 @@
         <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5875,19 +5745,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920140</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5895,19 +5765,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920140</v>
+        <v>21330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>361</v>
       </c>
       <c r="D4" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5915,19 +5785,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920140</v>
+        <v>21330051920143</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5935,19 +5805,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920145</v>
       </c>
       <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>370</v>
-      </c>
       <c r="D6" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5955,19 +5825,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920141</v>
+        <v>21330051920145</v>
       </c>
       <c r="B7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>370</v>
-      </c>
       <c r="D7" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5975,19 +5845,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920143</v>
+        <v>21330051920382</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5995,101 +5865,21 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920145</v>
+        <v>21330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>360</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="E9" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920145</v>
-      </c>
-      <c r="B10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>376</v>
-      </c>
-      <c r="E10" t="s">
-        <v>141</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920148</v>
-      </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" t="s">
-        <v>371</v>
-      </c>
-      <c r="D11" t="s">
-        <v>377</v>
-      </c>
-      <c r="E11" t="s">
-        <v>143</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920382</v>
-      </c>
-      <c r="B12" t="s">
-        <v>369</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>378</v>
-      </c>
-      <c r="E12" t="s">
-        <v>141</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920382</v>
-      </c>
-      <c r="B13" t="s">
-        <v>369</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>378</v>
-      </c>
-      <c r="E13" t="s">
-        <v>143</v>
-      </c>
-      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -6128,16 +5918,16 @@
         <v>18330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6148,16 +5938,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E3" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6168,16 +5958,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6191,13 +5981,13 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="E5" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6211,13 +6001,13 @@
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6228,16 +6018,16 @@
         <v>20330051920071</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>368</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6248,16 +6038,16 @@
         <v>20330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>368</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E8" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6268,16 +6058,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B9" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E9" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6288,16 +6078,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B10" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C10" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D10" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E10" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6311,13 +6101,13 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D11" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E11" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6331,13 +6121,13 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D12" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6351,13 +6141,13 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D13" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E13" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6371,13 +6161,13 @@
         <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D14" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E14" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6388,16 +6178,16 @@
         <v>20330051920091</v>
       </c>
       <c r="B15" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C15" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="E15" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6408,16 +6198,16 @@
         <v>20330051920091</v>
       </c>
       <c r="B16" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D16" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="E16" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6751,13 +6541,13 @@
         <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="E2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6771,13 +6561,13 @@
         <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="E3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6788,16 +6578,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6808,16 +6598,16 @@
         <v>20330051920191</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D5" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6831,13 +6621,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6848,16 +6638,16 @@
         <v>20330051920198</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D7" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="E7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6871,13 +6661,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="D8" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6891,13 +6681,13 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D9" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6908,16 +6698,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B10" t="s">
+        <v>381</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
         <v>391</v>
       </c>
-      <c r="C10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" t="s">
-        <v>401</v>
-      </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6928,16 +6718,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B11" t="s">
+        <v>381</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
         <v>391</v>
       </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>401</v>
-      </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6948,16 +6738,16 @@
         <v>20330051920259</v>
       </c>
       <c r="B12" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C12" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D12" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E12" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6968,16 +6758,16 @@
         <v>20330051920259</v>
       </c>
       <c r="B13" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D13" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="E13" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -7018,16 +6808,16 @@
         <v>19330051920314</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7038,16 +6828,16 @@
         <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="E3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7058,16 +6848,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="E4" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7078,16 +6868,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B5" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C5" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="D5" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7128,16 +6918,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="E2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7148,16 +6938,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="E3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7168,7 +6958,7 @@
         <v>19330051920383</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
         <v>53</v>
@@ -7177,7 +6967,7 @@
         <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7188,16 +6978,16 @@
         <v>19330051920393</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E5" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -7208,16 +6998,16 @@
         <v>19330051920393</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E6" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -7228,16 +7018,16 @@
         <v>19330051920399</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D7" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="E7" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7248,16 +7038,16 @@
         <v>19330051920436</v>
       </c>
       <c r="B8" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="E8" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F8">
         <v>-1</v>
@@ -7268,16 +7058,16 @@
         <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="E9" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -7318,16 +7108,16 @@
         <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C2" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D2" t="s">
         <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7338,16 +7128,16 @@
         <v>20330051920317</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C3" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D3" t="s">
         <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7358,16 +7148,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C4" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D4" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="E4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7378,16 +7168,16 @@
         <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D5" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7401,13 +7191,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D6" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E6" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7418,16 +7208,16 @@
         <v>20330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="E7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7438,16 +7228,16 @@
         <v>20330051920329</v>
       </c>
       <c r="B8" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D8" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7458,16 +7248,16 @@
         <v>20330051920330</v>
       </c>
       <c r="B9" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E9" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7481,13 +7271,13 @@
         <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="E10" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -7498,16 +7288,16 @@
         <v>20330051920335</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D11" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7518,16 +7308,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C12" t="s">
         <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -7540,7 +7330,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7565,16 +7355,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920100</v>
+        <v>22330051920091</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
@@ -7585,19 +7375,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920100</v>
+        <v>22330051920091</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7605,19 +7395,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920105</v>
+        <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7625,10 +7415,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920337</v>
+        <v>22330051920100</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>69</v>
@@ -7645,10 +7435,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920340</v>
+        <v>22330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>70</v>
@@ -7660,6 +7450,26 @@
         <v>20</v>
       </c>
       <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>22330051920340</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
         <v>5</v>
       </c>
     </row>
@@ -7670,7 +7480,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7695,19 +7505,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920126</v>
+        <v>22330051920136</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7715,19 +7525,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920138</v>
+        <v>22330051920136</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7735,19 +7545,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920144</v>
+        <v>22330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7755,19 +7565,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920244</v>
+        <v>22330051920141</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7781,7 +7591,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -7798,16 +7608,16 @@
         <v>22330051920247</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7815,19 +7625,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920247</v>
+        <v>22330051920348</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7835,101 +7645,21 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920342</v>
+        <v>22330051920354</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920343</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920346</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920348</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920354</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -7968,13 +7698,13 @@
         <v>22330051920157</v>
       </c>
       <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
         <v>100</v>
-      </c>
-      <c r="C2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>65</v>
@@ -7988,13 +7718,13 @@
         <v>22330051920160</v>
       </c>
       <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
         <v>101</v>
-      </c>
-      <c r="C3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" t="s">
-        <v>111</v>
       </c>
       <c r="E3" t="s">
         <v>66</v>
@@ -8008,13 +7738,13 @@
         <v>22330051920160</v>
       </c>
       <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
         <v>101</v>
-      </c>
-      <c r="C4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" t="s">
-        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -8034,7 +7764,7 @@
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>65</v>
@@ -8054,7 +7784,7 @@
         <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -8068,13 +7798,13 @@
         <v>22330051920172</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>66</v>
@@ -8088,13 +7818,13 @@
         <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -8111,10 +7841,10 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>66</v>
@@ -8131,10 +7861,10 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
         <v>65</v>
@@ -8148,13 +7878,13 @@
         <v>22330051920382</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -8168,13 +7898,13 @@
         <v>22330051920384</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
@@ -8188,13 +7918,13 @@
         <v>22330051920386</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>65</v>
@@ -8238,16 +7968,16 @@
         <v>21330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8258,16 +7988,16 @@
         <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
         <v>118</v>
       </c>
-      <c r="C3" t="s">
-        <v>127</v>
-      </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8278,16 +8008,16 @@
         <v>21330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8298,16 +8028,16 @@
         <v>21330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8318,16 +8048,16 @@
         <v>21330051920162</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8338,16 +8068,16 @@
         <v>21330051920164</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
         <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8358,16 +8088,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8378,16 +8108,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8398,16 +8128,16 @@
         <v>21330051920166</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8418,16 +8148,16 @@
         <v>21330051920166</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8438,16 +8168,16 @@
         <v>21330051920171</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8458,16 +8188,16 @@
         <v>21330051920181</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" t="s">
         <v>131</v>
-      </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" t="s">
-        <v>141</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8511,13 +8241,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8531,13 +8261,13 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8548,16 +8278,16 @@
         <v>21330051920252</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8568,16 +8298,16 @@
         <v>21330051920262</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8588,16 +8318,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8608,16 +8338,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F7">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="388">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -114,1170 +114,1077 @@
     <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA I</t>
   </si>
   <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
+  </si>
+  <si>
+    <t>JARED ABRAHAM</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>ÁLGEBRA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>NICOLAS</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>QUÍMICA I</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>DAMON</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VIDERIQUE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>LUIS BRANDON</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>RUFINA ISABEL</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>ADALY</t>
+  </si>
+  <si>
+    <t>GEOMETRÍA ANALÍTICA</t>
+  </si>
+  <si>
+    <t>BIOLOGÍA</t>
+  </si>
+  <si>
+    <t>INGLÉS III</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>DIEGO ANTONIO</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JASIEL</t>
+  </si>
+  <si>
+    <t>WENCESLAO</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
+  </si>
+  <si>
+    <t>ÉTICA</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>FÍSICA II</t>
+  </si>
+  <si>
+    <t>CÁLCULO INTEGRAL</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>INGLÉS V</t>
+  </si>
+  <si>
+    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>INGLÉS I</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>USCANGA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>EMILIANO DE JESUS</t>
+  </si>
+  <si>
+    <t>KARLA YARITZY</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>KARLOS ARATH</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
+    <t>LESLIE YAMILET</t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
     <t>GALVEZ</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>INGLÉS I</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>NICOLAS</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>QUÍMICA I</t>
-  </si>
-  <si>
-    <t>ÁLGEBRA</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>DAMON</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>GABRIELA AIMEE</t>
-  </si>
-  <si>
-    <t>BELEN</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>FLORENTINA ESMERALDA</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>LUIS BRANDON</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>RUFINA ISABEL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>ADALY</t>
-  </si>
-  <si>
-    <t>GEOMETRÍA ANALÍTICA</t>
-  </si>
-  <si>
-    <t>BIOLOGÍA</t>
-  </si>
-  <si>
-    <t>INGLÉS III</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MELANI PAOLA</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS BACTERIOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JASIEL</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>IDENTIFICA MICROORGANISMOS CON BASE EN TÉCNICAS PARASITOLÓGICAS</t>
-  </si>
-  <si>
-    <t>ÉTICA</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>FÍSICA II</t>
-  </si>
-  <si>
-    <t>CÁLCULO INTEGRAL</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
+    <t>DE LA TEJA</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
   </si>
   <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>CIENCIA, TECNOLOGÍA, SOCIEDAD Y VALORES</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>INGLÉS V</t>
-  </si>
-  <si>
-    <t>DISEÑA Y MANTIENE LOS SISTEMAS DE ILUMINACIÓN</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>JESUS IVAN</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>USCANGA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
-  </si>
-  <si>
-    <t>EMILIANO DE JESUS</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>TECNOLOGÍAS DE LA INFORMACIÓN Y LA COMUNICACIÓN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN YAEL</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>FRANCISCO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CAPORAL</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO A LAS INSTALACIONES ELÉCTRICAS RESIDENCIALES, COMERCIALES E INDUSTRIALES</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE LAS MEDIDAS DE HIGIENE Y SEGURIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>SUPERVISA EL CUMPLIMIENTO DE TAREAS Y PROCESOS PARA EVALUAR LA PRODUCTIVIDAD EN LA ORGANIZACIÓN</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
@@ -1294,9 +1201,6 @@
   </si>
   <si>
     <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
   </si>
   <si>
     <t>MICHELLE ROBERTA</t>
@@ -1844,13 +1748,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -1861,16 +1765,16 @@
         <v>21330051920222</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -1884,13 +1788,13 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -1901,16 +1805,16 @@
         <v>21330051920235</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1921,16 +1825,16 @@
         <v>21330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1941,16 +1845,16 @@
         <v>21330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1961,16 +1865,16 @@
         <v>21330051920240</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1981,16 +1885,16 @@
         <v>21330051920250</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2001,16 +1905,16 @@
         <v>21330051920359</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2021,16 +1925,16 @@
         <v>21330051920359</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2071,16 +1975,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2091,16 +1995,16 @@
         <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2111,16 +2015,16 @@
         <v>21330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2131,16 +2035,16 @@
         <v>21330051920199</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2151,16 +2055,16 @@
         <v>21330051920202</v>
       </c>
       <c r="B6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" t="s">
         <v>149</v>
       </c>
-      <c r="C6" t="s">
-        <v>163</v>
-      </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2171,16 +2075,16 @@
         <v>21330051920203</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2191,16 +2095,16 @@
         <v>21330051920203</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2211,16 +2115,16 @@
         <v>21330051920213</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2231,16 +2135,16 @@
         <v>21330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2281,16 +2185,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2301,16 +2205,16 @@
         <v>21330051920323</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2321,16 +2225,16 @@
         <v>21330051920328</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2341,16 +2245,16 @@
         <v>21330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2391,16 +2295,16 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2411,16 +2315,16 @@
         <v>20330051920011</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" t="s">
         <v>198</v>
-      </c>
-      <c r="E3" t="s">
-        <v>210</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2431,16 +2335,16 @@
         <v>20330051920012</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2451,16 +2355,16 @@
         <v>20330051920013</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2471,16 +2375,16 @@
         <v>20330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2491,16 +2395,16 @@
         <v>20330051920016</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E7" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2511,16 +2415,16 @@
         <v>20330051920021</v>
       </c>
       <c r="B8" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2531,16 +2435,16 @@
         <v>20330051920025</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="E9" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -2551,16 +2455,16 @@
         <v>20330051920026</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -2571,16 +2475,16 @@
         <v>20330051920029</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2591,16 +2495,16 @@
         <v>20330051920033</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -2611,16 +2515,16 @@
         <v>20330051920035</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" t="s">
         <v>194</v>
       </c>
-      <c r="D13" t="s">
-        <v>206</v>
-      </c>
       <c r="E13" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -2631,19 +2535,19 @@
         <v>20330051920035</v>
       </c>
       <c r="B14" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" t="s">
         <v>194</v>
       </c>
-      <c r="D14" t="s">
-        <v>206</v>
-      </c>
       <c r="E14" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2651,16 +2555,16 @@
         <v>20330051920037</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" t="s">
         <v>195</v>
       </c>
-      <c r="D15" t="s">
-        <v>207</v>
-      </c>
       <c r="E15" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -2671,19 +2575,19 @@
         <v>20330051920060</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" t="s">
         <v>196</v>
       </c>
-      <c r="D16" t="s">
-        <v>208</v>
-      </c>
       <c r="E16" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2691,16 +2595,16 @@
         <v>20330051920362</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E17" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -2713,7 +2617,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2741,16 +2645,16 @@
         <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2758,19 +2662,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920236</v>
+        <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E3" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2781,16 +2685,16 @@
         <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2798,19 +2702,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>20330051920244</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2818,19 +2722,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920241</v>
+        <v>20330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="E6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2838,81 +2742,21 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920244</v>
-      </c>
-      <c r="B8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" t="s">
-        <v>220</v>
-      </c>
-      <c r="E8" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920251</v>
-      </c>
-      <c r="B9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" t="s">
-        <v>221</v>
-      </c>
-      <c r="E9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920251</v>
-      </c>
-      <c r="B10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" t="s">
-        <v>216</v>
-      </c>
-      <c r="D10" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" t="s">
-        <v>211</v>
-      </c>
-      <c r="F10">
         <v>5</v>
       </c>
     </row>
@@ -2923,7 +2767,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2948,161 +2792,21 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920337</v>
+        <v>20330051920354</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920341</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920347</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920349</v>
-      </c>
-      <c r="B5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920354</v>
-      </c>
-      <c r="B6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>231</v>
-      </c>
-      <c r="E6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920354</v>
-      </c>
-      <c r="B7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920356</v>
-      </c>
-      <c r="B8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" t="s">
-        <v>226</v>
-      </c>
-      <c r="D8" t="s">
-        <v>232</v>
-      </c>
-      <c r="E8" t="s">
-        <v>210</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920381</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>233</v>
-      </c>
-      <c r="E9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -3113,7 +2817,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3138,19 +2842,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920157</v>
+        <v>20330051920168</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3158,19 +2862,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920158</v>
+        <v>20330051920168</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>209</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3178,161 +2882,21 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920164</v>
+        <v>20330051920182</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>210</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>211</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>246</v>
-      </c>
-      <c r="E5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920168</v>
-      </c>
-      <c r="B6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E6" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920173</v>
-      </c>
-      <c r="B7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>247</v>
-      </c>
-      <c r="E7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920174</v>
-      </c>
-      <c r="B8" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>248</v>
-      </c>
-      <c r="E8" t="s">
-        <v>210</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920182</v>
-      </c>
-      <c r="B9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920182</v>
-      </c>
-      <c r="B10" t="s">
-        <v>238</v>
-      </c>
-      <c r="C10" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>249</v>
-      </c>
-      <c r="F10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920388</v>
-      </c>
-      <c r="B11" t="s">
-        <v>239</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11">
         <v>5</v>
       </c>
     </row>
@@ -3343,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3371,16 +2935,16 @@
         <v>20330051920040</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="D2" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3391,16 +2955,16 @@
         <v>20330051920050</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3411,16 +2975,16 @@
         <v>20330051920058</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>215</v>
       </c>
       <c r="C4" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="D4" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3431,16 +2995,16 @@
         <v>20330051920111</v>
       </c>
       <c r="B5" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="C5" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3448,41 +3012,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920111</v>
+        <v>20330051920112</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>254</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="E6" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920112</v>
-      </c>
-      <c r="B7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E7" t="s">
-        <v>260</v>
-      </c>
-      <c r="F7">
         <v>5</v>
       </c>
     </row>
@@ -3493,7 +3037,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3521,16 +3065,16 @@
         <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3538,19 +3082,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920297</v>
+        <v>20330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3558,81 +3102,21 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920301</v>
+        <v>20330051920311</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920310</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920311</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" t="s">
-        <v>266</v>
-      </c>
-      <c r="E6" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920312</v>
-      </c>
-      <c r="B7" t="s">
-        <v>238</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>267</v>
-      </c>
-      <c r="E7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F7">
         <v>5</v>
       </c>
     </row>
@@ -3671,16 +3155,16 @@
         <v>21330051920265</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3691,16 +3175,16 @@
         <v>21330051920265</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3714,13 +3198,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="D4" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3734,13 +3218,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="D5" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3751,16 +3235,16 @@
         <v>22330051920195</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3771,16 +3255,16 @@
         <v>22330051920195</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>246</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3791,13 +3275,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="C8" t="s">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="D8" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -3811,13 +3295,13 @@
         <v>22330051920201</v>
       </c>
       <c r="B9" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -3831,16 +3315,16 @@
         <v>22330051920204</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>235</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -3851,13 +3335,13 @@
         <v>22330051920356</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -3871,16 +3355,16 @@
         <v>22330051920371</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>246</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -3891,16 +3375,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -3911,16 +3395,16 @@
         <v>22330051920378</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -3931,16 +3415,16 @@
         <v>22330051920388</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -3978,19 +3462,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920035</v>
+        <v>22330051920036</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3998,19 +3482,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920036</v>
+        <v>22330051920044</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
         <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4018,19 +3502,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920038</v>
+        <v>22330051920044</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4038,19 +3522,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920047</v>
+        <v>22330051920045</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4058,19 +3542,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920327</v>
+        <v>22330051920045</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4081,16 +3565,16 @@
         <v>22330051920327</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4131,13 +3615,13 @@
         <v>22330051920210</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -4154,10 +3638,10 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -4174,13 +3658,13 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4191,16 +3675,16 @@
         <v>22330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="D5" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4211,13 +3695,13 @@
         <v>22330051920224</v>
       </c>
       <c r="B6" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="D6" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -4231,16 +3715,16 @@
         <v>22330051920362</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4251,16 +3735,16 @@
         <v>22330051920365</v>
       </c>
       <c r="B8" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="D8" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4271,16 +3755,16 @@
         <v>22330051920365</v>
       </c>
       <c r="B9" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="D9" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4291,13 +3775,13 @@
         <v>22330051920374</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4313,7 +3797,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4338,39 +3822,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920231</v>
+        <v>22330051920232</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="E2" t="s">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920232</v>
+        <v>22330051920233</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="D3" t="s">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4378,19 +3862,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920236</v>
+        <v>22330051920233</v>
       </c>
       <c r="B4" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="D4" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4398,16 +3882,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920237</v>
+        <v>22330051920236</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="C5" t="s">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>305</v>
+        <v>271</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -4418,19 +3902,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920239</v>
+        <v>22330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>262</v>
       </c>
       <c r="C6" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="D6" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4438,19 +3922,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920242</v>
+        <v>22330051920239</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4458,16 +3942,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920366</v>
+        <v>22330051920242</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>268</v>
       </c>
       <c r="D8" t="s">
-        <v>307</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -4478,16 +3962,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920369</v>
+        <v>22330051920366</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -4501,16 +3985,16 @@
         <v>22330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4518,21 +4002,81 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
+        <v>22330051920369</v>
+      </c>
+      <c r="B11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
+        <v>275</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
         <v>22330051920400</v>
       </c>
-      <c r="B11" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="B12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E12" t="s">
         <v>21</v>
       </c>
-      <c r="F11">
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>22330051920422</v>
+      </c>
+      <c r="B13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>22330051920422</v>
+      </c>
+      <c r="B14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
+        <v>277</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -4571,13 +4115,13 @@
         <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -4591,13 +4135,13 @@
         <v>22330051920263</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="D3" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -4611,13 +4155,13 @@
         <v>22330051920281</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -4631,16 +4175,16 @@
         <v>22330051920281</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4651,13 +4195,13 @@
         <v>22330051920395</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D6" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -4671,13 +4215,13 @@
         <v>22330051920395</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="D7" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -4697,7 +4241,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -4717,7 +4261,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -4731,13 +4275,13 @@
         <v>22330051920403</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4751,13 +4295,13 @@
         <v>22330051920403</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -4777,7 +4321,7 @@
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -4793,7 +4337,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4824,10 +4368,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="D2" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -4841,13 +4385,13 @@
         <v>22330051920302</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -4864,10 +4408,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -4881,13 +4425,13 @@
         <v>22330051920307</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="D5" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -4901,10 +4445,10 @@
         <v>22330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -4915,19 +4459,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920314</v>
+        <v>22330051920315</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4935,19 +4479,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920315</v>
+        <v>22330051920370</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4958,16 +4502,16 @@
         <v>22330051920370</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4975,16 +4519,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920370</v>
+        <v>22330051920397</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -4995,16 +4539,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920397</v>
+        <v>22330051920417</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>289</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -5015,19 +4559,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920418</v>
+        <v>22330051920417</v>
       </c>
       <c r="B12" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5038,16 +4582,16 @@
         <v>22330051920418</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5055,21 +4599,41 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
+        <v>22330051920418</v>
+      </c>
+      <c r="B14" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" t="s">
+        <v>301</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
         <v>22330051920419</v>
       </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
         <v>16</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>21</v>
       </c>
-      <c r="F14">
+      <c r="F15">
         <v>5</v>
       </c>
     </row>
@@ -5108,16 +4672,16 @@
         <v>19330051920081</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5128,16 +4692,16 @@
         <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="D3" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5148,16 +4712,16 @@
         <v>20330051920019</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="D4" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5168,16 +4732,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5188,16 +4752,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="C6" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E6" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5208,16 +4772,16 @@
         <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5228,16 +4792,16 @@
         <v>21330051920195</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="E8" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5248,16 +4812,16 @@
         <v>21330051920393</v>
       </c>
       <c r="B9" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="C9" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="D9" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5268,16 +4832,16 @@
         <v>21330051920393</v>
       </c>
       <c r="B10" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="C10" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="D10" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="E10" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5321,13 +4885,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5338,16 +4902,16 @@
         <v>21330051920086</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5358,16 +4922,16 @@
         <v>21330051920086</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5378,16 +4942,16 @@
         <v>21330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5398,16 +4962,16 @@
         <v>21330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="D6" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="E6" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5418,16 +4982,16 @@
         <v>21330051920109</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5468,16 +5032,16 @@
         <v>20330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5488,16 +5052,16 @@
         <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>215</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5508,16 +5072,16 @@
         <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>215</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5528,16 +5092,16 @@
         <v>21330051920125</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5548,16 +5112,16 @@
         <v>21330051920127</v>
       </c>
       <c r="B6" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="D6" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5568,16 +5132,16 @@
         <v>21330051920127</v>
       </c>
       <c r="B7" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="C7" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="D7" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5588,16 +5152,16 @@
         <v>21330051920133</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C8" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="D8" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="E8" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5608,16 +5172,16 @@
         <v>21330051920391</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="D9" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5658,16 +5222,16 @@
         <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5678,16 +5242,16 @@
         <v>21330051920037</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5700,7 +5264,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5725,19 +5289,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5745,19 +5309,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920140</v>
+        <v>21330051920147</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>215</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5765,19 +5329,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920141</v>
+        <v>21330051920147</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>215</v>
       </c>
       <c r="C4" t="s">
-        <v>361</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5785,101 +5349,21 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920143</v>
+        <v>21330051920382</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>329</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920145</v>
-      </c>
-      <c r="B6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>366</v>
-      </c>
-      <c r="E6" t="s">
-        <v>133</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920145</v>
-      </c>
-      <c r="B7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>366</v>
-      </c>
-      <c r="E7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920382</v>
-      </c>
-      <c r="B8" t="s">
-        <v>360</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>367</v>
-      </c>
-      <c r="E8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920382</v>
-      </c>
-      <c r="B9" t="s">
-        <v>360</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>367</v>
-      </c>
-      <c r="E9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -5918,16 +5402,16 @@
         <v>18330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5938,16 +5422,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5958,16 +5442,16 @@
         <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="E4" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5978,16 +5462,16 @@
         <v>20330051920070</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5998,16 +5482,16 @@
         <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="E6" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6018,16 +5502,16 @@
         <v>20330051920071</v>
       </c>
       <c r="B7" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6038,16 +5522,16 @@
         <v>20330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="E8" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6058,16 +5542,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B9" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="C9" t="s">
-        <v>371</v>
+        <v>336</v>
       </c>
       <c r="D9" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6078,16 +5562,16 @@
         <v>20330051920073</v>
       </c>
       <c r="B10" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="C10" t="s">
-        <v>371</v>
+        <v>336</v>
       </c>
       <c r="D10" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6098,16 +5582,16 @@
         <v>20330051920080</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>215</v>
+        <v>337</v>
       </c>
       <c r="D11" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="E11" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6118,16 +5602,16 @@
         <v>20330051920080</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>215</v>
+        <v>337</v>
       </c>
       <c r="D12" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6138,16 +5622,16 @@
         <v>20330051920082</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="D13" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="E13" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6158,16 +5642,16 @@
         <v>20330051920082</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="D14" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="E14" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6178,16 +5662,16 @@
         <v>20330051920091</v>
       </c>
       <c r="B15" t="s">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="E15" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6198,16 +5682,16 @@
         <v>20330051920091</v>
       </c>
       <c r="B16" t="s">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="C16" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D16" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="E16" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6220,7 +5704,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6248,13 +5732,13 @@
         <v>22330051920054</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -6271,10 +5755,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -6288,13 +5772,13 @@
         <v>22330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -6314,7 +5798,7 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -6328,16 +5812,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
         <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6348,16 +5832,16 @@
         <v>22330051920068</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6368,13 +5852,13 @@
         <v>22330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -6385,19 +5869,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920071</v>
+        <v>22330051920072</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6405,19 +5889,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920072</v>
+        <v>22330051920079</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6425,19 +5909,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920079</v>
+        <v>22330051920084</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6445,16 +5929,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920084</v>
+        <v>22330051920316</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
@@ -6465,41 +5949,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920316</v>
+        <v>22330051920334</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
       </c>
       <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920334</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14">
         <v>5</v>
       </c>
     </row>
@@ -6510,7 +5974,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6538,16 +6002,16 @@
         <v>19330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6555,19 +6019,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920177</v>
+        <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>346</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6575,19 +6039,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920190</v>
+        <v>20330051920191</v>
       </c>
       <c r="B4" t="s">
-        <v>380</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>350</v>
       </c>
       <c r="D4" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6595,19 +6059,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920191</v>
+        <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6615,19 +6079,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920193</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>347</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="E6" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6635,19 +6099,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920198</v>
+        <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>347</v>
       </c>
       <c r="C7" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="D7" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6655,19 +6119,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920214</v>
+        <v>20330051920198</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>285</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6675,19 +6139,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920217</v>
+        <v>20330051920200</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>348</v>
       </c>
       <c r="C9" t="s">
-        <v>383</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="E9" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6695,19 +6159,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920218</v>
+        <v>20330051920200</v>
       </c>
       <c r="B10" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="E10" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6715,19 +6179,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920218</v>
+        <v>20330051920204</v>
       </c>
       <c r="B11" t="s">
-        <v>381</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>353</v>
       </c>
       <c r="D11" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="E11" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6735,19 +6199,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920259</v>
+        <v>20330051920204</v>
       </c>
       <c r="B12" t="s">
-        <v>269</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>269</v>
+        <v>353</v>
       </c>
       <c r="D12" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6755,21 +6219,101 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
+        <v>20330051920214</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>20330051920217</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>354</v>
+      </c>
+      <c r="D14" t="s">
+        <v>364</v>
+      </c>
+      <c r="E14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>20330051920218</v>
+      </c>
+      <c r="B15" t="s">
+        <v>349</v>
+      </c>
+      <c r="C15" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" t="s">
+        <v>365</v>
+      </c>
+      <c r="E15" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>20330051920218</v>
+      </c>
+      <c r="B16" t="s">
+        <v>349</v>
+      </c>
+      <c r="C16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E16" t="s">
+        <v>199</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
         <v>20330051920259</v>
       </c>
-      <c r="B13" t="s">
-        <v>269</v>
-      </c>
-      <c r="C13" t="s">
-        <v>269</v>
-      </c>
-      <c r="D13" t="s">
-        <v>392</v>
-      </c>
-      <c r="E13" t="s">
-        <v>259</v>
-      </c>
-      <c r="F13">
+      <c r="B17" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" t="s">
+        <v>232</v>
+      </c>
+      <c r="D17" t="s">
+        <v>366</v>
+      </c>
+      <c r="E17" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17">
         <v>5</v>
       </c>
     </row>
@@ -6808,16 +6352,16 @@
         <v>19330051920314</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>215</v>
       </c>
       <c r="D2" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6828,16 +6372,16 @@
         <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>215</v>
       </c>
       <c r="D3" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="E3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6848,16 +6392,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
-        <v>393</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="D4" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6868,16 +6412,16 @@
         <v>20330051920278</v>
       </c>
       <c r="B5" t="s">
-        <v>393</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6890,7 +6434,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6918,16 +6462,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="E2" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6938,16 +6482,16 @@
         <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="E3" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6958,16 +6502,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6975,102 +6519,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920393</v>
+        <v>19330051920436</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="E5" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="F5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920393</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" t="s">
-        <v>399</v>
-      </c>
-      <c r="E6" t="s">
-        <v>402</v>
-      </c>
-      <c r="F6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920399</v>
-      </c>
-      <c r="B7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" t="s">
-        <v>397</v>
-      </c>
-      <c r="D7" t="s">
-        <v>400</v>
-      </c>
-      <c r="E7" t="s">
-        <v>403</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920436</v>
-      </c>
-      <c r="B8" t="s">
-        <v>393</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>401</v>
-      </c>
-      <c r="E8" t="s">
-        <v>403</v>
-      </c>
-      <c r="F8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920436</v>
-      </c>
-      <c r="B9" t="s">
-        <v>393</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>401</v>
-      </c>
-      <c r="E9" t="s">
-        <v>402</v>
-      </c>
-      <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7080,7 +6544,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7108,16 +6572,16 @@
         <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="C2" t="s">
-        <v>407</v>
+        <v>347</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7125,19 +6589,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920317</v>
+        <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="C3" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>380</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7145,19 +6609,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920320</v>
+        <v>20330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="D4" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7165,19 +6629,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>409</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="E5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7185,19 +6649,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920322</v>
+        <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="E6" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7205,19 +6669,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
       <c r="D7" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7225,19 +6689,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920329</v>
+        <v>20330051920331</v>
       </c>
       <c r="B8" t="s">
-        <v>361</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7245,19 +6709,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920330</v>
+        <v>20330051920335</v>
       </c>
       <c r="B9" t="s">
-        <v>405</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>379</v>
       </c>
       <c r="D9" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="E9" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7265,61 +6729,21 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920331</v>
+        <v>20330051920397</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>266</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="E10" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920335</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>410</v>
-      </c>
-      <c r="D11" t="s">
-        <v>418</v>
-      </c>
-      <c r="E11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920397</v>
-      </c>
-      <c r="B12" t="s">
-        <v>406</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>419</v>
-      </c>
-      <c r="E12" t="s">
-        <v>210</v>
-      </c>
-      <c r="F12">
         <v>5</v>
       </c>
     </row>
@@ -7330,7 +6754,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7358,16 +6782,16 @@
         <v>22330051920091</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7375,19 +6799,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920091</v>
+        <v>22330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7395,81 +6819,21 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920100</v>
+        <v>22330051920340</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920100</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920337</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920340</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
         <v>5</v>
       </c>
     </row>
@@ -7480,7 +6844,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7508,13 +6872,13 @@
         <v>22330051920136</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -7528,16 +6892,16 @@
         <v>22330051920136</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7548,16 +6912,16 @@
         <v>22330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7565,19 +6929,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920141</v>
+        <v>22330051920244</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7585,19 +6949,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920244</v>
+        <v>22330051920247</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -7608,13 +6972,13 @@
         <v>22330051920247</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
@@ -7625,41 +6989,21 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920348</v>
+        <v>22330051920354</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920354</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9">
         <v>5</v>
       </c>
     </row>
@@ -7670,7 +7014,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7695,19 +7039,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920157</v>
+        <v>22330051920160</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7718,16 +7062,16 @@
         <v>22330051920160</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -7735,16 +7079,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920160</v>
+        <v>22330051920161</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
@@ -7755,19 +7099,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920161</v>
+        <v>22330051920172</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7775,16 +7119,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920161</v>
+        <v>22330051920172</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
@@ -7795,19 +7139,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920172</v>
+        <v>22330051920296</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7815,19 +7159,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920172</v>
+        <v>22330051920296</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -7835,19 +7179,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920296</v>
+        <v>22330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -7855,81 +7199,21 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920296</v>
+        <v>22330051920384</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920382</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920384</v>
-      </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920386</v>
-      </c>
-      <c r="B13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13">
         <v>5</v>
       </c>
     </row>
@@ -7968,16 +7252,16 @@
         <v>21330051920152</v>
       </c>
       <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
         <v>108</v>
       </c>
-      <c r="C2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" t="s">
-        <v>123</v>
-      </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7988,16 +7272,16 @@
         <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
         <v>109</v>
       </c>
-      <c r="C3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
-      </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8008,16 +7292,16 @@
         <v>21330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8028,16 +7312,16 @@
         <v>21330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8048,16 +7332,16 @@
         <v>21330051920162</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8068,16 +7352,16 @@
         <v>21330051920164</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -8088,16 +7372,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8108,16 +7392,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -8128,16 +7412,16 @@
         <v>21330051920166</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -8148,16 +7432,16 @@
         <v>21330051920166</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -8168,16 +7452,16 @@
         <v>21330051920171</v>
       </c>
       <c r="B12" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -8188,16 +7472,16 @@
         <v>21330051920181</v>
       </c>
       <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" t="s">
         <v>116</v>
-      </c>
-      <c r="C13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E13" t="s">
-        <v>131</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -8241,13 +7525,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8261,13 +7545,13 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8278,16 +7562,16 @@
         <v>21330051920252</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -8298,16 +7582,16 @@
         <v>21330051920262</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -8318,16 +7602,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -8338,16 +7622,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -2854,7 +2854,7 @@
         <v>212</v>
       </c>
       <c r="E2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -2874,7 +2874,7 @@
         <v>212</v>
       </c>
       <c r="E3" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3994,7 +3994,7 @@
         <v>275</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4014,7 +4014,7 @@
         <v>275</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -7111,7 +7111,7 @@
         <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7131,7 +7131,7 @@
         <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>5</v>

--- a/Rescatables.xlsx
+++ b/Rescatables.xlsx
@@ -141,12 +141,12 @@
     <t>DISEÑA INSTALACIONES ELÉCTRICAS</t>
   </si>
   <si>
+    <t>QUÍMICA II</t>
+  </si>
+  <si>
     <t>GEOMETRÍA Y TRIGONOMETRÍA</t>
   </si>
   <si>
-    <t>QUÍMICA II</t>
-  </si>
-  <si>
     <t>CAMACHO</t>
   </si>
   <si>
@@ -900,12 +900,12 @@
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
+    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
+  </si>
+  <si>
     <t>TEMAS DE FILOSOFÍA</t>
   </si>
   <si>
-    <t>TEMAS DE BIOLOGÍA CONTEMPORÁNEA</t>
-  </si>
-  <si>
     <t>NAMIGTLE</t>
   </si>
   <si>
@@ -1680,10 +1680,10 @@
     <t>JESUS URIEL</t>
   </si>
   <si>
+    <t>ANALIZA SANGRE CON BASE EN TÉCNICAS DE QUÍMICA CLÍNICA</t>
+  </si>
+  <si>
     <t>INTRODUCCIÓN A LA BIOQUÍMICA</t>
-  </si>
-  <si>
-    <t>ANALIZA SANGRE CON BASE EN TÉCNICAS DE QUÍMICA CLÍNICA</t>
   </si>
   <si>
     <t>CARRASCO</t>
@@ -2214,7 +2214,7 @@
         <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -2234,7 +2234,7 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -2784,7 +2784,7 @@
         <v>247</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2804,7 +2804,7 @@
         <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -2824,7 +2824,7 @@
         <v>248</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -2844,7 +2844,7 @@
         <v>248</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3044,7 +3044,7 @@
         <v>255</v>
       </c>
       <c r="E19" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -3064,7 +3064,7 @@
         <v>255</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -3084,7 +3084,7 @@
         <v>256</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -3104,7 +3104,7 @@
         <v>256</v>
       </c>
       <c r="E22" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -3144,7 +3144,7 @@
         <v>258</v>
       </c>
       <c r="E24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -3164,7 +3164,7 @@
         <v>258</v>
       </c>
       <c r="E25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -3254,7 +3254,7 @@
         <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3274,7 +3274,7 @@
         <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -3314,7 +3314,7 @@
         <v>268</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3334,7 +3334,7 @@
         <v>268</v>
       </c>
       <c r="E8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3584,7 +3584,7 @@
         <v>282</v>
       </c>
       <c r="E6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3714,7 +3714,7 @@
         <v>299</v>
       </c>
       <c r="E5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4004,7 +4004,7 @@
         <v>315</v>
       </c>
       <c r="E6" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4024,7 +4024,7 @@
         <v>315</v>
       </c>
       <c r="E7" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -4044,7 +4044,7 @@
         <v>316</v>
       </c>
       <c r="E8" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -4064,7 +4064,7 @@
         <v>316</v>
       </c>
       <c r="E9" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -4134,7 +4134,7 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4154,7 +4154,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4174,7 +4174,7 @@
         <v>333</v>
       </c>
       <c r="E4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4194,7 +4194,7 @@
         <v>333</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4414,7 +4414,7 @@
         <v>342</v>
       </c>
       <c r="E16" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4434,7 +4434,7 @@
         <v>342</v>
       </c>
       <c r="E17" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -4554,7 +4554,7 @@
         <v>347</v>
       </c>
       <c r="E23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -4574,7 +4574,7 @@
         <v>347</v>
       </c>
       <c r="E24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -4624,7 +4624,7 @@
         <v>350</v>
       </c>
       <c r="E2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -4644,7 +4644,7 @@
         <v>351</v>
       </c>
       <c r="E3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -4664,7 +4664,7 @@
         <v>352</v>
       </c>
       <c r="E4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4774,7 +4774,7 @@
         <v>358</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -4794,7 +4794,7 @@
         <v>358</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4894,7 +4894,7 @@
         <v>362</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -4914,7 +4914,7 @@
         <v>363</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4934,7 +4934,7 @@
         <v>363</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -4974,7 +4974,7 @@
         <v>194</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -4994,7 +4994,7 @@
         <v>194</v>
       </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5014,7 +5014,7 @@
         <v>365</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5084,7 +5084,7 @@
         <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5104,7 +5104,7 @@
         <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5164,7 +5164,7 @@
         <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5184,7 +5184,7 @@
         <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5204,7 +5204,7 @@
         <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5254,7 +5254,7 @@
         <v>381</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5274,7 +5274,7 @@
         <v>381</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5294,7 +5294,7 @@
         <v>382</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5314,7 +5314,7 @@
         <v>383</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5334,7 +5334,7 @@
         <v>383</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -5354,7 +5354,7 @@
         <v>384</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5374,7 +5374,7 @@
         <v>384</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5394,7 +5394,7 @@
         <v>385</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5434,7 +5434,7 @@
         <v>386</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5474,7 +5474,7 @@
         <v>388</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5494,7 +5494,7 @@
         <v>389</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5514,7 +5514,7 @@
         <v>390</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5534,7 +5534,7 @@
         <v>390</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5554,7 +5554,7 @@
         <v>391</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5574,7 +5574,7 @@
         <v>392</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -5624,7 +5624,7 @@
         <v>402</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -5644,7 +5644,7 @@
         <v>402</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5684,7 +5684,7 @@
         <v>403</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5764,7 +5764,7 @@
         <v>405</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5784,7 +5784,7 @@
         <v>406</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -5824,7 +5824,7 @@
         <v>363</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5844,7 +5844,7 @@
         <v>363</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5904,7 +5904,7 @@
         <v>409</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5944,7 +5944,7 @@
         <v>410</v>
       </c>
       <c r="E18" t="s">
-        <v>417</v>
+        <v>32</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -5964,7 +5964,7 @@
         <v>410</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>417</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -6044,7 +6044,7 @@
         <v>414</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -6064,7 +6064,7 @@
         <v>415</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -6114,7 +6114,7 @@
         <v>341</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -6134,7 +6134,7 @@
         <v>423</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6154,7 +6154,7 @@
         <v>424</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6174,7 +6174,7 @@
         <v>425</v>
       </c>
       <c r="E5" t="s">
-        <v>428</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6194,7 +6194,7 @@
         <v>425</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>428</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6214,7 +6214,7 @@
         <v>426</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6234,7 +6234,7 @@
         <v>427</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6254,7 +6254,7 @@
         <v>427</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6274,7 +6274,7 @@
         <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6384,7 +6384,7 @@
         <v>443</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6424,7 +6424,7 @@
         <v>444</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6444,7 +6444,7 @@
         <v>445</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>455</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6464,7 +6464,7 @@
         <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>455</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6484,7 +6484,7 @@
         <v>446</v>
       </c>
       <c r="E10" t="s">
-        <v>455</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6504,7 +6504,7 @@
         <v>446</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>455</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6524,7 +6524,7 @@
         <v>198</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>455</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6544,7 +6544,7 @@
         <v>198</v>
       </c>
       <c r="E13" t="s">
-        <v>455</v>
+        <v>32</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6564,7 +6564,7 @@
         <v>447</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6604,7 +6604,7 @@
         <v>185</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6621,7 +6621,7 @@
         <v>448</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -6641,7 +6641,7 @@
         <v>449</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>455</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -6661,7 +6661,7 @@
         <v>449</v>
       </c>
       <c r="E19" t="s">
-        <v>455</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -6701,7 +6701,7 @@
         <v>451</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21"